--- a/artfynd/A 21339-2024 artfynd.xlsx
+++ b/artfynd/A 21339-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133552483</v>
+        <v>133550168</v>
       </c>
       <c r="B3" t="n">
-        <v>89300</v>
+        <v>83181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580906</v>
+        <v>580801</v>
       </c>
       <c r="R3" t="n">
-        <v>6963679</v>
+        <v>6963652</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133552511</v>
+        <v>133550175</v>
       </c>
       <c r="B5" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580865</v>
+        <v>580879</v>
       </c>
       <c r="R5" t="n">
-        <v>6963889</v>
+        <v>6963696</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133552449</v>
+        <v>133552483</v>
       </c>
       <c r="B6" t="n">
-        <v>91918</v>
+        <v>89300</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580689</v>
+        <v>580906</v>
       </c>
       <c r="R6" t="n">
-        <v>6963874</v>
+        <v>6963679</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133550168</v>
+        <v>133552449</v>
       </c>
       <c r="B7" t="n">
-        <v>83181</v>
+        <v>91918</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580801</v>
+        <v>580689</v>
       </c>
       <c r="R7" t="n">
-        <v>6963652</v>
+        <v>6963874</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133550175</v>
+        <v>133552511</v>
       </c>
       <c r="B8" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580879</v>
+        <v>580865</v>
       </c>
       <c r="R8" t="n">
-        <v>6963696</v>
+        <v>6963889</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,32 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133552468</v>
+        <v>133550155</v>
       </c>
       <c r="B9" t="n">
-        <v>97995</v>
+        <v>80438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,13 +1459,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580758</v>
+        <v>580715</v>
       </c>
       <c r="R9" t="n">
-        <v>6963787</v>
+        <v>6963791</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1745,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133552456</v>
+        <v>133550174</v>
       </c>
       <c r="B12" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580695</v>
+        <v>580879</v>
       </c>
       <c r="R12" t="n">
-        <v>6963806</v>
+        <v>6963690</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1815,7 +1820,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1830,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1959,10 +1964,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133550174</v>
+        <v>133550153</v>
       </c>
       <c r="B14" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1975,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,13 +1999,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580879</v>
+        <v>580704</v>
       </c>
       <c r="R14" t="n">
-        <v>6963690</v>
+        <v>6963785</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2029,7 +2034,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2044,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Stora fina exemplar av lunglav, handflata storlek.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133550153</v>
+        <v>133552456</v>
       </c>
       <c r="B15" t="n">
-        <v>80438</v>
+        <v>91918</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2077,21 +2087,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,13 +2111,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580704</v>
+        <v>580695</v>
       </c>
       <c r="R15" t="n">
-        <v>6963785</v>
+        <v>6963806</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2136,7 +2146,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,12 +2156,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Stora fina exemplar av lunglav, handflata storlek.</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2178,32 +2183,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133550157</v>
+        <v>133552468</v>
       </c>
       <c r="B16" t="n">
-        <v>99130</v>
+        <v>97995</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2213,13 +2218,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580715</v>
+        <v>580758</v>
       </c>
       <c r="R16" t="n">
-        <v>6963786</v>
+        <v>6963787</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2248,7 +2253,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2258,12 +2263,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>150 ex</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2402,32 +2402,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133550155</v>
+        <v>133550157</v>
       </c>
       <c r="B18" t="n">
-        <v>80438</v>
+        <v>99130</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2440,10 +2440,10 @@
         <v>580715</v>
       </c>
       <c r="R18" t="n">
-        <v>6963791</v>
+        <v>6963786</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2514,7 +2514,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133552509</v>
+        <v>133550164</v>
       </c>
       <c r="B19" t="n">
         <v>79333</v>
@@ -2549,13 +2549,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580814</v>
+        <v>580751</v>
       </c>
       <c r="R19" t="n">
-        <v>6963859</v>
+        <v>6963748</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2621,10 +2621,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133552492</v>
+        <v>133552509</v>
       </c>
       <c r="B20" t="n">
-        <v>79091</v>
+        <v>79333</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2632,21 +2632,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580892</v>
+        <v>580814</v>
       </c>
       <c r="R20" t="n">
-        <v>6963759</v>
+        <v>6963859</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2728,10 +2728,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133550164</v>
+        <v>133552492</v>
       </c>
       <c r="B21" t="n">
-        <v>79333</v>
+        <v>79091</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2739,21 +2739,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2763,13 +2763,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580751</v>
+        <v>580892</v>
       </c>
       <c r="R21" t="n">
-        <v>6963748</v>
+        <v>6963759</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2835,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133552457</v>
+        <v>133550171</v>
       </c>
       <c r="B22" t="n">
-        <v>91918</v>
+        <v>80438</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2846,21 +2846,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2870,13 +2870,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580720</v>
+        <v>580857</v>
       </c>
       <c r="R22" t="n">
-        <v>6963788</v>
+        <v>6963688</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2942,7 +2942,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133552464</v>
+        <v>133552457</v>
       </c>
       <c r="B23" t="n">
         <v>91918</v>
@@ -2980,7 +2980,7 @@
         <v>580720</v>
       </c>
       <c r="R23" t="n">
-        <v>6963748</v>
+        <v>6963788</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3049,32 +3049,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133552451</v>
+        <v>133552464</v>
       </c>
       <c r="B24" t="n">
-        <v>91881</v>
+        <v>91918</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580669</v>
+        <v>580720</v>
       </c>
       <c r="R24" t="n">
-        <v>6963873</v>
+        <v>6963748</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3156,32 +3156,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133550171</v>
+        <v>133552451</v>
       </c>
       <c r="B25" t="n">
-        <v>80438</v>
+        <v>91881</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3191,13 +3191,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580857</v>
+        <v>580669</v>
       </c>
       <c r="R25" t="n">
-        <v>6963688</v>
+        <v>6963873</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3375,10 +3375,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133552472</v>
+        <v>133550156</v>
       </c>
       <c r="B27" t="n">
-        <v>91932</v>
+        <v>79333</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3386,21 +3386,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3410,13 +3410,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580713</v>
+        <v>580715</v>
       </c>
       <c r="R27" t="n">
-        <v>6963690</v>
+        <v>6963791</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3482,10 +3482,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133552447</v>
+        <v>133550185</v>
       </c>
       <c r="B28" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3493,21 +3493,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3517,13 +3517,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580697</v>
+        <v>580867</v>
       </c>
       <c r="R28" t="n">
-        <v>6963889</v>
+        <v>6963739</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3696,10 +3696,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133550156</v>
+        <v>133552472</v>
       </c>
       <c r="B30" t="n">
-        <v>79333</v>
+        <v>91932</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3731,13 +3731,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580715</v>
+        <v>580713</v>
       </c>
       <c r="R30" t="n">
-        <v>6963791</v>
+        <v>6963690</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3803,10 +3803,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133550185</v>
+        <v>133552447</v>
       </c>
       <c r="B31" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3814,21 +3814,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3838,13 +3838,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>580867</v>
+        <v>580697</v>
       </c>
       <c r="R31" t="n">
-        <v>6963739</v>
+        <v>6963889</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3910,32 +3910,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133550148</v>
+        <v>133552502</v>
       </c>
       <c r="B32" t="n">
-        <v>99130</v>
+        <v>80342</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3945,13 +3945,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>580696</v>
+        <v>580865</v>
       </c>
       <c r="R32" t="n">
-        <v>6963788</v>
+        <v>6963830</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3990,12 +3990,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:49</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>120 ex</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4022,10 +4017,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133550180</v>
+        <v>133550138</v>
       </c>
       <c r="B33" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4033,45 +4028,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>580876</v>
+        <v>580712</v>
       </c>
       <c r="R33" t="n">
-        <v>6963707</v>
+        <v>6963853</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4100,7 +4087,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4110,12 +4097,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:14</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4142,32 +4124,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133550163</v>
+        <v>133552488</v>
       </c>
       <c r="B34" t="n">
-        <v>97995</v>
+        <v>89300</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>510</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4177,10 +4159,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>580728</v>
+        <v>580943</v>
       </c>
       <c r="R34" t="n">
-        <v>6963787</v>
+        <v>6963738</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4212,7 +4194,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4222,7 +4204,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4249,10 +4231,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133550138</v>
+        <v>133550180</v>
       </c>
       <c r="B35" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4260,37 +4242,45 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>580712</v>
+        <v>580876</v>
       </c>
       <c r="R35" t="n">
-        <v>6963853</v>
+        <v>6963707</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4319,7 +4309,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4329,7 +4319,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4356,32 +4351,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133552488</v>
+        <v>133550148</v>
       </c>
       <c r="B36" t="n">
-        <v>89300</v>
+        <v>99130</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4391,13 +4386,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>580943</v>
+        <v>580696</v>
       </c>
       <c r="R36" t="n">
-        <v>6963738</v>
+        <v>6963788</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4426,7 +4421,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4436,7 +4431,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4463,10 +4463,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133552502</v>
+        <v>133550163</v>
       </c>
       <c r="B37" t="n">
-        <v>80342</v>
+        <v>97995</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4474,21 +4474,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6456</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>580865</v>
+        <v>580728</v>
       </c>
       <c r="R37" t="n">
-        <v>6963830</v>
+        <v>6963787</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4570,32 +4570,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133552497</v>
+        <v>133550136</v>
       </c>
       <c r="B38" t="n">
-        <v>79090</v>
+        <v>99130</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4605,10 +4605,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>580939</v>
+        <v>580702</v>
       </c>
       <c r="R38" t="n">
-        <v>6963799</v>
+        <v>6963851</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4650,7 +4650,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4677,10 +4682,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133552453</v>
+        <v>133552497</v>
       </c>
       <c r="B39" t="n">
-        <v>79333</v>
+        <v>79090</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4688,21 +4693,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4712,13 +4717,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>580737</v>
+        <v>580939</v>
       </c>
       <c r="R39" t="n">
-        <v>6963844</v>
+        <v>6963799</v>
       </c>
       <c r="S39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4747,7 +4752,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4757,7 +4762,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4784,27 +4789,27 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133552478</v>
+        <v>133552453</v>
       </c>
       <c r="B40" t="n">
-        <v>80473</v>
+        <v>79333</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4819,13 +4824,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>580763</v>
+        <v>580737</v>
       </c>
       <c r="R40" t="n">
-        <v>6963637</v>
+        <v>6963844</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4854,7 +4859,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4864,7 +4869,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4891,10 +4896,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133552494</v>
+        <v>133550132</v>
       </c>
       <c r="B41" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4902,21 +4907,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4926,10 +4931,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>580955</v>
+        <v>580695</v>
       </c>
       <c r="R41" t="n">
-        <v>6963798</v>
+        <v>6963885</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4961,7 +4966,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4971,7 +4976,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4998,7 +5003,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133550182</v>
+        <v>133550176</v>
       </c>
       <c r="B42" t="n">
         <v>79333</v>
@@ -5033,10 +5038,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>580856</v>
+        <v>580874</v>
       </c>
       <c r="R42" t="n">
-        <v>6963747</v>
+        <v>6963718</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5068,7 +5073,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5078,7 +5083,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5105,7 +5110,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133550132</v>
+        <v>133550182</v>
       </c>
       <c r="B43" t="n">
         <v>79333</v>
@@ -5140,10 +5145,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580695</v>
+        <v>580856</v>
       </c>
       <c r="R43" t="n">
-        <v>6963885</v>
+        <v>6963747</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5175,7 +5180,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5185,7 +5190,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5212,32 +5217,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133550136</v>
+        <v>133552478</v>
       </c>
       <c r="B44" t="n">
-        <v>99130</v>
+        <v>80473</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5247,10 +5252,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>580702</v>
+        <v>580763</v>
       </c>
       <c r="R44" t="n">
-        <v>6963851</v>
+        <v>6963637</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5282,7 +5287,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5292,12 +5297,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>150 ex</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5443,10 +5443,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133550176</v>
+        <v>133552494</v>
       </c>
       <c r="B46" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5454,21 +5454,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5478,10 +5478,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>580874</v>
+        <v>580955</v>
       </c>
       <c r="R46" t="n">
-        <v>6963718</v>
+        <v>6963798</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5550,10 +5550,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133552448</v>
+        <v>133552503</v>
       </c>
       <c r="B47" t="n">
-        <v>91918</v>
+        <v>89300</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5561,21 +5561,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>580691</v>
+        <v>580844</v>
       </c>
       <c r="R47" t="n">
-        <v>6963879</v>
+        <v>6963844</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5657,10 +5657,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133552508</v>
+        <v>133550160</v>
       </c>
       <c r="B48" t="n">
-        <v>57958</v>
+        <v>92217</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5668,45 +5668,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>580813</v>
+        <v>580715</v>
       </c>
       <c r="R48" t="n">
-        <v>6963779</v>
+        <v>6963743</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5735,7 +5727,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5745,12 +5737,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:04</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5777,10 +5764,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133552490</v>
+        <v>133552448</v>
       </c>
       <c r="B49" t="n">
-        <v>80438</v>
+        <v>91918</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5788,21 +5775,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5812,10 +5799,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>580853</v>
+        <v>580691</v>
       </c>
       <c r="R49" t="n">
-        <v>6963702</v>
+        <v>6963879</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5847,7 +5834,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5857,7 +5844,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5884,32 +5871,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133552503</v>
+        <v>133550162</v>
       </c>
       <c r="B50" t="n">
-        <v>89300</v>
+        <v>99130</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5919,10 +5906,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>580844</v>
+        <v>580728</v>
       </c>
       <c r="R50" t="n">
-        <v>6963844</v>
+        <v>6963787</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5954,7 +5941,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5964,7 +5951,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5991,32 +5983,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133552491</v>
+        <v>133550147</v>
       </c>
       <c r="B51" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6026,13 +6018,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>580883</v>
+        <v>580689</v>
       </c>
       <c r="R51" t="n">
-        <v>6963753</v>
+        <v>6963814</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6061,7 +6053,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6071,7 +6063,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6098,10 +6095,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133552482</v>
+        <v>133552490</v>
       </c>
       <c r="B52" t="n">
-        <v>83315</v>
+        <v>80438</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6109,21 +6106,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6133,10 +6130,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>580879</v>
+        <v>580853</v>
       </c>
       <c r="R52" t="n">
-        <v>6963658</v>
+        <v>6963702</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6168,7 +6165,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6178,7 +6175,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6205,10 +6202,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133552486</v>
+        <v>133552491</v>
       </c>
       <c r="B53" t="n">
-        <v>83315</v>
+        <v>79333</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6216,21 +6213,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6240,10 +6237,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>580985</v>
+        <v>580883</v>
       </c>
       <c r="R53" t="n">
-        <v>6963707</v>
+        <v>6963753</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6275,7 +6272,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6285,7 +6282,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6312,32 +6309,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133550147</v>
+        <v>133552482</v>
       </c>
       <c r="B54" t="n">
-        <v>99130</v>
+        <v>83315</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6347,13 +6344,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>580689</v>
+        <v>580879</v>
       </c>
       <c r="R54" t="n">
-        <v>6963814</v>
+        <v>6963658</v>
       </c>
       <c r="S54" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6382,7 +6379,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6392,12 +6389,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>70 ex</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6424,32 +6416,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133550162</v>
+        <v>133552486</v>
       </c>
       <c r="B55" t="n">
-        <v>99130</v>
+        <v>83315</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6459,10 +6451,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>580728</v>
+        <v>580985</v>
       </c>
       <c r="R55" t="n">
-        <v>6963787</v>
+        <v>6963707</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6494,7 +6486,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6504,12 +6496,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:34</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>50 ex</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6536,10 +6523,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133550160</v>
+        <v>133552508</v>
       </c>
       <c r="B56" t="n">
-        <v>92217</v>
+        <v>57958</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6547,37 +6534,45 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>580715</v>
+        <v>580813</v>
       </c>
       <c r="R56" t="n">
-        <v>6963743</v>
+        <v>6963779</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6606,7 +6601,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6616,7 +6611,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6643,7 +6643,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133552458</v>
+        <v>133550143</v>
       </c>
       <c r="B57" t="n">
         <v>79333</v>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>580716</v>
+        <v>580713</v>
       </c>
       <c r="R57" t="n">
-        <v>6963787</v>
+        <v>6963831</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6713,7 +6713,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6750,7 +6750,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133552450</v>
+        <v>133552458</v>
       </c>
       <c r="B58" t="n">
         <v>79333</v>
@@ -6785,13 +6785,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>580683</v>
+        <v>580716</v>
       </c>
       <c r="R58" t="n">
-        <v>6963870</v>
+        <v>6963787</v>
       </c>
       <c r="S58" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6857,10 +6857,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133552473</v>
+        <v>133552450</v>
       </c>
       <c r="B59" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6868,21 +6868,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6892,13 +6892,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>580754</v>
+        <v>580683</v>
       </c>
       <c r="R59" t="n">
-        <v>6963659</v>
+        <v>6963870</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6964,10 +6964,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133550143</v>
+        <v>133552473</v>
       </c>
       <c r="B60" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6975,21 +6975,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6999,10 +6999,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>580713</v>
+        <v>580754</v>
       </c>
       <c r="R60" t="n">
-        <v>6963831</v>
+        <v>6963659</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7285,32 +7285,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133552507</v>
+        <v>133550133</v>
       </c>
       <c r="B63" t="n">
-        <v>80398</v>
+        <v>99130</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7320,13 +7320,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>580830</v>
+        <v>580685</v>
       </c>
       <c r="R63" t="n">
-        <v>6963821</v>
+        <v>6963865</v>
       </c>
       <c r="S63" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7365,7 +7365,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7392,32 +7397,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133550170</v>
+        <v>133550134</v>
       </c>
       <c r="B64" t="n">
-        <v>79365</v>
+        <v>99130</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7427,10 +7432,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>580801</v>
+        <v>580691</v>
       </c>
       <c r="R64" t="n">
-        <v>6963652</v>
+        <v>6963863</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7462,7 +7467,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7472,7 +7477,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7499,32 +7509,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133550133</v>
+        <v>133550170</v>
       </c>
       <c r="B65" t="n">
-        <v>99130</v>
+        <v>79365</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7534,10 +7544,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>580685</v>
+        <v>580801</v>
       </c>
       <c r="R65" t="n">
-        <v>6963865</v>
+        <v>6963652</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7569,7 +7579,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7579,12 +7589,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>100 ex</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7611,32 +7616,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133550134</v>
+        <v>133552507</v>
       </c>
       <c r="B66" t="n">
-        <v>99130</v>
+        <v>80398</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7646,13 +7651,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>580691</v>
+        <v>580830</v>
       </c>
       <c r="R66" t="n">
-        <v>6963863</v>
+        <v>6963821</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7681,7 +7686,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7691,12 +7696,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>200 ex</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7937,10 +7937,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133552506</v>
+        <v>133550172</v>
       </c>
       <c r="B69" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7948,42 +7948,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>580826</v>
+        <v>580870</v>
       </c>
       <c r="R69" t="n">
-        <v>6963830</v>
+        <v>6963663</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8015,7 +8007,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8025,12 +8017,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8164,10 +8151,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133550172</v>
+        <v>133552506</v>
       </c>
       <c r="B71" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8175,34 +8162,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>580870</v>
+        <v>580826</v>
       </c>
       <c r="R71" t="n">
-        <v>6963663</v>
+        <v>6963830</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8234,7 +8229,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8244,7 +8239,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8271,10 +8271,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133552454</v>
+        <v>133550149</v>
       </c>
       <c r="B72" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8282,21 +8282,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8306,13 +8306,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>580734</v>
+        <v>580697</v>
       </c>
       <c r="R72" t="n">
-        <v>6963814</v>
+        <v>6963788</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8351,7 +8351,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8490,10 +8490,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133550149</v>
+        <v>133552454</v>
       </c>
       <c r="B74" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8501,21 +8501,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8525,13 +8525,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>580697</v>
+        <v>580734</v>
       </c>
       <c r="R74" t="n">
-        <v>6963788</v>
+        <v>6963814</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8597,10 +8597,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133552487</v>
+        <v>133550173</v>
       </c>
       <c r="B75" t="n">
-        <v>89300</v>
+        <v>80438</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8608,21 +8608,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>580983</v>
+        <v>580878</v>
       </c>
       <c r="R75" t="n">
-        <v>6963709</v>
+        <v>6963692</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8704,10 +8704,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133552513</v>
+        <v>133552487</v>
       </c>
       <c r="B76" t="n">
-        <v>83307</v>
+        <v>89300</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8715,21 +8715,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>308</v>
+        <v>510</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8739,13 +8739,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>580785</v>
+        <v>580983</v>
       </c>
       <c r="R76" t="n">
-        <v>6963796</v>
+        <v>6963709</v>
       </c>
       <c r="S76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8811,10 +8811,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133552499</v>
+        <v>133550186</v>
       </c>
       <c r="B77" t="n">
-        <v>91918</v>
+        <v>89300</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8822,21 +8822,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8846,13 +8846,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>580926</v>
+        <v>580871</v>
       </c>
       <c r="R77" t="n">
-        <v>6963805</v>
+        <v>6963767</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8918,10 +8918,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133552462</v>
+        <v>133550179</v>
       </c>
       <c r="B78" t="n">
-        <v>83307</v>
+        <v>91918</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8929,21 +8929,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8953,10 +8953,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>580738</v>
+        <v>580862</v>
       </c>
       <c r="R78" t="n">
-        <v>6963776</v>
+        <v>6963713</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8988,7 +8988,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9025,10 +9025,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133550186</v>
+        <v>133552513</v>
       </c>
       <c r="B79" t="n">
-        <v>89300</v>
+        <v>83307</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9036,21 +9036,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>510</v>
+        <v>308</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9060,10 +9060,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>580871</v>
+        <v>580785</v>
       </c>
       <c r="R79" t="n">
-        <v>6963767</v>
+        <v>6963796</v>
       </c>
       <c r="S79" t="n">
         <v>6</v>
@@ -9095,7 +9095,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9105,7 +9105,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9132,7 +9132,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133550179</v>
+        <v>133552499</v>
       </c>
       <c r="B80" t="n">
         <v>91918</v>
@@ -9167,10 +9167,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>580862</v>
+        <v>580926</v>
       </c>
       <c r="R80" t="n">
-        <v>6963713</v>
+        <v>6963805</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9239,32 +9239,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133550141</v>
+        <v>133552462</v>
       </c>
       <c r="B81" t="n">
-        <v>99130</v>
+        <v>83307</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9274,10 +9274,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>580713</v>
+        <v>580738</v>
       </c>
       <c r="R81" t="n">
-        <v>6963840</v>
+        <v>6963776</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9309,7 +9309,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9319,12 +9319,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>60 ex, troligen fler</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9351,32 +9346,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133550173</v>
+        <v>133550141</v>
       </c>
       <c r="B82" t="n">
-        <v>80438</v>
+        <v>99130</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9386,13 +9381,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>580878</v>
+        <v>580713</v>
       </c>
       <c r="R82" t="n">
-        <v>6963692</v>
+        <v>6963840</v>
       </c>
       <c r="S82" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9421,7 +9416,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9431,7 +9426,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>60 ex, troligen fler</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9458,48 +9458,60 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>133552467</v>
+        <v>133550165</v>
       </c>
       <c r="B83" t="n">
-        <v>92641</v>
+        <v>57136</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3298</v>
+        <v>102612</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>580754</v>
+        <v>580753</v>
       </c>
       <c r="R83" t="n">
-        <v>6963789</v>
+        <v>6963702</v>
       </c>
       <c r="S83" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9528,7 +9540,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9538,7 +9550,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9565,32 +9577,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133552505</v>
+        <v>133552467</v>
       </c>
       <c r="B84" t="n">
-        <v>79333</v>
+        <v>92641</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9600,13 +9612,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>580836</v>
+        <v>580754</v>
       </c>
       <c r="R84" t="n">
-        <v>6963844</v>
+        <v>6963789</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9635,7 +9647,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9645,7 +9657,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9672,32 +9684,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133552469</v>
+        <v>133550140</v>
       </c>
       <c r="B85" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9707,10 +9719,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>580751</v>
+        <v>580694</v>
       </c>
       <c r="R85" t="n">
-        <v>6963778</v>
+        <v>6963839</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9742,7 +9754,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9752,7 +9764,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>33 ex</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9779,10 +9796,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133552476</v>
+        <v>133552505</v>
       </c>
       <c r="B86" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9790,21 +9807,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9814,10 +9831,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>580767</v>
+        <v>580836</v>
       </c>
       <c r="R86" t="n">
-        <v>6963639</v>
+        <v>6963844</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9849,7 +9866,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9859,7 +9876,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9886,10 +9903,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133552463</v>
+        <v>133552469</v>
       </c>
       <c r="B87" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9897,21 +9914,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9921,10 +9938,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>580725</v>
+        <v>580751</v>
       </c>
       <c r="R87" t="n">
-        <v>6963773</v>
+        <v>6963778</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9956,7 +9973,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9966,7 +9983,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9993,10 +10010,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133550165</v>
+        <v>133552476</v>
       </c>
       <c r="B88" t="n">
-        <v>57136</v>
+        <v>80438</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10004,49 +10021,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>580753</v>
+        <v>580767</v>
       </c>
       <c r="R88" t="n">
-        <v>6963702</v>
+        <v>6963639</v>
       </c>
       <c r="S88" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10075,7 +10080,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10085,7 +10090,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10112,32 +10117,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133550140</v>
+        <v>133552463</v>
       </c>
       <c r="B89" t="n">
-        <v>99130</v>
+        <v>80438</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10147,10 +10152,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>580694</v>
+        <v>580725</v>
       </c>
       <c r="R89" t="n">
-        <v>6963839</v>
+        <v>6963773</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10182,7 +10187,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10192,12 +10197,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>33 ex</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10224,32 +10224,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133550193</v>
+        <v>133552510</v>
       </c>
       <c r="B90" t="n">
-        <v>99130</v>
+        <v>83315</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10259,10 +10259,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>580781</v>
+        <v>580829</v>
       </c>
       <c r="R90" t="n">
-        <v>6963825</v>
+        <v>6963885</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10294,7 +10294,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10304,12 +10304,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>16:41</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Ca 60 ex</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10336,7 +10331,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133552510</v>
+        <v>133552471</v>
       </c>
       <c r="B91" t="n">
         <v>83315</v>
@@ -10371,10 +10366,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>580829</v>
+        <v>580717</v>
       </c>
       <c r="R91" t="n">
-        <v>6963885</v>
+        <v>6963694</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10406,7 +10401,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10416,7 +10411,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10443,10 +10438,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133552471</v>
+        <v>133552493</v>
       </c>
       <c r="B92" t="n">
-        <v>83315</v>
+        <v>89300</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10454,21 +10449,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10478,10 +10473,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>580717</v>
+        <v>580914</v>
       </c>
       <c r="R92" t="n">
-        <v>6963694</v>
+        <v>6963757</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10513,7 +10508,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10523,7 +10518,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10550,7 +10545,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133552455</v>
+        <v>133550193</v>
       </c>
       <c r="B93" t="n">
         <v>99130</v>
@@ -10585,10 +10580,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>580733</v>
+        <v>580781</v>
       </c>
       <c r="R93" t="n">
-        <v>6963814</v>
+        <v>6963825</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10620,7 +10615,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10630,12 +10625,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>200 ex</t>
+          <t>Ca 60 ex</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10662,7 +10657,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133552512</v>
+        <v>133552455</v>
       </c>
       <c r="B94" t="n">
         <v>99130</v>
@@ -10697,10 +10692,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>580803</v>
+        <v>580733</v>
       </c>
       <c r="R94" t="n">
-        <v>6963894</v>
+        <v>6963814</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10732,7 +10727,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10742,12 +10737,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>150 + ex</t>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10774,32 +10769,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133552493</v>
+        <v>133552512</v>
       </c>
       <c r="B95" t="n">
-        <v>89300</v>
+        <v>99130</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10809,10 +10804,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>580914</v>
+        <v>580803</v>
       </c>
       <c r="R95" t="n">
-        <v>6963757</v>
+        <v>6963894</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10844,7 +10839,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10854,7 +10849,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>150 + ex</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10881,10 +10881,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133552501</v>
+        <v>133550187</v>
       </c>
       <c r="B96" t="n">
-        <v>89300</v>
+        <v>57136</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10892,37 +10892,49 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>510</v>
+        <v>102612</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>580895</v>
+        <v>580843</v>
       </c>
       <c r="R96" t="n">
-        <v>6963822</v>
+        <v>6963778</v>
       </c>
       <c r="S96" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10988,60 +11000,48 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>133550187</v>
+        <v>133550152</v>
       </c>
       <c r="B97" t="n">
-        <v>57136</v>
+        <v>97995</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>102612</v>
+        <v>221945</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>580843</v>
+        <v>580698</v>
       </c>
       <c r="R97" t="n">
-        <v>6963778</v>
+        <v>6963783</v>
       </c>
       <c r="S97" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11080,7 +11080,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11214,32 +11214,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>133550152</v>
+        <v>133552501</v>
       </c>
       <c r="B99" t="n">
-        <v>97995</v>
+        <v>89300</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221945</v>
+        <v>510</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11249,13 +11249,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>580698</v>
+        <v>580895</v>
       </c>
       <c r="R99" t="n">
-        <v>6963783</v>
+        <v>6963822</v>
       </c>
       <c r="S99" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11428,56 +11428,48 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133552495</v>
+        <v>133552477</v>
       </c>
       <c r="B101" t="n">
-        <v>57958</v>
+        <v>80467</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>580953</v>
+        <v>580764</v>
       </c>
       <c r="R101" t="n">
-        <v>6963811</v>
+        <v>6963638</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11506,7 +11498,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11516,12 +11508,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Ett färskt ringhack på tall</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11548,48 +11535,56 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133552477</v>
+        <v>133552495</v>
       </c>
       <c r="B102" t="n">
-        <v>80467</v>
+        <v>57958</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>580764</v>
+        <v>580953</v>
       </c>
       <c r="R102" t="n">
-        <v>6963638</v>
+        <v>6963811</v>
       </c>
       <c r="S102" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11618,7 +11613,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11628,7 +11623,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Ett färskt ringhack på tall</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11655,7 +11655,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133550177</v>
+        <v>133550188</v>
       </c>
       <c r="B103" t="n">
         <v>79333</v>
@@ -11690,13 +11690,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>580864</v>
+        <v>580833</v>
       </c>
       <c r="R103" t="n">
-        <v>6963715</v>
+        <v>6963785</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11735,7 +11735,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11869,7 +11869,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133550188</v>
+        <v>133550190</v>
       </c>
       <c r="B105" t="n">
         <v>79333</v>
@@ -11904,13 +11904,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>580833</v>
+        <v>580838</v>
       </c>
       <c r="R105" t="n">
-        <v>6963785</v>
+        <v>6963811</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11949,7 +11949,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11976,7 +11981,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133550190</v>
+        <v>133550177</v>
       </c>
       <c r="B106" t="n">
         <v>79333</v>
@@ -12011,10 +12016,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>580838</v>
+        <v>580864</v>
       </c>
       <c r="R106" t="n">
-        <v>6963811</v>
+        <v>6963715</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -12046,7 +12051,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12056,12 +12061,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12088,10 +12088,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133552500</v>
+        <v>133552465</v>
       </c>
       <c r="B107" t="n">
-        <v>79365</v>
+        <v>57958</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12099,37 +12099,45 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>580902</v>
+        <v>580724</v>
       </c>
       <c r="R107" t="n">
-        <v>6963823</v>
+        <v>6963746</v>
       </c>
       <c r="S107" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12158,7 +12166,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12168,7 +12176,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12195,10 +12208,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>133552465</v>
+        <v>133552500</v>
       </c>
       <c r="B108" t="n">
-        <v>57958</v>
+        <v>79365</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12206,45 +12219,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>580724</v>
+        <v>580902</v>
       </c>
       <c r="R108" t="n">
-        <v>6963746</v>
+        <v>6963823</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12273,7 +12278,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12283,12 +12288,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD108" t="b">

--- a/artfynd/A 21339-2024 artfynd.xlsx
+++ b/artfynd/A 21339-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133550168</v>
+        <v>133552511</v>
       </c>
       <c r="B3" t="n">
-        <v>83181</v>
+        <v>79365</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580801</v>
+        <v>580865</v>
       </c>
       <c r="R3" t="n">
-        <v>6963652</v>
+        <v>6963889</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133552481</v>
+        <v>133552483</v>
       </c>
       <c r="B4" t="n">
         <v>89300</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580869</v>
+        <v>580906</v>
       </c>
       <c r="R4" t="n">
-        <v>6963663</v>
+        <v>6963679</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133550175</v>
+        <v>133552449</v>
       </c>
       <c r="B5" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580879</v>
+        <v>580689</v>
       </c>
       <c r="R5" t="n">
-        <v>6963696</v>
+        <v>6963874</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133552483</v>
+        <v>133550168</v>
       </c>
       <c r="B6" t="n">
-        <v>89300</v>
+        <v>83181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580906</v>
+        <v>580801</v>
       </c>
       <c r="R6" t="n">
-        <v>6963679</v>
+        <v>6963652</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133552449</v>
+        <v>133552481</v>
       </c>
       <c r="B7" t="n">
-        <v>91918</v>
+        <v>89300</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580689</v>
+        <v>580869</v>
       </c>
       <c r="R7" t="n">
-        <v>6963874</v>
+        <v>6963663</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133552511</v>
+        <v>133550175</v>
       </c>
       <c r="B8" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580865</v>
+        <v>580879</v>
       </c>
       <c r="R8" t="n">
-        <v>6963889</v>
+        <v>6963696</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133550155</v>
+        <v>133552456</v>
       </c>
       <c r="B9" t="n">
-        <v>80438</v>
+        <v>91918</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,13 +1459,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580715</v>
+        <v>580695</v>
       </c>
       <c r="R9" t="n">
-        <v>6963791</v>
+        <v>6963806</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,12 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,32 +1531,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133552461</v>
+        <v>133550155</v>
       </c>
       <c r="B10" t="n">
-        <v>83298</v>
+        <v>80438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6439</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,13 +1566,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580740</v>
+        <v>580715</v>
       </c>
       <c r="R10" t="n">
-        <v>6963795</v>
+        <v>6963791</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1606,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,7 +1611,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1750,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133550174</v>
+        <v>133550153</v>
       </c>
       <c r="B12" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,13 +1785,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580879</v>
+        <v>580704</v>
       </c>
       <c r="R12" t="n">
-        <v>6963690</v>
+        <v>6963785</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1830,7 +1830,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Stora fina exemplar av lunglav, handflata storlek.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1857,32 +1862,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133552475</v>
+        <v>133552461</v>
       </c>
       <c r="B13" t="n">
-        <v>79333</v>
+        <v>83298</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1897,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580801</v>
+        <v>580740</v>
       </c>
       <c r="R13" t="n">
-        <v>6963655</v>
+        <v>6963795</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1927,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1937,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1964,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133550153</v>
+        <v>133550174</v>
       </c>
       <c r="B14" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1975,21 +1980,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1999,13 +2004,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580704</v>
+        <v>580879</v>
       </c>
       <c r="R14" t="n">
-        <v>6963785</v>
+        <v>6963690</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2034,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2044,12 +2049,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Stora fina exemplar av lunglav, handflata storlek.</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133552456</v>
+        <v>133552475</v>
       </c>
       <c r="B15" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2087,21 +2087,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580695</v>
+        <v>580801</v>
       </c>
       <c r="R15" t="n">
-        <v>6963806</v>
+        <v>6963655</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2183,32 +2183,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133552468</v>
+        <v>133550154</v>
       </c>
       <c r="B16" t="n">
-        <v>97995</v>
+        <v>99130</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2218,13 +2218,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580758</v>
+        <v>580712</v>
       </c>
       <c r="R16" t="n">
-        <v>6963787</v>
+        <v>6963788</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2263,7 +2263,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2290,7 +2295,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133550154</v>
+        <v>133550157</v>
       </c>
       <c r="B17" t="n">
         <v>99130</v>
@@ -2325,13 +2330,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580712</v>
+        <v>580715</v>
       </c>
       <c r="R17" t="n">
-        <v>6963788</v>
+        <v>6963786</v>
       </c>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2360,7 +2365,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2370,12 +2375,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>70 ex</t>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2402,32 +2407,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133550157</v>
+        <v>133552468</v>
       </c>
       <c r="B18" t="n">
-        <v>99130</v>
+        <v>97995</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2437,13 +2442,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580715</v>
+        <v>580758</v>
       </c>
       <c r="R18" t="n">
-        <v>6963786</v>
+        <v>6963787</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2472,7 +2477,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2482,12 +2487,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>150 ex</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2835,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133550171</v>
+        <v>133552457</v>
       </c>
       <c r="B22" t="n">
-        <v>80438</v>
+        <v>91918</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2846,21 +2846,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2870,13 +2870,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580857</v>
+        <v>580720</v>
       </c>
       <c r="R22" t="n">
-        <v>6963688</v>
+        <v>6963788</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2942,7 +2942,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133552457</v>
+        <v>133552464</v>
       </c>
       <c r="B23" t="n">
         <v>91918</v>
@@ -2980,7 +2980,7 @@
         <v>580720</v>
       </c>
       <c r="R23" t="n">
-        <v>6963788</v>
+        <v>6963748</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3049,32 +3049,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133552464</v>
+        <v>133552451</v>
       </c>
       <c r="B24" t="n">
-        <v>91918</v>
+        <v>91881</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580720</v>
+        <v>580669</v>
       </c>
       <c r="R24" t="n">
-        <v>6963748</v>
+        <v>6963873</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3156,32 +3156,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133552451</v>
+        <v>133550171</v>
       </c>
       <c r="B25" t="n">
-        <v>91881</v>
+        <v>80438</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3191,13 +3191,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580669</v>
+        <v>580857</v>
       </c>
       <c r="R25" t="n">
-        <v>6963873</v>
+        <v>6963688</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3375,10 +3375,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133550156</v>
+        <v>133552447</v>
       </c>
       <c r="B27" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3386,21 +3386,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3410,13 +3410,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580715</v>
+        <v>580697</v>
       </c>
       <c r="R27" t="n">
-        <v>6963791</v>
+        <v>6963889</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3482,10 +3482,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133550185</v>
+        <v>133550191</v>
       </c>
       <c r="B28" t="n">
-        <v>79333</v>
+        <v>92217</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3493,21 +3493,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3517,13 +3517,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580867</v>
+        <v>580787</v>
       </c>
       <c r="R28" t="n">
-        <v>6963739</v>
+        <v>6963783</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3589,10 +3589,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133550191</v>
+        <v>133552472</v>
       </c>
       <c r="B29" t="n">
-        <v>92217</v>
+        <v>91932</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3600,21 +3600,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3624,10 +3624,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580787</v>
+        <v>580713</v>
       </c>
       <c r="R29" t="n">
-        <v>6963783</v>
+        <v>6963690</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3696,10 +3696,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133552472</v>
+        <v>133550156</v>
       </c>
       <c r="B30" t="n">
-        <v>91932</v>
+        <v>79333</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3731,13 +3731,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580713</v>
+        <v>580715</v>
       </c>
       <c r="R30" t="n">
-        <v>6963690</v>
+        <v>6963791</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3803,10 +3803,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133552447</v>
+        <v>133550185</v>
       </c>
       <c r="B31" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3814,21 +3814,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3838,13 +3838,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>580697</v>
+        <v>580867</v>
       </c>
       <c r="R31" t="n">
-        <v>6963889</v>
+        <v>6963739</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4351,32 +4351,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133550148</v>
+        <v>133550163</v>
       </c>
       <c r="B36" t="n">
-        <v>99130</v>
+        <v>97995</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4386,13 +4386,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>580696</v>
+        <v>580728</v>
       </c>
       <c r="R36" t="n">
-        <v>6963788</v>
+        <v>6963787</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4431,12 +4431,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:49</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>120 ex</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4463,32 +4458,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133550163</v>
+        <v>133550148</v>
       </c>
       <c r="B37" t="n">
-        <v>97995</v>
+        <v>99130</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4498,13 +4493,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>580728</v>
+        <v>580696</v>
       </c>
       <c r="R37" t="n">
-        <v>6963787</v>
+        <v>6963788</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4533,7 +4528,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4543,7 +4538,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4682,10 +4682,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133552497</v>
+        <v>133552494</v>
       </c>
       <c r="B39" t="n">
-        <v>79090</v>
+        <v>79365</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4693,21 +4693,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>580939</v>
+        <v>580955</v>
       </c>
       <c r="R39" t="n">
-        <v>6963799</v>
+        <v>6963798</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5217,48 +5217,60 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133552478</v>
+        <v>133550166</v>
       </c>
       <c r="B44" t="n">
-        <v>80473</v>
+        <v>57136</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>102612</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>580763</v>
+        <v>580800</v>
       </c>
       <c r="R44" t="n">
-        <v>6963637</v>
+        <v>6963652</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5287,7 +5299,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5297,7 +5309,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5324,10 +5336,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133550166</v>
+        <v>133552497</v>
       </c>
       <c r="B45" t="n">
-        <v>57136</v>
+        <v>79090</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5335,49 +5347,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>102612</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580800</v>
+        <v>580939</v>
       </c>
       <c r="R45" t="n">
-        <v>6963652</v>
+        <v>6963799</v>
       </c>
       <c r="S45" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5443,32 +5443,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133552494</v>
+        <v>133552478</v>
       </c>
       <c r="B46" t="n">
-        <v>79365</v>
+        <v>80473</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>6463</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5478,10 +5478,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>580955</v>
+        <v>580763</v>
       </c>
       <c r="R46" t="n">
-        <v>6963798</v>
+        <v>6963637</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5871,32 +5871,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133550162</v>
+        <v>133552490</v>
       </c>
       <c r="B50" t="n">
-        <v>99130</v>
+        <v>80438</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>580728</v>
+        <v>580853</v>
       </c>
       <c r="R50" t="n">
-        <v>6963787</v>
+        <v>6963702</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5941,7 +5941,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5951,12 +5951,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:34</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>50 ex</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5983,32 +5978,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133550147</v>
+        <v>133552486</v>
       </c>
       <c r="B51" t="n">
-        <v>99130</v>
+        <v>83315</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6018,13 +6013,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>580689</v>
+        <v>580985</v>
       </c>
       <c r="R51" t="n">
-        <v>6963814</v>
+        <v>6963707</v>
       </c>
       <c r="S51" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6053,7 +6048,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6063,12 +6058,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>70 ex</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6095,10 +6085,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133552490</v>
+        <v>133552491</v>
       </c>
       <c r="B52" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6106,21 +6096,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6130,10 +6120,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>580853</v>
+        <v>580883</v>
       </c>
       <c r="R52" t="n">
-        <v>6963702</v>
+        <v>6963753</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6165,7 +6155,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6175,7 +6165,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6202,10 +6192,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133552491</v>
+        <v>133552482</v>
       </c>
       <c r="B53" t="n">
-        <v>79333</v>
+        <v>83315</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6213,21 +6203,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6237,10 +6227,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>580883</v>
+        <v>580879</v>
       </c>
       <c r="R53" t="n">
-        <v>6963753</v>
+        <v>6963658</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6272,7 +6262,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6282,7 +6272,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6309,10 +6299,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133552482</v>
+        <v>133552508</v>
       </c>
       <c r="B54" t="n">
-        <v>83315</v>
+        <v>57958</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6320,34 +6310,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>580879</v>
+        <v>580813</v>
       </c>
       <c r="R54" t="n">
-        <v>6963658</v>
+        <v>6963779</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6379,7 +6377,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6389,7 +6387,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6416,32 +6419,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133552486</v>
+        <v>133550162</v>
       </c>
       <c r="B55" t="n">
-        <v>83315</v>
+        <v>99130</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6451,10 +6454,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>580985</v>
+        <v>580728</v>
       </c>
       <c r="R55" t="n">
-        <v>6963707</v>
+        <v>6963787</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6486,7 +6489,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6496,7 +6499,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6523,56 +6531,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133552508</v>
+        <v>133550147</v>
       </c>
       <c r="B56" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>580813</v>
+        <v>580689</v>
       </c>
       <c r="R56" t="n">
-        <v>6963779</v>
+        <v>6963814</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6643,10 +6643,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133550143</v>
+        <v>133552473</v>
       </c>
       <c r="B57" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6654,21 +6654,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>580713</v>
+        <v>580754</v>
       </c>
       <c r="R57" t="n">
-        <v>6963831</v>
+        <v>6963659</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6713,7 +6713,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6750,7 +6750,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133552458</v>
+        <v>133550143</v>
       </c>
       <c r="B58" t="n">
         <v>79333</v>
@@ -6785,10 +6785,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>580716</v>
+        <v>580713</v>
       </c>
       <c r="R58" t="n">
-        <v>6963787</v>
+        <v>6963831</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6857,7 +6857,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133552450</v>
+        <v>133552458</v>
       </c>
       <c r="B59" t="n">
         <v>79333</v>
@@ -6892,13 +6892,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>580683</v>
+        <v>580716</v>
       </c>
       <c r="R59" t="n">
-        <v>6963870</v>
+        <v>6963787</v>
       </c>
       <c r="S59" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6964,10 +6964,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133552473</v>
+        <v>133552450</v>
       </c>
       <c r="B60" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6975,21 +6975,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6999,13 +6999,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>580754</v>
+        <v>580683</v>
       </c>
       <c r="R60" t="n">
-        <v>6963659</v>
+        <v>6963870</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7723,10 +7723,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133552484</v>
+        <v>133552460</v>
       </c>
       <c r="B67" t="n">
-        <v>79333</v>
+        <v>83315</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7734,21 +7734,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7758,10 +7758,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>580938</v>
+        <v>580722</v>
       </c>
       <c r="R67" t="n">
-        <v>6963702</v>
+        <v>6963787</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7830,10 +7830,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133552460</v>
+        <v>133552484</v>
       </c>
       <c r="B68" t="n">
-        <v>83315</v>
+        <v>79333</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7841,21 +7841,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7865,10 +7865,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>580722</v>
+        <v>580938</v>
       </c>
       <c r="R68" t="n">
-        <v>6963787</v>
+        <v>6963702</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7900,7 +7900,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8271,10 +8271,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133550149</v>
+        <v>133550139</v>
       </c>
       <c r="B72" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8282,21 +8282,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8306,13 +8306,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>580697</v>
+        <v>580689</v>
       </c>
       <c r="R72" t="n">
-        <v>6963788</v>
+        <v>6963841</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8351,7 +8351,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8378,10 +8383,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133550139</v>
+        <v>133550149</v>
       </c>
       <c r="B73" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8389,21 +8394,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8413,13 +8418,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>580689</v>
+        <v>580697</v>
       </c>
       <c r="R73" t="n">
-        <v>6963841</v>
+        <v>6963788</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8448,7 +8453,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8458,12 +8463,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:19</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8597,32 +8597,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133550173</v>
+        <v>133550141</v>
       </c>
       <c r="B75" t="n">
-        <v>80438</v>
+        <v>99130</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>580878</v>
+        <v>580713</v>
       </c>
       <c r="R75" t="n">
-        <v>6963692</v>
+        <v>6963840</v>
       </c>
       <c r="S75" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8677,7 +8677,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>60 ex, troligen fler</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9346,32 +9351,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133550141</v>
+        <v>133550173</v>
       </c>
       <c r="B82" t="n">
-        <v>99130</v>
+        <v>80438</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9381,13 +9386,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>580713</v>
+        <v>580878</v>
       </c>
       <c r="R82" t="n">
-        <v>6963840</v>
+        <v>6963692</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9416,7 +9421,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9426,12 +9431,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>60 ex, troligen fler</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9458,10 +9458,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>133550165</v>
+        <v>133552476</v>
       </c>
       <c r="B83" t="n">
-        <v>57136</v>
+        <v>80438</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9469,49 +9469,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>580753</v>
+        <v>580767</v>
       </c>
       <c r="R83" t="n">
-        <v>6963702</v>
+        <v>6963639</v>
       </c>
       <c r="S83" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9540,7 +9528,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9550,7 +9538,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9577,32 +9565,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133552467</v>
+        <v>133552463</v>
       </c>
       <c r="B84" t="n">
-        <v>92641</v>
+        <v>80438</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9612,13 +9600,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>580754</v>
+        <v>580725</v>
       </c>
       <c r="R84" t="n">
-        <v>6963789</v>
+        <v>6963773</v>
       </c>
       <c r="S84" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9647,7 +9635,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9657,7 +9645,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9684,32 +9672,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133550140</v>
+        <v>133552467</v>
       </c>
       <c r="B85" t="n">
-        <v>99130</v>
+        <v>92641</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9719,13 +9707,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>580694</v>
+        <v>580754</v>
       </c>
       <c r="R85" t="n">
-        <v>6963839</v>
+        <v>6963789</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9754,7 +9742,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9764,12 +9752,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>33 ex</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10010,32 +9993,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133552476</v>
+        <v>133550140</v>
       </c>
       <c r="B88" t="n">
-        <v>80438</v>
+        <v>99130</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10045,10 +10028,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>580767</v>
+        <v>580694</v>
       </c>
       <c r="R88" t="n">
-        <v>6963639</v>
+        <v>6963839</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10080,7 +10063,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10090,7 +10073,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>33 ex</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10117,10 +10105,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133552463</v>
+        <v>133550165</v>
       </c>
       <c r="B89" t="n">
-        <v>80438</v>
+        <v>57136</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10128,37 +10116,49 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>580725</v>
+        <v>580753</v>
       </c>
       <c r="R89" t="n">
-        <v>6963773</v>
+        <v>6963702</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10197,7 +10197,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10224,7 +10224,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133552510</v>
+        <v>133552471</v>
       </c>
       <c r="B90" t="n">
         <v>83315</v>
@@ -10259,10 +10259,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>580829</v>
+        <v>580717</v>
       </c>
       <c r="R90" t="n">
-        <v>6963885</v>
+        <v>6963694</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10294,7 +10294,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10331,7 +10331,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133552471</v>
+        <v>133552510</v>
       </c>
       <c r="B91" t="n">
         <v>83315</v>
@@ -10366,10 +10366,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>580717</v>
+        <v>580829</v>
       </c>
       <c r="R91" t="n">
-        <v>6963694</v>
+        <v>6963885</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10881,10 +10881,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133550187</v>
+        <v>133552501</v>
       </c>
       <c r="B96" t="n">
-        <v>57136</v>
+        <v>89300</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10892,49 +10892,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>102612</v>
+        <v>510</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>580843</v>
+        <v>580895</v>
       </c>
       <c r="R96" t="n">
-        <v>6963778</v>
+        <v>6963822</v>
       </c>
       <c r="S96" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11000,32 +10988,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>133550152</v>
+        <v>133550146</v>
       </c>
       <c r="B97" t="n">
-        <v>97995</v>
+        <v>79333</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11035,13 +11023,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>580698</v>
+        <v>580687</v>
       </c>
       <c r="R97" t="n">
-        <v>6963783</v>
+        <v>6963819</v>
       </c>
       <c r="S97" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11070,7 +11058,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11080,7 +11068,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11107,10 +11095,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>133550146</v>
+        <v>133550187</v>
       </c>
       <c r="B98" t="n">
-        <v>79333</v>
+        <v>57136</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11118,34 +11106,46 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>580687</v>
+        <v>580843</v>
       </c>
       <c r="R98" t="n">
-        <v>6963819</v>
+        <v>6963778</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11187,7 +11187,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11214,32 +11214,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>133552501</v>
+        <v>133550152</v>
       </c>
       <c r="B99" t="n">
-        <v>89300</v>
+        <v>97995</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>510</v>
+        <v>221945</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11249,13 +11249,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>580895</v>
+        <v>580698</v>
       </c>
       <c r="R99" t="n">
-        <v>6963822</v>
+        <v>6963783</v>
       </c>
       <c r="S99" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11321,32 +11321,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133550161</v>
+        <v>133552477</v>
       </c>
       <c r="B100" t="n">
-        <v>79333</v>
+        <v>80467</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11356,13 +11356,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>580727</v>
+        <v>580764</v>
       </c>
       <c r="R100" t="n">
-        <v>6963764</v>
+        <v>6963638</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11428,32 +11428,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133552477</v>
+        <v>133550161</v>
       </c>
       <c r="B101" t="n">
-        <v>80467</v>
+        <v>79333</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11463,13 +11463,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>580764</v>
+        <v>580727</v>
       </c>
       <c r="R101" t="n">
-        <v>6963638</v>
+        <v>6963764</v>
       </c>
       <c r="S101" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11498,7 +11498,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11508,7 +11508,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11655,10 +11655,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133550188</v>
+        <v>133552500</v>
       </c>
       <c r="B103" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11666,21 +11666,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11690,13 +11690,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>580833</v>
+        <v>580902</v>
       </c>
       <c r="R103" t="n">
-        <v>6963785</v>
+        <v>6963823</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11735,7 +11735,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11762,7 +11762,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133550158</v>
+        <v>133550188</v>
       </c>
       <c r="B104" t="n">
         <v>79333</v>
@@ -11797,10 +11797,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>580720</v>
+        <v>580833</v>
       </c>
       <c r="R104" t="n">
-        <v>6963787</v>
+        <v>6963785</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11832,7 +11832,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11869,7 +11869,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133550190</v>
+        <v>133550158</v>
       </c>
       <c r="B105" t="n">
         <v>79333</v>
@@ -11904,13 +11904,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>580838</v>
+        <v>580720</v>
       </c>
       <c r="R105" t="n">
-        <v>6963811</v>
+        <v>6963787</v>
       </c>
       <c r="S105" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11949,12 +11949,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11981,7 +11976,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133550177</v>
+        <v>133550190</v>
       </c>
       <c r="B106" t="n">
         <v>79333</v>
@@ -12016,10 +12011,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>580864</v>
+        <v>580838</v>
       </c>
       <c r="R106" t="n">
-        <v>6963715</v>
+        <v>6963811</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -12051,7 +12046,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12061,7 +12056,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12088,10 +12088,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133552465</v>
+        <v>133550177</v>
       </c>
       <c r="B107" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12099,42 +12099,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>580724</v>
+        <v>580864</v>
       </c>
       <c r="R107" t="n">
-        <v>6963746</v>
+        <v>6963715</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -12166,7 +12158,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12176,12 +12168,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12208,10 +12195,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>133552500</v>
+        <v>133552465</v>
       </c>
       <c r="B108" t="n">
-        <v>79365</v>
+        <v>57958</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12219,37 +12206,45 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>580902</v>
+        <v>580724</v>
       </c>
       <c r="R108" t="n">
-        <v>6963823</v>
+        <v>6963746</v>
       </c>
       <c r="S108" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12278,7 +12273,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12288,7 +12283,12 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD108" t="b">

--- a/artfynd/A 21339-2024 artfynd.xlsx
+++ b/artfynd/A 21339-2024 artfynd.xlsx
@@ -3910,48 +3910,56 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133552502</v>
+        <v>133550180</v>
       </c>
       <c r="B32" t="n">
-        <v>80342</v>
+        <v>57958</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>580865</v>
+        <v>580876</v>
       </c>
       <c r="R32" t="n">
-        <v>6963830</v>
+        <v>6963707</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3980,7 +3988,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3990,7 +3998,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4017,32 +4030,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133550138</v>
+        <v>133552502</v>
       </c>
       <c r="B33" t="n">
-        <v>79333</v>
+        <v>80342</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4052,10 +4065,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>580712</v>
+        <v>580865</v>
       </c>
       <c r="R33" t="n">
-        <v>6963853</v>
+        <v>6963830</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4087,7 +4100,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4097,7 +4110,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4124,10 +4137,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133552488</v>
+        <v>133550138</v>
       </c>
       <c r="B34" t="n">
-        <v>89300</v>
+        <v>79333</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4135,21 +4148,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4159,10 +4172,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>580943</v>
+        <v>580712</v>
       </c>
       <c r="R34" t="n">
-        <v>6963738</v>
+        <v>6963853</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4194,7 +4207,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4204,7 +4217,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4231,10 +4244,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133550180</v>
+        <v>133552488</v>
       </c>
       <c r="B35" t="n">
-        <v>57958</v>
+        <v>89300</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4242,45 +4255,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>580876</v>
+        <v>580943</v>
       </c>
       <c r="R35" t="n">
-        <v>6963707</v>
+        <v>6963738</v>
       </c>
       <c r="S35" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4309,7 +4314,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4319,12 +4324,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:14</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4570,32 +4570,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133550136</v>
+        <v>133552497</v>
       </c>
       <c r="B38" t="n">
-        <v>99130</v>
+        <v>79090</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4605,10 +4605,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>580702</v>
+        <v>580939</v>
       </c>
       <c r="R38" t="n">
-        <v>6963851</v>
+        <v>6963799</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4650,12 +4650,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>150 ex</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4682,32 +4677,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133552494</v>
+        <v>133552478</v>
       </c>
       <c r="B39" t="n">
-        <v>79365</v>
+        <v>80473</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>6463</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4717,10 +4712,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>580955</v>
+        <v>580763</v>
       </c>
       <c r="R39" t="n">
-        <v>6963798</v>
+        <v>6963637</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4752,7 +4747,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4762,7 +4757,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4789,10 +4784,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133552453</v>
+        <v>133552494</v>
       </c>
       <c r="B40" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4800,21 +4795,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4824,13 +4819,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>580737</v>
+        <v>580955</v>
       </c>
       <c r="R40" t="n">
-        <v>6963844</v>
+        <v>6963798</v>
       </c>
       <c r="S40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4859,7 +4854,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4869,7 +4864,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4896,7 +4891,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133550132</v>
+        <v>133552453</v>
       </c>
       <c r="B41" t="n">
         <v>79333</v>
@@ -4931,13 +4926,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>580695</v>
+        <v>580737</v>
       </c>
       <c r="R41" t="n">
-        <v>6963885</v>
+        <v>6963844</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4966,7 +4961,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4976,7 +4971,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5003,7 +4998,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133550176</v>
+        <v>133550132</v>
       </c>
       <c r="B42" t="n">
         <v>79333</v>
@@ -5038,10 +5033,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>580874</v>
+        <v>580695</v>
       </c>
       <c r="R42" t="n">
-        <v>6963718</v>
+        <v>6963885</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5073,7 +5068,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5083,7 +5078,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5110,7 +5105,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133550182</v>
+        <v>133550176</v>
       </c>
       <c r="B43" t="n">
         <v>79333</v>
@@ -5145,10 +5140,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580856</v>
+        <v>580874</v>
       </c>
       <c r="R43" t="n">
-        <v>6963747</v>
+        <v>6963718</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5180,7 +5175,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5190,7 +5185,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5217,10 +5212,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133550166</v>
+        <v>133550182</v>
       </c>
       <c r="B44" t="n">
-        <v>57136</v>
+        <v>79333</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5228,49 +5223,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>580800</v>
+        <v>580856</v>
       </c>
       <c r="R44" t="n">
-        <v>6963652</v>
+        <v>6963747</v>
       </c>
       <c r="S44" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5299,7 +5282,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5309,7 +5292,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5336,10 +5319,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133552497</v>
+        <v>133550166</v>
       </c>
       <c r="B45" t="n">
-        <v>79090</v>
+        <v>57136</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5347,37 +5330,49 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>102612</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580939</v>
+        <v>580800</v>
       </c>
       <c r="R45" t="n">
-        <v>6963799</v>
+        <v>6963652</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5406,7 +5401,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5416,7 +5411,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5443,32 +5438,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133552478</v>
+        <v>133550136</v>
       </c>
       <c r="B46" t="n">
-        <v>80473</v>
+        <v>99130</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5478,10 +5473,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>580763</v>
+        <v>580702</v>
       </c>
       <c r="R46" t="n">
-        <v>6963637</v>
+        <v>6963851</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5513,7 +5508,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5523,7 +5518,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -8271,10 +8271,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133550139</v>
+        <v>133552454</v>
       </c>
       <c r="B72" t="n">
-        <v>80438</v>
+        <v>91918</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8282,21 +8282,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8306,10 +8306,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>580689</v>
+        <v>580734</v>
       </c>
       <c r="R72" t="n">
-        <v>6963841</v>
+        <v>6963814</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8341,7 +8341,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8351,12 +8351,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:19</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8383,10 +8378,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133550149</v>
+        <v>133550139</v>
       </c>
       <c r="B73" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8394,21 +8389,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8418,13 +8413,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>580697</v>
+        <v>580689</v>
       </c>
       <c r="R73" t="n">
-        <v>6963788</v>
+        <v>6963841</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8453,7 +8448,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8463,7 +8458,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8490,10 +8490,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133552454</v>
+        <v>133550149</v>
       </c>
       <c r="B74" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8501,21 +8501,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8525,13 +8525,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>580734</v>
+        <v>580697</v>
       </c>
       <c r="R74" t="n">
-        <v>6963814</v>
+        <v>6963788</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8597,32 +8597,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133550141</v>
+        <v>133552487</v>
       </c>
       <c r="B75" t="n">
-        <v>99130</v>
+        <v>89300</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8632,10 +8632,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>580713</v>
+        <v>580983</v>
       </c>
       <c r="R75" t="n">
-        <v>6963840</v>
+        <v>6963709</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8667,7 +8667,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8677,12 +8677,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>60 ex, troligen fler</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8709,7 +8704,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133552487</v>
+        <v>133550186</v>
       </c>
       <c r="B76" t="n">
         <v>89300</v>
@@ -8744,13 +8739,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>580983</v>
+        <v>580871</v>
       </c>
       <c r="R76" t="n">
-        <v>6963709</v>
+        <v>6963767</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8779,7 +8774,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8789,7 +8784,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8816,10 +8811,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133550186</v>
+        <v>133550179</v>
       </c>
       <c r="B77" t="n">
-        <v>89300</v>
+        <v>91918</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8827,21 +8822,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8851,13 +8846,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>580871</v>
+        <v>580862</v>
       </c>
       <c r="R77" t="n">
-        <v>6963767</v>
+        <v>6963713</v>
       </c>
       <c r="S77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8886,7 +8881,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8896,7 +8891,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8923,10 +8918,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133550179</v>
+        <v>133552513</v>
       </c>
       <c r="B78" t="n">
-        <v>91918</v>
+        <v>83307</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8934,21 +8929,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8958,13 +8953,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>580862</v>
+        <v>580785</v>
       </c>
       <c r="R78" t="n">
-        <v>6963713</v>
+        <v>6963796</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8993,7 +8988,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9003,7 +8998,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9030,10 +9025,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133552513</v>
+        <v>133552499</v>
       </c>
       <c r="B79" t="n">
-        <v>83307</v>
+        <v>91918</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9041,21 +9036,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9065,13 +9060,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>580785</v>
+        <v>580926</v>
       </c>
       <c r="R79" t="n">
-        <v>6963796</v>
+        <v>6963805</v>
       </c>
       <c r="S79" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9100,7 +9095,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9110,7 +9105,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9137,10 +9132,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133552499</v>
+        <v>133552462</v>
       </c>
       <c r="B80" t="n">
-        <v>91918</v>
+        <v>83307</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9148,21 +9143,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9172,10 +9167,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>580926</v>
+        <v>580738</v>
       </c>
       <c r="R80" t="n">
-        <v>6963805</v>
+        <v>6963776</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9207,7 +9202,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9217,7 +9212,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9244,10 +9239,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133552462</v>
+        <v>133550173</v>
       </c>
       <c r="B81" t="n">
-        <v>83307</v>
+        <v>80438</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9255,21 +9250,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9279,13 +9274,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>580738</v>
+        <v>580878</v>
       </c>
       <c r="R81" t="n">
-        <v>6963776</v>
+        <v>6963692</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9314,7 +9309,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9324,7 +9319,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9351,32 +9346,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133550173</v>
+        <v>133550141</v>
       </c>
       <c r="B82" t="n">
-        <v>80438</v>
+        <v>99130</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9386,13 +9381,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>580878</v>
+        <v>580713</v>
       </c>
       <c r="R82" t="n">
-        <v>6963692</v>
+        <v>6963840</v>
       </c>
       <c r="S82" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9421,7 +9416,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9431,7 +9426,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>60 ex, troligen fler</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10881,32 +10881,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133552501</v>
+        <v>133550152</v>
       </c>
       <c r="B96" t="n">
-        <v>89300</v>
+        <v>97995</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>510</v>
+        <v>221945</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10916,13 +10916,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>580895</v>
+        <v>580698</v>
       </c>
       <c r="R96" t="n">
-        <v>6963822</v>
+        <v>6963783</v>
       </c>
       <c r="S96" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10961,7 +10961,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10988,10 +10988,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>133550146</v>
+        <v>133552501</v>
       </c>
       <c r="B97" t="n">
-        <v>79333</v>
+        <v>89300</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10999,21 +10999,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11023,13 +11023,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>580687</v>
+        <v>580895</v>
       </c>
       <c r="R97" t="n">
-        <v>6963819</v>
+        <v>6963822</v>
       </c>
       <c r="S97" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11068,7 +11068,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11214,32 +11214,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>133550152</v>
+        <v>133550146</v>
       </c>
       <c r="B99" t="n">
-        <v>97995</v>
+        <v>79333</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11249,13 +11249,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>580698</v>
+        <v>580687</v>
       </c>
       <c r="R99" t="n">
-        <v>6963783</v>
+        <v>6963819</v>
       </c>
       <c r="S99" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD99" t="b">

--- a/artfynd/A 21339-2024 artfynd.xlsx
+++ b/artfynd/A 21339-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133552511</v>
+        <v>133552483</v>
       </c>
       <c r="B3" t="n">
-        <v>79365</v>
+        <v>89300</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580865</v>
+        <v>580906</v>
       </c>
       <c r="R3" t="n">
-        <v>6963889</v>
+        <v>6963679</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133552483</v>
+        <v>133552449</v>
       </c>
       <c r="B4" t="n">
-        <v>89300</v>
+        <v>91918</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580906</v>
+        <v>580689</v>
       </c>
       <c r="R4" t="n">
-        <v>6963679</v>
+        <v>6963874</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133552449</v>
+        <v>133550168</v>
       </c>
       <c r="B5" t="n">
-        <v>91918</v>
+        <v>83181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580689</v>
+        <v>580801</v>
       </c>
       <c r="R5" t="n">
-        <v>6963874</v>
+        <v>6963652</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133550168</v>
+        <v>133552481</v>
       </c>
       <c r="B6" t="n">
-        <v>83181</v>
+        <v>89300</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580801</v>
+        <v>580869</v>
       </c>
       <c r="R6" t="n">
-        <v>6963652</v>
+        <v>6963663</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133552481</v>
+        <v>133552511</v>
       </c>
       <c r="B7" t="n">
-        <v>89300</v>
+        <v>79365</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>510</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580869</v>
+        <v>580865</v>
       </c>
       <c r="R7" t="n">
-        <v>6963663</v>
+        <v>6963889</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133552456</v>
+        <v>133550153</v>
       </c>
       <c r="B9" t="n">
-        <v>91918</v>
+        <v>80438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,13 +1459,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580695</v>
+        <v>580704</v>
       </c>
       <c r="R9" t="n">
-        <v>6963806</v>
+        <v>6963785</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Stora fina exemplar av lunglav, handflata storlek.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133550155</v>
+        <v>133552456</v>
       </c>
       <c r="B10" t="n">
-        <v>80438</v>
+        <v>91918</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1547,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,13 +1571,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580715</v>
+        <v>580695</v>
       </c>
       <c r="R10" t="n">
-        <v>6963791</v>
+        <v>6963806</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1601,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,12 +1616,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1643,10 +1643,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133552452</v>
+        <v>133550155</v>
       </c>
       <c r="B11" t="n">
-        <v>83315</v>
+        <v>80438</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,21 +1654,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1678,13 +1678,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580698</v>
+        <v>580715</v>
       </c>
       <c r="R11" t="n">
-        <v>6963860</v>
+        <v>6963791</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1723,7 +1723,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1750,32 +1755,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133550153</v>
+        <v>133552461</v>
       </c>
       <c r="B12" t="n">
-        <v>80438</v>
+        <v>83298</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,13 +1790,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580704</v>
+        <v>580740</v>
       </c>
       <c r="R12" t="n">
-        <v>6963785</v>
+        <v>6963795</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1820,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1830,12 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Stora fina exemplar av lunglav, handflata storlek.</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,32 +1862,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133552461</v>
+        <v>133552452</v>
       </c>
       <c r="B13" t="n">
-        <v>83298</v>
+        <v>83315</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6439</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,13 +1897,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580740</v>
+        <v>580698</v>
       </c>
       <c r="R13" t="n">
-        <v>6963795</v>
+        <v>6963860</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -3375,10 +3375,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133552447</v>
+        <v>133550156</v>
       </c>
       <c r="B27" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3386,21 +3386,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3410,13 +3410,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580697</v>
+        <v>580715</v>
       </c>
       <c r="R27" t="n">
-        <v>6963889</v>
+        <v>6963791</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3482,10 +3482,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133550191</v>
+        <v>133550185</v>
       </c>
       <c r="B28" t="n">
-        <v>92217</v>
+        <v>79333</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3493,21 +3493,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3517,13 +3517,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580787</v>
+        <v>580867</v>
       </c>
       <c r="R28" t="n">
-        <v>6963783</v>
+        <v>6963739</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3589,10 +3589,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133552472</v>
+        <v>133550191</v>
       </c>
       <c r="B29" t="n">
-        <v>91932</v>
+        <v>92217</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3600,21 +3600,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3624,10 +3624,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580713</v>
+        <v>580787</v>
       </c>
       <c r="R29" t="n">
-        <v>6963690</v>
+        <v>6963783</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3696,10 +3696,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133550156</v>
+        <v>133552472</v>
       </c>
       <c r="B30" t="n">
-        <v>79333</v>
+        <v>91932</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3731,13 +3731,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580715</v>
+        <v>580713</v>
       </c>
       <c r="R30" t="n">
-        <v>6963791</v>
+        <v>6963690</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3803,10 +3803,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133550185</v>
+        <v>133552447</v>
       </c>
       <c r="B31" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3814,21 +3814,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3838,13 +3838,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>580867</v>
+        <v>580697</v>
       </c>
       <c r="R31" t="n">
-        <v>6963739</v>
+        <v>6963889</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4351,32 +4351,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133550163</v>
+        <v>133550148</v>
       </c>
       <c r="B36" t="n">
-        <v>97995</v>
+        <v>99130</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4386,13 +4386,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>580728</v>
+        <v>580696</v>
       </c>
       <c r="R36" t="n">
-        <v>6963787</v>
+        <v>6963788</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4431,7 +4431,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4458,32 +4463,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133550148</v>
+        <v>133550163</v>
       </c>
       <c r="B37" t="n">
-        <v>99130</v>
+        <v>97995</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4493,13 +4498,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>580696</v>
+        <v>580728</v>
       </c>
       <c r="R37" t="n">
-        <v>6963788</v>
+        <v>6963787</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4528,7 +4533,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4538,12 +4543,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:49</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>120 ex</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4570,10 +4570,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133552497</v>
+        <v>133550166</v>
       </c>
       <c r="B38" t="n">
-        <v>79090</v>
+        <v>57136</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4581,37 +4581,49 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>102612</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>580939</v>
+        <v>580800</v>
       </c>
       <c r="R38" t="n">
-        <v>6963799</v>
+        <v>6963652</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4640,7 +4652,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4650,7 +4662,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4677,32 +4689,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133552478</v>
+        <v>133552494</v>
       </c>
       <c r="B39" t="n">
-        <v>80473</v>
+        <v>79365</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6463</v>
+        <v>185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4712,10 +4724,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>580763</v>
+        <v>580955</v>
       </c>
       <c r="R39" t="n">
-        <v>6963637</v>
+        <v>6963798</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4747,7 +4759,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4757,7 +4769,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4784,32 +4796,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133552494</v>
+        <v>133552478</v>
       </c>
       <c r="B40" t="n">
-        <v>79365</v>
+        <v>80473</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>6463</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4819,10 +4831,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>580955</v>
+        <v>580763</v>
       </c>
       <c r="R40" t="n">
-        <v>6963798</v>
+        <v>6963637</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4854,7 +4866,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4864,7 +4876,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4891,10 +4903,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133552453</v>
+        <v>133552497</v>
       </c>
       <c r="B41" t="n">
-        <v>79333</v>
+        <v>79090</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4902,21 +4914,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4926,13 +4938,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>580737</v>
+        <v>580939</v>
       </c>
       <c r="R41" t="n">
-        <v>6963844</v>
+        <v>6963799</v>
       </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4961,7 +4973,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4971,7 +4983,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4998,7 +5010,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133550132</v>
+        <v>133552453</v>
       </c>
       <c r="B42" t="n">
         <v>79333</v>
@@ -5033,13 +5045,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>580695</v>
+        <v>580737</v>
       </c>
       <c r="R42" t="n">
-        <v>6963885</v>
+        <v>6963844</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5068,7 +5080,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5078,7 +5090,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5105,7 +5117,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133550176</v>
+        <v>133550132</v>
       </c>
       <c r="B43" t="n">
         <v>79333</v>
@@ -5140,10 +5152,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580874</v>
+        <v>580695</v>
       </c>
       <c r="R43" t="n">
-        <v>6963718</v>
+        <v>6963885</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5175,7 +5187,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5185,7 +5197,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5212,7 +5224,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133550182</v>
+        <v>133550176</v>
       </c>
       <c r="B44" t="n">
         <v>79333</v>
@@ -5247,10 +5259,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>580856</v>
+        <v>580874</v>
       </c>
       <c r="R44" t="n">
-        <v>6963747</v>
+        <v>6963718</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5282,7 +5294,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5292,7 +5304,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5319,10 +5331,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133550166</v>
+        <v>133550182</v>
       </c>
       <c r="B45" t="n">
-        <v>57136</v>
+        <v>79333</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5330,49 +5342,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580800</v>
+        <v>580856</v>
       </c>
       <c r="R45" t="n">
-        <v>6963652</v>
+        <v>6963747</v>
       </c>
       <c r="S45" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5550,10 +5550,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133552503</v>
+        <v>133552490</v>
       </c>
       <c r="B47" t="n">
-        <v>89300</v>
+        <v>80438</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5561,21 +5561,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>580844</v>
+        <v>580853</v>
       </c>
       <c r="R47" t="n">
-        <v>6963844</v>
+        <v>6963702</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5657,10 +5657,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133550160</v>
+        <v>133552491</v>
       </c>
       <c r="B48" t="n">
-        <v>92217</v>
+        <v>79333</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5668,21 +5668,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5692,13 +5692,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>580715</v>
+        <v>580883</v>
       </c>
       <c r="R48" t="n">
-        <v>6963743</v>
+        <v>6963753</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5764,10 +5764,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133552448</v>
+        <v>133552482</v>
       </c>
       <c r="B49" t="n">
-        <v>91918</v>
+        <v>83315</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5775,21 +5775,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5799,10 +5799,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>580691</v>
+        <v>580879</v>
       </c>
       <c r="R49" t="n">
-        <v>6963879</v>
+        <v>6963658</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5871,10 +5871,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133552490</v>
+        <v>133552486</v>
       </c>
       <c r="B50" t="n">
-        <v>80438</v>
+        <v>83315</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5882,21 +5882,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>580853</v>
+        <v>580985</v>
       </c>
       <c r="R50" t="n">
-        <v>6963702</v>
+        <v>6963707</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5941,7 +5941,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5978,10 +5978,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133552486</v>
+        <v>133552508</v>
       </c>
       <c r="B51" t="n">
-        <v>83315</v>
+        <v>57958</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5989,34 +5989,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>580985</v>
+        <v>580813</v>
       </c>
       <c r="R51" t="n">
-        <v>6963707</v>
+        <v>6963779</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6048,7 +6056,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6058,7 +6066,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6085,32 +6098,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133552491</v>
+        <v>133550162</v>
       </c>
       <c r="B52" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6120,10 +6133,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>580883</v>
+        <v>580728</v>
       </c>
       <c r="R52" t="n">
-        <v>6963753</v>
+        <v>6963787</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6155,7 +6168,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6165,7 +6178,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6192,32 +6210,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133552482</v>
+        <v>133550147</v>
       </c>
       <c r="B53" t="n">
-        <v>83315</v>
+        <v>99130</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6227,13 +6245,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>580879</v>
+        <v>580689</v>
       </c>
       <c r="R53" t="n">
-        <v>6963658</v>
+        <v>6963814</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6262,7 +6280,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6272,7 +6290,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6299,10 +6322,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133552508</v>
+        <v>133552503</v>
       </c>
       <c r="B54" t="n">
-        <v>57958</v>
+        <v>89300</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6310,42 +6333,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>580813</v>
+        <v>580844</v>
       </c>
       <c r="R54" t="n">
-        <v>6963779</v>
+        <v>6963844</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6377,7 +6392,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6387,12 +6402,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:04</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6419,32 +6429,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133550162</v>
+        <v>133550160</v>
       </c>
       <c r="B55" t="n">
-        <v>99130</v>
+        <v>92217</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6454,13 +6464,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>580728</v>
+        <v>580715</v>
       </c>
       <c r="R55" t="n">
-        <v>6963787</v>
+        <v>6963743</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6489,7 +6499,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6499,12 +6509,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:34</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>50 ex</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6531,32 +6536,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133550147</v>
+        <v>133552448</v>
       </c>
       <c r="B56" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6566,13 +6571,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>580689</v>
+        <v>580691</v>
       </c>
       <c r="R56" t="n">
-        <v>6963814</v>
+        <v>6963879</v>
       </c>
       <c r="S56" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6601,7 +6606,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6611,12 +6616,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>70 ex</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7285,32 +7285,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133550133</v>
+        <v>133550170</v>
       </c>
       <c r="B63" t="n">
-        <v>99130</v>
+        <v>79365</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7320,10 +7320,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>580685</v>
+        <v>580801</v>
       </c>
       <c r="R63" t="n">
-        <v>6963865</v>
+        <v>6963652</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7365,12 +7365,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>100 ex</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7397,7 +7392,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133550134</v>
+        <v>133550133</v>
       </c>
       <c r="B64" t="n">
         <v>99130</v>
@@ -7432,10 +7427,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>580691</v>
+        <v>580685</v>
       </c>
       <c r="R64" t="n">
-        <v>6963863</v>
+        <v>6963865</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7467,7 +7462,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7477,12 +7472,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>200 ex</t>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7509,32 +7504,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133550170</v>
+        <v>133550134</v>
       </c>
       <c r="B65" t="n">
-        <v>79365</v>
+        <v>99130</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7544,10 +7539,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>580801</v>
+        <v>580691</v>
       </c>
       <c r="R65" t="n">
-        <v>6963652</v>
+        <v>6963863</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7579,7 +7574,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7589,7 +7584,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7723,10 +7723,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133552460</v>
+        <v>133552484</v>
       </c>
       <c r="B67" t="n">
-        <v>83315</v>
+        <v>79333</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7734,21 +7734,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7758,10 +7758,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>580722</v>
+        <v>580938</v>
       </c>
       <c r="R67" t="n">
-        <v>6963787</v>
+        <v>6963702</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7830,10 +7830,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133552484</v>
+        <v>133552460</v>
       </c>
       <c r="B68" t="n">
-        <v>79333</v>
+        <v>83315</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7841,21 +7841,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7865,10 +7865,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>580938</v>
+        <v>580722</v>
       </c>
       <c r="R68" t="n">
-        <v>6963702</v>
+        <v>6963787</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7900,7 +7900,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8378,10 +8378,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133550139</v>
+        <v>133550149</v>
       </c>
       <c r="B73" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8389,21 +8389,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8413,13 +8413,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>580689</v>
+        <v>580697</v>
       </c>
       <c r="R73" t="n">
-        <v>6963841</v>
+        <v>6963788</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8458,12 +8458,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:19</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8490,10 +8485,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133550149</v>
+        <v>133550139</v>
       </c>
       <c r="B74" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8501,21 +8496,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8525,13 +8520,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>580697</v>
+        <v>580689</v>
       </c>
       <c r="R74" t="n">
-        <v>6963788</v>
+        <v>6963841</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8560,7 +8555,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8570,7 +8565,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8597,10 +8597,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133552487</v>
+        <v>133550173</v>
       </c>
       <c r="B75" t="n">
-        <v>89300</v>
+        <v>80438</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8608,21 +8608,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>580983</v>
+        <v>580878</v>
       </c>
       <c r="R75" t="n">
-        <v>6963709</v>
+        <v>6963692</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8704,32 +8704,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133550186</v>
+        <v>133550141</v>
       </c>
       <c r="B76" t="n">
-        <v>89300</v>
+        <v>99130</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8739,13 +8739,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>580871</v>
+        <v>580713</v>
       </c>
       <c r="R76" t="n">
-        <v>6963767</v>
+        <v>6963840</v>
       </c>
       <c r="S76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8784,7 +8784,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>60 ex, troligen fler</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8811,10 +8816,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133550179</v>
+        <v>133552487</v>
       </c>
       <c r="B77" t="n">
-        <v>91918</v>
+        <v>89300</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8822,21 +8827,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8846,10 +8851,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>580862</v>
+        <v>580983</v>
       </c>
       <c r="R77" t="n">
-        <v>6963713</v>
+        <v>6963709</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8881,7 +8886,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8891,7 +8896,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8918,10 +8923,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133552513</v>
+        <v>133550179</v>
       </c>
       <c r="B78" t="n">
-        <v>83307</v>
+        <v>91918</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8929,21 +8934,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8953,13 +8958,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>580785</v>
+        <v>580862</v>
       </c>
       <c r="R78" t="n">
-        <v>6963796</v>
+        <v>6963713</v>
       </c>
       <c r="S78" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8988,7 +8993,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8998,7 +9003,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9025,10 +9030,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133552499</v>
+        <v>133552513</v>
       </c>
       <c r="B79" t="n">
-        <v>91918</v>
+        <v>83307</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9036,21 +9041,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9060,13 +9065,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>580926</v>
+        <v>580785</v>
       </c>
       <c r="R79" t="n">
-        <v>6963805</v>
+        <v>6963796</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9095,7 +9100,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9105,7 +9110,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9132,10 +9137,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133552462</v>
+        <v>133550186</v>
       </c>
       <c r="B80" t="n">
-        <v>83307</v>
+        <v>89300</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9143,21 +9148,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>308</v>
+        <v>510</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9167,13 +9172,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>580738</v>
+        <v>580871</v>
       </c>
       <c r="R80" t="n">
-        <v>6963776</v>
+        <v>6963767</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9202,7 +9207,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9212,7 +9217,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9239,10 +9244,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133550173</v>
+        <v>133552499</v>
       </c>
       <c r="B81" t="n">
-        <v>80438</v>
+        <v>91918</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9250,21 +9255,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9274,13 +9279,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>580878</v>
+        <v>580926</v>
       </c>
       <c r="R81" t="n">
-        <v>6963692</v>
+        <v>6963805</v>
       </c>
       <c r="S81" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9309,7 +9314,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9319,7 +9324,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9346,32 +9351,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133550141</v>
+        <v>133552462</v>
       </c>
       <c r="B82" t="n">
-        <v>99130</v>
+        <v>83307</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9381,10 +9386,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>580713</v>
+        <v>580738</v>
       </c>
       <c r="R82" t="n">
-        <v>6963840</v>
+        <v>6963776</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9416,7 +9421,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9426,12 +9431,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>60 ex, troligen fler</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9458,32 +9458,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>133552476</v>
+        <v>133550140</v>
       </c>
       <c r="B83" t="n">
-        <v>80438</v>
+        <v>99130</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>580767</v>
+        <v>580694</v>
       </c>
       <c r="R83" t="n">
-        <v>6963639</v>
+        <v>6963839</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9528,7 +9528,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9538,7 +9538,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>33 ex</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9565,32 +9570,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133552463</v>
+        <v>133552467</v>
       </c>
       <c r="B84" t="n">
-        <v>80438</v>
+        <v>92641</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9600,13 +9605,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>580725</v>
+        <v>580754</v>
       </c>
       <c r="R84" t="n">
-        <v>6963773</v>
+        <v>6963789</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9635,7 +9640,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9645,7 +9650,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9672,32 +9677,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133552467</v>
+        <v>133552476</v>
       </c>
       <c r="B85" t="n">
-        <v>92641</v>
+        <v>80438</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9707,13 +9712,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>580754</v>
+        <v>580767</v>
       </c>
       <c r="R85" t="n">
-        <v>6963789</v>
+        <v>6963639</v>
       </c>
       <c r="S85" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9742,7 +9747,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9752,7 +9757,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9779,10 +9784,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133552505</v>
+        <v>133552463</v>
       </c>
       <c r="B86" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9790,21 +9795,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9814,10 +9819,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>580836</v>
+        <v>580725</v>
       </c>
       <c r="R86" t="n">
-        <v>6963844</v>
+        <v>6963773</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9849,7 +9854,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9859,7 +9864,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9886,7 +9891,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133552469</v>
+        <v>133552505</v>
       </c>
       <c r="B87" t="n">
         <v>79333</v>
@@ -9921,10 +9926,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>580751</v>
+        <v>580836</v>
       </c>
       <c r="R87" t="n">
-        <v>6963778</v>
+        <v>6963844</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9956,7 +9961,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9966,7 +9971,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9993,32 +9998,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133550140</v>
+        <v>133552469</v>
       </c>
       <c r="B88" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10028,10 +10033,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>580694</v>
+        <v>580751</v>
       </c>
       <c r="R88" t="n">
-        <v>6963839</v>
+        <v>6963778</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10063,7 +10068,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10073,12 +10078,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>33 ex</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10224,32 +10224,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133552471</v>
+        <v>133550193</v>
       </c>
       <c r="B90" t="n">
-        <v>83315</v>
+        <v>99130</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10259,10 +10259,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>580717</v>
+        <v>580781</v>
       </c>
       <c r="R90" t="n">
-        <v>6963694</v>
+        <v>6963825</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10294,7 +10294,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10304,7 +10304,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ca 60 ex</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10331,32 +10336,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133552510</v>
+        <v>133552455</v>
       </c>
       <c r="B91" t="n">
-        <v>83315</v>
+        <v>99130</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10366,10 +10371,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>580829</v>
+        <v>580733</v>
       </c>
       <c r="R91" t="n">
-        <v>6963885</v>
+        <v>6963814</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10401,7 +10406,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10411,7 +10416,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10438,32 +10448,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133552493</v>
+        <v>133552512</v>
       </c>
       <c r="B92" t="n">
-        <v>89300</v>
+        <v>99130</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10473,10 +10483,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>580914</v>
+        <v>580803</v>
       </c>
       <c r="R92" t="n">
-        <v>6963757</v>
+        <v>6963894</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10508,7 +10518,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10518,7 +10528,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>150 + ex</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10545,32 +10560,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133550193</v>
+        <v>133552510</v>
       </c>
       <c r="B93" t="n">
-        <v>99130</v>
+        <v>83315</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10580,10 +10595,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>580781</v>
+        <v>580829</v>
       </c>
       <c r="R93" t="n">
-        <v>6963825</v>
+        <v>6963885</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10615,7 +10630,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10625,12 +10640,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>16:41</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Ca 60 ex</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10657,32 +10667,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133552455</v>
+        <v>133552471</v>
       </c>
       <c r="B94" t="n">
-        <v>99130</v>
+        <v>83315</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10692,10 +10702,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>580733</v>
+        <v>580717</v>
       </c>
       <c r="R94" t="n">
-        <v>6963814</v>
+        <v>6963694</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10727,7 +10737,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10737,12 +10747,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>200 ex</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10769,32 +10774,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133552512</v>
+        <v>133552493</v>
       </c>
       <c r="B95" t="n">
-        <v>99130</v>
+        <v>89300</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10804,10 +10809,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>580803</v>
+        <v>580914</v>
       </c>
       <c r="R95" t="n">
-        <v>6963894</v>
+        <v>6963757</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10839,7 +10844,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10849,12 +10854,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>150 + ex</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11095,10 +11095,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>133550187</v>
+        <v>133550146</v>
       </c>
       <c r="B98" t="n">
-        <v>57136</v>
+        <v>79333</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11106,46 +11106,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>580843</v>
+        <v>580687</v>
       </c>
       <c r="R98" t="n">
-        <v>6963778</v>
+        <v>6963819</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11177,7 +11165,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11187,7 +11175,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11214,10 +11202,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>133550146</v>
+        <v>133550187</v>
       </c>
       <c r="B99" t="n">
-        <v>79333</v>
+        <v>57136</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11225,34 +11213,46 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>580687</v>
+        <v>580843</v>
       </c>
       <c r="R99" t="n">
-        <v>6963819</v>
+        <v>6963778</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11284,7 +11284,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11321,48 +11321,56 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133552477</v>
+        <v>133552495</v>
       </c>
       <c r="B100" t="n">
-        <v>80467</v>
+        <v>57958</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>580764</v>
+        <v>580953</v>
       </c>
       <c r="R100" t="n">
-        <v>6963638</v>
+        <v>6963811</v>
       </c>
       <c r="S100" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11391,7 +11399,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11401,7 +11409,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Ett färskt ringhack på tall</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11535,56 +11548,48 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133552495</v>
+        <v>133552477</v>
       </c>
       <c r="B102" t="n">
-        <v>57958</v>
+        <v>80467</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>580953</v>
+        <v>580764</v>
       </c>
       <c r="R102" t="n">
-        <v>6963811</v>
+        <v>6963638</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11613,7 +11618,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11623,12 +11628,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Ett färskt ringhack på tall</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11655,10 +11655,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133552500</v>
+        <v>133550188</v>
       </c>
       <c r="B103" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11666,21 +11666,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11690,13 +11690,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>580902</v>
+        <v>580833</v>
       </c>
       <c r="R103" t="n">
-        <v>6963823</v>
+        <v>6963785</v>
       </c>
       <c r="S103" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11735,7 +11735,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11762,7 +11762,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133550188</v>
+        <v>133550158</v>
       </c>
       <c r="B104" t="n">
         <v>79333</v>
@@ -11797,10 +11797,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>580833</v>
+        <v>580720</v>
       </c>
       <c r="R104" t="n">
-        <v>6963785</v>
+        <v>6963787</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11832,7 +11832,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11869,7 +11869,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133550158</v>
+        <v>133550190</v>
       </c>
       <c r="B105" t="n">
         <v>79333</v>
@@ -11904,13 +11904,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>580720</v>
+        <v>580838</v>
       </c>
       <c r="R105" t="n">
-        <v>6963787</v>
+        <v>6963811</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11949,7 +11949,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11976,7 +11981,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133550190</v>
+        <v>133550177</v>
       </c>
       <c r="B106" t="n">
         <v>79333</v>
@@ -12011,10 +12016,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>580838</v>
+        <v>580864</v>
       </c>
       <c r="R106" t="n">
-        <v>6963811</v>
+        <v>6963715</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -12046,7 +12051,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12056,12 +12061,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12088,10 +12088,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133550177</v>
+        <v>133552500</v>
       </c>
       <c r="B107" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12099,21 +12099,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12123,13 +12123,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>580864</v>
+        <v>580902</v>
       </c>
       <c r="R107" t="n">
-        <v>6963715</v>
+        <v>6963823</v>
       </c>
       <c r="S107" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD107" t="b">

--- a/artfynd/A 21339-2024 artfynd.xlsx
+++ b/artfynd/A 21339-2024 artfynd.xlsx
@@ -3910,56 +3910,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133550180</v>
+        <v>133552502</v>
       </c>
       <c r="B32" t="n">
-        <v>57958</v>
+        <v>80342</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>580876</v>
+        <v>580865</v>
       </c>
       <c r="R32" t="n">
-        <v>6963707</v>
+        <v>6963830</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3988,7 +3980,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3998,12 +3990,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:14</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4030,32 +4017,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133552502</v>
+        <v>133550138</v>
       </c>
       <c r="B33" t="n">
-        <v>80342</v>
+        <v>79333</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4065,10 +4052,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>580865</v>
+        <v>580712</v>
       </c>
       <c r="R33" t="n">
-        <v>6963830</v>
+        <v>6963853</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4100,7 +4087,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4110,7 +4097,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4137,10 +4124,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133550138</v>
+        <v>133552488</v>
       </c>
       <c r="B34" t="n">
-        <v>79333</v>
+        <v>89300</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4148,21 +4135,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4172,10 +4159,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>580712</v>
+        <v>580943</v>
       </c>
       <c r="R34" t="n">
-        <v>6963853</v>
+        <v>6963738</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4207,7 +4194,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4217,7 +4204,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4244,10 +4231,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133552488</v>
+        <v>133550180</v>
       </c>
       <c r="B35" t="n">
-        <v>89300</v>
+        <v>57958</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4255,37 +4242,45 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>580943</v>
+        <v>580876</v>
       </c>
       <c r="R35" t="n">
-        <v>6963738</v>
+        <v>6963707</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4314,7 +4309,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4324,7 +4319,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4570,10 +4570,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133550166</v>
+        <v>133552494</v>
       </c>
       <c r="B38" t="n">
-        <v>57136</v>
+        <v>79365</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4581,49 +4581,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>102612</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>580800</v>
+        <v>580955</v>
       </c>
       <c r="R38" t="n">
-        <v>6963652</v>
+        <v>6963798</v>
       </c>
       <c r="S38" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4652,7 +4640,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4662,7 +4650,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4689,32 +4677,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133552494</v>
+        <v>133552478</v>
       </c>
       <c r="B39" t="n">
-        <v>79365</v>
+        <v>80473</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>6463</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4724,10 +4712,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>580955</v>
+        <v>580763</v>
       </c>
       <c r="R39" t="n">
-        <v>6963798</v>
+        <v>6963637</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4759,7 +4747,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4769,7 +4757,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4796,32 +4784,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133552478</v>
+        <v>133552497</v>
       </c>
       <c r="B40" t="n">
-        <v>80473</v>
+        <v>79090</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6463</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4831,10 +4819,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>580763</v>
+        <v>580939</v>
       </c>
       <c r="R40" t="n">
-        <v>6963637</v>
+        <v>6963799</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4866,7 +4854,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4876,7 +4864,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4903,10 +4891,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133552497</v>
+        <v>133552453</v>
       </c>
       <c r="B41" t="n">
-        <v>79090</v>
+        <v>79333</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4914,21 +4902,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4938,13 +4926,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>580939</v>
+        <v>580737</v>
       </c>
       <c r="R41" t="n">
-        <v>6963799</v>
+        <v>6963844</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4973,7 +4961,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4983,7 +4971,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5010,7 +4998,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133552453</v>
+        <v>133550132</v>
       </c>
       <c r="B42" t="n">
         <v>79333</v>
@@ -5045,13 +5033,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>580737</v>
+        <v>580695</v>
       </c>
       <c r="R42" t="n">
-        <v>6963844</v>
+        <v>6963885</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5080,7 +5068,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5090,7 +5078,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5117,7 +5105,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133550132</v>
+        <v>133550176</v>
       </c>
       <c r="B43" t="n">
         <v>79333</v>
@@ -5152,10 +5140,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580695</v>
+        <v>580874</v>
       </c>
       <c r="R43" t="n">
-        <v>6963885</v>
+        <v>6963718</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5187,7 +5175,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5197,7 +5185,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5224,7 +5212,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133550176</v>
+        <v>133550182</v>
       </c>
       <c r="B44" t="n">
         <v>79333</v>
@@ -5259,10 +5247,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>580874</v>
+        <v>580856</v>
       </c>
       <c r="R44" t="n">
-        <v>6963718</v>
+        <v>6963747</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5294,7 +5282,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5304,7 +5292,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5331,10 +5319,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133550182</v>
+        <v>133550166</v>
       </c>
       <c r="B45" t="n">
-        <v>79333</v>
+        <v>57136</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5342,37 +5330,49 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580856</v>
+        <v>580800</v>
       </c>
       <c r="R45" t="n">
-        <v>6963747</v>
+        <v>6963652</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -10224,32 +10224,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133550193</v>
+        <v>133552493</v>
       </c>
       <c r="B90" t="n">
-        <v>99130</v>
+        <v>89300</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10259,10 +10259,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>580781</v>
+        <v>580914</v>
       </c>
       <c r="R90" t="n">
-        <v>6963825</v>
+        <v>6963757</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10294,7 +10294,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10304,12 +10304,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>16:41</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Ca 60 ex</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10336,32 +10331,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133552455</v>
+        <v>133552510</v>
       </c>
       <c r="B91" t="n">
-        <v>99130</v>
+        <v>83315</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10371,10 +10366,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>580733</v>
+        <v>580829</v>
       </c>
       <c r="R91" t="n">
-        <v>6963814</v>
+        <v>6963885</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10406,7 +10401,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10416,12 +10411,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>200 ex</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10448,32 +10438,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133552512</v>
+        <v>133552471</v>
       </c>
       <c r="B92" t="n">
-        <v>99130</v>
+        <v>83315</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10483,10 +10473,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>580803</v>
+        <v>580717</v>
       </c>
       <c r="R92" t="n">
-        <v>6963894</v>
+        <v>6963694</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10518,7 +10508,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10528,12 +10518,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>150 + ex</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10560,32 +10545,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133552510</v>
+        <v>133550193</v>
       </c>
       <c r="B93" t="n">
-        <v>83315</v>
+        <v>99130</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10595,10 +10580,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>580829</v>
+        <v>580781</v>
       </c>
       <c r="R93" t="n">
-        <v>6963885</v>
+        <v>6963825</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10630,7 +10615,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10640,7 +10625,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Ca 60 ex</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10667,32 +10657,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133552471</v>
+        <v>133552455</v>
       </c>
       <c r="B94" t="n">
-        <v>83315</v>
+        <v>99130</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10702,10 +10692,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>580717</v>
+        <v>580733</v>
       </c>
       <c r="R94" t="n">
-        <v>6963694</v>
+        <v>6963814</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10737,7 +10727,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10747,7 +10737,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10774,32 +10769,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133552493</v>
+        <v>133552512</v>
       </c>
       <c r="B95" t="n">
-        <v>89300</v>
+        <v>99130</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10809,10 +10804,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>580914</v>
+        <v>580803</v>
       </c>
       <c r="R95" t="n">
-        <v>6963757</v>
+        <v>6963894</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10844,7 +10839,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10854,7 +10849,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>150 + ex</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11655,10 +11655,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133550188</v>
+        <v>133552500</v>
       </c>
       <c r="B103" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11666,21 +11666,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11690,13 +11690,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>580833</v>
+        <v>580902</v>
       </c>
       <c r="R103" t="n">
-        <v>6963785</v>
+        <v>6963823</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11735,7 +11735,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11762,7 +11762,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133550158</v>
+        <v>133550188</v>
       </c>
       <c r="B104" t="n">
         <v>79333</v>
@@ -11797,10 +11797,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>580720</v>
+        <v>580833</v>
       </c>
       <c r="R104" t="n">
-        <v>6963787</v>
+        <v>6963785</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11832,7 +11832,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11869,7 +11869,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133550190</v>
+        <v>133550158</v>
       </c>
       <c r="B105" t="n">
         <v>79333</v>
@@ -11904,13 +11904,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>580838</v>
+        <v>580720</v>
       </c>
       <c r="R105" t="n">
-        <v>6963811</v>
+        <v>6963787</v>
       </c>
       <c r="S105" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11949,12 +11949,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11981,7 +11976,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133550177</v>
+        <v>133550190</v>
       </c>
       <c r="B106" t="n">
         <v>79333</v>
@@ -12016,10 +12011,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>580864</v>
+        <v>580838</v>
       </c>
       <c r="R106" t="n">
-        <v>6963715</v>
+        <v>6963811</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -12051,7 +12046,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12061,7 +12056,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12088,10 +12088,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133552500</v>
+        <v>133550177</v>
       </c>
       <c r="B107" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12099,21 +12099,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12123,13 +12123,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>580902</v>
+        <v>580864</v>
       </c>
       <c r="R107" t="n">
-        <v>6963823</v>
+        <v>6963715</v>
       </c>
       <c r="S107" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD107" t="b">

--- a/artfynd/A 21339-2024 artfynd.xlsx
+++ b/artfynd/A 21339-2024 artfynd.xlsx
@@ -1424,32 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133550153</v>
+        <v>133550154</v>
       </c>
       <c r="B9" t="n">
-        <v>80438</v>
+        <v>99130</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,13 +1459,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580704</v>
+        <v>580712</v>
       </c>
       <c r="R9" t="n">
-        <v>6963785</v>
+        <v>6963788</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Stora fina exemplar av lunglav, handflata storlek.</t>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,32 +1536,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133552456</v>
+        <v>133550157</v>
       </c>
       <c r="B10" t="n">
-        <v>91918</v>
+        <v>99130</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,13 +1571,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580695</v>
+        <v>580715</v>
       </c>
       <c r="R10" t="n">
-        <v>6963806</v>
+        <v>6963786</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,7 +1616,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1643,32 +1648,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133550155</v>
+        <v>133552468</v>
       </c>
       <c r="B11" t="n">
-        <v>80438</v>
+        <v>97995</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1678,13 +1683,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580715</v>
+        <v>580758</v>
       </c>
       <c r="R11" t="n">
-        <v>6963791</v>
+        <v>6963787</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1713,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1723,12 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,32 +1755,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133552461</v>
+        <v>133552456</v>
       </c>
       <c r="B12" t="n">
-        <v>83298</v>
+        <v>91918</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6439</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580740</v>
+        <v>580695</v>
       </c>
       <c r="R12" t="n">
-        <v>6963795</v>
+        <v>6963806</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133552452</v>
+        <v>133550153</v>
       </c>
       <c r="B13" t="n">
-        <v>83315</v>
+        <v>80438</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,21 +1873,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,13 +1897,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580698</v>
+        <v>580704</v>
       </c>
       <c r="R13" t="n">
-        <v>6963860</v>
+        <v>6963785</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1942,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Stora fina exemplar av lunglav, handflata storlek.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133550174</v>
+        <v>133550155</v>
       </c>
       <c r="B14" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,21 +1985,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2004,13 +2009,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580879</v>
+        <v>580715</v>
       </c>
       <c r="R14" t="n">
-        <v>6963690</v>
+        <v>6963791</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2039,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2049,7 +2054,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,32 +2086,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133552475</v>
+        <v>133552461</v>
       </c>
       <c r="B15" t="n">
-        <v>79333</v>
+        <v>83298</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2111,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580801</v>
+        <v>580740</v>
       </c>
       <c r="R15" t="n">
-        <v>6963655</v>
+        <v>6963795</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2146,7 +2156,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2156,7 +2166,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2183,32 +2193,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133550154</v>
+        <v>133552452</v>
       </c>
       <c r="B16" t="n">
-        <v>99130</v>
+        <v>83315</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2218,13 +2228,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580712</v>
+        <v>580698</v>
       </c>
       <c r="R16" t="n">
-        <v>6963788</v>
+        <v>6963860</v>
       </c>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2253,7 +2263,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2263,12 +2273,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:59</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>70 ex</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,32 +2300,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133550157</v>
+        <v>133550174</v>
       </c>
       <c r="B17" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2330,13 +2335,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580715</v>
+        <v>580879</v>
       </c>
       <c r="R17" t="n">
-        <v>6963786</v>
+        <v>6963690</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2365,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2375,12 +2380,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>150 ex</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,32 +2407,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133552468</v>
+        <v>133552475</v>
       </c>
       <c r="B18" t="n">
-        <v>97995</v>
+        <v>79333</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580758</v>
+        <v>580801</v>
       </c>
       <c r="R18" t="n">
-        <v>6963787</v>
+        <v>6963655</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -4124,32 +4124,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133552488</v>
+        <v>133550148</v>
       </c>
       <c r="B34" t="n">
-        <v>89300</v>
+        <v>99130</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4159,13 +4159,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>580943</v>
+        <v>580696</v>
       </c>
       <c r="R34" t="n">
-        <v>6963738</v>
+        <v>6963788</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4204,7 +4204,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4231,10 +4236,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133550180</v>
+        <v>133552488</v>
       </c>
       <c r="B35" t="n">
-        <v>57958</v>
+        <v>89300</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4242,45 +4247,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>580876</v>
+        <v>580943</v>
       </c>
       <c r="R35" t="n">
-        <v>6963707</v>
+        <v>6963738</v>
       </c>
       <c r="S35" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4309,7 +4306,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4319,12 +4316,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:14</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4351,32 +4343,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133550148</v>
+        <v>133550163</v>
       </c>
       <c r="B36" t="n">
-        <v>99130</v>
+        <v>97995</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4386,13 +4378,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>580696</v>
+        <v>580728</v>
       </c>
       <c r="R36" t="n">
-        <v>6963788</v>
+        <v>6963787</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4421,7 +4413,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4431,12 +4423,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:49</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>120 ex</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4463,48 +4450,56 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133550163</v>
+        <v>133550180</v>
       </c>
       <c r="B37" t="n">
-        <v>97995</v>
+        <v>57958</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>580728</v>
+        <v>580876</v>
       </c>
       <c r="R37" t="n">
-        <v>6963787</v>
+        <v>6963707</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4533,7 +4528,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4543,7 +4538,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4570,10 +4570,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133552494</v>
+        <v>133550166</v>
       </c>
       <c r="B38" t="n">
-        <v>79365</v>
+        <v>57136</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4581,37 +4581,49 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>102612</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>580955</v>
+        <v>580800</v>
       </c>
       <c r="R38" t="n">
-        <v>6963798</v>
+        <v>6963652</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4640,7 +4652,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4650,7 +4662,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4677,32 +4689,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133552478</v>
+        <v>133552494</v>
       </c>
       <c r="B39" t="n">
-        <v>80473</v>
+        <v>79365</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6463</v>
+        <v>185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4712,10 +4724,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>580763</v>
+        <v>580955</v>
       </c>
       <c r="R39" t="n">
-        <v>6963637</v>
+        <v>6963798</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4747,7 +4759,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4757,7 +4769,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4784,32 +4796,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133552497</v>
+        <v>133552478</v>
       </c>
       <c r="B40" t="n">
-        <v>79090</v>
+        <v>80473</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6463</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4819,10 +4831,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>580939</v>
+        <v>580763</v>
       </c>
       <c r="R40" t="n">
-        <v>6963799</v>
+        <v>6963637</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4854,7 +4866,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4864,7 +4876,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4891,10 +4903,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133552453</v>
+        <v>133552497</v>
       </c>
       <c r="B41" t="n">
-        <v>79333</v>
+        <v>79090</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4902,21 +4914,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4926,13 +4938,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>580737</v>
+        <v>580939</v>
       </c>
       <c r="R41" t="n">
-        <v>6963844</v>
+        <v>6963799</v>
       </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4961,7 +4973,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4971,7 +4983,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4998,7 +5010,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133550132</v>
+        <v>133552453</v>
       </c>
       <c r="B42" t="n">
         <v>79333</v>
@@ -5033,13 +5045,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>580695</v>
+        <v>580737</v>
       </c>
       <c r="R42" t="n">
-        <v>6963885</v>
+        <v>6963844</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5068,7 +5080,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5078,7 +5090,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5105,7 +5117,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133550176</v>
+        <v>133550132</v>
       </c>
       <c r="B43" t="n">
         <v>79333</v>
@@ -5140,10 +5152,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580874</v>
+        <v>580695</v>
       </c>
       <c r="R43" t="n">
-        <v>6963718</v>
+        <v>6963885</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5175,7 +5187,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5185,7 +5197,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5212,7 +5224,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133550182</v>
+        <v>133550176</v>
       </c>
       <c r="B44" t="n">
         <v>79333</v>
@@ -5247,10 +5259,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>580856</v>
+        <v>580874</v>
       </c>
       <c r="R44" t="n">
-        <v>6963747</v>
+        <v>6963718</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5282,7 +5294,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5292,7 +5304,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5319,10 +5331,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133550166</v>
+        <v>133550182</v>
       </c>
       <c r="B45" t="n">
-        <v>57136</v>
+        <v>79333</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5330,49 +5342,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580800</v>
+        <v>580856</v>
       </c>
       <c r="R45" t="n">
-        <v>6963652</v>
+        <v>6963747</v>
       </c>
       <c r="S45" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -10881,32 +10881,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133550152</v>
+        <v>133550146</v>
       </c>
       <c r="B96" t="n">
-        <v>97995</v>
+        <v>79333</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10916,13 +10916,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>580698</v>
+        <v>580687</v>
       </c>
       <c r="R96" t="n">
-        <v>6963783</v>
+        <v>6963819</v>
       </c>
       <c r="S96" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10961,7 +10961,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10988,32 +10988,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>133552501</v>
+        <v>133550152</v>
       </c>
       <c r="B97" t="n">
-        <v>89300</v>
+        <v>97995</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>510</v>
+        <v>221945</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11023,13 +11023,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>580895</v>
+        <v>580698</v>
       </c>
       <c r="R97" t="n">
-        <v>6963822</v>
+        <v>6963783</v>
       </c>
       <c r="S97" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11068,7 +11068,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11095,10 +11095,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>133550146</v>
+        <v>133552501</v>
       </c>
       <c r="B98" t="n">
-        <v>79333</v>
+        <v>89300</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11106,21 +11106,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11130,13 +11130,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>580687</v>
+        <v>580895</v>
       </c>
       <c r="R98" t="n">
-        <v>6963819</v>
+        <v>6963822</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11175,7 +11175,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD98" t="b">

--- a/artfynd/A 21339-2024 artfynd.xlsx
+++ b/artfynd/A 21339-2024 artfynd.xlsx
@@ -1424,32 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133550154</v>
+        <v>133550153</v>
       </c>
       <c r="B9" t="n">
-        <v>99130</v>
+        <v>80438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,13 +1459,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580712</v>
+        <v>580704</v>
       </c>
       <c r="R9" t="n">
-        <v>6963788</v>
+        <v>6963785</v>
       </c>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>70 ex</t>
+          <t>Stora fina exemplar av lunglav, handflata storlek.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,32 +1536,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133550157</v>
+        <v>133552456</v>
       </c>
       <c r="B10" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,13 +1571,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580715</v>
+        <v>580695</v>
       </c>
       <c r="R10" t="n">
-        <v>6963786</v>
+        <v>6963806</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,12 +1616,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>150 ex</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,32 +1643,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133552468</v>
+        <v>133550155</v>
       </c>
       <c r="B11" t="n">
-        <v>97995</v>
+        <v>80438</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1683,13 +1678,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580758</v>
+        <v>580715</v>
       </c>
       <c r="R11" t="n">
-        <v>6963787</v>
+        <v>6963791</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1718,7 +1713,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1723,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,32 +1755,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133552456</v>
+        <v>133552461</v>
       </c>
       <c r="B12" t="n">
-        <v>91918</v>
+        <v>83298</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6439</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580695</v>
+        <v>580740</v>
       </c>
       <c r="R12" t="n">
-        <v>6963806</v>
+        <v>6963795</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133550153</v>
+        <v>133552452</v>
       </c>
       <c r="B13" t="n">
-        <v>80438</v>
+        <v>83315</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,21 +1873,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,13 +1897,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580704</v>
+        <v>580698</v>
       </c>
       <c r="R13" t="n">
-        <v>6963785</v>
+        <v>6963860</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,12 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Stora fina exemplar av lunglav, handflata storlek.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133550155</v>
+        <v>133550174</v>
       </c>
       <c r="B14" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,21 +1980,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2009,13 +2004,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580715</v>
+        <v>580879</v>
       </c>
       <c r="R14" t="n">
-        <v>6963791</v>
+        <v>6963690</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2044,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,12 +2049,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,32 +2076,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133552461</v>
+        <v>133552475</v>
       </c>
       <c r="B15" t="n">
-        <v>83298</v>
+        <v>79333</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2121,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580740</v>
+        <v>580801</v>
       </c>
       <c r="R15" t="n">
-        <v>6963795</v>
+        <v>6963655</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2156,7 +2146,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2166,7 +2156,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,32 +2183,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133552452</v>
+        <v>133550154</v>
       </c>
       <c r="B16" t="n">
-        <v>83315</v>
+        <v>99130</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2228,13 +2218,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580698</v>
+        <v>580712</v>
       </c>
       <c r="R16" t="n">
-        <v>6963860</v>
+        <v>6963788</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2263,7 +2253,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2273,7 +2263,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,32 +2295,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133550174</v>
+        <v>133550157</v>
       </c>
       <c r="B17" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2335,13 +2330,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580879</v>
+        <v>580715</v>
       </c>
       <c r="R17" t="n">
-        <v>6963690</v>
+        <v>6963786</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2370,7 +2365,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2375,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,32 +2407,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133552475</v>
+        <v>133552468</v>
       </c>
       <c r="B18" t="n">
-        <v>79333</v>
+        <v>97995</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580801</v>
+        <v>580758</v>
       </c>
       <c r="R18" t="n">
-        <v>6963655</v>
+        <v>6963787</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -4124,32 +4124,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133550148</v>
+        <v>133552488</v>
       </c>
       <c r="B34" t="n">
-        <v>99130</v>
+        <v>89300</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4159,13 +4159,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>580696</v>
+        <v>580943</v>
       </c>
       <c r="R34" t="n">
-        <v>6963788</v>
+        <v>6963738</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4204,12 +4204,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:49</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>120 ex</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4236,10 +4231,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133552488</v>
+        <v>133550180</v>
       </c>
       <c r="B35" t="n">
-        <v>89300</v>
+        <v>57958</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4247,37 +4242,45 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>580943</v>
+        <v>580876</v>
       </c>
       <c r="R35" t="n">
-        <v>6963738</v>
+        <v>6963707</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4306,7 +4309,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4316,7 +4319,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4343,32 +4351,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133550163</v>
+        <v>133550148</v>
       </c>
       <c r="B36" t="n">
-        <v>97995</v>
+        <v>99130</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4378,13 +4386,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>580728</v>
+        <v>580696</v>
       </c>
       <c r="R36" t="n">
-        <v>6963787</v>
+        <v>6963788</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4413,7 +4421,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4423,7 +4431,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4450,56 +4463,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133550180</v>
+        <v>133550163</v>
       </c>
       <c r="B37" t="n">
-        <v>57958</v>
+        <v>97995</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>580876</v>
+        <v>580728</v>
       </c>
       <c r="R37" t="n">
-        <v>6963707</v>
+        <v>6963787</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4528,7 +4533,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4538,12 +4543,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:14</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4570,10 +4570,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133550166</v>
+        <v>133552494</v>
       </c>
       <c r="B38" t="n">
-        <v>57136</v>
+        <v>79365</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4581,49 +4581,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>102612</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>580800</v>
+        <v>580955</v>
       </c>
       <c r="R38" t="n">
-        <v>6963652</v>
+        <v>6963798</v>
       </c>
       <c r="S38" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4652,7 +4640,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4662,7 +4650,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4689,32 +4677,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133552494</v>
+        <v>133552478</v>
       </c>
       <c r="B39" t="n">
-        <v>79365</v>
+        <v>80473</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>6463</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4724,10 +4712,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>580955</v>
+        <v>580763</v>
       </c>
       <c r="R39" t="n">
-        <v>6963798</v>
+        <v>6963637</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4759,7 +4747,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4769,7 +4757,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4796,32 +4784,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133552478</v>
+        <v>133552497</v>
       </c>
       <c r="B40" t="n">
-        <v>80473</v>
+        <v>79090</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6463</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4831,10 +4819,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>580763</v>
+        <v>580939</v>
       </c>
       <c r="R40" t="n">
-        <v>6963637</v>
+        <v>6963799</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4866,7 +4854,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4876,7 +4864,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4903,10 +4891,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133552497</v>
+        <v>133552453</v>
       </c>
       <c r="B41" t="n">
-        <v>79090</v>
+        <v>79333</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4914,21 +4902,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4938,13 +4926,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>580939</v>
+        <v>580737</v>
       </c>
       <c r="R41" t="n">
-        <v>6963799</v>
+        <v>6963844</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4973,7 +4961,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4983,7 +4971,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5010,7 +4998,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133552453</v>
+        <v>133550132</v>
       </c>
       <c r="B42" t="n">
         <v>79333</v>
@@ -5045,13 +5033,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>580737</v>
+        <v>580695</v>
       </c>
       <c r="R42" t="n">
-        <v>6963844</v>
+        <v>6963885</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5080,7 +5068,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5090,7 +5078,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5117,7 +5105,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133550132</v>
+        <v>133550176</v>
       </c>
       <c r="B43" t="n">
         <v>79333</v>
@@ -5152,10 +5140,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580695</v>
+        <v>580874</v>
       </c>
       <c r="R43" t="n">
-        <v>6963885</v>
+        <v>6963718</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5187,7 +5175,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5197,7 +5185,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5224,7 +5212,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133550176</v>
+        <v>133550182</v>
       </c>
       <c r="B44" t="n">
         <v>79333</v>
@@ -5259,10 +5247,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>580874</v>
+        <v>580856</v>
       </c>
       <c r="R44" t="n">
-        <v>6963718</v>
+        <v>6963747</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5294,7 +5282,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5304,7 +5292,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5331,10 +5319,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133550182</v>
+        <v>133550166</v>
       </c>
       <c r="B45" t="n">
-        <v>79333</v>
+        <v>57136</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5342,37 +5330,49 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580856</v>
+        <v>580800</v>
       </c>
       <c r="R45" t="n">
-        <v>6963747</v>
+        <v>6963652</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -9458,32 +9458,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>133550140</v>
+        <v>133552505</v>
       </c>
       <c r="B83" t="n">
-        <v>99130</v>
+        <v>79333</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>580694</v>
+        <v>580836</v>
       </c>
       <c r="R83" t="n">
-        <v>6963839</v>
+        <v>6963844</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9528,7 +9528,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9538,12 +9538,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>33 ex</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9570,32 +9565,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133552467</v>
+        <v>133552469</v>
       </c>
       <c r="B84" t="n">
-        <v>92641</v>
+        <v>79333</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9605,13 +9600,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>580754</v>
+        <v>580751</v>
       </c>
       <c r="R84" t="n">
-        <v>6963789</v>
+        <v>6963778</v>
       </c>
       <c r="S84" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9640,7 +9635,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9650,7 +9645,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9891,10 +9886,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133552505</v>
+        <v>133550165</v>
       </c>
       <c r="B87" t="n">
-        <v>79333</v>
+        <v>57136</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9902,37 +9897,49 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>580836</v>
+        <v>580753</v>
       </c>
       <c r="R87" t="n">
-        <v>6963844</v>
+        <v>6963702</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9961,7 +9968,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9971,7 +9978,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9998,32 +10005,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133552469</v>
+        <v>133550140</v>
       </c>
       <c r="B88" t="n">
-        <v>79333</v>
+        <v>99130</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10033,10 +10040,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>580751</v>
+        <v>580694</v>
       </c>
       <c r="R88" t="n">
-        <v>6963778</v>
+        <v>6963839</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10068,7 +10075,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10078,7 +10085,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>33 ex</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10105,60 +10117,48 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133550165</v>
+        <v>133552467</v>
       </c>
       <c r="B89" t="n">
-        <v>57136</v>
+        <v>92641</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>102612</v>
+        <v>3298</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>580753</v>
+        <v>580754</v>
       </c>
       <c r="R89" t="n">
-        <v>6963702</v>
+        <v>6963789</v>
       </c>
       <c r="S89" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10197,7 +10197,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10224,32 +10224,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133552493</v>
+        <v>133550193</v>
       </c>
       <c r="B90" t="n">
-        <v>89300</v>
+        <v>99130</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10259,10 +10259,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>580914</v>
+        <v>580781</v>
       </c>
       <c r="R90" t="n">
-        <v>6963757</v>
+        <v>6963825</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10294,7 +10294,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10304,7 +10304,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ca 60 ex</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10331,32 +10336,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133552510</v>
+        <v>133552455</v>
       </c>
       <c r="B91" t="n">
-        <v>83315</v>
+        <v>99130</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10366,10 +10371,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>580829</v>
+        <v>580733</v>
       </c>
       <c r="R91" t="n">
-        <v>6963885</v>
+        <v>6963814</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10401,7 +10406,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10411,7 +10416,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10438,32 +10448,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133552471</v>
+        <v>133552512</v>
       </c>
       <c r="B92" t="n">
-        <v>83315</v>
+        <v>99130</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10473,10 +10483,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>580717</v>
+        <v>580803</v>
       </c>
       <c r="R92" t="n">
-        <v>6963694</v>
+        <v>6963894</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10508,7 +10518,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10518,7 +10528,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>150 + ex</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10545,32 +10560,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133550193</v>
+        <v>133552510</v>
       </c>
       <c r="B93" t="n">
-        <v>99130</v>
+        <v>83315</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10580,10 +10595,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>580781</v>
+        <v>580829</v>
       </c>
       <c r="R93" t="n">
-        <v>6963825</v>
+        <v>6963885</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10615,7 +10630,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10625,12 +10640,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>16:41</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Ca 60 ex</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10657,32 +10667,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133552455</v>
+        <v>133552471</v>
       </c>
       <c r="B94" t="n">
-        <v>99130</v>
+        <v>83315</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10692,10 +10702,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>580733</v>
+        <v>580717</v>
       </c>
       <c r="R94" t="n">
-        <v>6963814</v>
+        <v>6963694</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10727,7 +10737,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10737,12 +10747,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>200 ex</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10769,32 +10774,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133552512</v>
+        <v>133552493</v>
       </c>
       <c r="B95" t="n">
-        <v>99130</v>
+        <v>89300</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10804,10 +10809,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>580803</v>
+        <v>580914</v>
       </c>
       <c r="R95" t="n">
-        <v>6963894</v>
+        <v>6963757</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10839,7 +10844,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10849,12 +10854,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>150 + ex</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11655,10 +11655,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133552500</v>
+        <v>133550188</v>
       </c>
       <c r="B103" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11666,21 +11666,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11690,13 +11690,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>580902</v>
+        <v>580833</v>
       </c>
       <c r="R103" t="n">
-        <v>6963823</v>
+        <v>6963785</v>
       </c>
       <c r="S103" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11735,7 +11735,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11762,7 +11762,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133550188</v>
+        <v>133550158</v>
       </c>
       <c r="B104" t="n">
         <v>79333</v>
@@ -11797,10 +11797,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>580833</v>
+        <v>580720</v>
       </c>
       <c r="R104" t="n">
-        <v>6963785</v>
+        <v>6963787</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11832,7 +11832,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11869,7 +11869,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133550158</v>
+        <v>133550190</v>
       </c>
       <c r="B105" t="n">
         <v>79333</v>
@@ -11904,13 +11904,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>580720</v>
+        <v>580838</v>
       </c>
       <c r="R105" t="n">
-        <v>6963787</v>
+        <v>6963811</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11949,7 +11949,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11976,7 +11981,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133550190</v>
+        <v>133550177</v>
       </c>
       <c r="B106" t="n">
         <v>79333</v>
@@ -12011,10 +12016,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>580838</v>
+        <v>580864</v>
       </c>
       <c r="R106" t="n">
-        <v>6963811</v>
+        <v>6963715</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -12046,7 +12051,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12056,12 +12061,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12088,10 +12088,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133550177</v>
+        <v>133552500</v>
       </c>
       <c r="B107" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12099,21 +12099,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12123,13 +12123,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>580864</v>
+        <v>580902</v>
       </c>
       <c r="R107" t="n">
-        <v>6963715</v>
+        <v>6963823</v>
       </c>
       <c r="S107" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD107" t="b">

--- a/artfynd/A 21339-2024 artfynd.xlsx
+++ b/artfynd/A 21339-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133550167</v>
       </c>
       <c r="B2" t="n">
-        <v>89300</v>
+        <v>89302</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133552483</v>
+        <v>133552511</v>
       </c>
       <c r="B3" t="n">
-        <v>89300</v>
+        <v>79366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580906</v>
+        <v>580865</v>
       </c>
       <c r="R3" t="n">
-        <v>6963679</v>
+        <v>6963889</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133552449</v>
+        <v>133552483</v>
       </c>
       <c r="B4" t="n">
-        <v>91918</v>
+        <v>89302</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580689</v>
+        <v>580906</v>
       </c>
       <c r="R4" t="n">
-        <v>6963874</v>
+        <v>6963679</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133550168</v>
+        <v>133552449</v>
       </c>
       <c r="B5" t="n">
-        <v>83181</v>
+        <v>91920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580801</v>
+        <v>580689</v>
       </c>
       <c r="R5" t="n">
-        <v>6963652</v>
+        <v>6963874</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133552481</v>
+        <v>133550168</v>
       </c>
       <c r="B6" t="n">
-        <v>89300</v>
+        <v>83182</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580869</v>
+        <v>580801</v>
       </c>
       <c r="R6" t="n">
-        <v>6963663</v>
+        <v>6963652</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133552511</v>
+        <v>133552481</v>
       </c>
       <c r="B7" t="n">
-        <v>79365</v>
+        <v>89302</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>510</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580865</v>
+        <v>580869</v>
       </c>
       <c r="R7" t="n">
-        <v>6963889</v>
+        <v>6963663</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,7 +1320,7 @@
         <v>133550175</v>
       </c>
       <c r="B8" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133550153</v>
+        <v>133552456</v>
       </c>
       <c r="B9" t="n">
-        <v>80438</v>
+        <v>91920</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,13 +1459,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580704</v>
+        <v>580695</v>
       </c>
       <c r="R9" t="n">
-        <v>6963785</v>
+        <v>6963806</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,12 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Stora fina exemplar av lunglav, handflata storlek.</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133552456</v>
+        <v>133550155</v>
       </c>
       <c r="B10" t="n">
-        <v>91918</v>
+        <v>80439</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1547,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,13 +1566,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580695</v>
+        <v>580715</v>
       </c>
       <c r="R10" t="n">
-        <v>6963806</v>
+        <v>6963791</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1606,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,7 +1611,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1643,32 +1643,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133550155</v>
+        <v>133552461</v>
       </c>
       <c r="B11" t="n">
-        <v>80438</v>
+        <v>83299</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1678,13 +1678,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580715</v>
+        <v>580740</v>
       </c>
       <c r="R11" t="n">
-        <v>6963791</v>
+        <v>6963795</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1723,12 +1723,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,32 +1750,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133552461</v>
+        <v>133552452</v>
       </c>
       <c r="B12" t="n">
-        <v>83298</v>
+        <v>83316</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6439</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,13 +1785,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580740</v>
+        <v>580698</v>
       </c>
       <c r="R12" t="n">
-        <v>6963795</v>
+        <v>6963860</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1825,7 +1820,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1830,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133552452</v>
+        <v>133550174</v>
       </c>
       <c r="B13" t="n">
-        <v>83315</v>
+        <v>79334</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,21 +1868,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,13 +1892,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580698</v>
+        <v>580879</v>
       </c>
       <c r="R13" t="n">
-        <v>6963860</v>
+        <v>6963690</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1932,7 +1927,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1937,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,10 +1964,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133550174</v>
+        <v>133552475</v>
       </c>
       <c r="B14" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2004,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580879</v>
+        <v>580801</v>
       </c>
       <c r="R14" t="n">
-        <v>6963690</v>
+        <v>6963655</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2039,7 +2034,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2049,7 +2044,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,10 +2071,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133552475</v>
+        <v>133550153</v>
       </c>
       <c r="B15" t="n">
-        <v>79333</v>
+        <v>80439</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2087,21 +2082,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2111,13 +2106,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580801</v>
+        <v>580704</v>
       </c>
       <c r="R15" t="n">
-        <v>6963655</v>
+        <v>6963785</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2146,7 +2141,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2156,7 +2151,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Stora fina exemplar av lunglav, handflata storlek.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2183,32 +2183,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133550154</v>
+        <v>133552468</v>
       </c>
       <c r="B16" t="n">
-        <v>99130</v>
+        <v>97997</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2218,13 +2218,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580712</v>
+        <v>580758</v>
       </c>
       <c r="R16" t="n">
-        <v>6963788</v>
+        <v>6963787</v>
       </c>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2263,12 +2263,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:59</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>70 ex</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,10 +2290,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133550157</v>
+        <v>133550154</v>
       </c>
       <c r="B17" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,13 +2325,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580715</v>
+        <v>580712</v>
       </c>
       <c r="R17" t="n">
-        <v>6963786</v>
+        <v>6963788</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2365,7 +2360,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2375,12 +2370,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>150 ex</t>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,32 +2402,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133552468</v>
+        <v>133550157</v>
       </c>
       <c r="B18" t="n">
-        <v>97995</v>
+        <v>99132</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2442,13 +2437,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580758</v>
+        <v>580715</v>
       </c>
       <c r="R18" t="n">
-        <v>6963787</v>
+        <v>6963786</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2477,7 +2472,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2487,7 +2482,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2517,7 +2517,7 @@
         <v>133550164</v>
       </c>
       <c r="B19" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>133552509</v>
       </c>
       <c r="B20" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>133552492</v>
       </c>
       <c r="B21" t="n">
-        <v>79091</v>
+        <v>79092</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>133552457</v>
       </c>
       <c r="B22" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>133552464</v>
       </c>
       <c r="B23" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3049,32 +3049,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133552451</v>
+        <v>133550184</v>
       </c>
       <c r="B24" t="n">
-        <v>91881</v>
+        <v>99132</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580669</v>
+        <v>580867</v>
       </c>
       <c r="R24" t="n">
-        <v>6963873</v>
+        <v>6963739</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3129,7 +3129,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>36 ex</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3156,32 +3161,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133550171</v>
+        <v>133552451</v>
       </c>
       <c r="B25" t="n">
-        <v>80438</v>
+        <v>91883</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3191,13 +3196,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580857</v>
+        <v>580669</v>
       </c>
       <c r="R25" t="n">
-        <v>6963688</v>
+        <v>6963873</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3226,7 +3231,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3236,7 +3241,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3263,32 +3268,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133550184</v>
+        <v>133550171</v>
       </c>
       <c r="B26" t="n">
-        <v>99130</v>
+        <v>80439</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3298,13 +3303,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580867</v>
+        <v>580857</v>
       </c>
       <c r="R26" t="n">
-        <v>6963739</v>
+        <v>6963688</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3333,7 +3338,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3343,12 +3348,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>36 ex</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3375,10 +3375,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133550156</v>
+        <v>133552447</v>
       </c>
       <c r="B27" t="n">
-        <v>79333</v>
+        <v>79366</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3386,21 +3386,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3410,13 +3410,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580715</v>
+        <v>580697</v>
       </c>
       <c r="R27" t="n">
-        <v>6963791</v>
+        <v>6963889</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3485,7 +3485,7 @@
         <v>133550185</v>
       </c>
       <c r="B28" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>133550191</v>
       </c>
       <c r="B29" t="n">
-        <v>92217</v>
+        <v>92219</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>133552472</v>
       </c>
       <c r="B30" t="n">
-        <v>91932</v>
+        <v>91934</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3803,10 +3803,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133552447</v>
+        <v>133550156</v>
       </c>
       <c r="B31" t="n">
-        <v>79365</v>
+        <v>79334</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3814,21 +3814,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3838,13 +3838,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>580697</v>
+        <v>580715</v>
       </c>
       <c r="R31" t="n">
-        <v>6963889</v>
+        <v>6963791</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3910,48 +3910,56 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133552502</v>
+        <v>133550180</v>
       </c>
       <c r="B32" t="n">
-        <v>80342</v>
+        <v>57958</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>580865</v>
+        <v>580876</v>
       </c>
       <c r="R32" t="n">
-        <v>6963830</v>
+        <v>6963707</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3980,7 +3988,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3990,7 +3998,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4017,10 +4030,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133550138</v>
+        <v>133552488</v>
       </c>
       <c r="B33" t="n">
-        <v>79333</v>
+        <v>89302</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4028,21 +4041,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4052,10 +4065,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>580712</v>
+        <v>580943</v>
       </c>
       <c r="R33" t="n">
-        <v>6963853</v>
+        <v>6963738</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4087,7 +4100,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4097,7 +4110,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4124,32 +4137,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133552488</v>
+        <v>133552502</v>
       </c>
       <c r="B34" t="n">
-        <v>89300</v>
+        <v>80343</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>510</v>
+        <v>6456</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4159,10 +4172,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>580943</v>
+        <v>580865</v>
       </c>
       <c r="R34" t="n">
-        <v>6963738</v>
+        <v>6963830</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4194,7 +4207,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4204,7 +4217,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4231,10 +4244,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133550180</v>
+        <v>133550138</v>
       </c>
       <c r="B35" t="n">
-        <v>57958</v>
+        <v>79334</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4242,45 +4255,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>580876</v>
+        <v>580712</v>
       </c>
       <c r="R35" t="n">
-        <v>6963707</v>
+        <v>6963853</v>
       </c>
       <c r="S35" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4309,7 +4314,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4319,12 +4324,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:14</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4354,7 +4354,7 @@
         <v>133550148</v>
       </c>
       <c r="B36" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         <v>133550163</v>
       </c>
       <c r="B37" t="n">
-        <v>97995</v>
+        <v>97997</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>133552494</v>
       </c>
       <c r="B38" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4677,32 +4677,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133552478</v>
+        <v>133552497</v>
       </c>
       <c r="B39" t="n">
-        <v>80473</v>
+        <v>79091</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6463</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>580763</v>
+        <v>580939</v>
       </c>
       <c r="R39" t="n">
-        <v>6963637</v>
+        <v>6963799</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4784,10 +4784,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133552497</v>
+        <v>133552453</v>
       </c>
       <c r="B40" t="n">
-        <v>79090</v>
+        <v>79334</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4795,21 +4795,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4819,13 +4819,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>580939</v>
+        <v>580737</v>
       </c>
       <c r="R40" t="n">
-        <v>6963799</v>
+        <v>6963844</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4891,10 +4891,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133552453</v>
+        <v>133550132</v>
       </c>
       <c r="B41" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>580737</v>
+        <v>580695</v>
       </c>
       <c r="R41" t="n">
-        <v>6963844</v>
+        <v>6963885</v>
       </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4998,10 +4998,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133550132</v>
+        <v>133550176</v>
       </c>
       <c r="B42" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5033,10 +5033,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>580695</v>
+        <v>580874</v>
       </c>
       <c r="R42" t="n">
-        <v>6963885</v>
+        <v>6963718</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5078,7 +5078,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5105,10 +5105,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133550176</v>
+        <v>133550182</v>
       </c>
       <c r="B43" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5140,10 +5140,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580874</v>
+        <v>580856</v>
       </c>
       <c r="R43" t="n">
-        <v>6963718</v>
+        <v>6963747</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5212,27 +5212,27 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133550182</v>
+        <v>133552478</v>
       </c>
       <c r="B44" t="n">
-        <v>79333</v>
+        <v>80474</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>580856</v>
+        <v>580763</v>
       </c>
       <c r="R44" t="n">
-        <v>6963747</v>
+        <v>6963637</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5441,7 +5441,7 @@
         <v>133550136</v>
       </c>
       <c r="B46" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5550,10 +5550,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133552490</v>
+        <v>133552508</v>
       </c>
       <c r="B47" t="n">
-        <v>80438</v>
+        <v>57958</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5561,34 +5561,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>580853</v>
+        <v>580813</v>
       </c>
       <c r="R47" t="n">
-        <v>6963702</v>
+        <v>6963779</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5620,7 +5628,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5630,7 +5638,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5657,10 +5670,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133552491</v>
+        <v>133552503</v>
       </c>
       <c r="B48" t="n">
-        <v>79333</v>
+        <v>89302</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5668,21 +5681,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5692,10 +5705,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>580883</v>
+        <v>580844</v>
       </c>
       <c r="R48" t="n">
-        <v>6963753</v>
+        <v>6963844</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5727,7 +5740,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5737,7 +5750,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5764,10 +5777,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133552482</v>
+        <v>133550160</v>
       </c>
       <c r="B49" t="n">
-        <v>83315</v>
+        <v>92219</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5775,21 +5788,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5799,13 +5812,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>580879</v>
+        <v>580715</v>
       </c>
       <c r="R49" t="n">
-        <v>6963658</v>
+        <v>6963743</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5834,7 +5847,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5844,7 +5857,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5871,10 +5884,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133552486</v>
+        <v>133552448</v>
       </c>
       <c r="B50" t="n">
-        <v>83315</v>
+        <v>91920</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5882,21 +5895,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5906,10 +5919,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>580985</v>
+        <v>580691</v>
       </c>
       <c r="R50" t="n">
-        <v>6963707</v>
+        <v>6963879</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5941,7 +5954,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5951,7 +5964,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5978,10 +5991,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133552508</v>
+        <v>133552490</v>
       </c>
       <c r="B51" t="n">
-        <v>57958</v>
+        <v>80439</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5989,42 +6002,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>580813</v>
+        <v>580853</v>
       </c>
       <c r="R51" t="n">
-        <v>6963779</v>
+        <v>6963702</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6056,7 +6061,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6066,12 +6071,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:04</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6098,32 +6098,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133550162</v>
+        <v>133552491</v>
       </c>
       <c r="B52" t="n">
-        <v>99130</v>
+        <v>79334</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>580728</v>
+        <v>580883</v>
       </c>
       <c r="R52" t="n">
-        <v>6963787</v>
+        <v>6963753</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6178,12 +6178,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:34</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>50 ex</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6210,32 +6205,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133550147</v>
+        <v>133552486</v>
       </c>
       <c r="B53" t="n">
-        <v>99130</v>
+        <v>83316</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6245,13 +6240,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>580689</v>
+        <v>580985</v>
       </c>
       <c r="R53" t="n">
-        <v>6963814</v>
+        <v>6963707</v>
       </c>
       <c r="S53" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6280,7 +6275,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6290,12 +6285,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>70 ex</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6322,10 +6312,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133552503</v>
+        <v>133552482</v>
       </c>
       <c r="B54" t="n">
-        <v>89300</v>
+        <v>83316</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6333,21 +6323,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6357,10 +6347,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>580844</v>
+        <v>580879</v>
       </c>
       <c r="R54" t="n">
-        <v>6963844</v>
+        <v>6963658</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6392,7 +6382,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6402,7 +6392,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6429,32 +6419,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133550160</v>
+        <v>133550162</v>
       </c>
       <c r="B55" t="n">
-        <v>92217</v>
+        <v>99132</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6464,13 +6454,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>580715</v>
+        <v>580728</v>
       </c>
       <c r="R55" t="n">
-        <v>6963743</v>
+        <v>6963787</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6499,7 +6489,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6509,7 +6499,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6536,32 +6531,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133552448</v>
+        <v>133550147</v>
       </c>
       <c r="B56" t="n">
-        <v>91918</v>
+        <v>99132</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6571,13 +6566,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>580691</v>
+        <v>580689</v>
       </c>
       <c r="R56" t="n">
-        <v>6963879</v>
+        <v>6963814</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6606,7 +6601,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6616,7 +6611,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6643,10 +6643,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133552473</v>
+        <v>133550143</v>
       </c>
       <c r="B57" t="n">
-        <v>80438</v>
+        <v>79334</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6654,21 +6654,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>580754</v>
+        <v>580713</v>
       </c>
       <c r="R57" t="n">
-        <v>6963659</v>
+        <v>6963831</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6713,7 +6713,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6750,10 +6750,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133550143</v>
+        <v>133552458</v>
       </c>
       <c r="B58" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6785,10 +6785,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>580713</v>
+        <v>580716</v>
       </c>
       <c r="R58" t="n">
-        <v>6963831</v>
+        <v>6963787</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6857,10 +6857,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133552458</v>
+        <v>133552450</v>
       </c>
       <c r="B59" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6892,13 +6892,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>580716</v>
+        <v>580683</v>
       </c>
       <c r="R59" t="n">
-        <v>6963787</v>
+        <v>6963870</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6964,10 +6964,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133552450</v>
+        <v>133552473</v>
       </c>
       <c r="B60" t="n">
-        <v>79333</v>
+        <v>80439</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6975,21 +6975,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6999,13 +6999,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>580683</v>
+        <v>580754</v>
       </c>
       <c r="R60" t="n">
-        <v>6963870</v>
+        <v>6963659</v>
       </c>
       <c r="S60" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7074,7 +7074,7 @@
         <v>133552485</v>
       </c>
       <c r="B61" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         <v>133552466</v>
       </c>
       <c r="B62" t="n">
-        <v>83315</v>
+        <v>83316</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7285,32 +7285,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133550170</v>
+        <v>133550133</v>
       </c>
       <c r="B63" t="n">
-        <v>79365</v>
+        <v>99132</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7320,10 +7320,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>580801</v>
+        <v>580685</v>
       </c>
       <c r="R63" t="n">
-        <v>6963652</v>
+        <v>6963865</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7365,7 +7365,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7392,10 +7397,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133550133</v>
+        <v>133550134</v>
       </c>
       <c r="B64" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7427,10 +7432,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>580685</v>
+        <v>580691</v>
       </c>
       <c r="R64" t="n">
-        <v>6963865</v>
+        <v>6963863</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7462,7 +7467,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7472,12 +7477,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>100 ex</t>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7504,32 +7509,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133550134</v>
+        <v>133552507</v>
       </c>
       <c r="B65" t="n">
-        <v>99130</v>
+        <v>80399</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7539,13 +7544,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>580691</v>
+        <v>580830</v>
       </c>
       <c r="R65" t="n">
-        <v>6963863</v>
+        <v>6963821</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7574,7 +7579,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7584,12 +7589,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>200 ex</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7616,32 +7616,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133552507</v>
+        <v>133550170</v>
       </c>
       <c r="B66" t="n">
-        <v>80398</v>
+        <v>79366</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229497</v>
+        <v>185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7651,13 +7651,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>580830</v>
+        <v>580801</v>
       </c>
       <c r="R66" t="n">
-        <v>6963821</v>
+        <v>6963652</v>
       </c>
       <c r="S66" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7723,10 +7723,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133552484</v>
+        <v>133552506</v>
       </c>
       <c r="B67" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7734,34 +7734,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>580938</v>
+        <v>580826</v>
       </c>
       <c r="R67" t="n">
-        <v>6963702</v>
+        <v>6963830</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7793,7 +7801,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7803,7 +7811,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7830,10 +7843,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133552460</v>
+        <v>133550172</v>
       </c>
       <c r="B68" t="n">
-        <v>83315</v>
+        <v>91920</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7841,21 +7854,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7865,10 +7878,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>580722</v>
+        <v>580870</v>
       </c>
       <c r="R68" t="n">
-        <v>6963787</v>
+        <v>6963663</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7900,7 +7913,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7910,7 +7923,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7937,10 +7950,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133550172</v>
+        <v>133550144</v>
       </c>
       <c r="B69" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7972,10 +7985,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>580870</v>
+        <v>580699</v>
       </c>
       <c r="R69" t="n">
-        <v>6963663</v>
+        <v>6963819</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8007,7 +8020,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8017,7 +8030,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8044,10 +8057,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133550144</v>
+        <v>133552484</v>
       </c>
       <c r="B70" t="n">
-        <v>91918</v>
+        <v>79334</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8055,21 +8068,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8079,10 +8092,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>580699</v>
+        <v>580938</v>
       </c>
       <c r="R70" t="n">
-        <v>6963819</v>
+        <v>6963702</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8114,7 +8127,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8124,7 +8137,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8151,10 +8164,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133552506</v>
+        <v>133552460</v>
       </c>
       <c r="B71" t="n">
-        <v>57958</v>
+        <v>83316</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8162,42 +8175,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>580826</v>
+        <v>580722</v>
       </c>
       <c r="R71" t="n">
-        <v>6963830</v>
+        <v>6963787</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8229,7 +8234,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8239,12 +8244,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8274,7 +8274,7 @@
         <v>133552454</v>
       </c>
       <c r="B72" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>133550149</v>
       </c>
       <c r="B73" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>133550139</v>
       </c>
       <c r="B74" t="n">
-        <v>80438</v>
+        <v>80439</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8597,10 +8597,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133550173</v>
+        <v>133552513</v>
       </c>
       <c r="B75" t="n">
-        <v>80438</v>
+        <v>83308</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8608,21 +8608,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>580878</v>
+        <v>580785</v>
       </c>
       <c r="R75" t="n">
-        <v>6963692</v>
+        <v>6963796</v>
       </c>
       <c r="S75" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8704,32 +8704,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133550141</v>
+        <v>133552462</v>
       </c>
       <c r="B76" t="n">
-        <v>99130</v>
+        <v>83308</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8739,10 +8739,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>580713</v>
+        <v>580738</v>
       </c>
       <c r="R76" t="n">
-        <v>6963840</v>
+        <v>6963776</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8784,12 +8784,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>60 ex, troligen fler</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8819,7 +8814,7 @@
         <v>133552487</v>
       </c>
       <c r="B77" t="n">
-        <v>89300</v>
+        <v>89302</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8923,10 +8918,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133550179</v>
+        <v>133550186</v>
       </c>
       <c r="B78" t="n">
-        <v>91918</v>
+        <v>89302</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8934,21 +8929,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8958,13 +8953,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>580862</v>
+        <v>580871</v>
       </c>
       <c r="R78" t="n">
-        <v>6963713</v>
+        <v>6963767</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8993,7 +8988,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9003,7 +8998,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9030,10 +9025,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133552513</v>
+        <v>133550179</v>
       </c>
       <c r="B79" t="n">
-        <v>83307</v>
+        <v>91920</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9041,21 +9036,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9065,13 +9060,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>580785</v>
+        <v>580862</v>
       </c>
       <c r="R79" t="n">
-        <v>6963796</v>
+        <v>6963713</v>
       </c>
       <c r="S79" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9100,7 +9095,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9110,7 +9105,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9137,10 +9132,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133550186</v>
+        <v>133552499</v>
       </c>
       <c r="B80" t="n">
-        <v>89300</v>
+        <v>91920</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9148,21 +9143,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9172,13 +9167,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>580871</v>
+        <v>580926</v>
       </c>
       <c r="R80" t="n">
-        <v>6963767</v>
+        <v>6963805</v>
       </c>
       <c r="S80" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9207,7 +9202,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9217,7 +9212,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9244,10 +9239,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133552499</v>
+        <v>133550173</v>
       </c>
       <c r="B81" t="n">
-        <v>91918</v>
+        <v>80439</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9255,21 +9250,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9279,13 +9274,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>580926</v>
+        <v>580878</v>
       </c>
       <c r="R81" t="n">
-        <v>6963805</v>
+        <v>6963692</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9314,7 +9309,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9324,7 +9319,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9351,32 +9346,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133552462</v>
+        <v>133550141</v>
       </c>
       <c r="B82" t="n">
-        <v>83307</v>
+        <v>99132</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>308</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9386,10 +9381,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>580738</v>
+        <v>580713</v>
       </c>
       <c r="R82" t="n">
-        <v>6963776</v>
+        <v>6963840</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9421,7 +9416,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9431,7 +9426,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>60 ex, troligen fler</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9458,32 +9458,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>133552505</v>
+        <v>133550140</v>
       </c>
       <c r="B83" t="n">
-        <v>79333</v>
+        <v>99132</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>580836</v>
+        <v>580694</v>
       </c>
       <c r="R83" t="n">
-        <v>6963844</v>
+        <v>6963839</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9528,7 +9528,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9538,7 +9538,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>33 ex</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9568,7 +9573,7 @@
         <v>133552469</v>
       </c>
       <c r="B84" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9672,32 +9677,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133552476</v>
+        <v>133552467</v>
       </c>
       <c r="B85" t="n">
-        <v>80438</v>
+        <v>92643</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9707,13 +9712,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>580767</v>
+        <v>580754</v>
       </c>
       <c r="R85" t="n">
-        <v>6963639</v>
+        <v>6963789</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9742,7 +9747,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9752,7 +9757,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9779,10 +9784,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133552463</v>
+        <v>133552505</v>
       </c>
       <c r="B86" t="n">
-        <v>80438</v>
+        <v>79334</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9790,21 +9795,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9814,10 +9819,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>580725</v>
+        <v>580836</v>
       </c>
       <c r="R86" t="n">
-        <v>6963773</v>
+        <v>6963844</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9849,7 +9854,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9859,7 +9864,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9886,10 +9891,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133550165</v>
+        <v>133552476</v>
       </c>
       <c r="B87" t="n">
-        <v>57136</v>
+        <v>80439</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9897,49 +9902,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>580753</v>
+        <v>580767</v>
       </c>
       <c r="R87" t="n">
-        <v>6963702</v>
+        <v>6963639</v>
       </c>
       <c r="S87" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9968,7 +9961,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9978,7 +9971,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10005,32 +9998,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133550140</v>
+        <v>133552463</v>
       </c>
       <c r="B88" t="n">
-        <v>99130</v>
+        <v>80439</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10040,10 +10033,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>580694</v>
+        <v>580725</v>
       </c>
       <c r="R88" t="n">
-        <v>6963839</v>
+        <v>6963773</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10075,7 +10068,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10085,12 +10078,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>33 ex</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10117,48 +10105,60 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133552467</v>
+        <v>133550165</v>
       </c>
       <c r="B89" t="n">
-        <v>92641</v>
+        <v>57136</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>3298</v>
+        <v>102612</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>580754</v>
+        <v>580753</v>
       </c>
       <c r="R89" t="n">
-        <v>6963789</v>
+        <v>6963702</v>
       </c>
       <c r="S89" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10197,7 +10197,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10224,32 +10224,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133550193</v>
+        <v>133552493</v>
       </c>
       <c r="B90" t="n">
-        <v>99130</v>
+        <v>89302</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10259,10 +10259,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>580781</v>
+        <v>580914</v>
       </c>
       <c r="R90" t="n">
-        <v>6963825</v>
+        <v>6963757</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10294,7 +10294,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10304,12 +10304,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>16:41</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Ca 60 ex</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10336,32 +10331,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133552455</v>
+        <v>133552510</v>
       </c>
       <c r="B91" t="n">
-        <v>99130</v>
+        <v>83316</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10371,10 +10366,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>580733</v>
+        <v>580829</v>
       </c>
       <c r="R91" t="n">
-        <v>6963814</v>
+        <v>6963885</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10406,7 +10401,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10416,12 +10411,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>200 ex</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10448,32 +10438,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133552512</v>
+        <v>133552471</v>
       </c>
       <c r="B92" t="n">
-        <v>99130</v>
+        <v>83316</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10483,10 +10473,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>580803</v>
+        <v>580717</v>
       </c>
       <c r="R92" t="n">
-        <v>6963894</v>
+        <v>6963694</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10518,7 +10508,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10528,12 +10518,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>150 + ex</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10560,32 +10545,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133552510</v>
+        <v>133550193</v>
       </c>
       <c r="B93" t="n">
-        <v>83315</v>
+        <v>99132</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10595,10 +10580,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>580829</v>
+        <v>580781</v>
       </c>
       <c r="R93" t="n">
-        <v>6963885</v>
+        <v>6963825</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10630,7 +10615,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10640,7 +10625,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Ca 60 ex</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10667,32 +10657,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133552471</v>
+        <v>133552455</v>
       </c>
       <c r="B94" t="n">
-        <v>83315</v>
+        <v>99132</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10702,10 +10692,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>580717</v>
+        <v>580733</v>
       </c>
       <c r="R94" t="n">
-        <v>6963694</v>
+        <v>6963814</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10737,7 +10727,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10747,7 +10737,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10774,32 +10769,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133552493</v>
+        <v>133552512</v>
       </c>
       <c r="B95" t="n">
-        <v>89300</v>
+        <v>99132</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10809,10 +10804,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>580914</v>
+        <v>580803</v>
       </c>
       <c r="R95" t="n">
-        <v>6963757</v>
+        <v>6963894</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10844,7 +10839,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10854,7 +10849,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>150 + ex</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10884,7 +10884,7 @@
         <v>133550146</v>
       </c>
       <c r="B96" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10988,32 +10988,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>133550152</v>
+        <v>133552501</v>
       </c>
       <c r="B97" t="n">
-        <v>97995</v>
+        <v>89302</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>221945</v>
+        <v>510</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11023,13 +11023,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>580698</v>
+        <v>580895</v>
       </c>
       <c r="R97" t="n">
-        <v>6963783</v>
+        <v>6963822</v>
       </c>
       <c r="S97" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11068,7 +11068,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11095,32 +11095,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>133552501</v>
+        <v>133550152</v>
       </c>
       <c r="B98" t="n">
-        <v>89300</v>
+        <v>97997</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>510</v>
+        <v>221945</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11130,13 +11130,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>580895</v>
+        <v>580698</v>
       </c>
       <c r="R98" t="n">
-        <v>6963822</v>
+        <v>6963783</v>
       </c>
       <c r="S98" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11175,7 +11175,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11444,7 +11444,7 @@
         <v>133550161</v>
       </c>
       <c r="B101" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>133552477</v>
       </c>
       <c r="B102" t="n">
-        <v>80467</v>
+        <v>80468</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11655,10 +11655,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133550188</v>
+        <v>133552500</v>
       </c>
       <c r="B103" t="n">
-        <v>79333</v>
+        <v>79366</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11666,21 +11666,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11690,13 +11690,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>580833</v>
+        <v>580902</v>
       </c>
       <c r="R103" t="n">
-        <v>6963785</v>
+        <v>6963823</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11735,7 +11735,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11765,7 +11765,7 @@
         <v>133550158</v>
       </c>
       <c r="B104" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11869,10 +11869,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133550190</v>
+        <v>133550188</v>
       </c>
       <c r="B105" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11904,13 +11904,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>580838</v>
+        <v>580833</v>
       </c>
       <c r="R105" t="n">
-        <v>6963811</v>
+        <v>6963785</v>
       </c>
       <c r="S105" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11949,12 +11949,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11981,10 +11976,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133550177</v>
+        <v>133550190</v>
       </c>
       <c r="B106" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12016,10 +12011,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>580864</v>
+        <v>580838</v>
       </c>
       <c r="R106" t="n">
-        <v>6963715</v>
+        <v>6963811</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -12051,7 +12046,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12061,7 +12056,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12088,10 +12088,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133552500</v>
+        <v>133550177</v>
       </c>
       <c r="B107" t="n">
-        <v>79365</v>
+        <v>79334</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12099,21 +12099,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12123,13 +12123,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>580902</v>
+        <v>580864</v>
       </c>
       <c r="R107" t="n">
-        <v>6963823</v>
+        <v>6963715</v>
       </c>
       <c r="S107" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD107" t="b">

--- a/artfynd/A 21339-2024 artfynd.xlsx
+++ b/artfynd/A 21339-2024 artfynd.xlsx
@@ -10224,32 +10224,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133552493</v>
+        <v>133550193</v>
       </c>
       <c r="B90" t="n">
-        <v>89302</v>
+        <v>99132</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10259,10 +10259,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>580914</v>
+        <v>580781</v>
       </c>
       <c r="R90" t="n">
-        <v>6963757</v>
+        <v>6963825</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10294,7 +10294,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10304,7 +10304,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ca 60 ex</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10331,32 +10336,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133552510</v>
+        <v>133552455</v>
       </c>
       <c r="B91" t="n">
-        <v>83316</v>
+        <v>99132</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10366,10 +10371,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>580829</v>
+        <v>580733</v>
       </c>
       <c r="R91" t="n">
-        <v>6963885</v>
+        <v>6963814</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10401,7 +10406,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10411,7 +10416,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10438,32 +10448,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133552471</v>
+        <v>133552512</v>
       </c>
       <c r="B92" t="n">
-        <v>83316</v>
+        <v>99132</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10473,10 +10483,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>580717</v>
+        <v>580803</v>
       </c>
       <c r="R92" t="n">
-        <v>6963694</v>
+        <v>6963894</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10508,7 +10518,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10518,7 +10528,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>150 + ex</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10545,32 +10560,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133550193</v>
+        <v>133552493</v>
       </c>
       <c r="B93" t="n">
-        <v>99132</v>
+        <v>89302</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10580,10 +10595,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>580781</v>
+        <v>580914</v>
       </c>
       <c r="R93" t="n">
-        <v>6963825</v>
+        <v>6963757</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10615,7 +10630,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10625,12 +10640,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>16:41</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Ca 60 ex</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10657,32 +10667,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133552455</v>
+        <v>133552510</v>
       </c>
       <c r="B94" t="n">
-        <v>99132</v>
+        <v>83316</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10692,10 +10702,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>580733</v>
+        <v>580829</v>
       </c>
       <c r="R94" t="n">
-        <v>6963814</v>
+        <v>6963885</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10727,7 +10737,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10737,12 +10747,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>200 ex</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10769,32 +10774,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133552512</v>
+        <v>133552471</v>
       </c>
       <c r="B95" t="n">
-        <v>99132</v>
+        <v>83316</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10804,10 +10809,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>580803</v>
+        <v>580717</v>
       </c>
       <c r="R95" t="n">
-        <v>6963894</v>
+        <v>6963694</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10839,7 +10844,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10849,12 +10854,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>150 + ex</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD95" t="b">

--- a/artfynd/A 21339-2024 artfynd.xlsx
+++ b/artfynd/A 21339-2024 artfynd.xlsx
@@ -4570,10 +4570,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133552494</v>
+        <v>133550166</v>
       </c>
       <c r="B38" t="n">
-        <v>79366</v>
+        <v>57136</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4581,37 +4581,49 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>102612</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>580955</v>
+        <v>580800</v>
       </c>
       <c r="R38" t="n">
-        <v>6963798</v>
+        <v>6963652</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4640,7 +4652,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4650,7 +4662,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4677,32 +4689,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133552497</v>
+        <v>133550136</v>
       </c>
       <c r="B39" t="n">
-        <v>79091</v>
+        <v>99132</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4712,10 +4724,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>580939</v>
+        <v>580702</v>
       </c>
       <c r="R39" t="n">
-        <v>6963799</v>
+        <v>6963851</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4747,7 +4759,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4757,7 +4769,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4784,10 +4801,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133552453</v>
+        <v>133552494</v>
       </c>
       <c r="B40" t="n">
-        <v>79334</v>
+        <v>79366</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4795,21 +4812,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4819,13 +4836,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>580737</v>
+        <v>580955</v>
       </c>
       <c r="R40" t="n">
-        <v>6963844</v>
+        <v>6963798</v>
       </c>
       <c r="S40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4854,7 +4871,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4864,7 +4881,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4891,10 +4908,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133550132</v>
+        <v>133552497</v>
       </c>
       <c r="B41" t="n">
-        <v>79334</v>
+        <v>79091</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4902,21 +4919,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4926,10 +4943,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>580695</v>
+        <v>580939</v>
       </c>
       <c r="R41" t="n">
-        <v>6963885</v>
+        <v>6963799</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4961,7 +4978,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4971,7 +4988,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4998,7 +5015,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133550176</v>
+        <v>133552453</v>
       </c>
       <c r="B42" t="n">
         <v>79334</v>
@@ -5033,13 +5050,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>580874</v>
+        <v>580737</v>
       </c>
       <c r="R42" t="n">
-        <v>6963718</v>
+        <v>6963844</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5068,7 +5085,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5078,7 +5095,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5105,7 +5122,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133550182</v>
+        <v>133550132</v>
       </c>
       <c r="B43" t="n">
         <v>79334</v>
@@ -5140,10 +5157,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580856</v>
+        <v>580695</v>
       </c>
       <c r="R43" t="n">
-        <v>6963747</v>
+        <v>6963885</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5175,7 +5192,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5185,7 +5202,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5212,27 +5229,27 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133552478</v>
+        <v>133550176</v>
       </c>
       <c r="B44" t="n">
-        <v>80474</v>
+        <v>79334</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5247,10 +5264,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>580763</v>
+        <v>580874</v>
       </c>
       <c r="R44" t="n">
-        <v>6963637</v>
+        <v>6963718</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5282,7 +5299,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5292,7 +5309,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5319,10 +5336,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133550166</v>
+        <v>133550182</v>
       </c>
       <c r="B45" t="n">
-        <v>57136</v>
+        <v>79334</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5330,49 +5347,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580800</v>
+        <v>580856</v>
       </c>
       <c r="R45" t="n">
-        <v>6963652</v>
+        <v>6963747</v>
       </c>
       <c r="S45" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5401,7 +5406,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5411,7 +5416,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5438,32 +5443,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133550136</v>
+        <v>133552478</v>
       </c>
       <c r="B46" t="n">
-        <v>99132</v>
+        <v>80474</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5473,10 +5478,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>580702</v>
+        <v>580763</v>
       </c>
       <c r="R46" t="n">
-        <v>6963851</v>
+        <v>6963637</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5508,7 +5513,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5518,12 +5523,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>150 ex</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 21339-2024 artfynd.xlsx
+++ b/artfynd/A 21339-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133550167</v>
       </c>
       <c r="B2" t="n">
-        <v>89302</v>
+        <v>89310</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133552511</v>
+        <v>133552449</v>
       </c>
       <c r="B3" t="n">
-        <v>79366</v>
+        <v>91928</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580865</v>
+        <v>580689</v>
       </c>
       <c r="R3" t="n">
-        <v>6963889</v>
+        <v>6963874</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133552483</v>
+        <v>133550175</v>
       </c>
       <c r="B4" t="n">
-        <v>89302</v>
+        <v>79334</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580906</v>
+        <v>580879</v>
       </c>
       <c r="R4" t="n">
-        <v>6963679</v>
+        <v>6963696</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133552449</v>
+        <v>133550168</v>
       </c>
       <c r="B5" t="n">
-        <v>91920</v>
+        <v>83183</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580689</v>
+        <v>580801</v>
       </c>
       <c r="R5" t="n">
-        <v>6963874</v>
+        <v>6963652</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133550168</v>
+        <v>133552483</v>
       </c>
       <c r="B6" t="n">
-        <v>83182</v>
+        <v>89310</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580801</v>
+        <v>580906</v>
       </c>
       <c r="R6" t="n">
-        <v>6963652</v>
+        <v>6963679</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,7 +1213,7 @@
         <v>133552481</v>
       </c>
       <c r="B7" t="n">
-        <v>89302</v>
+        <v>89310</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133550175</v>
+        <v>133552511</v>
       </c>
       <c r="B8" t="n">
-        <v>79334</v>
+        <v>79366</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580879</v>
+        <v>580865</v>
       </c>
       <c r="R8" t="n">
-        <v>6963696</v>
+        <v>6963889</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,7 +1427,7 @@
         <v>133552456</v>
       </c>
       <c r="B9" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133550155</v>
+        <v>133550174</v>
       </c>
       <c r="B10" t="n">
-        <v>80439</v>
+        <v>79334</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,13 +1566,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580715</v>
+        <v>580879</v>
       </c>
       <c r="R10" t="n">
-        <v>6963791</v>
+        <v>6963690</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,12 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1643,32 +1638,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133552461</v>
+        <v>133552475</v>
       </c>
       <c r="B11" t="n">
-        <v>83299</v>
+        <v>79334</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1678,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580740</v>
+        <v>580801</v>
       </c>
       <c r="R11" t="n">
-        <v>6963795</v>
+        <v>6963655</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1713,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1723,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1750,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133552452</v>
+        <v>133550155</v>
       </c>
       <c r="B12" t="n">
-        <v>83316</v>
+        <v>80439</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,13 +1780,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580698</v>
+        <v>580715</v>
       </c>
       <c r="R12" t="n">
-        <v>6963860</v>
+        <v>6963791</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1820,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1830,7 +1825,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1857,32 +1857,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133550174</v>
+        <v>133552461</v>
       </c>
       <c r="B13" t="n">
-        <v>79334</v>
+        <v>83302</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580879</v>
+        <v>580740</v>
       </c>
       <c r="R13" t="n">
-        <v>6963690</v>
+        <v>6963795</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1964,10 +1964,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133552475</v>
+        <v>133552452</v>
       </c>
       <c r="B14" t="n">
-        <v>79334</v>
+        <v>83319</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1975,21 +1975,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1999,13 +1999,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580801</v>
+        <v>580698</v>
       </c>
       <c r="R14" t="n">
-        <v>6963655</v>
+        <v>6963860</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2183,32 +2183,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133552468</v>
+        <v>133550154</v>
       </c>
       <c r="B16" t="n">
-        <v>97997</v>
+        <v>99140</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2218,13 +2218,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580758</v>
+        <v>580712</v>
       </c>
       <c r="R16" t="n">
-        <v>6963787</v>
+        <v>6963788</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2263,7 +2263,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2290,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133550154</v>
+        <v>133550157</v>
       </c>
       <c r="B17" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2325,13 +2330,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580712</v>
+        <v>580715</v>
       </c>
       <c r="R17" t="n">
-        <v>6963788</v>
+        <v>6963786</v>
       </c>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2360,7 +2365,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2370,12 +2375,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>70 ex</t>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2402,32 +2407,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133550157</v>
+        <v>133552468</v>
       </c>
       <c r="B18" t="n">
-        <v>99132</v>
+        <v>98005</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2437,13 +2442,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580715</v>
+        <v>580758</v>
       </c>
       <c r="R18" t="n">
-        <v>6963786</v>
+        <v>6963787</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2472,7 +2477,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2482,12 +2487,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>150 ex</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2838,7 +2838,7 @@
         <v>133552457</v>
       </c>
       <c r="B22" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>133552464</v>
       </c>
       <c r="B23" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3049,32 +3049,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133550184</v>
+        <v>133552451</v>
       </c>
       <c r="B24" t="n">
-        <v>99132</v>
+        <v>91891</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580867</v>
+        <v>580669</v>
       </c>
       <c r="R24" t="n">
-        <v>6963739</v>
+        <v>6963873</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3129,12 +3129,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>36 ex</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3161,32 +3156,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133552451</v>
+        <v>133550171</v>
       </c>
       <c r="B25" t="n">
-        <v>91883</v>
+        <v>80439</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3196,13 +3191,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580669</v>
+        <v>580857</v>
       </c>
       <c r="R25" t="n">
-        <v>6963873</v>
+        <v>6963688</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3231,7 +3226,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3241,7 +3236,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3268,32 +3263,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133550171</v>
+        <v>133550184</v>
       </c>
       <c r="B26" t="n">
-        <v>80439</v>
+        <v>99140</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3303,13 +3298,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580857</v>
+        <v>580867</v>
       </c>
       <c r="R26" t="n">
-        <v>6963688</v>
+        <v>6963739</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3338,7 +3333,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3348,7 +3343,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>36 ex</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3375,10 +3375,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133552447</v>
+        <v>133550156</v>
       </c>
       <c r="B27" t="n">
-        <v>79366</v>
+        <v>79334</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3386,21 +3386,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3410,13 +3410,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580697</v>
+        <v>580715</v>
       </c>
       <c r="R27" t="n">
-        <v>6963889</v>
+        <v>6963791</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3589,10 +3589,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133550191</v>
+        <v>133552472</v>
       </c>
       <c r="B29" t="n">
-        <v>92219</v>
+        <v>91942</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3600,21 +3600,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3624,10 +3624,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580787</v>
+        <v>580713</v>
       </c>
       <c r="R29" t="n">
-        <v>6963783</v>
+        <v>6963690</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3696,10 +3696,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133552472</v>
+        <v>133550191</v>
       </c>
       <c r="B30" t="n">
-        <v>91934</v>
+        <v>92227</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580713</v>
+        <v>580787</v>
       </c>
       <c r="R30" t="n">
-        <v>6963690</v>
+        <v>6963783</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3803,10 +3803,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133550156</v>
+        <v>133552447</v>
       </c>
       <c r="B31" t="n">
-        <v>79334</v>
+        <v>79366</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3814,21 +3814,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3838,13 +3838,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>580715</v>
+        <v>580697</v>
       </c>
       <c r="R31" t="n">
-        <v>6963791</v>
+        <v>6963889</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3910,56 +3910,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133550180</v>
+        <v>133550148</v>
       </c>
       <c r="B32" t="n">
-        <v>57958</v>
+        <v>99140</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>580876</v>
+        <v>580696</v>
       </c>
       <c r="R32" t="n">
-        <v>6963707</v>
+        <v>6963788</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3988,7 +3980,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3998,12 +3990,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4030,10 +4022,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133552488</v>
+        <v>133550138</v>
       </c>
       <c r="B33" t="n">
-        <v>89302</v>
+        <v>79334</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4041,21 +4033,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4065,10 +4057,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>580943</v>
+        <v>580712</v>
       </c>
       <c r="R33" t="n">
-        <v>6963738</v>
+        <v>6963853</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4100,7 +4092,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4110,7 +4102,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4244,10 +4236,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133550138</v>
+        <v>133552488</v>
       </c>
       <c r="B35" t="n">
-        <v>79334</v>
+        <v>89310</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4255,21 +4247,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4279,10 +4271,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>580712</v>
+        <v>580943</v>
       </c>
       <c r="R35" t="n">
-        <v>6963853</v>
+        <v>6963738</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4314,7 +4306,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4324,7 +4316,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4351,48 +4343,56 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133550148</v>
+        <v>133550180</v>
       </c>
       <c r="B36" t="n">
-        <v>99132</v>
+        <v>57958</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>580696</v>
+        <v>580876</v>
       </c>
       <c r="R36" t="n">
-        <v>6963788</v>
+        <v>6963707</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>120 ex</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4466,7 +4466,7 @@
         <v>133550163</v>
       </c>
       <c r="B37" t="n">
-        <v>97997</v>
+        <v>98005</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4570,10 +4570,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133550166</v>
+        <v>133552453</v>
       </c>
       <c r="B38" t="n">
-        <v>57136</v>
+        <v>79334</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4581,49 +4581,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>580800</v>
+        <v>580737</v>
       </c>
       <c r="R38" t="n">
-        <v>6963652</v>
+        <v>6963844</v>
       </c>
       <c r="S38" t="n">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4652,7 +4640,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4662,7 +4650,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4689,32 +4677,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133550136</v>
+        <v>133550132</v>
       </c>
       <c r="B39" t="n">
-        <v>99132</v>
+        <v>79334</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4724,10 +4712,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>580702</v>
+        <v>580695</v>
       </c>
       <c r="R39" t="n">
-        <v>6963851</v>
+        <v>6963885</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4759,7 +4747,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4769,12 +4757,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>150 ex</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4801,10 +4784,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133552494</v>
+        <v>133550176</v>
       </c>
       <c r="B40" t="n">
-        <v>79366</v>
+        <v>79334</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4812,21 +4795,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4836,10 +4819,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>580955</v>
+        <v>580874</v>
       </c>
       <c r="R40" t="n">
-        <v>6963798</v>
+        <v>6963718</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4871,7 +4854,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4881,7 +4864,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4908,10 +4891,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133552497</v>
+        <v>133550182</v>
       </c>
       <c r="B41" t="n">
-        <v>79091</v>
+        <v>79334</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4919,21 +4902,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4943,10 +4926,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>580939</v>
+        <v>580856</v>
       </c>
       <c r="R41" t="n">
-        <v>6963799</v>
+        <v>6963747</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4978,7 +4961,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4988,7 +4971,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5015,10 +4998,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133552453</v>
+        <v>133550166</v>
       </c>
       <c r="B42" t="n">
-        <v>79334</v>
+        <v>57136</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5026,37 +5009,49 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>580737</v>
+        <v>580800</v>
       </c>
       <c r="R42" t="n">
-        <v>6963844</v>
+        <v>6963652</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5085,7 +5080,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5095,7 +5090,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5122,10 +5117,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133550132</v>
+        <v>133552497</v>
       </c>
       <c r="B43" t="n">
-        <v>79334</v>
+        <v>79091</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5133,21 +5128,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5157,10 +5152,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580695</v>
+        <v>580939</v>
       </c>
       <c r="R43" t="n">
-        <v>6963885</v>
+        <v>6963799</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5192,7 +5187,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5202,7 +5197,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5229,27 +5224,27 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133550176</v>
+        <v>133552478</v>
       </c>
       <c r="B44" t="n">
-        <v>79334</v>
+        <v>80474</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5264,10 +5259,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>580874</v>
+        <v>580763</v>
       </c>
       <c r="R44" t="n">
-        <v>6963718</v>
+        <v>6963637</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5299,7 +5294,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5309,7 +5304,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5336,10 +5331,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133550182</v>
+        <v>133552494</v>
       </c>
       <c r="B45" t="n">
-        <v>79334</v>
+        <v>79366</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5347,21 +5342,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5371,10 +5366,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580856</v>
+        <v>580955</v>
       </c>
       <c r="R45" t="n">
-        <v>6963747</v>
+        <v>6963798</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5406,7 +5401,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5416,7 +5411,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5443,32 +5438,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133552478</v>
+        <v>133550136</v>
       </c>
       <c r="B46" t="n">
-        <v>80474</v>
+        <v>99140</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5478,10 +5473,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>580763</v>
+        <v>580702</v>
       </c>
       <c r="R46" t="n">
-        <v>6963637</v>
+        <v>6963851</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5513,7 +5508,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5523,7 +5518,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5550,10 +5550,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133552508</v>
+        <v>133552491</v>
       </c>
       <c r="B47" t="n">
-        <v>57958</v>
+        <v>79334</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5561,42 +5561,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>580813</v>
+        <v>580883</v>
       </c>
       <c r="R47" t="n">
-        <v>6963779</v>
+        <v>6963753</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5628,7 +5620,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5638,12 +5630,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:04</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5670,10 +5657,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133552503</v>
+        <v>133552448</v>
       </c>
       <c r="B48" t="n">
-        <v>89302</v>
+        <v>91928</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5681,21 +5668,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5705,10 +5692,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>580844</v>
+        <v>580691</v>
       </c>
       <c r="R48" t="n">
-        <v>6963844</v>
+        <v>6963879</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5740,7 +5727,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5750,7 +5737,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5777,10 +5764,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133550160</v>
+        <v>133552503</v>
       </c>
       <c r="B49" t="n">
-        <v>92219</v>
+        <v>89310</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5788,21 +5775,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5812,13 +5799,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>580715</v>
+        <v>580844</v>
       </c>
       <c r="R49" t="n">
-        <v>6963743</v>
+        <v>6963844</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5847,7 +5834,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5857,7 +5844,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5884,10 +5871,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133552448</v>
+        <v>133550160</v>
       </c>
       <c r="B50" t="n">
-        <v>91920</v>
+        <v>92227</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5895,21 +5882,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5919,13 +5906,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>580691</v>
+        <v>580715</v>
       </c>
       <c r="R50" t="n">
-        <v>6963879</v>
+        <v>6963743</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5954,7 +5941,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5964,7 +5951,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5991,10 +5978,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133552490</v>
+        <v>133552508</v>
       </c>
       <c r="B51" t="n">
-        <v>80439</v>
+        <v>57958</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6002,34 +5989,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>580853</v>
+        <v>580813</v>
       </c>
       <c r="R51" t="n">
-        <v>6963702</v>
+        <v>6963779</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6061,7 +6056,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6071,7 +6066,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6098,32 +6098,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133552491</v>
+        <v>133550162</v>
       </c>
       <c r="B52" t="n">
-        <v>79334</v>
+        <v>99140</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>580883</v>
+        <v>580728</v>
       </c>
       <c r="R52" t="n">
-        <v>6963753</v>
+        <v>6963787</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6178,7 +6178,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6205,32 +6210,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133552486</v>
+        <v>133550147</v>
       </c>
       <c r="B53" t="n">
-        <v>83316</v>
+        <v>99140</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6240,13 +6245,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>580985</v>
+        <v>580689</v>
       </c>
       <c r="R53" t="n">
-        <v>6963707</v>
+        <v>6963814</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6275,7 +6280,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6285,7 +6290,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6312,10 +6322,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133552482</v>
+        <v>133552490</v>
       </c>
       <c r="B54" t="n">
-        <v>83316</v>
+        <v>80439</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6323,21 +6333,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6347,10 +6357,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>580879</v>
+        <v>580853</v>
       </c>
       <c r="R54" t="n">
-        <v>6963658</v>
+        <v>6963702</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6382,7 +6392,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6392,7 +6402,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6419,32 +6429,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133550162</v>
+        <v>133552482</v>
       </c>
       <c r="B55" t="n">
-        <v>99132</v>
+        <v>83319</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6454,10 +6464,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>580728</v>
+        <v>580879</v>
       </c>
       <c r="R55" t="n">
-        <v>6963787</v>
+        <v>6963658</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6489,7 +6499,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6499,12 +6509,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:34</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>50 ex</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6531,32 +6536,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133550147</v>
+        <v>133552486</v>
       </c>
       <c r="B56" t="n">
-        <v>99132</v>
+        <v>83319</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6566,13 +6571,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>580689</v>
+        <v>580985</v>
       </c>
       <c r="R56" t="n">
-        <v>6963814</v>
+        <v>6963707</v>
       </c>
       <c r="S56" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6601,7 +6606,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6611,12 +6616,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>70 ex</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7181,7 +7181,7 @@
         <v>133552466</v>
       </c>
       <c r="B62" t="n">
-        <v>83316</v>
+        <v>83319</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7285,32 +7285,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133550133</v>
+        <v>133550170</v>
       </c>
       <c r="B63" t="n">
-        <v>99132</v>
+        <v>79366</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7320,10 +7320,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>580685</v>
+        <v>580801</v>
       </c>
       <c r="R63" t="n">
-        <v>6963865</v>
+        <v>6963652</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7365,12 +7365,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>100 ex</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7397,10 +7392,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133550134</v>
+        <v>133550133</v>
       </c>
       <c r="B64" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7432,10 +7427,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>580691</v>
+        <v>580685</v>
       </c>
       <c r="R64" t="n">
-        <v>6963863</v>
+        <v>6963865</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7467,7 +7462,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7477,12 +7472,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>200 ex</t>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7509,32 +7504,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133552507</v>
+        <v>133550134</v>
       </c>
       <c r="B65" t="n">
-        <v>80399</v>
+        <v>99140</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7544,13 +7539,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>580830</v>
+        <v>580691</v>
       </c>
       <c r="R65" t="n">
-        <v>6963821</v>
+        <v>6963863</v>
       </c>
       <c r="S65" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7579,7 +7574,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7589,7 +7584,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7616,32 +7616,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133550170</v>
+        <v>133552507</v>
       </c>
       <c r="B66" t="n">
-        <v>79366</v>
+        <v>80399</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>185</v>
+        <v>229497</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7651,13 +7651,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>580801</v>
+        <v>580830</v>
       </c>
       <c r="R66" t="n">
-        <v>6963652</v>
+        <v>6963821</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7723,10 +7723,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133552506</v>
+        <v>133550172</v>
       </c>
       <c r="B67" t="n">
-        <v>57958</v>
+        <v>91928</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7734,42 +7734,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>580826</v>
+        <v>580870</v>
       </c>
       <c r="R67" t="n">
-        <v>6963830</v>
+        <v>6963663</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7801,7 +7793,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7811,12 +7803,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7843,10 +7830,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133550172</v>
+        <v>133552484</v>
       </c>
       <c r="B68" t="n">
-        <v>91920</v>
+        <v>79334</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7854,21 +7841,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7878,10 +7865,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>580870</v>
+        <v>580938</v>
       </c>
       <c r="R68" t="n">
-        <v>6963663</v>
+        <v>6963702</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7913,7 +7900,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7923,7 +7910,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7953,7 +7940,7 @@
         <v>133550144</v>
       </c>
       <c r="B69" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8057,10 +8044,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133552484</v>
+        <v>133552460</v>
       </c>
       <c r="B70" t="n">
-        <v>79334</v>
+        <v>83319</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8068,21 +8055,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8092,10 +8079,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>580938</v>
+        <v>580722</v>
       </c>
       <c r="R70" t="n">
-        <v>6963702</v>
+        <v>6963787</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8127,7 +8114,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8137,7 +8124,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8164,10 +8151,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133552460</v>
+        <v>133552506</v>
       </c>
       <c r="B71" t="n">
-        <v>83316</v>
+        <v>57958</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8175,34 +8162,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>580722</v>
+        <v>580826</v>
       </c>
       <c r="R71" t="n">
-        <v>6963787</v>
+        <v>6963830</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8234,7 +8229,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8244,7 +8239,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8271,10 +8271,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133552454</v>
+        <v>133550149</v>
       </c>
       <c r="B72" t="n">
-        <v>91920</v>
+        <v>79334</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8282,21 +8282,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8306,13 +8306,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>580734</v>
+        <v>580697</v>
       </c>
       <c r="R72" t="n">
-        <v>6963814</v>
+        <v>6963788</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8351,7 +8351,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8378,10 +8378,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133550149</v>
+        <v>133552454</v>
       </c>
       <c r="B73" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8389,21 +8389,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8413,13 +8413,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>580697</v>
+        <v>580734</v>
       </c>
       <c r="R73" t="n">
-        <v>6963788</v>
+        <v>6963814</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8597,10 +8597,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133552513</v>
+        <v>133550179</v>
       </c>
       <c r="B75" t="n">
-        <v>83308</v>
+        <v>91928</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8608,21 +8608,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>580785</v>
+        <v>580862</v>
       </c>
       <c r="R75" t="n">
-        <v>6963796</v>
+        <v>6963713</v>
       </c>
       <c r="S75" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8704,10 +8704,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133552462</v>
+        <v>133552499</v>
       </c>
       <c r="B76" t="n">
-        <v>83308</v>
+        <v>91928</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8715,21 +8715,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8739,10 +8739,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>580738</v>
+        <v>580926</v>
       </c>
       <c r="R76" t="n">
-        <v>6963776</v>
+        <v>6963805</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8811,10 +8811,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133552487</v>
+        <v>133550173</v>
       </c>
       <c r="B77" t="n">
-        <v>89302</v>
+        <v>80439</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8822,21 +8822,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8846,13 +8846,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>580983</v>
+        <v>580878</v>
       </c>
       <c r="R77" t="n">
-        <v>6963709</v>
+        <v>6963692</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8918,10 +8918,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133550186</v>
+        <v>133552487</v>
       </c>
       <c r="B78" t="n">
-        <v>89302</v>
+        <v>89310</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8953,13 +8953,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>580871</v>
+        <v>580983</v>
       </c>
       <c r="R78" t="n">
-        <v>6963767</v>
+        <v>6963709</v>
       </c>
       <c r="S78" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9025,10 +9025,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133550179</v>
+        <v>133550186</v>
       </c>
       <c r="B79" t="n">
-        <v>91920</v>
+        <v>89310</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9036,21 +9036,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9060,13 +9060,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>580862</v>
+        <v>580871</v>
       </c>
       <c r="R79" t="n">
-        <v>6963713</v>
+        <v>6963767</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9105,7 +9105,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9132,10 +9132,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133552499</v>
+        <v>133552513</v>
       </c>
       <c r="B80" t="n">
-        <v>91920</v>
+        <v>83311</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9143,21 +9143,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9167,13 +9167,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>580926</v>
+        <v>580785</v>
       </c>
       <c r="R80" t="n">
-        <v>6963805</v>
+        <v>6963796</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9239,10 +9239,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133550173</v>
+        <v>133552462</v>
       </c>
       <c r="B81" t="n">
-        <v>80439</v>
+        <v>83311</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9250,21 +9250,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>580878</v>
+        <v>580738</v>
       </c>
       <c r="R81" t="n">
-        <v>6963692</v>
+        <v>6963776</v>
       </c>
       <c r="S81" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9309,7 +9309,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9319,7 +9319,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9349,7 +9349,7 @@
         <v>133550141</v>
       </c>
       <c r="B82" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9458,32 +9458,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>133550140</v>
+        <v>133552467</v>
       </c>
       <c r="B83" t="n">
-        <v>99132</v>
+        <v>92651</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9493,13 +9493,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>580694</v>
+        <v>580754</v>
       </c>
       <c r="R83" t="n">
-        <v>6963839</v>
+        <v>6963789</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9538,12 +9538,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>33 ex</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9570,7 +9565,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133552469</v>
+        <v>133552505</v>
       </c>
       <c r="B84" t="n">
         <v>79334</v>
@@ -9605,10 +9600,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>580751</v>
+        <v>580836</v>
       </c>
       <c r="R84" t="n">
-        <v>6963778</v>
+        <v>6963844</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9640,7 +9635,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9650,7 +9645,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9677,32 +9672,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133552467</v>
+        <v>133552469</v>
       </c>
       <c r="B85" t="n">
-        <v>92643</v>
+        <v>79334</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9712,13 +9707,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>580754</v>
+        <v>580751</v>
       </c>
       <c r="R85" t="n">
-        <v>6963789</v>
+        <v>6963778</v>
       </c>
       <c r="S85" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9747,7 +9742,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9757,7 +9752,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9784,10 +9779,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133552505</v>
+        <v>133552476</v>
       </c>
       <c r="B86" t="n">
-        <v>79334</v>
+        <v>80439</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9795,21 +9790,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9819,10 +9814,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>580836</v>
+        <v>580767</v>
       </c>
       <c r="R86" t="n">
-        <v>6963844</v>
+        <v>6963639</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9854,7 +9849,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9864,7 +9859,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9891,7 +9886,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133552476</v>
+        <v>133552463</v>
       </c>
       <c r="B87" t="n">
         <v>80439</v>
@@ -9926,10 +9921,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>580767</v>
+        <v>580725</v>
       </c>
       <c r="R87" t="n">
-        <v>6963639</v>
+        <v>6963773</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9961,7 +9956,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9971,7 +9966,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9998,10 +9993,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133552463</v>
+        <v>133550165</v>
       </c>
       <c r="B88" t="n">
-        <v>80439</v>
+        <v>57136</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10009,37 +10004,49 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>580725</v>
+        <v>580753</v>
       </c>
       <c r="R88" t="n">
-        <v>6963773</v>
+        <v>6963702</v>
       </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10068,7 +10075,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10078,7 +10085,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10105,60 +10112,48 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133550165</v>
+        <v>133550140</v>
       </c>
       <c r="B89" t="n">
-        <v>57136</v>
+        <v>99140</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>580753</v>
+        <v>580694</v>
       </c>
       <c r="R89" t="n">
-        <v>6963702</v>
+        <v>6963839</v>
       </c>
       <c r="S89" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10187,7 +10182,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10197,7 +10192,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>33 ex</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10227,7 +10227,7 @@
         <v>133550193</v>
       </c>
       <c r="B90" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>133552455</v>
       </c>
       <c r="B91" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10448,32 +10448,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133552512</v>
+        <v>133552510</v>
       </c>
       <c r="B92" t="n">
-        <v>99132</v>
+        <v>83319</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10483,10 +10483,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>580803</v>
+        <v>580829</v>
       </c>
       <c r="R92" t="n">
-        <v>6963894</v>
+        <v>6963885</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10518,7 +10518,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10528,12 +10528,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>150 + ex</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10560,10 +10555,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133552493</v>
+        <v>133552471</v>
       </c>
       <c r="B93" t="n">
-        <v>89302</v>
+        <v>83319</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10571,21 +10566,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10595,10 +10590,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>580914</v>
+        <v>580717</v>
       </c>
       <c r="R93" t="n">
-        <v>6963757</v>
+        <v>6963694</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10630,7 +10625,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10640,7 +10635,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10667,10 +10662,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133552510</v>
+        <v>133552493</v>
       </c>
       <c r="B94" t="n">
-        <v>83316</v>
+        <v>89310</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10678,21 +10673,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10702,10 +10697,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>580829</v>
+        <v>580914</v>
       </c>
       <c r="R94" t="n">
-        <v>6963885</v>
+        <v>6963757</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10737,7 +10732,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10747,7 +10742,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10774,32 +10769,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133552471</v>
+        <v>133552512</v>
       </c>
       <c r="B95" t="n">
-        <v>83316</v>
+        <v>99140</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10809,10 +10804,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>580717</v>
+        <v>580803</v>
       </c>
       <c r="R95" t="n">
-        <v>6963694</v>
+        <v>6963894</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10844,7 +10839,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10854,7 +10849,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>150 + ex</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10991,7 +10991,7 @@
         <v>133552501</v>
       </c>
       <c r="B97" t="n">
-        <v>89302</v>
+        <v>89310</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11095,48 +11095,60 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>133550152</v>
+        <v>133550187</v>
       </c>
       <c r="B98" t="n">
-        <v>97997</v>
+        <v>57136</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>221945</v>
+        <v>102612</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>580698</v>
+        <v>580843</v>
       </c>
       <c r="R98" t="n">
-        <v>6963783</v>
+        <v>6963778</v>
       </c>
       <c r="S98" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11165,7 +11177,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11175,7 +11187,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11202,60 +11214,48 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>133550187</v>
+        <v>133550152</v>
       </c>
       <c r="B99" t="n">
-        <v>57136</v>
+        <v>98005</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>102612</v>
+        <v>221945</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>580843</v>
+        <v>580698</v>
       </c>
       <c r="R99" t="n">
-        <v>6963778</v>
+        <v>6963783</v>
       </c>
       <c r="S99" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11321,56 +11321,48 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133552495</v>
+        <v>133552477</v>
       </c>
       <c r="B100" t="n">
-        <v>57958</v>
+        <v>80468</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>580953</v>
+        <v>580764</v>
       </c>
       <c r="R100" t="n">
-        <v>6963811</v>
+        <v>6963638</v>
       </c>
       <c r="S100" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11399,7 +11391,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11409,12 +11401,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Ett färskt ringhack på tall</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11441,10 +11428,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133550161</v>
+        <v>133552495</v>
       </c>
       <c r="B101" t="n">
-        <v>79334</v>
+        <v>57958</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11452,37 +11439,45 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>580727</v>
+        <v>580953</v>
       </c>
       <c r="R101" t="n">
-        <v>6963764</v>
+        <v>6963811</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11511,7 +11506,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11521,7 +11516,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Ett färskt ringhack på tall</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11548,32 +11548,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133552477</v>
+        <v>133550161</v>
       </c>
       <c r="B102" t="n">
-        <v>80468</v>
+        <v>79334</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11583,13 +11583,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>580764</v>
+        <v>580727</v>
       </c>
       <c r="R102" t="n">
-        <v>6963638</v>
+        <v>6963764</v>
       </c>
       <c r="S102" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11628,7 +11628,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11655,10 +11655,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133552500</v>
+        <v>133550188</v>
       </c>
       <c r="B103" t="n">
-        <v>79366</v>
+        <v>79334</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11666,21 +11666,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11690,13 +11690,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>580902</v>
+        <v>580833</v>
       </c>
       <c r="R103" t="n">
-        <v>6963823</v>
+        <v>6963785</v>
       </c>
       <c r="S103" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11735,7 +11735,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11869,7 +11869,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133550188</v>
+        <v>133550190</v>
       </c>
       <c r="B105" t="n">
         <v>79334</v>
@@ -11904,13 +11904,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>580833</v>
+        <v>580838</v>
       </c>
       <c r="R105" t="n">
-        <v>6963785</v>
+        <v>6963811</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11949,7 +11949,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11976,7 +11981,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133550190</v>
+        <v>133550177</v>
       </c>
       <c r="B106" t="n">
         <v>79334</v>
@@ -12011,10 +12016,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>580838</v>
+        <v>580864</v>
       </c>
       <c r="R106" t="n">
-        <v>6963811</v>
+        <v>6963715</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -12046,7 +12051,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12056,12 +12061,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12088,10 +12088,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133550177</v>
+        <v>133552500</v>
       </c>
       <c r="B107" t="n">
-        <v>79334</v>
+        <v>79366</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12099,21 +12099,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12123,13 +12123,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>580864</v>
+        <v>580902</v>
       </c>
       <c r="R107" t="n">
-        <v>6963715</v>
+        <v>6963823</v>
       </c>
       <c r="S107" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD107" t="b">

--- a/artfynd/A 21339-2024 artfynd.xlsx
+++ b/artfynd/A 21339-2024 artfynd.xlsx
@@ -4998,10 +4998,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133550166</v>
+        <v>133552497</v>
       </c>
       <c r="B42" t="n">
-        <v>57136</v>
+        <v>79091</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5009,49 +5009,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102612</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>580800</v>
+        <v>580939</v>
       </c>
       <c r="R42" t="n">
-        <v>6963652</v>
+        <v>6963799</v>
       </c>
       <c r="S42" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5080,7 +5068,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5090,7 +5078,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5117,32 +5105,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133552497</v>
+        <v>133552478</v>
       </c>
       <c r="B43" t="n">
-        <v>79091</v>
+        <v>80474</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5152,10 +5140,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580939</v>
+        <v>580763</v>
       </c>
       <c r="R43" t="n">
-        <v>6963799</v>
+        <v>6963637</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5187,7 +5175,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5197,7 +5185,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5224,32 +5212,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133552478</v>
+        <v>133552494</v>
       </c>
       <c r="B44" t="n">
-        <v>80474</v>
+        <v>79366</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>185</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5259,10 +5247,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>580763</v>
+        <v>580955</v>
       </c>
       <c r="R44" t="n">
-        <v>6963637</v>
+        <v>6963798</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5294,7 +5282,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5304,7 +5292,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5331,10 +5319,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133552494</v>
+        <v>133550166</v>
       </c>
       <c r="B45" t="n">
-        <v>79366</v>
+        <v>57136</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5342,37 +5330,49 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>102612</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580955</v>
+        <v>580800</v>
       </c>
       <c r="R45" t="n">
-        <v>6963798</v>
+        <v>6963652</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -7071,10 +7071,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133552485</v>
+        <v>133552466</v>
       </c>
       <c r="B61" t="n">
-        <v>79334</v>
+        <v>83319</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7082,21 +7082,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7106,13 +7106,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>580999</v>
+        <v>580746</v>
       </c>
       <c r="R61" t="n">
-        <v>6963688</v>
+        <v>6963790</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7178,10 +7178,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133552466</v>
+        <v>133552485</v>
       </c>
       <c r="B62" t="n">
-        <v>83319</v>
+        <v>79334</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7189,21 +7189,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7213,13 +7213,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>580746</v>
+        <v>580999</v>
       </c>
       <c r="R62" t="n">
-        <v>6963790</v>
+        <v>6963688</v>
       </c>
       <c r="S62" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8597,32 +8597,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133550179</v>
+        <v>133550141</v>
       </c>
       <c r="B75" t="n">
-        <v>91928</v>
+        <v>99140</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8632,10 +8632,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>580862</v>
+        <v>580713</v>
       </c>
       <c r="R75" t="n">
-        <v>6963713</v>
+        <v>6963840</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8667,7 +8667,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8677,7 +8677,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>60 ex, troligen fler</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8704,10 +8709,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133552499</v>
+        <v>133552487</v>
       </c>
       <c r="B76" t="n">
-        <v>91928</v>
+        <v>89310</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8715,21 +8720,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8739,10 +8744,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>580926</v>
+        <v>580983</v>
       </c>
       <c r="R76" t="n">
-        <v>6963805</v>
+        <v>6963709</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8774,7 +8779,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8784,7 +8789,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8811,10 +8816,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133550173</v>
+        <v>133550186</v>
       </c>
       <c r="B77" t="n">
-        <v>80439</v>
+        <v>89310</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8822,21 +8827,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8846,13 +8851,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>580878</v>
+        <v>580871</v>
       </c>
       <c r="R77" t="n">
-        <v>6963692</v>
+        <v>6963767</v>
       </c>
       <c r="S77" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8881,7 +8886,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8891,7 +8896,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8918,10 +8923,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133552487</v>
+        <v>133552513</v>
       </c>
       <c r="B78" t="n">
-        <v>89310</v>
+        <v>83311</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8929,21 +8934,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>510</v>
+        <v>308</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8953,13 +8958,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>580983</v>
+        <v>580785</v>
       </c>
       <c r="R78" t="n">
-        <v>6963709</v>
+        <v>6963796</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8988,7 +8993,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8998,7 +9003,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9025,10 +9030,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133550186</v>
+        <v>133552462</v>
       </c>
       <c r="B79" t="n">
-        <v>89310</v>
+        <v>83311</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9036,21 +9041,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>510</v>
+        <v>308</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9060,13 +9065,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>580871</v>
+        <v>580738</v>
       </c>
       <c r="R79" t="n">
-        <v>6963767</v>
+        <v>6963776</v>
       </c>
       <c r="S79" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9095,7 +9100,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9105,7 +9110,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9132,10 +9137,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133552513</v>
+        <v>133550179</v>
       </c>
       <c r="B80" t="n">
-        <v>83311</v>
+        <v>91928</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9143,21 +9148,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9167,13 +9172,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>580785</v>
+        <v>580862</v>
       </c>
       <c r="R80" t="n">
-        <v>6963796</v>
+        <v>6963713</v>
       </c>
       <c r="S80" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9202,7 +9207,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9212,7 +9217,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9239,10 +9244,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133552462</v>
+        <v>133552499</v>
       </c>
       <c r="B81" t="n">
-        <v>83311</v>
+        <v>91928</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9250,21 +9255,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9274,10 +9279,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>580738</v>
+        <v>580926</v>
       </c>
       <c r="R81" t="n">
-        <v>6963776</v>
+        <v>6963805</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9309,7 +9314,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9319,7 +9324,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9346,32 +9351,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133550141</v>
+        <v>133550173</v>
       </c>
       <c r="B82" t="n">
-        <v>99140</v>
+        <v>80439</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9381,13 +9386,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>580713</v>
+        <v>580878</v>
       </c>
       <c r="R82" t="n">
-        <v>6963840</v>
+        <v>6963692</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9416,7 +9421,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9426,12 +9431,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>60 ex, troligen fler</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10224,32 +10224,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133550193</v>
+        <v>133552510</v>
       </c>
       <c r="B90" t="n">
-        <v>99140</v>
+        <v>83319</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10259,10 +10259,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>580781</v>
+        <v>580829</v>
       </c>
       <c r="R90" t="n">
-        <v>6963825</v>
+        <v>6963885</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10294,7 +10294,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10304,12 +10304,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>16:41</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Ca 60 ex</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10336,32 +10331,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133552455</v>
+        <v>133552471</v>
       </c>
       <c r="B91" t="n">
-        <v>99140</v>
+        <v>83319</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10371,10 +10366,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>580733</v>
+        <v>580717</v>
       </c>
       <c r="R91" t="n">
-        <v>6963814</v>
+        <v>6963694</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10406,7 +10401,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10416,12 +10411,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>200 ex</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10448,10 +10438,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133552510</v>
+        <v>133552493</v>
       </c>
       <c r="B92" t="n">
-        <v>83319</v>
+        <v>89310</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10459,21 +10449,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10483,10 +10473,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>580829</v>
+        <v>580914</v>
       </c>
       <c r="R92" t="n">
-        <v>6963885</v>
+        <v>6963757</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10518,7 +10508,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10528,7 +10518,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10555,32 +10545,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133552471</v>
+        <v>133550193</v>
       </c>
       <c r="B93" t="n">
-        <v>83319</v>
+        <v>99140</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10590,10 +10580,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>580717</v>
+        <v>580781</v>
       </c>
       <c r="R93" t="n">
-        <v>6963694</v>
+        <v>6963825</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10625,7 +10615,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10635,7 +10625,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Ca 60 ex</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10662,32 +10657,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133552493</v>
+        <v>133552455</v>
       </c>
       <c r="B94" t="n">
-        <v>89310</v>
+        <v>99140</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10697,10 +10692,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>580914</v>
+        <v>580733</v>
       </c>
       <c r="R94" t="n">
-        <v>6963757</v>
+        <v>6963814</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10732,7 +10727,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10742,7 +10737,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11321,32 +11321,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133552477</v>
+        <v>133550161</v>
       </c>
       <c r="B100" t="n">
-        <v>80468</v>
+        <v>79334</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11356,13 +11356,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>580764</v>
+        <v>580727</v>
       </c>
       <c r="R100" t="n">
-        <v>6963638</v>
+        <v>6963764</v>
       </c>
       <c r="S100" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11428,56 +11428,48 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133552495</v>
+        <v>133552477</v>
       </c>
       <c r="B101" t="n">
-        <v>57958</v>
+        <v>80468</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>580953</v>
+        <v>580764</v>
       </c>
       <c r="R101" t="n">
-        <v>6963811</v>
+        <v>6963638</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11506,7 +11498,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11516,12 +11508,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Ett färskt ringhack på tall</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11548,10 +11535,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133550161</v>
+        <v>133552495</v>
       </c>
       <c r="B102" t="n">
-        <v>79334</v>
+        <v>57958</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11559,37 +11546,45 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>580727</v>
+        <v>580953</v>
       </c>
       <c r="R102" t="n">
-        <v>6963764</v>
+        <v>6963811</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11618,7 +11613,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11628,7 +11623,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Ett färskt ringhack på tall</t>
         </is>
       </c>
       <c r="AD102" t="b">

--- a/artfynd/A 21339-2024 artfynd.xlsx
+++ b/artfynd/A 21339-2024 artfynd.xlsx
@@ -3375,10 +3375,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133550156</v>
+        <v>133550191</v>
       </c>
       <c r="B27" t="n">
-        <v>79334</v>
+        <v>92227</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3386,21 +3386,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3410,13 +3410,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580715</v>
+        <v>580787</v>
       </c>
       <c r="R27" t="n">
-        <v>6963791</v>
+        <v>6963783</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3482,10 +3482,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133550185</v>
+        <v>133552447</v>
       </c>
       <c r="B28" t="n">
-        <v>79334</v>
+        <v>79366</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3493,21 +3493,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3517,13 +3517,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580867</v>
+        <v>580697</v>
       </c>
       <c r="R28" t="n">
-        <v>6963739</v>
+        <v>6963889</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3589,10 +3589,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133552472</v>
+        <v>133550156</v>
       </c>
       <c r="B29" t="n">
-        <v>91942</v>
+        <v>79334</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3600,21 +3600,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3624,13 +3624,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580713</v>
+        <v>580715</v>
       </c>
       <c r="R29" t="n">
-        <v>6963690</v>
+        <v>6963791</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3696,10 +3696,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133550191</v>
+        <v>133550185</v>
       </c>
       <c r="B30" t="n">
-        <v>92227</v>
+        <v>79334</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3731,13 +3731,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580787</v>
+        <v>580867</v>
       </c>
       <c r="R30" t="n">
-        <v>6963783</v>
+        <v>6963739</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3803,10 +3803,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133552447</v>
+        <v>133552472</v>
       </c>
       <c r="B31" t="n">
-        <v>79366</v>
+        <v>91942</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3814,21 +3814,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3838,10 +3838,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>580697</v>
+        <v>580713</v>
       </c>
       <c r="R31" t="n">
-        <v>6963889</v>
+        <v>6963690</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4998,10 +4998,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133552497</v>
+        <v>133550166</v>
       </c>
       <c r="B42" t="n">
-        <v>79091</v>
+        <v>57136</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5009,37 +5009,49 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>102612</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>580939</v>
+        <v>580800</v>
       </c>
       <c r="R42" t="n">
-        <v>6963799</v>
+        <v>6963652</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5068,7 +5080,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5078,7 +5090,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5105,32 +5117,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133552478</v>
+        <v>133552497</v>
       </c>
       <c r="B43" t="n">
-        <v>80474</v>
+        <v>79091</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6463</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5140,10 +5152,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580763</v>
+        <v>580939</v>
       </c>
       <c r="R43" t="n">
-        <v>6963637</v>
+        <v>6963799</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5175,7 +5187,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5185,7 +5197,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5212,32 +5224,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133552494</v>
+        <v>133552478</v>
       </c>
       <c r="B44" t="n">
-        <v>79366</v>
+        <v>80474</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>185</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5247,10 +5259,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>580955</v>
+        <v>580763</v>
       </c>
       <c r="R44" t="n">
-        <v>6963798</v>
+        <v>6963637</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5282,7 +5294,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5292,7 +5304,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5319,10 +5331,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133550166</v>
+        <v>133552494</v>
       </c>
       <c r="B45" t="n">
-        <v>57136</v>
+        <v>79366</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5330,49 +5342,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>102612</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580800</v>
+        <v>580955</v>
       </c>
       <c r="R45" t="n">
-        <v>6963652</v>
+        <v>6963798</v>
       </c>
       <c r="S45" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -7071,10 +7071,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133552466</v>
+        <v>133552485</v>
       </c>
       <c r="B61" t="n">
-        <v>83319</v>
+        <v>79334</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7082,21 +7082,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7106,13 +7106,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>580746</v>
+        <v>580999</v>
       </c>
       <c r="R61" t="n">
-        <v>6963790</v>
+        <v>6963688</v>
       </c>
       <c r="S61" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7178,10 +7178,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133552485</v>
+        <v>133552466</v>
       </c>
       <c r="B62" t="n">
-        <v>79334</v>
+        <v>83319</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7189,21 +7189,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7213,13 +7213,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>580999</v>
+        <v>580746</v>
       </c>
       <c r="R62" t="n">
-        <v>6963688</v>
+        <v>6963790</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8597,32 +8597,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133550141</v>
+        <v>133552487</v>
       </c>
       <c r="B75" t="n">
-        <v>99140</v>
+        <v>89310</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8632,10 +8632,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>580713</v>
+        <v>580983</v>
       </c>
       <c r="R75" t="n">
-        <v>6963840</v>
+        <v>6963709</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8667,7 +8667,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8677,12 +8677,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>60 ex, troligen fler</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8709,7 +8704,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133552487</v>
+        <v>133550186</v>
       </c>
       <c r="B76" t="n">
         <v>89310</v>
@@ -8744,13 +8739,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>580983</v>
+        <v>580871</v>
       </c>
       <c r="R76" t="n">
-        <v>6963709</v>
+        <v>6963767</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8779,7 +8774,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8789,7 +8784,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8816,10 +8811,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133550186</v>
+        <v>133552513</v>
       </c>
       <c r="B77" t="n">
-        <v>89310</v>
+        <v>83311</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8827,21 +8822,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>510</v>
+        <v>308</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8851,10 +8846,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>580871</v>
+        <v>580785</v>
       </c>
       <c r="R77" t="n">
-        <v>6963767</v>
+        <v>6963796</v>
       </c>
       <c r="S77" t="n">
         <v>6</v>
@@ -8886,7 +8881,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8896,7 +8891,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8923,7 +8918,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133552513</v>
+        <v>133552462</v>
       </c>
       <c r="B78" t="n">
         <v>83311</v>
@@ -8958,13 +8953,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>580785</v>
+        <v>580738</v>
       </c>
       <c r="R78" t="n">
-        <v>6963796</v>
+        <v>6963776</v>
       </c>
       <c r="S78" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8993,7 +8988,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9003,7 +8998,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9030,10 +9025,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133552462</v>
+        <v>133550179</v>
       </c>
       <c r="B79" t="n">
-        <v>83311</v>
+        <v>91928</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9041,21 +9036,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9065,10 +9060,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>580738</v>
+        <v>580862</v>
       </c>
       <c r="R79" t="n">
-        <v>6963776</v>
+        <v>6963713</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9100,7 +9095,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9110,7 +9105,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9137,7 +9132,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133550179</v>
+        <v>133552499</v>
       </c>
       <c r="B80" t="n">
         <v>91928</v>
@@ -9172,10 +9167,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>580862</v>
+        <v>580926</v>
       </c>
       <c r="R80" t="n">
-        <v>6963713</v>
+        <v>6963805</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9207,7 +9202,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9217,7 +9212,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9244,10 +9239,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133552499</v>
+        <v>133550173</v>
       </c>
       <c r="B81" t="n">
-        <v>91928</v>
+        <v>80439</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9255,21 +9250,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9279,13 +9274,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>580926</v>
+        <v>580878</v>
       </c>
       <c r="R81" t="n">
-        <v>6963805</v>
+        <v>6963692</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9314,7 +9309,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9324,7 +9319,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9351,32 +9346,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133550173</v>
+        <v>133550141</v>
       </c>
       <c r="B82" t="n">
-        <v>80439</v>
+        <v>99140</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9386,13 +9381,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>580878</v>
+        <v>580713</v>
       </c>
       <c r="R82" t="n">
-        <v>6963692</v>
+        <v>6963840</v>
       </c>
       <c r="S82" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9421,7 +9416,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9431,7 +9426,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>60 ex, troligen fler</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10224,32 +10224,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133552510</v>
+        <v>133550193</v>
       </c>
       <c r="B90" t="n">
-        <v>83319</v>
+        <v>99140</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10259,10 +10259,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>580829</v>
+        <v>580781</v>
       </c>
       <c r="R90" t="n">
-        <v>6963885</v>
+        <v>6963825</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10294,7 +10294,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10304,7 +10304,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ca 60 ex</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10331,32 +10336,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133552471</v>
+        <v>133552455</v>
       </c>
       <c r="B91" t="n">
-        <v>83319</v>
+        <v>99140</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10366,10 +10371,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>580717</v>
+        <v>580733</v>
       </c>
       <c r="R91" t="n">
-        <v>6963694</v>
+        <v>6963814</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10401,7 +10406,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10411,7 +10416,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10438,10 +10448,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133552493</v>
+        <v>133552510</v>
       </c>
       <c r="B92" t="n">
-        <v>89310</v>
+        <v>83319</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10449,21 +10459,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10473,10 +10483,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>580914</v>
+        <v>580829</v>
       </c>
       <c r="R92" t="n">
-        <v>6963757</v>
+        <v>6963885</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10508,7 +10518,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10518,7 +10528,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10545,32 +10555,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133550193</v>
+        <v>133552471</v>
       </c>
       <c r="B93" t="n">
-        <v>99140</v>
+        <v>83319</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10580,10 +10590,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>580781</v>
+        <v>580717</v>
       </c>
       <c r="R93" t="n">
-        <v>6963825</v>
+        <v>6963694</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10615,7 +10625,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10625,12 +10635,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>16:41</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Ca 60 ex</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10657,32 +10662,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133552455</v>
+        <v>133552493</v>
       </c>
       <c r="B94" t="n">
-        <v>99140</v>
+        <v>89310</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10692,10 +10697,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>580733</v>
+        <v>580914</v>
       </c>
       <c r="R94" t="n">
-        <v>6963814</v>
+        <v>6963757</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10727,7 +10732,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10737,12 +10742,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>200 ex</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD94" t="b">

--- a/artfynd/A 21339-2024 artfynd.xlsx
+++ b/artfynd/A 21339-2024 artfynd.xlsx
@@ -3375,10 +3375,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133550191</v>
+        <v>133550156</v>
       </c>
       <c r="B27" t="n">
-        <v>92227</v>
+        <v>79334</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3386,21 +3386,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3410,13 +3410,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580787</v>
+        <v>580715</v>
       </c>
       <c r="R27" t="n">
-        <v>6963783</v>
+        <v>6963791</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3482,10 +3482,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133552447</v>
+        <v>133550185</v>
       </c>
       <c r="B28" t="n">
-        <v>79366</v>
+        <v>79334</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3493,21 +3493,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3517,13 +3517,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580697</v>
+        <v>580867</v>
       </c>
       <c r="R28" t="n">
-        <v>6963889</v>
+        <v>6963739</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3589,10 +3589,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133550156</v>
+        <v>133552472</v>
       </c>
       <c r="B29" t="n">
-        <v>79334</v>
+        <v>91942</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3600,21 +3600,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3624,13 +3624,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580715</v>
+        <v>580713</v>
       </c>
       <c r="R29" t="n">
-        <v>6963791</v>
+        <v>6963690</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3696,10 +3696,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133550185</v>
+        <v>133550191</v>
       </c>
       <c r="B30" t="n">
-        <v>79334</v>
+        <v>92227</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3731,13 +3731,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580867</v>
+        <v>580787</v>
       </c>
       <c r="R30" t="n">
-        <v>6963739</v>
+        <v>6963783</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3803,10 +3803,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133552472</v>
+        <v>133552447</v>
       </c>
       <c r="B31" t="n">
-        <v>91942</v>
+        <v>79366</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3814,21 +3814,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3838,10 +3838,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>580713</v>
+        <v>580697</v>
       </c>
       <c r="R31" t="n">
-        <v>6963690</v>
+        <v>6963889</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -5550,32 +5550,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133552491</v>
+        <v>133550162</v>
       </c>
       <c r="B47" t="n">
-        <v>79334</v>
+        <v>99140</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>580883</v>
+        <v>580728</v>
       </c>
       <c r="R47" t="n">
-        <v>6963753</v>
+        <v>6963787</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5630,7 +5630,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5657,10 +5662,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133552448</v>
+        <v>133552503</v>
       </c>
       <c r="B48" t="n">
-        <v>91928</v>
+        <v>89310</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5668,21 +5673,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5692,10 +5697,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>580691</v>
+        <v>580844</v>
       </c>
       <c r="R48" t="n">
-        <v>6963879</v>
+        <v>6963844</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5727,7 +5732,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5737,7 +5742,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5764,10 +5769,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133552503</v>
+        <v>133550160</v>
       </c>
       <c r="B49" t="n">
-        <v>89310</v>
+        <v>92227</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5775,21 +5780,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5799,13 +5804,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>580844</v>
+        <v>580715</v>
       </c>
       <c r="R49" t="n">
-        <v>6963844</v>
+        <v>6963743</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5834,7 +5839,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5844,7 +5849,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5871,10 +5876,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133550160</v>
+        <v>133552508</v>
       </c>
       <c r="B50" t="n">
-        <v>92227</v>
+        <v>57958</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5882,37 +5887,45 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>580715</v>
+        <v>580813</v>
       </c>
       <c r="R50" t="n">
-        <v>6963743</v>
+        <v>6963779</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5941,7 +5954,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5951,7 +5964,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5978,10 +5996,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133552508</v>
+        <v>133552491</v>
       </c>
       <c r="B51" t="n">
-        <v>57958</v>
+        <v>79334</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5989,42 +6007,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>580813</v>
+        <v>580883</v>
       </c>
       <c r="R51" t="n">
-        <v>6963779</v>
+        <v>6963753</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6056,7 +6066,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6066,12 +6076,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:04</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6098,32 +6103,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133550162</v>
+        <v>133552448</v>
       </c>
       <c r="B52" t="n">
-        <v>99140</v>
+        <v>91928</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6133,10 +6138,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>580728</v>
+        <v>580691</v>
       </c>
       <c r="R52" t="n">
-        <v>6963787</v>
+        <v>6963879</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6168,7 +6173,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6178,12 +6183,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:34</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>50 ex</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6210,32 +6210,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133550147</v>
+        <v>133552490</v>
       </c>
       <c r="B53" t="n">
-        <v>99140</v>
+        <v>80439</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6245,13 +6245,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>580689</v>
+        <v>580853</v>
       </c>
       <c r="R53" t="n">
-        <v>6963814</v>
+        <v>6963702</v>
       </c>
       <c r="S53" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6290,12 +6290,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>70 ex</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6322,10 +6317,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133552490</v>
+        <v>133552482</v>
       </c>
       <c r="B54" t="n">
-        <v>80439</v>
+        <v>83319</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6333,21 +6328,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6357,10 +6352,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>580853</v>
+        <v>580879</v>
       </c>
       <c r="R54" t="n">
-        <v>6963702</v>
+        <v>6963658</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6392,7 +6387,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6402,7 +6397,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6429,7 +6424,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133552482</v>
+        <v>133552486</v>
       </c>
       <c r="B55" t="n">
         <v>83319</v>
@@ -6464,10 +6459,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>580879</v>
+        <v>580985</v>
       </c>
       <c r="R55" t="n">
-        <v>6963658</v>
+        <v>6963707</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6499,7 +6494,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6509,7 +6504,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6536,32 +6531,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133552486</v>
+        <v>133550147</v>
       </c>
       <c r="B56" t="n">
-        <v>83319</v>
+        <v>99140</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6571,13 +6566,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>580985</v>
+        <v>580689</v>
       </c>
       <c r="R56" t="n">
-        <v>6963707</v>
+        <v>6963814</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6606,7 +6601,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6616,7 +6611,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7071,10 +7071,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133552485</v>
+        <v>133552466</v>
       </c>
       <c r="B61" t="n">
-        <v>79334</v>
+        <v>83319</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7082,21 +7082,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7106,13 +7106,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>580999</v>
+        <v>580746</v>
       </c>
       <c r="R61" t="n">
-        <v>6963688</v>
+        <v>6963790</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7178,10 +7178,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133552466</v>
+        <v>133552485</v>
       </c>
       <c r="B62" t="n">
-        <v>83319</v>
+        <v>79334</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7189,21 +7189,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7213,13 +7213,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>580746</v>
+        <v>580999</v>
       </c>
       <c r="R62" t="n">
-        <v>6963790</v>
+        <v>6963688</v>
       </c>
       <c r="S62" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -10224,32 +10224,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133550193</v>
+        <v>133552510</v>
       </c>
       <c r="B90" t="n">
-        <v>99140</v>
+        <v>83319</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10259,10 +10259,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>580781</v>
+        <v>580829</v>
       </c>
       <c r="R90" t="n">
-        <v>6963825</v>
+        <v>6963885</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10294,7 +10294,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10304,12 +10304,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>16:41</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Ca 60 ex</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10336,32 +10331,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133552455</v>
+        <v>133552471</v>
       </c>
       <c r="B91" t="n">
-        <v>99140</v>
+        <v>83319</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10371,10 +10366,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>580733</v>
+        <v>580717</v>
       </c>
       <c r="R91" t="n">
-        <v>6963814</v>
+        <v>6963694</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10406,7 +10401,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10416,12 +10411,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>200 ex</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10448,10 +10438,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133552510</v>
+        <v>133552493</v>
       </c>
       <c r="B92" t="n">
-        <v>83319</v>
+        <v>89310</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10459,21 +10449,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10483,10 +10473,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>580829</v>
+        <v>580914</v>
       </c>
       <c r="R92" t="n">
-        <v>6963885</v>
+        <v>6963757</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10518,7 +10508,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10528,7 +10518,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10555,32 +10545,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133552471</v>
+        <v>133550193</v>
       </c>
       <c r="B93" t="n">
-        <v>83319</v>
+        <v>99140</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10590,10 +10580,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>580717</v>
+        <v>580781</v>
       </c>
       <c r="R93" t="n">
-        <v>6963694</v>
+        <v>6963825</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10625,7 +10615,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10635,7 +10625,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Ca 60 ex</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10662,32 +10657,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133552493</v>
+        <v>133552455</v>
       </c>
       <c r="B94" t="n">
-        <v>89310</v>
+        <v>99140</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10697,10 +10692,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>580914</v>
+        <v>580733</v>
       </c>
       <c r="R94" t="n">
-        <v>6963757</v>
+        <v>6963814</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10732,7 +10727,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10742,7 +10737,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">

--- a/artfynd/A 21339-2024 artfynd.xlsx
+++ b/artfynd/A 21339-2024 artfynd.xlsx
@@ -8597,32 +8597,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133552487</v>
+        <v>133550141</v>
       </c>
       <c r="B75" t="n">
-        <v>89310</v>
+        <v>99140</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8632,10 +8632,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>580983</v>
+        <v>580713</v>
       </c>
       <c r="R75" t="n">
-        <v>6963709</v>
+        <v>6963840</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8667,7 +8667,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8677,7 +8677,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>60 ex, troligen fler</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8704,7 +8709,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133550186</v>
+        <v>133552487</v>
       </c>
       <c r="B76" t="n">
         <v>89310</v>
@@ -8739,13 +8744,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>580871</v>
+        <v>580983</v>
       </c>
       <c r="R76" t="n">
-        <v>6963767</v>
+        <v>6963709</v>
       </c>
       <c r="S76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8774,7 +8779,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8784,7 +8789,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8811,10 +8816,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133552513</v>
+        <v>133550186</v>
       </c>
       <c r="B77" t="n">
-        <v>83311</v>
+        <v>89310</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8822,21 +8827,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>308</v>
+        <v>510</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8846,10 +8851,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>580785</v>
+        <v>580871</v>
       </c>
       <c r="R77" t="n">
-        <v>6963796</v>
+        <v>6963767</v>
       </c>
       <c r="S77" t="n">
         <v>6</v>
@@ -8881,7 +8886,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8891,7 +8896,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8918,7 +8923,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133552462</v>
+        <v>133552513</v>
       </c>
       <c r="B78" t="n">
         <v>83311</v>
@@ -8953,13 +8958,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>580738</v>
+        <v>580785</v>
       </c>
       <c r="R78" t="n">
-        <v>6963776</v>
+        <v>6963796</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8988,7 +8993,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8998,7 +9003,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9025,10 +9030,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133550179</v>
+        <v>133552462</v>
       </c>
       <c r="B79" t="n">
-        <v>91928</v>
+        <v>83311</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9036,21 +9041,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9060,10 +9065,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>580862</v>
+        <v>580738</v>
       </c>
       <c r="R79" t="n">
-        <v>6963713</v>
+        <v>6963776</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9095,7 +9100,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9105,7 +9110,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9132,7 +9137,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133552499</v>
+        <v>133550179</v>
       </c>
       <c r="B80" t="n">
         <v>91928</v>
@@ -9167,10 +9172,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>580926</v>
+        <v>580862</v>
       </c>
       <c r="R80" t="n">
-        <v>6963805</v>
+        <v>6963713</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9202,7 +9207,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9212,7 +9217,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9239,10 +9244,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133550173</v>
+        <v>133552499</v>
       </c>
       <c r="B81" t="n">
-        <v>80439</v>
+        <v>91928</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9250,21 +9255,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9274,13 +9279,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>580878</v>
+        <v>580926</v>
       </c>
       <c r="R81" t="n">
-        <v>6963692</v>
+        <v>6963805</v>
       </c>
       <c r="S81" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9309,7 +9314,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9319,7 +9324,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9346,32 +9351,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133550141</v>
+        <v>133550173</v>
       </c>
       <c r="B82" t="n">
-        <v>99140</v>
+        <v>80439</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9381,13 +9386,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>580713</v>
+        <v>580878</v>
       </c>
       <c r="R82" t="n">
-        <v>6963840</v>
+        <v>6963692</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9416,7 +9421,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9426,12 +9431,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>60 ex, troligen fler</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10224,32 +10224,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133552510</v>
+        <v>133550193</v>
       </c>
       <c r="B90" t="n">
-        <v>83319</v>
+        <v>99140</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10259,10 +10259,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>580829</v>
+        <v>580781</v>
       </c>
       <c r="R90" t="n">
-        <v>6963885</v>
+        <v>6963825</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10294,7 +10294,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10304,7 +10304,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ca 60 ex</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10331,32 +10336,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133552471</v>
+        <v>133552455</v>
       </c>
       <c r="B91" t="n">
-        <v>83319</v>
+        <v>99140</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10366,10 +10371,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>580717</v>
+        <v>580733</v>
       </c>
       <c r="R91" t="n">
-        <v>6963694</v>
+        <v>6963814</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10401,7 +10406,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10411,7 +10416,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10438,10 +10448,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133552493</v>
+        <v>133552510</v>
       </c>
       <c r="B92" t="n">
-        <v>89310</v>
+        <v>83319</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10449,21 +10459,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10473,10 +10483,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>580914</v>
+        <v>580829</v>
       </c>
       <c r="R92" t="n">
-        <v>6963757</v>
+        <v>6963885</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10508,7 +10518,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10518,7 +10528,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10545,32 +10555,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133550193</v>
+        <v>133552471</v>
       </c>
       <c r="B93" t="n">
-        <v>99140</v>
+        <v>83319</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10580,10 +10590,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>580781</v>
+        <v>580717</v>
       </c>
       <c r="R93" t="n">
-        <v>6963825</v>
+        <v>6963694</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10615,7 +10625,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10625,12 +10635,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>16:41</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Ca 60 ex</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10657,32 +10662,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133552455</v>
+        <v>133552493</v>
       </c>
       <c r="B94" t="n">
-        <v>99140</v>
+        <v>89310</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10692,10 +10697,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>580733</v>
+        <v>580914</v>
       </c>
       <c r="R94" t="n">
-        <v>6963814</v>
+        <v>6963757</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10727,7 +10732,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10737,12 +10742,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>200 ex</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD94" t="b">

--- a/artfynd/A 21339-2024 artfynd.xlsx
+++ b/artfynd/A 21339-2024 artfynd.xlsx
@@ -2514,10 +2514,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133550164</v>
+        <v>133552492</v>
       </c>
       <c r="B19" t="n">
-        <v>79334</v>
+        <v>79092</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2525,21 +2525,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2549,13 +2549,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580751</v>
+        <v>580892</v>
       </c>
       <c r="R19" t="n">
-        <v>6963748</v>
+        <v>6963759</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2621,7 +2621,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133552509</v>
+        <v>133550164</v>
       </c>
       <c r="B20" t="n">
         <v>79334</v>
@@ -2656,13 +2656,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580814</v>
+        <v>580751</v>
       </c>
       <c r="R20" t="n">
-        <v>6963859</v>
+        <v>6963748</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2728,10 +2728,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133552492</v>
+        <v>133552509</v>
       </c>
       <c r="B21" t="n">
-        <v>79092</v>
+        <v>79334</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2739,21 +2739,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580892</v>
+        <v>580814</v>
       </c>
       <c r="R21" t="n">
-        <v>6963759</v>
+        <v>6963859</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3375,10 +3375,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133550156</v>
+        <v>133550191</v>
       </c>
       <c r="B27" t="n">
-        <v>79334</v>
+        <v>92227</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3386,21 +3386,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3410,13 +3410,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580715</v>
+        <v>580787</v>
       </c>
       <c r="R27" t="n">
-        <v>6963791</v>
+        <v>6963783</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3482,10 +3482,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133550185</v>
+        <v>133552447</v>
       </c>
       <c r="B28" t="n">
-        <v>79334</v>
+        <v>79366</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3493,21 +3493,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3517,13 +3517,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580867</v>
+        <v>580697</v>
       </c>
       <c r="R28" t="n">
-        <v>6963739</v>
+        <v>6963889</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3589,10 +3589,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133552472</v>
+        <v>133550156</v>
       </c>
       <c r="B29" t="n">
-        <v>91942</v>
+        <v>79334</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3600,21 +3600,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3624,13 +3624,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580713</v>
+        <v>580715</v>
       </c>
       <c r="R29" t="n">
-        <v>6963690</v>
+        <v>6963791</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3696,10 +3696,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133550191</v>
+        <v>133550185</v>
       </c>
       <c r="B30" t="n">
-        <v>92227</v>
+        <v>79334</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3731,13 +3731,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580787</v>
+        <v>580867</v>
       </c>
       <c r="R30" t="n">
-        <v>6963783</v>
+        <v>6963739</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3803,10 +3803,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133552447</v>
+        <v>133552472</v>
       </c>
       <c r="B31" t="n">
-        <v>79366</v>
+        <v>91942</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3814,21 +3814,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3838,10 +3838,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>580697</v>
+        <v>580713</v>
       </c>
       <c r="R31" t="n">
-        <v>6963889</v>
+        <v>6963690</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4022,32 +4022,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133550138</v>
+        <v>133550163</v>
       </c>
       <c r="B33" t="n">
-        <v>79334</v>
+        <v>98005</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4057,10 +4057,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>580712</v>
+        <v>580728</v>
       </c>
       <c r="R33" t="n">
-        <v>6963853</v>
+        <v>6963787</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4129,32 +4129,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133552502</v>
+        <v>133550138</v>
       </c>
       <c r="B34" t="n">
-        <v>80343</v>
+        <v>79334</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4164,10 +4164,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>580865</v>
+        <v>580712</v>
       </c>
       <c r="R34" t="n">
-        <v>6963830</v>
+        <v>6963853</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4343,56 +4343,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133550180</v>
+        <v>133552502</v>
       </c>
       <c r="B36" t="n">
-        <v>57958</v>
+        <v>80343</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>580876</v>
+        <v>580865</v>
       </c>
       <c r="R36" t="n">
-        <v>6963707</v>
+        <v>6963830</v>
       </c>
       <c r="S36" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4421,7 +4413,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4431,12 +4423,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:14</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4463,48 +4450,56 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133550163</v>
+        <v>133550180</v>
       </c>
       <c r="B37" t="n">
-        <v>98005</v>
+        <v>57958</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>580728</v>
+        <v>580876</v>
       </c>
       <c r="R37" t="n">
-        <v>6963787</v>
+        <v>6963707</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4533,7 +4528,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4543,7 +4538,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4998,10 +4998,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133550166</v>
+        <v>133552497</v>
       </c>
       <c r="B42" t="n">
-        <v>57136</v>
+        <v>79091</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5009,49 +5009,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102612</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>580800</v>
+        <v>580939</v>
       </c>
       <c r="R42" t="n">
-        <v>6963652</v>
+        <v>6963799</v>
       </c>
       <c r="S42" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5080,7 +5068,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5090,7 +5078,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5117,32 +5105,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133552497</v>
+        <v>133552478</v>
       </c>
       <c r="B43" t="n">
-        <v>79091</v>
+        <v>80474</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5152,10 +5140,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580939</v>
+        <v>580763</v>
       </c>
       <c r="R43" t="n">
-        <v>6963799</v>
+        <v>6963637</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5187,7 +5175,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5197,7 +5185,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5224,32 +5212,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133552478</v>
+        <v>133552494</v>
       </c>
       <c r="B44" t="n">
-        <v>80474</v>
+        <v>79366</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>185</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5259,10 +5247,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>580763</v>
+        <v>580955</v>
       </c>
       <c r="R44" t="n">
-        <v>6963637</v>
+        <v>6963798</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5294,7 +5282,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5304,7 +5292,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5331,10 +5319,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133552494</v>
+        <v>133550166</v>
       </c>
       <c r="B45" t="n">
-        <v>79366</v>
+        <v>57136</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5342,37 +5330,49 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>102612</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580955</v>
+        <v>580800</v>
       </c>
       <c r="R45" t="n">
-        <v>6963798</v>
+        <v>6963652</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5550,32 +5550,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133550162</v>
+        <v>133552491</v>
       </c>
       <c r="B47" t="n">
-        <v>99140</v>
+        <v>79334</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>580728</v>
+        <v>580883</v>
       </c>
       <c r="R47" t="n">
-        <v>6963787</v>
+        <v>6963753</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5630,12 +5630,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:34</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>50 ex</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5662,10 +5657,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133552503</v>
+        <v>133552448</v>
       </c>
       <c r="B48" t="n">
-        <v>89310</v>
+        <v>91928</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5673,21 +5668,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5697,10 +5692,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>580844</v>
+        <v>580691</v>
       </c>
       <c r="R48" t="n">
-        <v>6963844</v>
+        <v>6963879</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5732,7 +5727,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5742,7 +5737,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5769,10 +5764,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133550160</v>
+        <v>133552503</v>
       </c>
       <c r="B49" t="n">
-        <v>92227</v>
+        <v>89310</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5780,21 +5775,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5804,13 +5799,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>580715</v>
+        <v>580844</v>
       </c>
       <c r="R49" t="n">
-        <v>6963743</v>
+        <v>6963844</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5839,7 +5834,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5849,7 +5844,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5876,10 +5871,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133552508</v>
+        <v>133550160</v>
       </c>
       <c r="B50" t="n">
-        <v>57958</v>
+        <v>92227</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5887,45 +5882,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>580813</v>
+        <v>580715</v>
       </c>
       <c r="R50" t="n">
-        <v>6963779</v>
+        <v>6963743</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5954,7 +5941,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5964,12 +5951,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:04</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5996,10 +5978,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133552491</v>
+        <v>133552508</v>
       </c>
       <c r="B51" t="n">
-        <v>79334</v>
+        <v>57958</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6007,34 +5989,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>580883</v>
+        <v>580813</v>
       </c>
       <c r="R51" t="n">
-        <v>6963753</v>
+        <v>6963779</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6066,7 +6056,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6076,7 +6066,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6103,32 +6098,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133552448</v>
+        <v>133550162</v>
       </c>
       <c r="B52" t="n">
-        <v>91928</v>
+        <v>99140</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6138,10 +6133,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>580691</v>
+        <v>580728</v>
       </c>
       <c r="R52" t="n">
-        <v>6963879</v>
+        <v>6963787</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6173,7 +6168,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6183,7 +6178,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6210,32 +6210,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133552490</v>
+        <v>133550147</v>
       </c>
       <c r="B53" t="n">
-        <v>80439</v>
+        <v>99140</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6245,13 +6245,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>580853</v>
+        <v>580689</v>
       </c>
       <c r="R53" t="n">
-        <v>6963702</v>
+        <v>6963814</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6290,7 +6290,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6317,10 +6322,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133552482</v>
+        <v>133552490</v>
       </c>
       <c r="B54" t="n">
-        <v>83319</v>
+        <v>80439</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6328,21 +6333,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6352,10 +6357,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>580879</v>
+        <v>580853</v>
       </c>
       <c r="R54" t="n">
-        <v>6963658</v>
+        <v>6963702</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6387,7 +6392,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6397,7 +6402,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6424,7 +6429,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133552486</v>
+        <v>133552482</v>
       </c>
       <c r="B55" t="n">
         <v>83319</v>
@@ -6459,10 +6464,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>580985</v>
+        <v>580879</v>
       </c>
       <c r="R55" t="n">
-        <v>6963707</v>
+        <v>6963658</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6494,7 +6499,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6504,7 +6509,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6531,32 +6536,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133550147</v>
+        <v>133552486</v>
       </c>
       <c r="B56" t="n">
-        <v>99140</v>
+        <v>83319</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6566,13 +6571,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>580689</v>
+        <v>580985</v>
       </c>
       <c r="R56" t="n">
-        <v>6963814</v>
+        <v>6963707</v>
       </c>
       <c r="S56" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6601,7 +6606,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6611,12 +6616,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>70 ex</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8597,32 +8597,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133550141</v>
+        <v>133552487</v>
       </c>
       <c r="B75" t="n">
-        <v>99140</v>
+        <v>89310</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8632,10 +8632,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>580713</v>
+        <v>580983</v>
       </c>
       <c r="R75" t="n">
-        <v>6963840</v>
+        <v>6963709</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8667,7 +8667,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8677,12 +8677,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>60 ex, troligen fler</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8709,7 +8704,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133552487</v>
+        <v>133550186</v>
       </c>
       <c r="B76" t="n">
         <v>89310</v>
@@ -8744,13 +8739,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>580983</v>
+        <v>580871</v>
       </c>
       <c r="R76" t="n">
-        <v>6963709</v>
+        <v>6963767</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8779,7 +8774,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8789,7 +8784,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8816,10 +8811,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133550186</v>
+        <v>133552513</v>
       </c>
       <c r="B77" t="n">
-        <v>89310</v>
+        <v>83311</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8827,21 +8822,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>510</v>
+        <v>308</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8851,10 +8846,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>580871</v>
+        <v>580785</v>
       </c>
       <c r="R77" t="n">
-        <v>6963767</v>
+        <v>6963796</v>
       </c>
       <c r="S77" t="n">
         <v>6</v>
@@ -8886,7 +8881,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8896,7 +8891,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8923,7 +8918,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133552513</v>
+        <v>133552462</v>
       </c>
       <c r="B78" t="n">
         <v>83311</v>
@@ -8958,13 +8953,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>580785</v>
+        <v>580738</v>
       </c>
       <c r="R78" t="n">
-        <v>6963796</v>
+        <v>6963776</v>
       </c>
       <c r="S78" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8993,7 +8988,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9003,7 +8998,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9030,10 +9025,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133552462</v>
+        <v>133550179</v>
       </c>
       <c r="B79" t="n">
-        <v>83311</v>
+        <v>91928</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9041,21 +9036,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9065,10 +9060,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>580738</v>
+        <v>580862</v>
       </c>
       <c r="R79" t="n">
-        <v>6963776</v>
+        <v>6963713</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9100,7 +9095,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9110,7 +9105,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9137,7 +9132,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133550179</v>
+        <v>133552499</v>
       </c>
       <c r="B80" t="n">
         <v>91928</v>
@@ -9172,10 +9167,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>580862</v>
+        <v>580926</v>
       </c>
       <c r="R80" t="n">
-        <v>6963713</v>
+        <v>6963805</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9207,7 +9202,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9217,7 +9212,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9244,10 +9239,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133552499</v>
+        <v>133550173</v>
       </c>
       <c r="B81" t="n">
-        <v>91928</v>
+        <v>80439</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9255,21 +9250,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9279,13 +9274,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>580926</v>
+        <v>580878</v>
       </c>
       <c r="R81" t="n">
-        <v>6963805</v>
+        <v>6963692</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9314,7 +9309,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9324,7 +9319,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9351,32 +9346,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133550173</v>
+        <v>133550141</v>
       </c>
       <c r="B82" t="n">
-        <v>80439</v>
+        <v>99140</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9386,13 +9381,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>580878</v>
+        <v>580713</v>
       </c>
       <c r="R82" t="n">
-        <v>6963692</v>
+        <v>6963840</v>
       </c>
       <c r="S82" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9421,7 +9416,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9431,7 +9426,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>60 ex, troligen fler</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10224,32 +10224,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133550193</v>
+        <v>133552510</v>
       </c>
       <c r="B90" t="n">
-        <v>99140</v>
+        <v>83319</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10259,10 +10259,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>580781</v>
+        <v>580829</v>
       </c>
       <c r="R90" t="n">
-        <v>6963825</v>
+        <v>6963885</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10294,7 +10294,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10304,12 +10304,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>16:41</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Ca 60 ex</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10336,32 +10331,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133552455</v>
+        <v>133552471</v>
       </c>
       <c r="B91" t="n">
-        <v>99140</v>
+        <v>83319</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10371,10 +10366,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>580733</v>
+        <v>580717</v>
       </c>
       <c r="R91" t="n">
-        <v>6963814</v>
+        <v>6963694</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10406,7 +10401,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10416,12 +10411,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>200 ex</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10448,10 +10438,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133552510</v>
+        <v>133552493</v>
       </c>
       <c r="B92" t="n">
-        <v>83319</v>
+        <v>89310</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10459,21 +10449,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10483,10 +10473,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>580829</v>
+        <v>580914</v>
       </c>
       <c r="R92" t="n">
-        <v>6963885</v>
+        <v>6963757</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10518,7 +10508,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10528,7 +10518,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10555,32 +10545,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133552471</v>
+        <v>133550193</v>
       </c>
       <c r="B93" t="n">
-        <v>83319</v>
+        <v>99140</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10590,10 +10580,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>580717</v>
+        <v>580781</v>
       </c>
       <c r="R93" t="n">
-        <v>6963694</v>
+        <v>6963825</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10625,7 +10615,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10635,7 +10625,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Ca 60 ex</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10662,32 +10657,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133552493</v>
+        <v>133552455</v>
       </c>
       <c r="B94" t="n">
-        <v>89310</v>
+        <v>99140</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10697,10 +10692,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>580914</v>
+        <v>580733</v>
       </c>
       <c r="R94" t="n">
-        <v>6963757</v>
+        <v>6963814</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10732,7 +10727,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10742,7 +10737,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">

--- a/artfynd/A 21339-2024 artfynd.xlsx
+++ b/artfynd/A 21339-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133550167</v>
       </c>
       <c r="B2" t="n">
-        <v>89310</v>
+        <v>89328</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133552449</v>
+        <v>133552483</v>
       </c>
       <c r="B3" t="n">
-        <v>91928</v>
+        <v>89328</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580689</v>
+        <v>580906</v>
       </c>
       <c r="R3" t="n">
-        <v>6963874</v>
+        <v>6963679</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +892,7 @@
         <v>133550175</v>
       </c>
       <c r="B4" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>133550168</v>
       </c>
       <c r="B5" t="n">
-        <v>83183</v>
+        <v>83197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133552483</v>
+        <v>133552481</v>
       </c>
       <c r="B6" t="n">
-        <v>89310</v>
+        <v>89328</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580906</v>
+        <v>580869</v>
       </c>
       <c r="R6" t="n">
-        <v>6963679</v>
+        <v>6963663</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133552481</v>
+        <v>133552511</v>
       </c>
       <c r="B7" t="n">
-        <v>89310</v>
+        <v>79380</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>510</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580869</v>
+        <v>580865</v>
       </c>
       <c r="R7" t="n">
-        <v>6963663</v>
+        <v>6963889</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133552511</v>
+        <v>133552449</v>
       </c>
       <c r="B8" t="n">
-        <v>79366</v>
+        <v>91947</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580865</v>
+        <v>580689</v>
       </c>
       <c r="R8" t="n">
-        <v>6963889</v>
+        <v>6963874</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133552456</v>
+        <v>133550155</v>
       </c>
       <c r="B9" t="n">
-        <v>91928</v>
+        <v>80453</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,13 +1459,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580695</v>
+        <v>580715</v>
       </c>
       <c r="R9" t="n">
-        <v>6963806</v>
+        <v>6963791</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,32 +1536,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133550174</v>
+        <v>133550154</v>
       </c>
       <c r="B10" t="n">
-        <v>79334</v>
+        <v>99168</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,13 +1571,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580879</v>
+        <v>580712</v>
       </c>
       <c r="R10" t="n">
-        <v>6963690</v>
+        <v>6963788</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1601,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1616,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,32 +1648,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133552475</v>
+        <v>133550157</v>
       </c>
       <c r="B11" t="n">
-        <v>79334</v>
+        <v>99168</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,13 +1683,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580801</v>
+        <v>580715</v>
       </c>
       <c r="R11" t="n">
-        <v>6963655</v>
+        <v>6963786</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1708,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1728,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133550155</v>
+        <v>133550153</v>
       </c>
       <c r="B12" t="n">
-        <v>80439</v>
+        <v>80453</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,13 +1795,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580715</v>
+        <v>580704</v>
       </c>
       <c r="R12" t="n">
-        <v>6963791</v>
+        <v>6963785</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1815,7 +1830,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,12 +1840,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>Stora fina exemplar av lunglav, handflata storlek.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1857,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133552461</v>
+        <v>133552468</v>
       </c>
       <c r="B13" t="n">
-        <v>83302</v>
+        <v>98033</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,21 +1883,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6439</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580740</v>
+        <v>580758</v>
       </c>
       <c r="R13" t="n">
-        <v>6963795</v>
+        <v>6963787</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1927,7 +1942,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1937,7 +1952,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1964,32 +1979,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133552452</v>
+        <v>133552461</v>
       </c>
       <c r="B14" t="n">
-        <v>83319</v>
+        <v>83316</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1999,13 +2014,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580698</v>
+        <v>580740</v>
       </c>
       <c r="R14" t="n">
-        <v>6963860</v>
+        <v>6963795</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2034,7 +2049,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2044,7 +2059,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2071,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133550153</v>
+        <v>133552452</v>
       </c>
       <c r="B15" t="n">
-        <v>80439</v>
+        <v>83333</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2082,21 +2097,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2106,13 +2121,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580704</v>
+        <v>580698</v>
       </c>
       <c r="R15" t="n">
-        <v>6963785</v>
+        <v>6963860</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2141,7 +2156,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2151,12 +2166,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Stora fina exemplar av lunglav, handflata storlek.</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2183,32 +2193,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133550154</v>
+        <v>133552456</v>
       </c>
       <c r="B16" t="n">
-        <v>99140</v>
+        <v>91947</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2218,13 +2228,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580712</v>
+        <v>580695</v>
       </c>
       <c r="R16" t="n">
-        <v>6963788</v>
+        <v>6963806</v>
       </c>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2253,7 +2263,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2263,12 +2273,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:59</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>70 ex</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,32 +2300,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133550157</v>
+        <v>133550174</v>
       </c>
       <c r="B17" t="n">
-        <v>99140</v>
+        <v>79348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2330,13 +2335,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580715</v>
+        <v>580879</v>
       </c>
       <c r="R17" t="n">
-        <v>6963786</v>
+        <v>6963690</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2365,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2375,12 +2380,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>150 ex</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,32 +2407,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133552468</v>
+        <v>133552475</v>
       </c>
       <c r="B18" t="n">
-        <v>98005</v>
+        <v>79348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580758</v>
+        <v>580801</v>
       </c>
       <c r="R18" t="n">
-        <v>6963787</v>
+        <v>6963655</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2514,10 +2514,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133552492</v>
+        <v>133550164</v>
       </c>
       <c r="B19" t="n">
-        <v>79092</v>
+        <v>79348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2525,21 +2525,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2549,13 +2549,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580892</v>
+        <v>580751</v>
       </c>
       <c r="R19" t="n">
-        <v>6963759</v>
+        <v>6963748</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2621,10 +2621,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133550164</v>
+        <v>133552509</v>
       </c>
       <c r="B20" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2656,13 +2656,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580751</v>
+        <v>580814</v>
       </c>
       <c r="R20" t="n">
-        <v>6963748</v>
+        <v>6963859</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2728,10 +2728,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133552509</v>
+        <v>133552492</v>
       </c>
       <c r="B21" t="n">
-        <v>79334</v>
+        <v>79106</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2739,21 +2739,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580814</v>
+        <v>580892</v>
       </c>
       <c r="R21" t="n">
-        <v>6963859</v>
+        <v>6963759</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2835,32 +2835,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133552457</v>
+        <v>133550184</v>
       </c>
       <c r="B22" t="n">
-        <v>91928</v>
+        <v>99168</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580720</v>
+        <v>580867</v>
       </c>
       <c r="R22" t="n">
-        <v>6963788</v>
+        <v>6963739</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2915,7 +2915,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>36 ex</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2942,10 +2947,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133552464</v>
+        <v>133552457</v>
       </c>
       <c r="B23" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2980,7 +2985,7 @@
         <v>580720</v>
       </c>
       <c r="R23" t="n">
-        <v>6963748</v>
+        <v>6963788</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3012,7 +3017,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3022,7 +3027,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3049,32 +3054,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133552451</v>
+        <v>133550171</v>
       </c>
       <c r="B24" t="n">
-        <v>91891</v>
+        <v>80453</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3084,13 +3089,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580669</v>
+        <v>580857</v>
       </c>
       <c r="R24" t="n">
-        <v>6963873</v>
+        <v>6963688</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3119,7 +3124,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3129,7 +3134,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3156,10 +3161,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133550171</v>
+        <v>133552464</v>
       </c>
       <c r="B25" t="n">
-        <v>80439</v>
+        <v>91947</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3167,21 +3172,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3191,13 +3196,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580857</v>
+        <v>580720</v>
       </c>
       <c r="R25" t="n">
-        <v>6963688</v>
+        <v>6963748</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3226,7 +3231,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3236,7 +3241,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3263,32 +3268,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133550184</v>
+        <v>133552451</v>
       </c>
       <c r="B26" t="n">
-        <v>99140</v>
+        <v>91910</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3298,10 +3303,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580867</v>
+        <v>580669</v>
       </c>
       <c r="R26" t="n">
-        <v>6963739</v>
+        <v>6963873</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3333,7 +3338,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3343,12 +3348,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>36 ex</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3375,10 +3375,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133550191</v>
+        <v>133550185</v>
       </c>
       <c r="B27" t="n">
-        <v>92227</v>
+        <v>79348</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3386,21 +3386,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3410,13 +3410,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580787</v>
+        <v>580867</v>
       </c>
       <c r="R27" t="n">
-        <v>6963783</v>
+        <v>6963739</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3482,10 +3482,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133552447</v>
+        <v>133550191</v>
       </c>
       <c r="B28" t="n">
-        <v>79366</v>
+        <v>92218</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3493,21 +3493,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580697</v>
+        <v>580787</v>
       </c>
       <c r="R28" t="n">
-        <v>6963889</v>
+        <v>6963783</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3589,10 +3589,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133550156</v>
+        <v>133552472</v>
       </c>
       <c r="B29" t="n">
-        <v>79334</v>
+        <v>91961</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3600,21 +3600,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3624,13 +3624,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580715</v>
+        <v>580713</v>
       </c>
       <c r="R29" t="n">
-        <v>6963791</v>
+        <v>6963690</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3696,10 +3696,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133550185</v>
+        <v>133550156</v>
       </c>
       <c r="B30" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3731,13 +3731,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580867</v>
+        <v>580715</v>
       </c>
       <c r="R30" t="n">
-        <v>6963739</v>
+        <v>6963791</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3803,10 +3803,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133552472</v>
+        <v>133552447</v>
       </c>
       <c r="B31" t="n">
-        <v>91942</v>
+        <v>79380</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3814,21 +3814,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3838,10 +3838,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>580713</v>
+        <v>580697</v>
       </c>
       <c r="R31" t="n">
-        <v>6963690</v>
+        <v>6963889</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3913,7 +3913,7 @@
         <v>133550148</v>
       </c>
       <c r="B32" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4022,48 +4022,56 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133550163</v>
+        <v>133550180</v>
       </c>
       <c r="B33" t="n">
-        <v>98005</v>
+        <v>57965</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>580728</v>
+        <v>580876</v>
       </c>
       <c r="R33" t="n">
-        <v>6963787</v>
+        <v>6963707</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4092,7 +4100,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4102,7 +4110,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4129,10 +4142,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133550138</v>
+        <v>133552488</v>
       </c>
       <c r="B34" t="n">
-        <v>79334</v>
+        <v>89328</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4140,21 +4153,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4164,10 +4177,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>580712</v>
+        <v>580943</v>
       </c>
       <c r="R34" t="n">
-        <v>6963853</v>
+        <v>6963738</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4199,7 +4212,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4209,7 +4222,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4236,32 +4249,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133552488</v>
+        <v>133552502</v>
       </c>
       <c r="B35" t="n">
-        <v>89310</v>
+        <v>80357</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>510</v>
+        <v>6456</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4271,10 +4284,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>580943</v>
+        <v>580865</v>
       </c>
       <c r="R35" t="n">
-        <v>6963738</v>
+        <v>6963830</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4306,7 +4319,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4316,7 +4329,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4343,32 +4356,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133552502</v>
+        <v>133550138</v>
       </c>
       <c r="B36" t="n">
-        <v>80343</v>
+        <v>79348</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4378,10 +4391,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>580865</v>
+        <v>580712</v>
       </c>
       <c r="R36" t="n">
-        <v>6963830</v>
+        <v>6963853</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4413,7 +4426,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4423,7 +4436,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4450,56 +4463,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133550180</v>
+        <v>133550163</v>
       </c>
       <c r="B37" t="n">
-        <v>57958</v>
+        <v>98033</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>580876</v>
+        <v>580728</v>
       </c>
       <c r="R37" t="n">
-        <v>6963707</v>
+        <v>6963787</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4528,7 +4533,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4538,12 +4543,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:14</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4570,32 +4570,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133552453</v>
+        <v>133550136</v>
       </c>
       <c r="B38" t="n">
-        <v>79334</v>
+        <v>99168</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4605,13 +4605,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>580737</v>
+        <v>580702</v>
       </c>
       <c r="R38" t="n">
-        <v>6963844</v>
+        <v>6963851</v>
       </c>
       <c r="S38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4650,7 +4650,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4677,10 +4682,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133550132</v>
+        <v>133552497</v>
       </c>
       <c r="B39" t="n">
-        <v>79334</v>
+        <v>79105</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4688,21 +4693,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4712,10 +4717,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>580695</v>
+        <v>580939</v>
       </c>
       <c r="R39" t="n">
-        <v>6963885</v>
+        <v>6963799</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4747,7 +4752,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4757,7 +4762,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4784,10 +4789,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133550176</v>
+        <v>133552453</v>
       </c>
       <c r="B40" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4819,13 +4824,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>580874</v>
+        <v>580737</v>
       </c>
       <c r="R40" t="n">
-        <v>6963718</v>
+        <v>6963844</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4854,7 +4859,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4864,7 +4869,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4894,7 +4899,7 @@
         <v>133550182</v>
       </c>
       <c r="B41" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4998,32 +5003,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133552497</v>
+        <v>133552478</v>
       </c>
       <c r="B42" t="n">
-        <v>79091</v>
+        <v>80488</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6463</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5033,10 +5038,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>580939</v>
+        <v>580763</v>
       </c>
       <c r="R42" t="n">
-        <v>6963799</v>
+        <v>6963637</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5068,7 +5073,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5078,7 +5083,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5105,32 +5110,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133552478</v>
+        <v>133552494</v>
       </c>
       <c r="B43" t="n">
-        <v>80474</v>
+        <v>79380</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6463</v>
+        <v>185</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5140,10 +5145,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580763</v>
+        <v>580955</v>
       </c>
       <c r="R43" t="n">
-        <v>6963637</v>
+        <v>6963798</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5175,7 +5180,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5185,7 +5190,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5212,10 +5217,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133552494</v>
+        <v>133550166</v>
       </c>
       <c r="B44" t="n">
-        <v>79366</v>
+        <v>57143</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5223,37 +5228,49 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>185</v>
+        <v>102612</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>580955</v>
+        <v>580800</v>
       </c>
       <c r="R44" t="n">
-        <v>6963798</v>
+        <v>6963652</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5282,7 +5299,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5292,7 +5309,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5319,10 +5336,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133550166</v>
+        <v>133550176</v>
       </c>
       <c r="B45" t="n">
-        <v>57136</v>
+        <v>79348</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5330,49 +5347,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580800</v>
+        <v>580874</v>
       </c>
       <c r="R45" t="n">
-        <v>6963652</v>
+        <v>6963718</v>
       </c>
       <c r="S45" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5401,7 +5406,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5411,7 +5416,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5438,32 +5443,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133550136</v>
+        <v>133550132</v>
       </c>
       <c r="B46" t="n">
-        <v>99140</v>
+        <v>79348</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5473,10 +5478,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>580702</v>
+        <v>580695</v>
       </c>
       <c r="R46" t="n">
-        <v>6963851</v>
+        <v>6963885</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5508,7 +5513,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5518,12 +5523,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>150 ex</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5550,32 +5550,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133552491</v>
+        <v>133550162</v>
       </c>
       <c r="B47" t="n">
-        <v>79334</v>
+        <v>99168</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>580883</v>
+        <v>580728</v>
       </c>
       <c r="R47" t="n">
-        <v>6963753</v>
+        <v>6963787</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5630,7 +5630,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5657,32 +5662,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133552448</v>
+        <v>133550147</v>
       </c>
       <c r="B48" t="n">
-        <v>91928</v>
+        <v>99168</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5692,13 +5697,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>580691</v>
+        <v>580689</v>
       </c>
       <c r="R48" t="n">
-        <v>6963879</v>
+        <v>6963814</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5727,7 +5732,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5737,7 +5742,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5764,10 +5774,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133552503</v>
+        <v>133552482</v>
       </c>
       <c r="B49" t="n">
-        <v>89310</v>
+        <v>83333</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5775,21 +5785,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5799,10 +5809,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>580844</v>
+        <v>580879</v>
       </c>
       <c r="R49" t="n">
-        <v>6963844</v>
+        <v>6963658</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5834,7 +5844,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5844,7 +5854,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5871,10 +5881,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133550160</v>
+        <v>133552491</v>
       </c>
       <c r="B50" t="n">
-        <v>92227</v>
+        <v>79348</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5882,21 +5892,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5906,13 +5916,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>580715</v>
+        <v>580883</v>
       </c>
       <c r="R50" t="n">
-        <v>6963743</v>
+        <v>6963753</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5941,7 +5951,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5951,7 +5961,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5978,10 +5988,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133552508</v>
+        <v>133550160</v>
       </c>
       <c r="B51" t="n">
-        <v>57958</v>
+        <v>92218</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5989,45 +5999,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>580813</v>
+        <v>580715</v>
       </c>
       <c r="R51" t="n">
-        <v>6963779</v>
+        <v>6963743</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6056,7 +6058,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6066,12 +6068,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:04</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6098,32 +6095,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133550162</v>
+        <v>133552448</v>
       </c>
       <c r="B52" t="n">
-        <v>99140</v>
+        <v>91947</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6133,10 +6130,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>580728</v>
+        <v>580691</v>
       </c>
       <c r="R52" t="n">
-        <v>6963787</v>
+        <v>6963879</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6168,7 +6165,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6178,12 +6175,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:34</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>50 ex</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6210,48 +6202,56 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133550147</v>
+        <v>133552508</v>
       </c>
       <c r="B53" t="n">
-        <v>99140</v>
+        <v>57965</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>580689</v>
+        <v>580813</v>
       </c>
       <c r="R53" t="n">
-        <v>6963814</v>
+        <v>6963779</v>
       </c>
       <c r="S53" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6290,12 +6290,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>70 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6325,7 +6325,7 @@
         <v>133552490</v>
       </c>
       <c r="B54" t="n">
-        <v>80439</v>
+        <v>80453</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6429,10 +6429,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133552482</v>
+        <v>133552503</v>
       </c>
       <c r="B55" t="n">
-        <v>83319</v>
+        <v>89328</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6440,21 +6440,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6464,10 +6464,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>580879</v>
+        <v>580844</v>
       </c>
       <c r="R55" t="n">
-        <v>6963658</v>
+        <v>6963844</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6499,7 +6499,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6539,7 +6539,7 @@
         <v>133552486</v>
       </c>
       <c r="B56" t="n">
-        <v>83319</v>
+        <v>83333</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>133550143</v>
       </c>
       <c r="B57" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6753,7 +6753,7 @@
         <v>133552458</v>
       </c>
       <c r="B58" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
         <v>133552450</v>
       </c>
       <c r="B59" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>133552473</v>
       </c>
       <c r="B60" t="n">
-        <v>80439</v>
+        <v>80453</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7071,10 +7071,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133552466</v>
+        <v>133552485</v>
       </c>
       <c r="B61" t="n">
-        <v>83319</v>
+        <v>79348</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7082,21 +7082,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7106,13 +7106,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>580746</v>
+        <v>580999</v>
       </c>
       <c r="R61" t="n">
-        <v>6963790</v>
+        <v>6963688</v>
       </c>
       <c r="S61" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7178,10 +7178,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133552485</v>
+        <v>133552466</v>
       </c>
       <c r="B62" t="n">
-        <v>79334</v>
+        <v>83333</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7189,21 +7189,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7213,13 +7213,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>580999</v>
+        <v>580746</v>
       </c>
       <c r="R62" t="n">
-        <v>6963688</v>
+        <v>6963790</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7285,32 +7285,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133550170</v>
+        <v>133550133</v>
       </c>
       <c r="B63" t="n">
-        <v>79366</v>
+        <v>99168</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7320,10 +7320,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>580801</v>
+        <v>580685</v>
       </c>
       <c r="R63" t="n">
-        <v>6963652</v>
+        <v>6963865</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7365,7 +7365,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7392,10 +7397,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133550133</v>
+        <v>133550134</v>
       </c>
       <c r="B64" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7427,10 +7432,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>580685</v>
+        <v>580691</v>
       </c>
       <c r="R64" t="n">
-        <v>6963865</v>
+        <v>6963863</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7462,7 +7467,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7472,12 +7477,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>100 ex</t>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7504,32 +7509,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133550134</v>
+        <v>133552507</v>
       </c>
       <c r="B65" t="n">
-        <v>99140</v>
+        <v>80413</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7539,13 +7544,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>580691</v>
+        <v>580830</v>
       </c>
       <c r="R65" t="n">
-        <v>6963863</v>
+        <v>6963821</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7574,7 +7579,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7584,12 +7589,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>200 ex</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7616,32 +7616,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133552507</v>
+        <v>133550170</v>
       </c>
       <c r="B66" t="n">
-        <v>80399</v>
+        <v>79380</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229497</v>
+        <v>185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7651,13 +7651,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>580830</v>
+        <v>580801</v>
       </c>
       <c r="R66" t="n">
-        <v>6963821</v>
+        <v>6963652</v>
       </c>
       <c r="S66" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7726,7 +7726,7 @@
         <v>133550172</v>
       </c>
       <c r="B67" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>133552484</v>
       </c>
       <c r="B68" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7937,10 +7937,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133550144</v>
+        <v>133552460</v>
       </c>
       <c r="B69" t="n">
-        <v>91928</v>
+        <v>83333</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7948,21 +7948,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7972,10 +7972,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>580699</v>
+        <v>580722</v>
       </c>
       <c r="R69" t="n">
-        <v>6963819</v>
+        <v>6963787</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8007,7 +8007,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8044,10 +8044,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133552460</v>
+        <v>133552506</v>
       </c>
       <c r="B70" t="n">
-        <v>83319</v>
+        <v>57965</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8055,34 +8055,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>580722</v>
+        <v>580826</v>
       </c>
       <c r="R70" t="n">
-        <v>6963787</v>
+        <v>6963830</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8114,7 +8122,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8124,7 +8132,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8151,10 +8164,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133552506</v>
+        <v>133550144</v>
       </c>
       <c r="B71" t="n">
-        <v>57958</v>
+        <v>91947</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8162,42 +8175,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>580826</v>
+        <v>580699</v>
       </c>
       <c r="R71" t="n">
-        <v>6963830</v>
+        <v>6963819</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8229,7 +8234,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8239,12 +8244,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8271,10 +8271,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133550149</v>
+        <v>133550139</v>
       </c>
       <c r="B72" t="n">
-        <v>79334</v>
+        <v>80453</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8282,21 +8282,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8306,13 +8306,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>580697</v>
+        <v>580689</v>
       </c>
       <c r="R72" t="n">
-        <v>6963788</v>
+        <v>6963841</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8351,7 +8351,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8378,10 +8383,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133552454</v>
+        <v>133550149</v>
       </c>
       <c r="B73" t="n">
-        <v>91928</v>
+        <v>79348</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8389,21 +8394,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8413,13 +8418,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>580734</v>
+        <v>580697</v>
       </c>
       <c r="R73" t="n">
-        <v>6963814</v>
+        <v>6963788</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8448,7 +8453,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8458,7 +8463,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8485,10 +8490,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133550139</v>
+        <v>133552454</v>
       </c>
       <c r="B74" t="n">
-        <v>80439</v>
+        <v>91947</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8496,21 +8501,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8520,10 +8525,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>580689</v>
+        <v>580734</v>
       </c>
       <c r="R74" t="n">
-        <v>6963841</v>
+        <v>6963814</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8555,7 +8560,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8565,12 +8570,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:19</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8600,7 +8600,7 @@
         <v>133552487</v>
       </c>
       <c r="B75" t="n">
-        <v>89310</v>
+        <v>89328</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>133550186</v>
       </c>
       <c r="B76" t="n">
-        <v>89310</v>
+        <v>89328</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8811,10 +8811,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133552513</v>
+        <v>133550179</v>
       </c>
       <c r="B77" t="n">
-        <v>83311</v>
+        <v>91947</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8822,21 +8822,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8846,13 +8846,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>580785</v>
+        <v>580862</v>
       </c>
       <c r="R77" t="n">
-        <v>6963796</v>
+        <v>6963713</v>
       </c>
       <c r="S77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8918,10 +8918,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133552462</v>
+        <v>133552513</v>
       </c>
       <c r="B78" t="n">
-        <v>83311</v>
+        <v>83325</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8953,13 +8953,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>580738</v>
+        <v>580785</v>
       </c>
       <c r="R78" t="n">
-        <v>6963776</v>
+        <v>6963796</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9025,10 +9025,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133550179</v>
+        <v>133552499</v>
       </c>
       <c r="B79" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9060,10 +9060,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>580862</v>
+        <v>580926</v>
       </c>
       <c r="R79" t="n">
-        <v>6963713</v>
+        <v>6963805</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9095,7 +9095,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9105,7 +9105,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9132,10 +9132,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133552499</v>
+        <v>133552462</v>
       </c>
       <c r="B80" t="n">
-        <v>91928</v>
+        <v>83325</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9143,21 +9143,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9167,10 +9167,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>580926</v>
+        <v>580738</v>
       </c>
       <c r="R80" t="n">
-        <v>6963805</v>
+        <v>6963776</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9242,7 +9242,7 @@
         <v>133550173</v>
       </c>
       <c r="B81" t="n">
-        <v>80439</v>
+        <v>80453</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         <v>133550141</v>
       </c>
       <c r="B82" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9458,32 +9458,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>133552467</v>
+        <v>133552469</v>
       </c>
       <c r="B83" t="n">
-        <v>92651</v>
+        <v>79348</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9493,13 +9493,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>580754</v>
+        <v>580751</v>
       </c>
       <c r="R83" t="n">
-        <v>6963789</v>
+        <v>6963778</v>
       </c>
       <c r="S83" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9538,7 +9538,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9565,10 +9565,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133552505</v>
+        <v>133550165</v>
       </c>
       <c r="B84" t="n">
-        <v>79334</v>
+        <v>57143</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9576,37 +9576,49 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>580836</v>
+        <v>580753</v>
       </c>
       <c r="R84" t="n">
-        <v>6963844</v>
+        <v>6963702</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9635,7 +9647,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9645,7 +9657,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9672,10 +9684,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133552469</v>
+        <v>133552476</v>
       </c>
       <c r="B85" t="n">
-        <v>79334</v>
+        <v>80453</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9683,21 +9695,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9707,10 +9719,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>580751</v>
+        <v>580767</v>
       </c>
       <c r="R85" t="n">
-        <v>6963778</v>
+        <v>6963639</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9742,7 +9754,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9752,7 +9764,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9779,10 +9791,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133552476</v>
+        <v>133552463</v>
       </c>
       <c r="B86" t="n">
-        <v>80439</v>
+        <v>80453</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9814,10 +9826,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>580767</v>
+        <v>580725</v>
       </c>
       <c r="R86" t="n">
-        <v>6963639</v>
+        <v>6963773</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9849,7 +9861,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9859,7 +9871,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9886,32 +9898,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133552463</v>
+        <v>133550140</v>
       </c>
       <c r="B87" t="n">
-        <v>80439</v>
+        <v>99168</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9921,10 +9933,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>580725</v>
+        <v>580694</v>
       </c>
       <c r="R87" t="n">
-        <v>6963773</v>
+        <v>6963839</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9956,7 +9968,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9966,7 +9978,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>33 ex</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9993,60 +10010,48 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133550165</v>
+        <v>133552467</v>
       </c>
       <c r="B88" t="n">
-        <v>57136</v>
+        <v>92172</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>102612</v>
+        <v>3298</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>580753</v>
+        <v>580754</v>
       </c>
       <c r="R88" t="n">
-        <v>6963702</v>
+        <v>6963789</v>
       </c>
       <c r="S88" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10075,7 +10080,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10085,7 +10090,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10112,32 +10117,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133550140</v>
+        <v>133552505</v>
       </c>
       <c r="B89" t="n">
-        <v>99140</v>
+        <v>79348</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10147,10 +10152,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>580694</v>
+        <v>580836</v>
       </c>
       <c r="R89" t="n">
-        <v>6963839</v>
+        <v>6963844</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10182,7 +10187,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10192,12 +10197,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>33 ex</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10227,7 +10227,7 @@
         <v>133552510</v>
       </c>
       <c r="B90" t="n">
-        <v>83319</v>
+        <v>83333</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         <v>133552471</v>
       </c>
       <c r="B91" t="n">
-        <v>83319</v>
+        <v>83333</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10438,32 +10438,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133552493</v>
+        <v>133552512</v>
       </c>
       <c r="B92" t="n">
-        <v>89310</v>
+        <v>99168</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10473,10 +10473,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>580914</v>
+        <v>580803</v>
       </c>
       <c r="R92" t="n">
-        <v>6963757</v>
+        <v>6963894</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10508,7 +10508,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10518,7 +10518,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>150 + ex</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10545,32 +10550,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133550193</v>
+        <v>133552493</v>
       </c>
       <c r="B93" t="n">
-        <v>99140</v>
+        <v>89328</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10580,10 +10585,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>580781</v>
+        <v>580914</v>
       </c>
       <c r="R93" t="n">
-        <v>6963825</v>
+        <v>6963757</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10615,7 +10620,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10625,12 +10630,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>16:41</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Ca 60 ex</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10657,10 +10657,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133552455</v>
+        <v>133550193</v>
       </c>
       <c r="B94" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10692,10 +10692,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>580733</v>
+        <v>580781</v>
       </c>
       <c r="R94" t="n">
-        <v>6963814</v>
+        <v>6963825</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10727,7 +10727,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>200 ex</t>
+          <t>Ca 60 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10769,10 +10769,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133552512</v>
+        <v>133552455</v>
       </c>
       <c r="B95" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10804,10 +10804,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>580803</v>
+        <v>580733</v>
       </c>
       <c r="R95" t="n">
-        <v>6963894</v>
+        <v>6963814</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10839,7 +10839,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10849,12 +10849,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>150 + ex</t>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10881,32 +10881,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133550146</v>
+        <v>133550152</v>
       </c>
       <c r="B96" t="n">
-        <v>79334</v>
+        <v>98033</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10916,13 +10916,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>580687</v>
+        <v>580698</v>
       </c>
       <c r="R96" t="n">
-        <v>6963819</v>
+        <v>6963783</v>
       </c>
       <c r="S96" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10961,7 +10961,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10991,7 +10991,7 @@
         <v>133552501</v>
       </c>
       <c r="B97" t="n">
-        <v>89310</v>
+        <v>89328</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11095,10 +11095,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>133550187</v>
+        <v>133550146</v>
       </c>
       <c r="B98" t="n">
-        <v>57136</v>
+        <v>79348</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11106,46 +11106,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>580843</v>
+        <v>580687</v>
       </c>
       <c r="R98" t="n">
-        <v>6963778</v>
+        <v>6963819</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11177,7 +11165,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11187,7 +11175,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11214,48 +11202,60 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>133550152</v>
+        <v>133550187</v>
       </c>
       <c r="B99" t="n">
-        <v>98005</v>
+        <v>57143</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221945</v>
+        <v>102612</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>580698</v>
+        <v>580843</v>
       </c>
       <c r="R99" t="n">
-        <v>6963783</v>
+        <v>6963778</v>
       </c>
       <c r="S99" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11324,7 +11324,7 @@
         <v>133550161</v>
       </c>
       <c r="B100" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11428,48 +11428,56 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133552477</v>
+        <v>133552495</v>
       </c>
       <c r="B101" t="n">
-        <v>80468</v>
+        <v>57965</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>580764</v>
+        <v>580953</v>
       </c>
       <c r="R101" t="n">
-        <v>6963638</v>
+        <v>6963811</v>
       </c>
       <c r="S101" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11498,7 +11506,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11508,7 +11516,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Ett färskt ringhack på tall</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11535,56 +11548,48 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133552495</v>
+        <v>133552477</v>
       </c>
       <c r="B102" t="n">
-        <v>57958</v>
+        <v>80482</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>580953</v>
+        <v>580764</v>
       </c>
       <c r="R102" t="n">
-        <v>6963811</v>
+        <v>6963638</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11613,7 +11618,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11623,12 +11628,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Ett färskt ringhack på tall</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11655,10 +11655,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133550188</v>
+        <v>133550190</v>
       </c>
       <c r="B103" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11690,13 +11690,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>580833</v>
+        <v>580838</v>
       </c>
       <c r="R103" t="n">
-        <v>6963785</v>
+        <v>6963811</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11735,7 +11735,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11762,10 +11767,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133550158</v>
+        <v>133552500</v>
       </c>
       <c r="B104" t="n">
-        <v>79334</v>
+        <v>79380</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11773,21 +11778,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11797,13 +11802,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>580720</v>
+        <v>580902</v>
       </c>
       <c r="R104" t="n">
-        <v>6963787</v>
+        <v>6963823</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11832,7 +11837,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11842,7 +11847,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11869,10 +11874,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133550190</v>
+        <v>133550188</v>
       </c>
       <c r="B105" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11904,13 +11909,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>580838</v>
+        <v>580833</v>
       </c>
       <c r="R105" t="n">
-        <v>6963811</v>
+        <v>6963785</v>
       </c>
       <c r="S105" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11939,7 +11944,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11949,12 +11954,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11981,10 +11981,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133550177</v>
+        <v>133550158</v>
       </c>
       <c r="B106" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12016,13 +12016,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>580864</v>
+        <v>580720</v>
       </c>
       <c r="R106" t="n">
-        <v>6963715</v>
+        <v>6963787</v>
       </c>
       <c r="S106" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12051,7 +12051,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12061,7 +12061,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12088,10 +12088,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133552500</v>
+        <v>133552465</v>
       </c>
       <c r="B107" t="n">
-        <v>79366</v>
+        <v>57965</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12099,37 +12099,45 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>580902</v>
+        <v>580724</v>
       </c>
       <c r="R107" t="n">
-        <v>6963823</v>
+        <v>6963746</v>
       </c>
       <c r="S107" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12158,7 +12166,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12168,7 +12176,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12195,10 +12208,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>133552465</v>
+        <v>133550177</v>
       </c>
       <c r="B108" t="n">
-        <v>57958</v>
+        <v>79348</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12206,42 +12219,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>580724</v>
+        <v>580864</v>
       </c>
       <c r="R108" t="n">
-        <v>6963746</v>
+        <v>6963715</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12273,7 +12278,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12283,12 +12288,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD108" t="b">

--- a/artfynd/A 21339-2024 artfynd.xlsx
+++ b/artfynd/A 21339-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133552483</v>
+        <v>133550168</v>
       </c>
       <c r="B3" t="n">
-        <v>89328</v>
+        <v>83197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580906</v>
+        <v>580801</v>
       </c>
       <c r="R3" t="n">
-        <v>6963679</v>
+        <v>6963652</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133550175</v>
+        <v>133552449</v>
       </c>
       <c r="B4" t="n">
-        <v>79348</v>
+        <v>91947</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580879</v>
+        <v>580689</v>
       </c>
       <c r="R4" t="n">
-        <v>6963696</v>
+        <v>6963874</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133550168</v>
+        <v>133552511</v>
       </c>
       <c r="B5" t="n">
-        <v>83197</v>
+        <v>79380</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580801</v>
+        <v>580865</v>
       </c>
       <c r="R5" t="n">
-        <v>6963652</v>
+        <v>6963889</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133552481</v>
+        <v>133550175</v>
       </c>
       <c r="B6" t="n">
-        <v>89328</v>
+        <v>79348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580869</v>
+        <v>580879</v>
       </c>
       <c r="R6" t="n">
-        <v>6963663</v>
+        <v>6963696</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133552511</v>
+        <v>133552483</v>
       </c>
       <c r="B7" t="n">
-        <v>79380</v>
+        <v>89328</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>510</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580865</v>
+        <v>580906</v>
       </c>
       <c r="R7" t="n">
-        <v>6963889</v>
+        <v>6963679</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133552449</v>
+        <v>133552481</v>
       </c>
       <c r="B8" t="n">
-        <v>91947</v>
+        <v>89328</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580689</v>
+        <v>580869</v>
       </c>
       <c r="R8" t="n">
-        <v>6963874</v>
+        <v>6963663</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133550155</v>
+        <v>133550153</v>
       </c>
       <c r="B9" t="n">
         <v>80453</v>
@@ -1459,13 +1459,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580715</v>
+        <v>580704</v>
       </c>
       <c r="R9" t="n">
-        <v>6963791</v>
+        <v>6963785</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>Stora fina exemplar av lunglav, handflata storlek.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133550154</v>
+        <v>133550157</v>
       </c>
       <c r="B10" t="n">
         <v>99168</v>
@@ -1571,13 +1571,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580712</v>
+        <v>580715</v>
       </c>
       <c r="R10" t="n">
-        <v>6963788</v>
+        <v>6963786</v>
       </c>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>70 ex</t>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,32 +1648,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133550157</v>
+        <v>133552475</v>
       </c>
       <c r="B11" t="n">
-        <v>99168</v>
+        <v>79348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1683,13 +1683,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580715</v>
+        <v>580801</v>
       </c>
       <c r="R11" t="n">
-        <v>6963786</v>
+        <v>6963655</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,12 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>150 ex</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,32 +1755,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133550153</v>
+        <v>133550154</v>
       </c>
       <c r="B12" t="n">
-        <v>80453</v>
+        <v>99168</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,13 +1790,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580704</v>
+        <v>580712</v>
       </c>
       <c r="R12" t="n">
-        <v>6963785</v>
+        <v>6963788</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1830,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1840,12 +1835,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Stora fina exemplar av lunglav, handflata storlek.</t>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,32 +1867,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133552468</v>
+        <v>133550155</v>
       </c>
       <c r="B13" t="n">
-        <v>98033</v>
+        <v>80453</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,13 +1902,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580758</v>
+        <v>580715</v>
       </c>
       <c r="R13" t="n">
-        <v>6963787</v>
+        <v>6963791</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1942,7 +1937,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1952,7 +1947,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1979,32 +1979,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133552461</v>
+        <v>133552452</v>
       </c>
       <c r="B14" t="n">
-        <v>83316</v>
+        <v>83333</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6439</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,13 +2014,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580740</v>
+        <v>580698</v>
       </c>
       <c r="R14" t="n">
-        <v>6963795</v>
+        <v>6963860</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133552452</v>
+        <v>133550174</v>
       </c>
       <c r="B15" t="n">
-        <v>83333</v>
+        <v>79348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,21 +2097,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2121,13 +2121,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580698</v>
+        <v>580879</v>
       </c>
       <c r="R15" t="n">
-        <v>6963860</v>
+        <v>6963690</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,32 +2193,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133552456</v>
+        <v>133552461</v>
       </c>
       <c r="B16" t="n">
-        <v>91947</v>
+        <v>83316</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6439</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580695</v>
+        <v>580740</v>
       </c>
       <c r="R16" t="n">
-        <v>6963806</v>
+        <v>6963795</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,32 +2300,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133550174</v>
+        <v>133552468</v>
       </c>
       <c r="B17" t="n">
-        <v>79348</v>
+        <v>98033</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580879</v>
+        <v>580758</v>
       </c>
       <c r="R17" t="n">
-        <v>6963690</v>
+        <v>6963787</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133552475</v>
+        <v>133552456</v>
       </c>
       <c r="B18" t="n">
-        <v>79348</v>
+        <v>91947</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2418,21 +2418,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580801</v>
+        <v>580695</v>
       </c>
       <c r="R18" t="n">
-        <v>6963655</v>
+        <v>6963806</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2835,32 +2835,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133550184</v>
+        <v>133552451</v>
       </c>
       <c r="B22" t="n">
-        <v>99168</v>
+        <v>91910</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580867</v>
+        <v>580669</v>
       </c>
       <c r="R22" t="n">
-        <v>6963739</v>
+        <v>6963873</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2915,12 +2915,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>36 ex</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2947,10 +2942,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133552457</v>
+        <v>133550171</v>
       </c>
       <c r="B23" t="n">
-        <v>91947</v>
+        <v>80453</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2958,21 +2953,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2982,13 +2977,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580720</v>
+        <v>580857</v>
       </c>
       <c r="R23" t="n">
-        <v>6963788</v>
+        <v>6963688</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3017,7 +3012,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3027,7 +3022,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3054,10 +3049,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133550171</v>
+        <v>133552464</v>
       </c>
       <c r="B24" t="n">
-        <v>80453</v>
+        <v>91947</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3065,21 +3060,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3089,13 +3084,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580857</v>
+        <v>580720</v>
       </c>
       <c r="R24" t="n">
-        <v>6963688</v>
+        <v>6963748</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3124,7 +3119,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3134,7 +3129,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3161,7 +3156,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133552464</v>
+        <v>133552457</v>
       </c>
       <c r="B25" t="n">
         <v>91947</v>
@@ -3199,7 +3194,7 @@
         <v>580720</v>
       </c>
       <c r="R25" t="n">
-        <v>6963748</v>
+        <v>6963788</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3231,7 +3226,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3241,7 +3236,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3268,32 +3263,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133552451</v>
+        <v>133550184</v>
       </c>
       <c r="B26" t="n">
-        <v>91910</v>
+        <v>99168</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3303,10 +3298,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580669</v>
+        <v>580867</v>
       </c>
       <c r="R26" t="n">
-        <v>6963873</v>
+        <v>6963739</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3338,7 +3333,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3348,7 +3343,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>36 ex</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3375,7 +3375,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133550185</v>
+        <v>133550156</v>
       </c>
       <c r="B27" t="n">
         <v>79348</v>
@@ -3410,13 +3410,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580867</v>
+        <v>580715</v>
       </c>
       <c r="R27" t="n">
-        <v>6963739</v>
+        <v>6963791</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3696,10 +3696,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133550156</v>
+        <v>133552447</v>
       </c>
       <c r="B30" t="n">
-        <v>79348</v>
+        <v>79380</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3731,13 +3731,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580715</v>
+        <v>580697</v>
       </c>
       <c r="R30" t="n">
-        <v>6963791</v>
+        <v>6963889</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3803,10 +3803,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133552447</v>
+        <v>133550185</v>
       </c>
       <c r="B31" t="n">
-        <v>79380</v>
+        <v>79348</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3814,21 +3814,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3838,13 +3838,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>580697</v>
+        <v>580867</v>
       </c>
       <c r="R31" t="n">
-        <v>6963889</v>
+        <v>6963739</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4142,10 +4142,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133552488</v>
+        <v>133550138</v>
       </c>
       <c r="B34" t="n">
-        <v>89328</v>
+        <v>79348</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4153,21 +4153,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4177,10 +4177,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>580943</v>
+        <v>580712</v>
       </c>
       <c r="R34" t="n">
-        <v>6963738</v>
+        <v>6963853</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4212,7 +4212,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4222,7 +4222,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4249,32 +4249,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133552502</v>
+        <v>133552488</v>
       </c>
       <c r="B35" t="n">
-        <v>80357</v>
+        <v>89328</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6456</v>
+        <v>510</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4284,10 +4284,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>580865</v>
+        <v>580943</v>
       </c>
       <c r="R35" t="n">
-        <v>6963830</v>
+        <v>6963738</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4329,7 +4329,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4356,32 +4356,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133550138</v>
+        <v>133552502</v>
       </c>
       <c r="B36" t="n">
-        <v>79348</v>
+        <v>80357</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4391,10 +4391,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>580712</v>
+        <v>580865</v>
       </c>
       <c r="R36" t="n">
-        <v>6963853</v>
+        <v>6963830</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4570,32 +4570,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133550136</v>
+        <v>133552497</v>
       </c>
       <c r="B38" t="n">
-        <v>99168</v>
+        <v>79105</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4605,10 +4605,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>580702</v>
+        <v>580939</v>
       </c>
       <c r="R38" t="n">
-        <v>6963851</v>
+        <v>6963799</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4650,12 +4650,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>150 ex</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4682,32 +4677,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133552497</v>
+        <v>133550136</v>
       </c>
       <c r="B39" t="n">
-        <v>79105</v>
+        <v>99168</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4717,10 +4712,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>580939</v>
+        <v>580702</v>
       </c>
       <c r="R39" t="n">
-        <v>6963799</v>
+        <v>6963851</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4752,7 +4747,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4762,7 +4757,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4789,27 +4789,27 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133552453</v>
+        <v>133552478</v>
       </c>
       <c r="B40" t="n">
-        <v>79348</v>
+        <v>80488</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>580737</v>
+        <v>580763</v>
       </c>
       <c r="R40" t="n">
-        <v>6963844</v>
+        <v>6963637</v>
       </c>
       <c r="S40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4896,10 +4896,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133550182</v>
+        <v>133552494</v>
       </c>
       <c r="B41" t="n">
-        <v>79348</v>
+        <v>79380</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4907,21 +4907,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4931,10 +4931,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>580856</v>
+        <v>580955</v>
       </c>
       <c r="R41" t="n">
-        <v>6963747</v>
+        <v>6963798</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5003,27 +5003,27 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133552478</v>
+        <v>133550182</v>
       </c>
       <c r="B42" t="n">
-        <v>80488</v>
+        <v>79348</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5038,10 +5038,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>580763</v>
+        <v>580856</v>
       </c>
       <c r="R42" t="n">
-        <v>6963637</v>
+        <v>6963747</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5073,7 +5073,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5110,10 +5110,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133552494</v>
+        <v>133550132</v>
       </c>
       <c r="B43" t="n">
-        <v>79380</v>
+        <v>79348</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5121,21 +5121,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5145,10 +5145,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580955</v>
+        <v>580695</v>
       </c>
       <c r="R43" t="n">
-        <v>6963798</v>
+        <v>6963885</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5336,7 +5336,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133550176</v>
+        <v>133552453</v>
       </c>
       <c r="B45" t="n">
         <v>79348</v>
@@ -5371,13 +5371,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580874</v>
+        <v>580737</v>
       </c>
       <c r="R45" t="n">
-        <v>6963718</v>
+        <v>6963844</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5443,7 +5443,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133550132</v>
+        <v>133550176</v>
       </c>
       <c r="B46" t="n">
         <v>79348</v>
@@ -5478,10 +5478,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>580695</v>
+        <v>580874</v>
       </c>
       <c r="R46" t="n">
-        <v>6963885</v>
+        <v>6963718</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5550,7 +5550,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133550162</v>
+        <v>133550147</v>
       </c>
       <c r="B47" t="n">
         <v>99168</v>
@@ -5585,13 +5585,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>580728</v>
+        <v>580689</v>
       </c>
       <c r="R47" t="n">
-        <v>6963787</v>
+        <v>6963814</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5630,12 +5630,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>50 ex</t>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5662,32 +5662,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133550147</v>
+        <v>133552482</v>
       </c>
       <c r="B48" t="n">
-        <v>99168</v>
+        <v>83333</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5697,13 +5697,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>580689</v>
+        <v>580879</v>
       </c>
       <c r="R48" t="n">
-        <v>6963814</v>
+        <v>6963658</v>
       </c>
       <c r="S48" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5742,12 +5742,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>70 ex</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5774,32 +5769,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133552482</v>
+        <v>133550162</v>
       </c>
       <c r="B49" t="n">
-        <v>83333</v>
+        <v>99168</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5809,10 +5804,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>580879</v>
+        <v>580728</v>
       </c>
       <c r="R49" t="n">
-        <v>6963658</v>
+        <v>6963787</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5844,7 +5839,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5854,7 +5849,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5881,10 +5881,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133552491</v>
+        <v>133550160</v>
       </c>
       <c r="B50" t="n">
-        <v>79348</v>
+        <v>92218</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5892,21 +5892,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5916,13 +5916,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>580883</v>
+        <v>580715</v>
       </c>
       <c r="R50" t="n">
-        <v>6963753</v>
+        <v>6963743</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5988,10 +5988,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133550160</v>
+        <v>133552490</v>
       </c>
       <c r="B51" t="n">
-        <v>92218</v>
+        <v>80453</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5999,21 +5999,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6023,13 +6023,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>580715</v>
+        <v>580853</v>
       </c>
       <c r="R51" t="n">
-        <v>6963743</v>
+        <v>6963702</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6095,10 +6095,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133552448</v>
+        <v>133552508</v>
       </c>
       <c r="B52" t="n">
-        <v>91947</v>
+        <v>57965</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6106,34 +6106,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>580691</v>
+        <v>580813</v>
       </c>
       <c r="R52" t="n">
-        <v>6963879</v>
+        <v>6963779</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6165,7 +6173,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6175,7 +6183,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6202,10 +6215,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133552508</v>
+        <v>133552448</v>
       </c>
       <c r="B53" t="n">
-        <v>57965</v>
+        <v>91947</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6213,42 +6226,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>580813</v>
+        <v>580691</v>
       </c>
       <c r="R53" t="n">
-        <v>6963779</v>
+        <v>6963879</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6280,7 +6285,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6290,12 +6295,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:04</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6322,10 +6322,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133552490</v>
+        <v>133552486</v>
       </c>
       <c r="B54" t="n">
-        <v>80453</v>
+        <v>83333</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6333,21 +6333,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6357,10 +6357,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>580853</v>
+        <v>580985</v>
       </c>
       <c r="R54" t="n">
-        <v>6963702</v>
+        <v>6963707</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6392,7 +6392,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6536,10 +6536,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133552486</v>
+        <v>133552491</v>
       </c>
       <c r="B56" t="n">
-        <v>83333</v>
+        <v>79348</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6547,21 +6547,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6571,10 +6571,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>580985</v>
+        <v>580883</v>
       </c>
       <c r="R56" t="n">
-        <v>6963707</v>
+        <v>6963753</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6750,10 +6750,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133552458</v>
+        <v>133552473</v>
       </c>
       <c r="B58" t="n">
-        <v>79348</v>
+        <v>80453</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6761,21 +6761,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6785,10 +6785,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>580716</v>
+        <v>580754</v>
       </c>
       <c r="R58" t="n">
-        <v>6963787</v>
+        <v>6963659</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6964,10 +6964,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133552473</v>
+        <v>133552458</v>
       </c>
       <c r="B60" t="n">
-        <v>80453</v>
+        <v>79348</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6975,21 +6975,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6999,10 +6999,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>580754</v>
+        <v>580716</v>
       </c>
       <c r="R60" t="n">
-        <v>6963659</v>
+        <v>6963787</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7071,10 +7071,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133552485</v>
+        <v>133552466</v>
       </c>
       <c r="B61" t="n">
-        <v>79348</v>
+        <v>83333</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7082,21 +7082,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7106,13 +7106,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>580999</v>
+        <v>580746</v>
       </c>
       <c r="R61" t="n">
-        <v>6963688</v>
+        <v>6963790</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7178,10 +7178,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133552466</v>
+        <v>133552485</v>
       </c>
       <c r="B62" t="n">
-        <v>83333</v>
+        <v>79348</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7189,21 +7189,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7213,13 +7213,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>580746</v>
+        <v>580999</v>
       </c>
       <c r="R62" t="n">
-        <v>6963790</v>
+        <v>6963688</v>
       </c>
       <c r="S62" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7285,32 +7285,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133550133</v>
+        <v>133550170</v>
       </c>
       <c r="B63" t="n">
-        <v>99168</v>
+        <v>79380</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7320,10 +7320,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>580685</v>
+        <v>580801</v>
       </c>
       <c r="R63" t="n">
-        <v>6963865</v>
+        <v>6963652</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7365,12 +7365,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>100 ex</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7397,32 +7392,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133550134</v>
+        <v>133552507</v>
       </c>
       <c r="B64" t="n">
-        <v>99168</v>
+        <v>80413</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7432,13 +7427,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>580691</v>
+        <v>580830</v>
       </c>
       <c r="R64" t="n">
-        <v>6963863</v>
+        <v>6963821</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7467,7 +7462,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7477,12 +7472,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>200 ex</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7509,32 +7499,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133552507</v>
+        <v>133550133</v>
       </c>
       <c r="B65" t="n">
-        <v>80413</v>
+        <v>99168</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7544,13 +7534,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>580830</v>
+        <v>580685</v>
       </c>
       <c r="R65" t="n">
-        <v>6963821</v>
+        <v>6963865</v>
       </c>
       <c r="S65" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7579,7 +7569,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7589,7 +7579,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7616,32 +7611,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133550170</v>
+        <v>133550134</v>
       </c>
       <c r="B66" t="n">
-        <v>79380</v>
+        <v>99168</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7651,10 +7646,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>580801</v>
+        <v>580691</v>
       </c>
       <c r="R66" t="n">
-        <v>6963652</v>
+        <v>6963863</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7686,7 +7681,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7696,7 +7691,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7723,7 +7723,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133550172</v>
+        <v>133550144</v>
       </c>
       <c r="B67" t="n">
         <v>91947</v>
@@ -7758,10 +7758,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>580870</v>
+        <v>580699</v>
       </c>
       <c r="R67" t="n">
-        <v>6963663</v>
+        <v>6963819</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7830,10 +7830,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133552484</v>
+        <v>133552460</v>
       </c>
       <c r="B68" t="n">
-        <v>79348</v>
+        <v>83333</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7841,21 +7841,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7865,10 +7865,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>580938</v>
+        <v>580722</v>
       </c>
       <c r="R68" t="n">
-        <v>6963702</v>
+        <v>6963787</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7900,7 +7900,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7937,10 +7937,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133552460</v>
+        <v>133552506</v>
       </c>
       <c r="B69" t="n">
-        <v>83333</v>
+        <v>57965</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7948,34 +7948,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>580722</v>
+        <v>580826</v>
       </c>
       <c r="R69" t="n">
-        <v>6963787</v>
+        <v>6963830</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8007,7 +8015,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8017,7 +8025,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8044,10 +8057,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133552506</v>
+        <v>133550172</v>
       </c>
       <c r="B70" t="n">
-        <v>57965</v>
+        <v>91947</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8055,42 +8068,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>580826</v>
+        <v>580870</v>
       </c>
       <c r="R70" t="n">
-        <v>6963830</v>
+        <v>6963663</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8122,7 +8127,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8132,12 +8137,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8164,10 +8164,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133550144</v>
+        <v>133552484</v>
       </c>
       <c r="B71" t="n">
-        <v>91947</v>
+        <v>79348</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8175,21 +8175,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8199,10 +8199,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>580699</v>
+        <v>580938</v>
       </c>
       <c r="R71" t="n">
-        <v>6963819</v>
+        <v>6963702</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8383,10 +8383,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133550149</v>
+        <v>133552454</v>
       </c>
       <c r="B73" t="n">
-        <v>79348</v>
+        <v>91947</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8394,21 +8394,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8418,13 +8418,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>580697</v>
+        <v>580734</v>
       </c>
       <c r="R73" t="n">
-        <v>6963788</v>
+        <v>6963814</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8490,10 +8490,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133552454</v>
+        <v>133550149</v>
       </c>
       <c r="B74" t="n">
-        <v>91947</v>
+        <v>79348</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8501,21 +8501,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8525,13 +8525,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>580734</v>
+        <v>580697</v>
       </c>
       <c r="R74" t="n">
-        <v>6963814</v>
+        <v>6963788</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8597,7 +8597,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133552487</v>
+        <v>133550186</v>
       </c>
       <c r="B75" t="n">
         <v>89328</v>
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>580983</v>
+        <v>580871</v>
       </c>
       <c r="R75" t="n">
-        <v>6963709</v>
+        <v>6963767</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8704,10 +8704,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133550186</v>
+        <v>133550179</v>
       </c>
       <c r="B76" t="n">
-        <v>89328</v>
+        <v>91947</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8715,21 +8715,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8739,13 +8739,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>580871</v>
+        <v>580862</v>
       </c>
       <c r="R76" t="n">
-        <v>6963767</v>
+        <v>6963713</v>
       </c>
       <c r="S76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8811,32 +8811,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133550179</v>
+        <v>133550141</v>
       </c>
       <c r="B77" t="n">
-        <v>91947</v>
+        <v>99168</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8846,10 +8846,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>580862</v>
+        <v>580713</v>
       </c>
       <c r="R77" t="n">
-        <v>6963713</v>
+        <v>6963840</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8881,7 +8881,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8891,7 +8891,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>60 ex, troligen fler</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8918,10 +8923,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133552513</v>
+        <v>133552499</v>
       </c>
       <c r="B78" t="n">
-        <v>83325</v>
+        <v>91947</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8929,21 +8934,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8953,13 +8958,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>580785</v>
+        <v>580926</v>
       </c>
       <c r="R78" t="n">
-        <v>6963796</v>
+        <v>6963805</v>
       </c>
       <c r="S78" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8988,7 +8993,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8998,7 +9003,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9025,10 +9030,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133552499</v>
+        <v>133552513</v>
       </c>
       <c r="B79" t="n">
-        <v>91947</v>
+        <v>83325</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9036,21 +9041,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9060,13 +9065,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>580926</v>
+        <v>580785</v>
       </c>
       <c r="R79" t="n">
-        <v>6963805</v>
+        <v>6963796</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9095,7 +9100,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9105,7 +9110,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9132,10 +9137,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133552462</v>
+        <v>133550173</v>
       </c>
       <c r="B80" t="n">
-        <v>83325</v>
+        <v>80453</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9143,21 +9148,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9167,13 +9172,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>580738</v>
+        <v>580878</v>
       </c>
       <c r="R80" t="n">
-        <v>6963776</v>
+        <v>6963692</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9202,7 +9207,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9212,7 +9217,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9239,10 +9244,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133550173</v>
+        <v>133552487</v>
       </c>
       <c r="B81" t="n">
-        <v>80453</v>
+        <v>89328</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9250,21 +9255,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9274,13 +9279,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>580878</v>
+        <v>580983</v>
       </c>
       <c r="R81" t="n">
-        <v>6963692</v>
+        <v>6963709</v>
       </c>
       <c r="S81" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9309,7 +9314,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9319,7 +9324,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9346,32 +9351,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133550141</v>
+        <v>133552462</v>
       </c>
       <c r="B82" t="n">
-        <v>99168</v>
+        <v>83325</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9381,10 +9386,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>580713</v>
+        <v>580738</v>
       </c>
       <c r="R82" t="n">
-        <v>6963840</v>
+        <v>6963776</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9416,7 +9421,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9426,12 +9431,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>60 ex, troligen fler</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9458,32 +9458,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>133552469</v>
+        <v>133550140</v>
       </c>
       <c r="B83" t="n">
-        <v>79348</v>
+        <v>99168</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>580751</v>
+        <v>580694</v>
       </c>
       <c r="R83" t="n">
-        <v>6963778</v>
+        <v>6963839</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9528,7 +9528,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9538,7 +9538,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>33 ex</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9565,10 +9570,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133550165</v>
+        <v>133552505</v>
       </c>
       <c r="B84" t="n">
-        <v>57143</v>
+        <v>79348</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9576,49 +9581,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>580753</v>
+        <v>580836</v>
       </c>
       <c r="R84" t="n">
-        <v>6963702</v>
+        <v>6963844</v>
       </c>
       <c r="S84" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9647,7 +9640,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9657,7 +9650,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9791,10 +9784,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133552463</v>
+        <v>133550165</v>
       </c>
       <c r="B86" t="n">
-        <v>80453</v>
+        <v>57143</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9802,37 +9795,49 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>580725</v>
+        <v>580753</v>
       </c>
       <c r="R86" t="n">
-        <v>6963773</v>
+        <v>6963702</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9861,7 +9866,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9871,7 +9876,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9898,32 +9903,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133550140</v>
+        <v>133552469</v>
       </c>
       <c r="B87" t="n">
-        <v>99168</v>
+        <v>79348</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9933,10 +9938,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>580694</v>
+        <v>580751</v>
       </c>
       <c r="R87" t="n">
-        <v>6963839</v>
+        <v>6963778</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9968,7 +9973,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9978,12 +9983,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>33 ex</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10117,10 +10117,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133552505</v>
+        <v>133552463</v>
       </c>
       <c r="B89" t="n">
-        <v>79348</v>
+        <v>80453</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10128,21 +10128,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10152,10 +10152,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>580836</v>
+        <v>580725</v>
       </c>
       <c r="R89" t="n">
-        <v>6963844</v>
+        <v>6963773</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10187,7 +10187,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10197,7 +10197,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10224,32 +10224,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133552510</v>
+        <v>133550193</v>
       </c>
       <c r="B90" t="n">
-        <v>83333</v>
+        <v>99168</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10259,10 +10259,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>580829</v>
+        <v>580781</v>
       </c>
       <c r="R90" t="n">
-        <v>6963885</v>
+        <v>6963825</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10294,7 +10294,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10304,7 +10304,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ca 60 ex</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10331,32 +10336,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133552471</v>
+        <v>133552512</v>
       </c>
       <c r="B91" t="n">
-        <v>83333</v>
+        <v>99168</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10366,10 +10371,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>580717</v>
+        <v>580803</v>
       </c>
       <c r="R91" t="n">
-        <v>6963694</v>
+        <v>6963894</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10401,7 +10406,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10411,7 +10416,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>150 + ex</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10438,7 +10448,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133552512</v>
+        <v>133552455</v>
       </c>
       <c r="B92" t="n">
         <v>99168</v>
@@ -10473,10 +10483,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>580803</v>
+        <v>580733</v>
       </c>
       <c r="R92" t="n">
-        <v>6963894</v>
+        <v>6963814</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10508,7 +10518,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10518,12 +10528,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>150 + ex</t>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10657,32 +10667,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133550193</v>
+        <v>133552471</v>
       </c>
       <c r="B94" t="n">
-        <v>99168</v>
+        <v>83333</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10692,10 +10702,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>580781</v>
+        <v>580717</v>
       </c>
       <c r="R94" t="n">
-        <v>6963825</v>
+        <v>6963694</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10727,7 +10737,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10737,12 +10747,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>16:41</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Ca 60 ex</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10769,32 +10774,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133552455</v>
+        <v>133552510</v>
       </c>
       <c r="B95" t="n">
-        <v>99168</v>
+        <v>83333</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10804,10 +10809,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>580733</v>
+        <v>580829</v>
       </c>
       <c r="R95" t="n">
-        <v>6963814</v>
+        <v>6963885</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10839,7 +10844,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10849,12 +10854,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>200 ex</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10881,32 +10881,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133550152</v>
+        <v>133552501</v>
       </c>
       <c r="B96" t="n">
-        <v>98033</v>
+        <v>89328</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221945</v>
+        <v>510</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10916,13 +10916,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>580698</v>
+        <v>580895</v>
       </c>
       <c r="R96" t="n">
-        <v>6963783</v>
+        <v>6963822</v>
       </c>
       <c r="S96" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10961,7 +10961,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10988,10 +10988,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>133552501</v>
+        <v>133550146</v>
       </c>
       <c r="B97" t="n">
-        <v>89328</v>
+        <v>79348</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10999,21 +10999,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11023,13 +11023,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>580895</v>
+        <v>580687</v>
       </c>
       <c r="R97" t="n">
-        <v>6963822</v>
+        <v>6963819</v>
       </c>
       <c r="S97" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11068,7 +11068,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11095,32 +11095,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>133550146</v>
+        <v>133550152</v>
       </c>
       <c r="B98" t="n">
-        <v>79348</v>
+        <v>98033</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11130,13 +11130,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>580687</v>
+        <v>580698</v>
       </c>
       <c r="R98" t="n">
-        <v>6963819</v>
+        <v>6963783</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11175,7 +11175,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11321,32 +11321,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133550161</v>
+        <v>133552477</v>
       </c>
       <c r="B100" t="n">
-        <v>79348</v>
+        <v>80482</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11356,13 +11356,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>580727</v>
+        <v>580764</v>
       </c>
       <c r="R100" t="n">
-        <v>6963764</v>
+        <v>6963638</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11428,10 +11428,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133552495</v>
+        <v>133550161</v>
       </c>
       <c r="B101" t="n">
-        <v>57965</v>
+        <v>79348</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11439,45 +11439,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>580953</v>
+        <v>580727</v>
       </c>
       <c r="R101" t="n">
-        <v>6963811</v>
+        <v>6963764</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11506,7 +11498,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11516,12 +11508,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Ett färskt ringhack på tall</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11548,48 +11535,56 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133552477</v>
+        <v>133552495</v>
       </c>
       <c r="B102" t="n">
-        <v>80482</v>
+        <v>57965</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>580764</v>
+        <v>580953</v>
       </c>
       <c r="R102" t="n">
-        <v>6963638</v>
+        <v>6963811</v>
       </c>
       <c r="S102" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11618,7 +11613,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11628,7 +11623,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Ett färskt ringhack på tall</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11655,7 +11655,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133550190</v>
+        <v>133550177</v>
       </c>
       <c r="B103" t="n">
         <v>79348</v>
@@ -11690,10 +11690,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>580838</v>
+        <v>580864</v>
       </c>
       <c r="R103" t="n">
-        <v>6963811</v>
+        <v>6963715</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -11725,7 +11725,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11735,12 +11735,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11767,10 +11762,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133552500</v>
+        <v>133552465</v>
       </c>
       <c r="B104" t="n">
-        <v>79380</v>
+        <v>57965</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11778,37 +11773,45 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>580902</v>
+        <v>580724</v>
       </c>
       <c r="R104" t="n">
-        <v>6963823</v>
+        <v>6963746</v>
       </c>
       <c r="S104" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11837,7 +11840,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11847,7 +11850,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11874,7 +11882,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133550188</v>
+        <v>133550158</v>
       </c>
       <c r="B105" t="n">
         <v>79348</v>
@@ -11909,10 +11917,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>580833</v>
+        <v>580720</v>
       </c>
       <c r="R105" t="n">
-        <v>6963785</v>
+        <v>6963787</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11944,7 +11952,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11954,7 +11962,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11981,7 +11989,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133550158</v>
+        <v>133550188</v>
       </c>
       <c r="B106" t="n">
         <v>79348</v>
@@ -12016,10 +12024,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>580720</v>
+        <v>580833</v>
       </c>
       <c r="R106" t="n">
-        <v>6963787</v>
+        <v>6963785</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12051,7 +12059,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12061,7 +12069,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12088,10 +12096,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133552465</v>
+        <v>133550190</v>
       </c>
       <c r="B107" t="n">
-        <v>57965</v>
+        <v>79348</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12099,42 +12107,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>580724</v>
+        <v>580838</v>
       </c>
       <c r="R107" t="n">
-        <v>6963746</v>
+        <v>6963811</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12208,10 +12208,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>133550177</v>
+        <v>133552500</v>
       </c>
       <c r="B108" t="n">
-        <v>79348</v>
+        <v>79380</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12219,21 +12219,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12243,13 +12243,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>580864</v>
+        <v>580902</v>
       </c>
       <c r="R108" t="n">
-        <v>6963715</v>
+        <v>6963823</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12288,7 +12288,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD108" t="b">

--- a/artfynd/A 21339-2024 artfynd.xlsx
+++ b/artfynd/A 21339-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133550167</v>
       </c>
       <c r="B2" t="n">
-        <v>89328</v>
+        <v>89338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133550168</v>
+        <v>133552483</v>
       </c>
       <c r="B3" t="n">
-        <v>83197</v>
+        <v>89338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580801</v>
+        <v>580906</v>
       </c>
       <c r="R3" t="n">
-        <v>6963652</v>
+        <v>6963679</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +892,7 @@
         <v>133552449</v>
       </c>
       <c r="B4" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133552511</v>
+        <v>133550175</v>
       </c>
       <c r="B5" t="n">
-        <v>79380</v>
+        <v>79358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580865</v>
+        <v>580879</v>
       </c>
       <c r="R5" t="n">
-        <v>6963889</v>
+        <v>6963696</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133550175</v>
+        <v>133550168</v>
       </c>
       <c r="B6" t="n">
-        <v>79348</v>
+        <v>83207</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580879</v>
+        <v>580801</v>
       </c>
       <c r="R6" t="n">
-        <v>6963696</v>
+        <v>6963652</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133552483</v>
+        <v>133552481</v>
       </c>
       <c r="B7" t="n">
-        <v>89328</v>
+        <v>89338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580906</v>
+        <v>580869</v>
       </c>
       <c r="R7" t="n">
-        <v>6963679</v>
+        <v>6963663</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133552481</v>
+        <v>133552511</v>
       </c>
       <c r="B8" t="n">
-        <v>89328</v>
+        <v>79390</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>510</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580869</v>
+        <v>580865</v>
       </c>
       <c r="R8" t="n">
-        <v>6963663</v>
+        <v>6963889</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,32 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133550153</v>
+        <v>133552468</v>
       </c>
       <c r="B9" t="n">
-        <v>80453</v>
+        <v>98043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,13 +1459,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580704</v>
+        <v>580758</v>
       </c>
       <c r="R9" t="n">
-        <v>6963785</v>
+        <v>6963787</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,12 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Stora fina exemplar av lunglav, handflata storlek.</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,32 +1531,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133550157</v>
+        <v>133550155</v>
       </c>
       <c r="B10" t="n">
-        <v>99168</v>
+        <v>80473</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1574,10 +1569,10 @@
         <v>580715</v>
       </c>
       <c r="R10" t="n">
-        <v>6963786</v>
+        <v>6963791</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1606,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,12 +1611,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>150 ex</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,32 +1643,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133552475</v>
+        <v>133552461</v>
       </c>
       <c r="B11" t="n">
-        <v>79348</v>
+        <v>83326</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1683,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580801</v>
+        <v>580740</v>
       </c>
       <c r="R11" t="n">
-        <v>6963655</v>
+        <v>6963795</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1718,7 +1713,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1723,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1758,7 +1753,7 @@
         <v>133550154</v>
       </c>
       <c r="B12" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1867,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133550155</v>
+        <v>133552452</v>
       </c>
       <c r="B13" t="n">
-        <v>80453</v>
+        <v>83343</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1878,21 +1873,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1902,13 +1897,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580715</v>
+        <v>580698</v>
       </c>
       <c r="R13" t="n">
-        <v>6963791</v>
+        <v>6963860</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1937,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1947,12 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1979,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133552452</v>
+        <v>133552456</v>
       </c>
       <c r="B14" t="n">
-        <v>83333</v>
+        <v>91957</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1990,21 +1980,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,13 +2004,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580698</v>
+        <v>580695</v>
       </c>
       <c r="R14" t="n">
-        <v>6963860</v>
+        <v>6963806</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2049,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2059,7 +2049,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2089,7 +2079,7 @@
         <v>133550174</v>
       </c>
       <c r="B15" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2193,32 +2183,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133552461</v>
+        <v>133552475</v>
       </c>
       <c r="B16" t="n">
-        <v>83316</v>
+        <v>79358</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2228,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580740</v>
+        <v>580801</v>
       </c>
       <c r="R16" t="n">
-        <v>6963795</v>
+        <v>6963655</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2263,7 +2253,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2273,7 +2263,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,32 +2290,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133552468</v>
+        <v>133550157</v>
       </c>
       <c r="B17" t="n">
-        <v>98033</v>
+        <v>99178</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2335,13 +2325,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580758</v>
+        <v>580715</v>
       </c>
       <c r="R17" t="n">
-        <v>6963787</v>
+        <v>6963786</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2370,7 +2360,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2370,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,10 +2402,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133552456</v>
+        <v>133550153</v>
       </c>
       <c r="B18" t="n">
-        <v>91947</v>
+        <v>80473</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2418,21 +2413,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2442,13 +2437,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580695</v>
+        <v>580704</v>
       </c>
       <c r="R18" t="n">
-        <v>6963806</v>
+        <v>6963785</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2477,7 +2472,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2487,7 +2482,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Stora fina exemplar av lunglav, handflata storlek.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2517,7 +2517,7 @@
         <v>133550164</v>
       </c>
       <c r="B19" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>133552509</v>
       </c>
       <c r="B20" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>133552492</v>
       </c>
       <c r="B21" t="n">
-        <v>79106</v>
+        <v>79116</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2835,32 +2835,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133552451</v>
+        <v>133552457</v>
       </c>
       <c r="B22" t="n">
-        <v>91910</v>
+        <v>91957</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580669</v>
+        <v>580720</v>
       </c>
       <c r="R22" t="n">
-        <v>6963873</v>
+        <v>6963788</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2945,7 +2945,7 @@
         <v>133550171</v>
       </c>
       <c r="B23" t="n">
-        <v>80453</v>
+        <v>80473</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>133552464</v>
       </c>
       <c r="B24" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3156,32 +3156,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133552457</v>
+        <v>133552451</v>
       </c>
       <c r="B25" t="n">
-        <v>91947</v>
+        <v>91920</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3191,10 +3191,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580720</v>
+        <v>580669</v>
       </c>
       <c r="R25" t="n">
-        <v>6963788</v>
+        <v>6963873</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3266,7 +3266,7 @@
         <v>133550184</v>
       </c>
       <c r="B26" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>133550156</v>
       </c>
       <c r="B27" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3482,10 +3482,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133550191</v>
+        <v>133550185</v>
       </c>
       <c r="B28" t="n">
-        <v>92218</v>
+        <v>79358</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3493,21 +3493,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3517,13 +3517,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580787</v>
+        <v>580867</v>
       </c>
       <c r="R28" t="n">
-        <v>6963783</v>
+        <v>6963739</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3589,10 +3589,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133552472</v>
+        <v>133550191</v>
       </c>
       <c r="B29" t="n">
-        <v>91961</v>
+        <v>92228</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3600,21 +3600,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3624,10 +3624,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580713</v>
+        <v>580787</v>
       </c>
       <c r="R29" t="n">
-        <v>6963690</v>
+        <v>6963783</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3696,10 +3696,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133552447</v>
+        <v>133552472</v>
       </c>
       <c r="B30" t="n">
-        <v>79380</v>
+        <v>91971</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>1204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580697</v>
+        <v>580713</v>
       </c>
       <c r="R30" t="n">
-        <v>6963889</v>
+        <v>6963690</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3803,10 +3803,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133550185</v>
+        <v>133552447</v>
       </c>
       <c r="B31" t="n">
-        <v>79348</v>
+        <v>79390</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3814,21 +3814,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3838,13 +3838,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>580867</v>
+        <v>580697</v>
       </c>
       <c r="R31" t="n">
-        <v>6963739</v>
+        <v>6963889</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3910,32 +3910,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133550148</v>
+        <v>133552488</v>
       </c>
       <c r="B32" t="n">
-        <v>99168</v>
+        <v>89338</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3945,13 +3945,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>580696</v>
+        <v>580943</v>
       </c>
       <c r="R32" t="n">
-        <v>6963788</v>
+        <v>6963738</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3990,12 +3990,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:49</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>120 ex</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4022,56 +4017,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133550180</v>
+        <v>133552502</v>
       </c>
       <c r="B33" t="n">
-        <v>57965</v>
+        <v>80367</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>580876</v>
+        <v>580865</v>
       </c>
       <c r="R33" t="n">
-        <v>6963707</v>
+        <v>6963830</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4100,7 +4087,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4110,12 +4097,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:14</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4142,32 +4124,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133550138</v>
+        <v>133550148</v>
       </c>
       <c r="B34" t="n">
-        <v>79348</v>
+        <v>99178</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4177,13 +4159,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>580712</v>
+        <v>580696</v>
       </c>
       <c r="R34" t="n">
-        <v>6963853</v>
+        <v>6963788</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4212,7 +4194,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4222,7 +4204,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4249,10 +4236,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133552488</v>
+        <v>133550138</v>
       </c>
       <c r="B35" t="n">
-        <v>89328</v>
+        <v>79358</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4260,21 +4247,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4284,10 +4271,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>580943</v>
+        <v>580712</v>
       </c>
       <c r="R35" t="n">
-        <v>6963738</v>
+        <v>6963853</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4319,7 +4306,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4329,7 +4316,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4356,48 +4343,56 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133552502</v>
+        <v>133550180</v>
       </c>
       <c r="B36" t="n">
-        <v>80357</v>
+        <v>57975</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>580865</v>
+        <v>580876</v>
       </c>
       <c r="R36" t="n">
-        <v>6963830</v>
+        <v>6963707</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4426,7 +4421,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4436,7 +4431,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4466,7 +4466,7 @@
         <v>133550163</v>
       </c>
       <c r="B37" t="n">
-        <v>98033</v>
+        <v>98043</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>133552497</v>
       </c>
       <c r="B38" t="n">
-        <v>79105</v>
+        <v>79115</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4677,32 +4677,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133550136</v>
+        <v>133552453</v>
       </c>
       <c r="B39" t="n">
-        <v>99168</v>
+        <v>79358</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4712,13 +4712,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>580702</v>
+        <v>580737</v>
       </c>
       <c r="R39" t="n">
-        <v>6963851</v>
+        <v>6963844</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4757,12 +4757,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>150 ex</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4789,32 +4784,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133552478</v>
+        <v>133550136</v>
       </c>
       <c r="B40" t="n">
-        <v>80488</v>
+        <v>99178</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4824,10 +4819,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>580763</v>
+        <v>580702</v>
       </c>
       <c r="R40" t="n">
-        <v>6963637</v>
+        <v>6963851</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4859,7 +4854,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4869,7 +4864,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4896,10 +4896,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133552494</v>
+        <v>133550132</v>
       </c>
       <c r="B41" t="n">
-        <v>79380</v>
+        <v>79358</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4907,21 +4907,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4931,10 +4931,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>580955</v>
+        <v>580695</v>
       </c>
       <c r="R41" t="n">
-        <v>6963798</v>
+        <v>6963885</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5003,10 +5003,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133550182</v>
+        <v>133550176</v>
       </c>
       <c r="B42" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5038,10 +5038,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>580856</v>
+        <v>580874</v>
       </c>
       <c r="R42" t="n">
-        <v>6963747</v>
+        <v>6963718</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5073,7 +5073,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5110,10 +5110,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133550132</v>
+        <v>133550182</v>
       </c>
       <c r="B43" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5145,10 +5145,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580695</v>
+        <v>580856</v>
       </c>
       <c r="R43" t="n">
-        <v>6963885</v>
+        <v>6963747</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5217,60 +5217,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133550166</v>
+        <v>133552478</v>
       </c>
       <c r="B44" t="n">
-        <v>57143</v>
+        <v>80484</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>102612</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>580800</v>
+        <v>580763</v>
       </c>
       <c r="R44" t="n">
-        <v>6963652</v>
+        <v>6963637</v>
       </c>
       <c r="S44" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5299,7 +5287,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5309,7 +5297,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5336,10 +5324,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133552453</v>
+        <v>133552494</v>
       </c>
       <c r="B45" t="n">
-        <v>79348</v>
+        <v>79390</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5347,21 +5335,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5371,13 +5359,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580737</v>
+        <v>580955</v>
       </c>
       <c r="R45" t="n">
-        <v>6963844</v>
+        <v>6963798</v>
       </c>
       <c r="S45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5406,7 +5394,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5416,7 +5404,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5443,10 +5431,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133550176</v>
+        <v>133550166</v>
       </c>
       <c r="B46" t="n">
-        <v>79348</v>
+        <v>57153</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5454,37 +5442,49 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>580874</v>
+        <v>580800</v>
       </c>
       <c r="R46" t="n">
-        <v>6963718</v>
+        <v>6963652</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5550,10 +5550,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133550147</v>
+        <v>133550162</v>
       </c>
       <c r="B47" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5585,13 +5585,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>580689</v>
+        <v>580728</v>
       </c>
       <c r="R47" t="n">
-        <v>6963814</v>
+        <v>6963787</v>
       </c>
       <c r="S47" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5630,12 +5630,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>70 ex</t>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5662,10 +5662,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133552482</v>
+        <v>133552508</v>
       </c>
       <c r="B48" t="n">
-        <v>83333</v>
+        <v>57975</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5673,34 +5673,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>580879</v>
+        <v>580813</v>
       </c>
       <c r="R48" t="n">
-        <v>6963658</v>
+        <v>6963779</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5732,7 +5740,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5742,7 +5750,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5769,10 +5782,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133550162</v>
+        <v>133550147</v>
       </c>
       <c r="B49" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5804,13 +5817,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>580728</v>
+        <v>580689</v>
       </c>
       <c r="R49" t="n">
-        <v>6963787</v>
+        <v>6963814</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5839,7 +5852,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5849,12 +5862,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>50 ex</t>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5881,10 +5894,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133550160</v>
+        <v>133552490</v>
       </c>
       <c r="B50" t="n">
-        <v>92218</v>
+        <v>80473</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5892,21 +5905,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5916,13 +5929,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>580715</v>
+        <v>580853</v>
       </c>
       <c r="R50" t="n">
-        <v>6963743</v>
+        <v>6963702</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5951,7 +5964,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5961,7 +5974,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5988,10 +6001,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133552490</v>
+        <v>133552503</v>
       </c>
       <c r="B51" t="n">
-        <v>80453</v>
+        <v>89338</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5999,21 +6012,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6023,10 +6036,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>580853</v>
+        <v>580844</v>
       </c>
       <c r="R51" t="n">
-        <v>6963702</v>
+        <v>6963844</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6058,7 +6071,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6068,7 +6081,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6095,10 +6108,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133552508</v>
+        <v>133552491</v>
       </c>
       <c r="B52" t="n">
-        <v>57965</v>
+        <v>79358</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6106,42 +6119,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>580813</v>
+        <v>580883</v>
       </c>
       <c r="R52" t="n">
-        <v>6963779</v>
+        <v>6963753</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6173,7 +6178,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6183,12 +6188,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:04</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6215,10 +6215,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133552448</v>
+        <v>133552482</v>
       </c>
       <c r="B53" t="n">
-        <v>91947</v>
+        <v>83343</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6226,21 +6226,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6250,10 +6250,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>580691</v>
+        <v>580879</v>
       </c>
       <c r="R53" t="n">
-        <v>6963879</v>
+        <v>6963658</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6295,7 +6295,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6325,7 +6325,7 @@
         <v>133552486</v>
       </c>
       <c r="B54" t="n">
-        <v>83333</v>
+        <v>83343</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6429,10 +6429,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133552503</v>
+        <v>133550160</v>
       </c>
       <c r="B55" t="n">
-        <v>89328</v>
+        <v>92228</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6440,21 +6440,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6464,13 +6464,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>580844</v>
+        <v>580715</v>
       </c>
       <c r="R55" t="n">
-        <v>6963844</v>
+        <v>6963743</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6536,10 +6536,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133552491</v>
+        <v>133552448</v>
       </c>
       <c r="B56" t="n">
-        <v>79348</v>
+        <v>91957</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6547,21 +6547,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6571,10 +6571,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>580883</v>
+        <v>580691</v>
       </c>
       <c r="R56" t="n">
-        <v>6963753</v>
+        <v>6963879</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6646,7 +6646,7 @@
         <v>133550143</v>
       </c>
       <c r="B57" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6750,10 +6750,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133552473</v>
+        <v>133552458</v>
       </c>
       <c r="B58" t="n">
-        <v>80453</v>
+        <v>79358</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6761,21 +6761,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6785,10 +6785,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>580754</v>
+        <v>580716</v>
       </c>
       <c r="R58" t="n">
-        <v>6963659</v>
+        <v>6963787</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6860,7 +6860,7 @@
         <v>133552450</v>
       </c>
       <c r="B59" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6964,10 +6964,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133552458</v>
+        <v>133552473</v>
       </c>
       <c r="B60" t="n">
-        <v>79348</v>
+        <v>80473</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6975,21 +6975,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6999,10 +6999,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>580716</v>
+        <v>580754</v>
       </c>
       <c r="R60" t="n">
-        <v>6963787</v>
+        <v>6963659</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7071,10 +7071,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133552466</v>
+        <v>133552485</v>
       </c>
       <c r="B61" t="n">
-        <v>83333</v>
+        <v>79358</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7082,21 +7082,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7106,13 +7106,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>580746</v>
+        <v>580999</v>
       </c>
       <c r="R61" t="n">
-        <v>6963790</v>
+        <v>6963688</v>
       </c>
       <c r="S61" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7178,10 +7178,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133552485</v>
+        <v>133552466</v>
       </c>
       <c r="B62" t="n">
-        <v>79348</v>
+        <v>83343</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7189,21 +7189,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7213,13 +7213,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>580999</v>
+        <v>580746</v>
       </c>
       <c r="R62" t="n">
-        <v>6963688</v>
+        <v>6963790</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7285,32 +7285,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133550170</v>
+        <v>133550133</v>
       </c>
       <c r="B63" t="n">
-        <v>79380</v>
+        <v>99178</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7320,10 +7320,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>580801</v>
+        <v>580685</v>
       </c>
       <c r="R63" t="n">
-        <v>6963652</v>
+        <v>6963865</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7365,7 +7365,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7395,7 +7400,7 @@
         <v>133552507</v>
       </c>
       <c r="B64" t="n">
-        <v>80413</v>
+        <v>80423</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7499,10 +7504,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133550133</v>
+        <v>133550134</v>
       </c>
       <c r="B65" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7534,10 +7539,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>580685</v>
+        <v>580691</v>
       </c>
       <c r="R65" t="n">
-        <v>6963865</v>
+        <v>6963863</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7569,7 +7574,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7579,12 +7584,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>100 ex</t>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7611,32 +7616,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133550134</v>
+        <v>133550170</v>
       </c>
       <c r="B66" t="n">
-        <v>99168</v>
+        <v>79390</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7646,10 +7651,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>580691</v>
+        <v>580801</v>
       </c>
       <c r="R66" t="n">
-        <v>6963863</v>
+        <v>6963652</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7681,7 +7686,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7691,12 +7696,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>200 ex</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7723,10 +7723,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133550144</v>
+        <v>133550172</v>
       </c>
       <c r="B67" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7758,10 +7758,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>580699</v>
+        <v>580870</v>
       </c>
       <c r="R67" t="n">
-        <v>6963819</v>
+        <v>6963663</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7830,10 +7830,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133552460</v>
+        <v>133552484</v>
       </c>
       <c r="B68" t="n">
-        <v>83333</v>
+        <v>79358</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7841,21 +7841,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7865,10 +7865,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>580722</v>
+        <v>580938</v>
       </c>
       <c r="R68" t="n">
-        <v>6963787</v>
+        <v>6963702</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7900,7 +7900,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7937,10 +7937,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133552506</v>
+        <v>133552460</v>
       </c>
       <c r="B69" t="n">
-        <v>57965</v>
+        <v>83343</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7948,42 +7948,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>580826</v>
+        <v>580722</v>
       </c>
       <c r="R69" t="n">
-        <v>6963830</v>
+        <v>6963787</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8015,7 +8007,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8025,12 +8017,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8057,10 +8044,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133550172</v>
+        <v>133552506</v>
       </c>
       <c r="B70" t="n">
-        <v>91947</v>
+        <v>57975</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8068,34 +8055,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>580870</v>
+        <v>580826</v>
       </c>
       <c r="R70" t="n">
-        <v>6963663</v>
+        <v>6963830</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8127,7 +8122,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8137,7 +8132,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8164,10 +8164,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133552484</v>
+        <v>133550144</v>
       </c>
       <c r="B71" t="n">
-        <v>79348</v>
+        <v>91957</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8175,21 +8175,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8199,10 +8199,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>580938</v>
+        <v>580699</v>
       </c>
       <c r="R71" t="n">
-        <v>6963702</v>
+        <v>6963819</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8271,10 +8271,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133550139</v>
+        <v>133550149</v>
       </c>
       <c r="B72" t="n">
-        <v>80453</v>
+        <v>79358</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8282,21 +8282,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8306,13 +8306,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>580689</v>
+        <v>580697</v>
       </c>
       <c r="R72" t="n">
-        <v>6963841</v>
+        <v>6963788</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8351,12 +8351,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:19</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8386,7 +8381,7 @@
         <v>133552454</v>
       </c>
       <c r="B73" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8490,10 +8485,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133550149</v>
+        <v>133550139</v>
       </c>
       <c r="B74" t="n">
-        <v>79348</v>
+        <v>80473</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8501,21 +8496,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8525,13 +8520,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>580697</v>
+        <v>580689</v>
       </c>
       <c r="R74" t="n">
-        <v>6963788</v>
+        <v>6963841</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8560,7 +8555,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8570,7 +8565,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8597,10 +8597,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133550186</v>
+        <v>133552487</v>
       </c>
       <c r="B75" t="n">
-        <v>89328</v>
+        <v>89338</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>580871</v>
+        <v>580983</v>
       </c>
       <c r="R75" t="n">
-        <v>6963767</v>
+        <v>6963709</v>
       </c>
       <c r="S75" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8704,10 +8704,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133550179</v>
+        <v>133550186</v>
       </c>
       <c r="B76" t="n">
-        <v>91947</v>
+        <v>89338</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8715,21 +8715,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8739,13 +8739,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>580862</v>
+        <v>580871</v>
       </c>
       <c r="R76" t="n">
-        <v>6963713</v>
+        <v>6963767</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8811,32 +8811,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133550141</v>
+        <v>133550179</v>
       </c>
       <c r="B77" t="n">
-        <v>99168</v>
+        <v>91957</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8846,10 +8846,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>580713</v>
+        <v>580862</v>
       </c>
       <c r="R77" t="n">
-        <v>6963840</v>
+        <v>6963713</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8881,7 +8881,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8891,12 +8891,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>60 ex, troligen fler</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8923,10 +8918,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133552499</v>
+        <v>133552513</v>
       </c>
       <c r="B78" t="n">
-        <v>91947</v>
+        <v>83335</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8934,21 +8929,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8958,13 +8953,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>580926</v>
+        <v>580785</v>
       </c>
       <c r="R78" t="n">
-        <v>6963805</v>
+        <v>6963796</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8993,7 +8988,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9003,7 +8998,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9030,10 +9025,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133552513</v>
+        <v>133552499</v>
       </c>
       <c r="B79" t="n">
-        <v>83325</v>
+        <v>91957</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9041,21 +9036,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9065,13 +9060,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>580785</v>
+        <v>580926</v>
       </c>
       <c r="R79" t="n">
-        <v>6963796</v>
+        <v>6963805</v>
       </c>
       <c r="S79" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9100,7 +9095,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9110,7 +9105,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9137,10 +9132,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133550173</v>
+        <v>133552462</v>
       </c>
       <c r="B80" t="n">
-        <v>80453</v>
+        <v>83335</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9148,21 +9143,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9172,13 +9167,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>580878</v>
+        <v>580738</v>
       </c>
       <c r="R80" t="n">
-        <v>6963692</v>
+        <v>6963776</v>
       </c>
       <c r="S80" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9207,7 +9202,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9217,7 +9212,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9244,32 +9239,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133552487</v>
+        <v>133550141</v>
       </c>
       <c r="B81" t="n">
-        <v>89328</v>
+        <v>99178</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9279,10 +9274,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>580983</v>
+        <v>580713</v>
       </c>
       <c r="R81" t="n">
-        <v>6963709</v>
+        <v>6963840</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9314,7 +9309,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9324,7 +9319,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>60 ex, troligen fler</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9351,10 +9351,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133552462</v>
+        <v>133550173</v>
       </c>
       <c r="B82" t="n">
-        <v>83325</v>
+        <v>80473</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9362,21 +9362,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>580738</v>
+        <v>580878</v>
       </c>
       <c r="R82" t="n">
-        <v>6963776</v>
+        <v>6963692</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9458,32 +9458,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>133550140</v>
+        <v>133552467</v>
       </c>
       <c r="B83" t="n">
-        <v>99168</v>
+        <v>92182</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9493,13 +9493,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>580694</v>
+        <v>580754</v>
       </c>
       <c r="R83" t="n">
-        <v>6963839</v>
+        <v>6963789</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9538,12 +9538,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>33 ex</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9573,7 +9568,7 @@
         <v>133552505</v>
       </c>
       <c r="B84" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9677,10 +9672,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133552476</v>
+        <v>133552469</v>
       </c>
       <c r="B85" t="n">
-        <v>80453</v>
+        <v>79358</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9688,21 +9683,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9712,10 +9707,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>580767</v>
+        <v>580751</v>
       </c>
       <c r="R85" t="n">
-        <v>6963639</v>
+        <v>6963778</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9747,7 +9742,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9757,7 +9752,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9787,7 +9782,7 @@
         <v>133550165</v>
       </c>
       <c r="B86" t="n">
-        <v>57143</v>
+        <v>57153</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9903,32 +9898,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133552469</v>
+        <v>133550140</v>
       </c>
       <c r="B87" t="n">
-        <v>79348</v>
+        <v>99178</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9938,10 +9933,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>580751</v>
+        <v>580694</v>
       </c>
       <c r="R87" t="n">
-        <v>6963778</v>
+        <v>6963839</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9973,7 +9968,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9983,7 +9978,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>33 ex</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10010,32 +10010,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133552467</v>
+        <v>133552476</v>
       </c>
       <c r="B88" t="n">
-        <v>92172</v>
+        <v>80473</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10045,13 +10045,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>580754</v>
+        <v>580767</v>
       </c>
       <c r="R88" t="n">
-        <v>6963789</v>
+        <v>6963639</v>
       </c>
       <c r="S88" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10090,7 +10090,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10120,7 +10120,7 @@
         <v>133552463</v>
       </c>
       <c r="B89" t="n">
-        <v>80453</v>
+        <v>80473</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         <v>133550193</v>
       </c>
       <c r="B90" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10336,32 +10336,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133552512</v>
+        <v>133552510</v>
       </c>
       <c r="B91" t="n">
-        <v>99168</v>
+        <v>83343</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10371,10 +10371,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>580803</v>
+        <v>580829</v>
       </c>
       <c r="R91" t="n">
-        <v>6963894</v>
+        <v>6963885</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10416,12 +10416,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>150 + ex</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10448,32 +10443,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133552455</v>
+        <v>133552471</v>
       </c>
       <c r="B92" t="n">
-        <v>99168</v>
+        <v>83343</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10483,10 +10478,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>580733</v>
+        <v>580717</v>
       </c>
       <c r="R92" t="n">
-        <v>6963814</v>
+        <v>6963694</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10518,7 +10513,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10528,12 +10523,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>200 ex</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10560,32 +10550,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133552493</v>
+        <v>133552455</v>
       </c>
       <c r="B93" t="n">
-        <v>89328</v>
+        <v>99178</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10595,10 +10585,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>580914</v>
+        <v>580733</v>
       </c>
       <c r="R93" t="n">
-        <v>6963757</v>
+        <v>6963814</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10630,7 +10620,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10640,7 +10630,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10667,32 +10662,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133552471</v>
+        <v>133552512</v>
       </c>
       <c r="B94" t="n">
-        <v>83333</v>
+        <v>99178</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10702,10 +10697,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>580717</v>
+        <v>580803</v>
       </c>
       <c r="R94" t="n">
-        <v>6963694</v>
+        <v>6963894</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10737,7 +10732,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10747,7 +10742,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>150 + ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10774,10 +10774,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133552510</v>
+        <v>133552493</v>
       </c>
       <c r="B95" t="n">
-        <v>83333</v>
+        <v>89338</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10785,21 +10785,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10809,10 +10809,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>580829</v>
+        <v>580914</v>
       </c>
       <c r="R95" t="n">
-        <v>6963885</v>
+        <v>6963757</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10881,10 +10881,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133552501</v>
+        <v>133550146</v>
       </c>
       <c r="B96" t="n">
-        <v>89328</v>
+        <v>79358</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10892,21 +10892,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10916,13 +10916,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>580895</v>
+        <v>580687</v>
       </c>
       <c r="R96" t="n">
-        <v>6963822</v>
+        <v>6963819</v>
       </c>
       <c r="S96" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10961,7 +10961,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10988,32 +10988,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>133550146</v>
+        <v>133550152</v>
       </c>
       <c r="B97" t="n">
-        <v>79348</v>
+        <v>98043</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11023,13 +11023,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>580687</v>
+        <v>580698</v>
       </c>
       <c r="R97" t="n">
-        <v>6963819</v>
+        <v>6963783</v>
       </c>
       <c r="S97" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11068,7 +11068,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11095,48 +11095,60 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>133550152</v>
+        <v>133550187</v>
       </c>
       <c r="B98" t="n">
-        <v>98033</v>
+        <v>57153</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>221945</v>
+        <v>102612</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>580698</v>
+        <v>580843</v>
       </c>
       <c r="R98" t="n">
-        <v>6963783</v>
+        <v>6963778</v>
       </c>
       <c r="S98" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11165,7 +11177,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11175,7 +11187,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11202,10 +11214,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>133550187</v>
+        <v>133552501</v>
       </c>
       <c r="B99" t="n">
-        <v>57143</v>
+        <v>89338</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11213,49 +11225,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>102612</v>
+        <v>510</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>580843</v>
+        <v>580895</v>
       </c>
       <c r="R99" t="n">
-        <v>6963778</v>
+        <v>6963822</v>
       </c>
       <c r="S99" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11321,32 +11321,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133552477</v>
+        <v>133550161</v>
       </c>
       <c r="B100" t="n">
-        <v>80482</v>
+        <v>79358</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11356,13 +11356,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>580764</v>
+        <v>580727</v>
       </c>
       <c r="R100" t="n">
-        <v>6963638</v>
+        <v>6963764</v>
       </c>
       <c r="S100" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11428,10 +11428,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133550161</v>
+        <v>133552495</v>
       </c>
       <c r="B101" t="n">
-        <v>79348</v>
+        <v>57975</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11439,37 +11439,45 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>580727</v>
+        <v>580953</v>
       </c>
       <c r="R101" t="n">
-        <v>6963764</v>
+        <v>6963811</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11498,7 +11506,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11508,7 +11516,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Ett färskt ringhack på tall</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11535,56 +11548,48 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133552495</v>
+        <v>133552477</v>
       </c>
       <c r="B102" t="n">
-        <v>57965</v>
+        <v>80478</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>580953</v>
+        <v>580764</v>
       </c>
       <c r="R102" t="n">
-        <v>6963811</v>
+        <v>6963638</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11613,7 +11618,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11623,12 +11628,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Ett färskt ringhack på tall</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11655,10 +11655,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133550177</v>
+        <v>133552500</v>
       </c>
       <c r="B103" t="n">
-        <v>79348</v>
+        <v>79390</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11666,21 +11666,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11690,13 +11690,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>580864</v>
+        <v>580902</v>
       </c>
       <c r="R103" t="n">
-        <v>6963715</v>
+        <v>6963823</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11735,7 +11735,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11762,10 +11762,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133552465</v>
+        <v>133550188</v>
       </c>
       <c r="B104" t="n">
-        <v>57965</v>
+        <v>79358</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11773,45 +11773,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>580724</v>
+        <v>580833</v>
       </c>
       <c r="R104" t="n">
-        <v>6963746</v>
+        <v>6963785</v>
       </c>
       <c r="S104" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11840,7 +11832,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11850,12 +11842,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11885,7 +11872,7 @@
         <v>133550158</v>
       </c>
       <c r="B105" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11989,10 +11976,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133550188</v>
+        <v>133552465</v>
       </c>
       <c r="B106" t="n">
-        <v>79348</v>
+        <v>57975</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12000,37 +11987,45 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>580833</v>
+        <v>580724</v>
       </c>
       <c r="R106" t="n">
-        <v>6963785</v>
+        <v>6963746</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12059,7 +12054,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12069,7 +12064,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12099,7 +12099,7 @@
         <v>133550190</v>
       </c>
       <c r="B107" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12208,10 +12208,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>133552500</v>
+        <v>133550177</v>
       </c>
       <c r="B108" t="n">
-        <v>79380</v>
+        <v>79358</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12219,21 +12219,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12243,13 +12243,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>580902</v>
+        <v>580864</v>
       </c>
       <c r="R108" t="n">
-        <v>6963823</v>
+        <v>6963715</v>
       </c>
       <c r="S108" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12288,7 +12288,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD108" t="b">

--- a/artfynd/A 21339-2024 artfynd.xlsx
+++ b/artfynd/A 21339-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133552483</v>
+        <v>133550168</v>
       </c>
       <c r="B3" t="n">
-        <v>89338</v>
+        <v>83207</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580906</v>
+        <v>580801</v>
       </c>
       <c r="R3" t="n">
-        <v>6963679</v>
+        <v>6963652</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133552449</v>
+        <v>133552483</v>
       </c>
       <c r="B4" t="n">
-        <v>91957</v>
+        <v>89338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580689</v>
+        <v>580906</v>
       </c>
       <c r="R4" t="n">
-        <v>6963874</v>
+        <v>6963679</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133550175</v>
+        <v>133552481</v>
       </c>
       <c r="B5" t="n">
-        <v>79358</v>
+        <v>89338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580879</v>
+        <v>580869</v>
       </c>
       <c r="R5" t="n">
-        <v>6963696</v>
+        <v>6963663</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133550168</v>
+        <v>133552511</v>
       </c>
       <c r="B6" t="n">
-        <v>83207</v>
+        <v>79390</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580801</v>
+        <v>580865</v>
       </c>
       <c r="R6" t="n">
-        <v>6963652</v>
+        <v>6963889</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133552481</v>
+        <v>133552449</v>
       </c>
       <c r="B7" t="n">
-        <v>89338</v>
+        <v>91957</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580869</v>
+        <v>580689</v>
       </c>
       <c r="R7" t="n">
-        <v>6963663</v>
+        <v>6963874</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133552511</v>
+        <v>133550175</v>
       </c>
       <c r="B8" t="n">
-        <v>79390</v>
+        <v>79358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580865</v>
+        <v>580879</v>
       </c>
       <c r="R8" t="n">
-        <v>6963889</v>
+        <v>6963696</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,32 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133552468</v>
+        <v>133550155</v>
       </c>
       <c r="B9" t="n">
-        <v>98043</v>
+        <v>80473</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,13 +1459,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580758</v>
+        <v>580715</v>
       </c>
       <c r="R9" t="n">
-        <v>6963787</v>
+        <v>6963791</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,32 +1536,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133550155</v>
+        <v>133550154</v>
       </c>
       <c r="B10" t="n">
-        <v>80473</v>
+        <v>99178</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,13 +1571,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580715</v>
+        <v>580712</v>
       </c>
       <c r="R10" t="n">
-        <v>6963791</v>
+        <v>6963788</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1601,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,12 +1616,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1643,32 +1648,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133552461</v>
+        <v>133552456</v>
       </c>
       <c r="B11" t="n">
-        <v>83326</v>
+        <v>91957</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6439</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1678,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580740</v>
+        <v>580695</v>
       </c>
       <c r="R11" t="n">
-        <v>6963795</v>
+        <v>6963806</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1713,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1723,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1750,32 +1755,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133550154</v>
+        <v>133552475</v>
       </c>
       <c r="B12" t="n">
-        <v>99178</v>
+        <v>79358</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,13 +1790,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580712</v>
+        <v>580801</v>
       </c>
       <c r="R12" t="n">
-        <v>6963788</v>
+        <v>6963655</v>
       </c>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1820,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1830,12 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:59</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>70 ex</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,32 +1862,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133552452</v>
+        <v>133550157</v>
       </c>
       <c r="B13" t="n">
-        <v>83343</v>
+        <v>99178</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,13 +1897,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580698</v>
+        <v>580715</v>
       </c>
       <c r="R13" t="n">
-        <v>6963860</v>
+        <v>6963786</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1942,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133552456</v>
+        <v>133550153</v>
       </c>
       <c r="B14" t="n">
-        <v>91957</v>
+        <v>80473</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,21 +1985,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2004,13 +2009,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580695</v>
+        <v>580704</v>
       </c>
       <c r="R14" t="n">
-        <v>6963806</v>
+        <v>6963785</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2039,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2049,7 +2054,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Stora fina exemplar av lunglav, handflata storlek.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,32 +2086,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133550174</v>
+        <v>133552468</v>
       </c>
       <c r="B15" t="n">
-        <v>79358</v>
+        <v>98043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2111,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580879</v>
+        <v>580758</v>
       </c>
       <c r="R15" t="n">
-        <v>6963690</v>
+        <v>6963787</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2146,7 +2156,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2156,7 +2166,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2183,32 +2193,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133552475</v>
+        <v>133552461</v>
       </c>
       <c r="B16" t="n">
-        <v>79358</v>
+        <v>83326</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2218,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580801</v>
+        <v>580740</v>
       </c>
       <c r="R16" t="n">
-        <v>6963655</v>
+        <v>6963795</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2253,7 +2263,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2263,7 +2273,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2290,32 +2300,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133550157</v>
+        <v>133552452</v>
       </c>
       <c r="B17" t="n">
-        <v>99178</v>
+        <v>83343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2325,13 +2335,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580715</v>
+        <v>580698</v>
       </c>
       <c r="R17" t="n">
-        <v>6963786</v>
+        <v>6963860</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2360,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2370,12 +2380,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>150 ex</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2402,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133550153</v>
+        <v>133550174</v>
       </c>
       <c r="B18" t="n">
-        <v>80473</v>
+        <v>79358</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2413,21 +2418,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2437,13 +2442,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580704</v>
+        <v>580879</v>
       </c>
       <c r="R18" t="n">
-        <v>6963785</v>
+        <v>6963690</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2472,7 +2477,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2482,12 +2487,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Stora fina exemplar av lunglav, handflata storlek.</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2514,7 +2514,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133550164</v>
+        <v>133552509</v>
       </c>
       <c r="B19" t="n">
         <v>79358</v>
@@ -2549,13 +2549,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580751</v>
+        <v>580814</v>
       </c>
       <c r="R19" t="n">
-        <v>6963748</v>
+        <v>6963859</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2621,10 +2621,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133552509</v>
+        <v>133552492</v>
       </c>
       <c r="B20" t="n">
-        <v>79358</v>
+        <v>79116</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2632,21 +2632,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580814</v>
+        <v>580892</v>
       </c>
       <c r="R20" t="n">
-        <v>6963859</v>
+        <v>6963759</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2728,10 +2728,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133552492</v>
+        <v>133550164</v>
       </c>
       <c r="B21" t="n">
-        <v>79116</v>
+        <v>79358</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2739,21 +2739,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2763,13 +2763,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580892</v>
+        <v>580751</v>
       </c>
       <c r="R21" t="n">
-        <v>6963759</v>
+        <v>6963748</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2835,32 +2835,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133552457</v>
+        <v>133550184</v>
       </c>
       <c r="B22" t="n">
-        <v>91957</v>
+        <v>99178</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580720</v>
+        <v>580867</v>
       </c>
       <c r="R22" t="n">
-        <v>6963788</v>
+        <v>6963739</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2915,7 +2915,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>36 ex</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2942,10 +2947,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133550171</v>
+        <v>133552457</v>
       </c>
       <c r="B23" t="n">
-        <v>80473</v>
+        <v>91957</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2953,21 +2958,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2977,13 +2982,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580857</v>
+        <v>580720</v>
       </c>
       <c r="R23" t="n">
-        <v>6963688</v>
+        <v>6963788</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3012,7 +3017,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3022,7 +3027,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3049,10 +3054,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133552464</v>
+        <v>133550171</v>
       </c>
       <c r="B24" t="n">
-        <v>91957</v>
+        <v>80473</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3060,21 +3065,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3084,13 +3089,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580720</v>
+        <v>580857</v>
       </c>
       <c r="R24" t="n">
-        <v>6963748</v>
+        <v>6963688</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3119,7 +3124,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3129,7 +3134,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3156,32 +3161,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133552451</v>
+        <v>133552464</v>
       </c>
       <c r="B25" t="n">
-        <v>91920</v>
+        <v>91957</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3191,10 +3196,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580669</v>
+        <v>580720</v>
       </c>
       <c r="R25" t="n">
-        <v>6963873</v>
+        <v>6963748</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3226,7 +3231,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3236,7 +3241,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3263,32 +3268,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133550184</v>
+        <v>133552451</v>
       </c>
       <c r="B26" t="n">
-        <v>99178</v>
+        <v>91920</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3298,10 +3303,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580867</v>
+        <v>580669</v>
       </c>
       <c r="R26" t="n">
-        <v>6963739</v>
+        <v>6963873</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3333,7 +3338,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3343,12 +3348,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>36 ex</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3910,32 +3910,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133552488</v>
+        <v>133552502</v>
       </c>
       <c r="B32" t="n">
-        <v>89338</v>
+        <v>80367</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>510</v>
+        <v>6456</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3945,10 +3945,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>580943</v>
+        <v>580865</v>
       </c>
       <c r="R32" t="n">
-        <v>6963738</v>
+        <v>6963830</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4017,32 +4017,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133552502</v>
+        <v>133550148</v>
       </c>
       <c r="B33" t="n">
-        <v>80367</v>
+        <v>99178</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4052,13 +4052,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>580865</v>
+        <v>580696</v>
       </c>
       <c r="R33" t="n">
-        <v>6963830</v>
+        <v>6963788</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4097,7 +4097,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4124,48 +4129,56 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133550148</v>
+        <v>133550180</v>
       </c>
       <c r="B34" t="n">
-        <v>99178</v>
+        <v>57975</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>580696</v>
+        <v>580876</v>
       </c>
       <c r="R34" t="n">
-        <v>6963788</v>
+        <v>6963707</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4194,7 +4207,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4204,12 +4217,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>120 ex</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4236,10 +4249,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133550138</v>
+        <v>133552488</v>
       </c>
       <c r="B35" t="n">
-        <v>79358</v>
+        <v>89338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4247,21 +4260,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4271,10 +4284,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>580712</v>
+        <v>580943</v>
       </c>
       <c r="R35" t="n">
-        <v>6963853</v>
+        <v>6963738</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4306,7 +4319,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4316,7 +4329,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4343,10 +4356,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133550180</v>
+        <v>133550138</v>
       </c>
       <c r="B36" t="n">
-        <v>57975</v>
+        <v>79358</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4354,45 +4367,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>580876</v>
+        <v>580712</v>
       </c>
       <c r="R36" t="n">
-        <v>6963707</v>
+        <v>6963853</v>
       </c>
       <c r="S36" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4421,7 +4426,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4431,12 +4436,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:14</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4570,10 +4570,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133552497</v>
+        <v>133552453</v>
       </c>
       <c r="B38" t="n">
-        <v>79115</v>
+        <v>79358</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4605,13 +4605,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>580939</v>
+        <v>580737</v>
       </c>
       <c r="R38" t="n">
-        <v>6963799</v>
+        <v>6963844</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4677,7 +4677,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133552453</v>
+        <v>133550132</v>
       </c>
       <c r="B39" t="n">
         <v>79358</v>
@@ -4712,13 +4712,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>580737</v>
+        <v>580695</v>
       </c>
       <c r="R39" t="n">
-        <v>6963844</v>
+        <v>6963885</v>
       </c>
       <c r="S39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4784,32 +4784,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133550136</v>
+        <v>133550176</v>
       </c>
       <c r="B40" t="n">
-        <v>99178</v>
+        <v>79358</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4819,10 +4819,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>580702</v>
+        <v>580874</v>
       </c>
       <c r="R40" t="n">
-        <v>6963851</v>
+        <v>6963718</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4864,12 +4864,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>150 ex</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4896,7 +4891,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133550132</v>
+        <v>133550182</v>
       </c>
       <c r="B41" t="n">
         <v>79358</v>
@@ -4931,10 +4926,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>580695</v>
+        <v>580856</v>
       </c>
       <c r="R41" t="n">
-        <v>6963885</v>
+        <v>6963747</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4966,7 +4961,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4976,7 +4971,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5003,10 +4998,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133550176</v>
+        <v>133552494</v>
       </c>
       <c r="B42" t="n">
-        <v>79358</v>
+        <v>79390</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5014,21 +5009,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5038,10 +5033,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>580874</v>
+        <v>580955</v>
       </c>
       <c r="R42" t="n">
-        <v>6963718</v>
+        <v>6963798</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5073,7 +5068,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5083,7 +5078,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5110,10 +5105,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133550182</v>
+        <v>133550166</v>
       </c>
       <c r="B43" t="n">
-        <v>79358</v>
+        <v>57153</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5121,37 +5116,49 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580856</v>
+        <v>580800</v>
       </c>
       <c r="R43" t="n">
-        <v>6963747</v>
+        <v>6963652</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5180,7 +5187,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5190,7 +5197,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5217,32 +5224,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133552478</v>
+        <v>133552497</v>
       </c>
       <c r="B44" t="n">
-        <v>80484</v>
+        <v>79115</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5252,10 +5259,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>580763</v>
+        <v>580939</v>
       </c>
       <c r="R44" t="n">
-        <v>6963637</v>
+        <v>6963799</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5287,7 +5294,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5297,7 +5304,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5324,32 +5331,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133552494</v>
+        <v>133550136</v>
       </c>
       <c r="B45" t="n">
-        <v>79390</v>
+        <v>99178</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5359,10 +5366,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580955</v>
+        <v>580702</v>
       </c>
       <c r="R45" t="n">
-        <v>6963798</v>
+        <v>6963851</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5394,7 +5401,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5404,7 +5411,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5431,60 +5443,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133550166</v>
+        <v>133552478</v>
       </c>
       <c r="B46" t="n">
-        <v>57153</v>
+        <v>80484</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102612</v>
+        <v>6463</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>580800</v>
+        <v>580763</v>
       </c>
       <c r="R46" t="n">
-        <v>6963652</v>
+        <v>6963637</v>
       </c>
       <c r="S46" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5550,32 +5550,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133550162</v>
+        <v>133552503</v>
       </c>
       <c r="B47" t="n">
-        <v>99178</v>
+        <v>89338</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>580728</v>
+        <v>580844</v>
       </c>
       <c r="R47" t="n">
-        <v>6963787</v>
+        <v>6963844</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5630,12 +5630,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:34</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>50 ex</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5662,10 +5657,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133552508</v>
+        <v>133550160</v>
       </c>
       <c r="B48" t="n">
-        <v>57975</v>
+        <v>92228</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5673,45 +5668,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>580813</v>
+        <v>580715</v>
       </c>
       <c r="R48" t="n">
-        <v>6963779</v>
+        <v>6963743</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5740,7 +5727,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5750,12 +5737,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:04</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5782,32 +5764,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133550147</v>
+        <v>133552448</v>
       </c>
       <c r="B49" t="n">
-        <v>99178</v>
+        <v>91957</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5817,13 +5799,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>580689</v>
+        <v>580691</v>
       </c>
       <c r="R49" t="n">
-        <v>6963814</v>
+        <v>6963879</v>
       </c>
       <c r="S49" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5852,7 +5834,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5862,12 +5844,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>70 ex</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5894,10 +5871,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133552490</v>
+        <v>133552508</v>
       </c>
       <c r="B50" t="n">
-        <v>80473</v>
+        <v>57975</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5905,34 +5882,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>580853</v>
+        <v>580813</v>
       </c>
       <c r="R50" t="n">
-        <v>6963702</v>
+        <v>6963779</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5964,7 +5949,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5974,7 +5959,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6001,10 +5991,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133552503</v>
+        <v>133552491</v>
       </c>
       <c r="B51" t="n">
-        <v>89338</v>
+        <v>79358</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6012,21 +6002,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6036,10 +6026,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>580844</v>
+        <v>580883</v>
       </c>
       <c r="R51" t="n">
-        <v>6963844</v>
+        <v>6963753</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6071,7 +6061,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6081,7 +6071,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6108,10 +6098,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133552491</v>
+        <v>133552486</v>
       </c>
       <c r="B52" t="n">
-        <v>79358</v>
+        <v>83343</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6119,21 +6109,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6143,10 +6133,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>580883</v>
+        <v>580985</v>
       </c>
       <c r="R52" t="n">
-        <v>6963753</v>
+        <v>6963707</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6178,7 +6168,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6188,7 +6178,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6215,32 +6205,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133552482</v>
+        <v>133550162</v>
       </c>
       <c r="B53" t="n">
-        <v>83343</v>
+        <v>99178</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6250,10 +6240,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>580879</v>
+        <v>580728</v>
       </c>
       <c r="R53" t="n">
-        <v>6963658</v>
+        <v>6963787</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6285,7 +6275,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6295,7 +6285,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6322,32 +6317,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133552486</v>
+        <v>133550147</v>
       </c>
       <c r="B54" t="n">
-        <v>83343</v>
+        <v>99178</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6357,13 +6352,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>580985</v>
+        <v>580689</v>
       </c>
       <c r="R54" t="n">
-        <v>6963707</v>
+        <v>6963814</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6392,7 +6387,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6402,7 +6397,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6429,10 +6429,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133550160</v>
+        <v>133552490</v>
       </c>
       <c r="B55" t="n">
-        <v>92228</v>
+        <v>80473</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6440,21 +6440,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6464,13 +6464,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>580715</v>
+        <v>580853</v>
       </c>
       <c r="R55" t="n">
-        <v>6963743</v>
+        <v>6963702</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6536,10 +6536,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133552448</v>
+        <v>133552482</v>
       </c>
       <c r="B56" t="n">
-        <v>91957</v>
+        <v>83343</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6547,21 +6547,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6571,10 +6571,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>580691</v>
+        <v>580879</v>
       </c>
       <c r="R56" t="n">
-        <v>6963879</v>
+        <v>6963658</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6643,7 +6643,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133550143</v>
+        <v>133552450</v>
       </c>
       <c r="B57" t="n">
         <v>79358</v>
@@ -6678,13 +6678,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>580713</v>
+        <v>580683</v>
       </c>
       <c r="R57" t="n">
-        <v>6963831</v>
+        <v>6963870</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6713,7 +6713,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6750,7 +6750,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133552458</v>
+        <v>133550143</v>
       </c>
       <c r="B58" t="n">
         <v>79358</v>
@@ -6785,10 +6785,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>580716</v>
+        <v>580713</v>
       </c>
       <c r="R58" t="n">
-        <v>6963787</v>
+        <v>6963831</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6857,7 +6857,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133552450</v>
+        <v>133552458</v>
       </c>
       <c r="B59" t="n">
         <v>79358</v>
@@ -6892,13 +6892,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>580683</v>
+        <v>580716</v>
       </c>
       <c r="R59" t="n">
-        <v>6963870</v>
+        <v>6963787</v>
       </c>
       <c r="S59" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7285,32 +7285,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133550133</v>
+        <v>133552507</v>
       </c>
       <c r="B63" t="n">
-        <v>99178</v>
+        <v>80423</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7320,13 +7320,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>580685</v>
+        <v>580830</v>
       </c>
       <c r="R63" t="n">
-        <v>6963865</v>
+        <v>6963821</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7365,12 +7365,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>100 ex</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7397,32 +7392,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133552507</v>
+        <v>133550170</v>
       </c>
       <c r="B64" t="n">
-        <v>80423</v>
+        <v>79390</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229497</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7432,13 +7427,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>580830</v>
+        <v>580801</v>
       </c>
       <c r="R64" t="n">
-        <v>6963821</v>
+        <v>6963652</v>
       </c>
       <c r="S64" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7467,7 +7462,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7477,7 +7472,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7504,7 +7499,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133550134</v>
+        <v>133550133</v>
       </c>
       <c r="B65" t="n">
         <v>99178</v>
@@ -7539,10 +7534,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>580691</v>
+        <v>580685</v>
       </c>
       <c r="R65" t="n">
-        <v>6963863</v>
+        <v>6963865</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7574,7 +7569,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7584,12 +7579,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>200 ex</t>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7616,32 +7611,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133550170</v>
+        <v>133550134</v>
       </c>
       <c r="B66" t="n">
-        <v>79390</v>
+        <v>99178</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7651,10 +7646,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>580801</v>
+        <v>580691</v>
       </c>
       <c r="R66" t="n">
-        <v>6963652</v>
+        <v>6963863</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7686,7 +7681,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7696,7 +7691,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8271,10 +8271,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133550149</v>
+        <v>133552454</v>
       </c>
       <c r="B72" t="n">
-        <v>79358</v>
+        <v>91957</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8282,21 +8282,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8306,13 +8306,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>580697</v>
+        <v>580734</v>
       </c>
       <c r="R72" t="n">
-        <v>6963788</v>
+        <v>6963814</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8351,7 +8351,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8378,10 +8378,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133552454</v>
+        <v>133550149</v>
       </c>
       <c r="B73" t="n">
-        <v>91957</v>
+        <v>79358</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8389,21 +8389,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8413,13 +8413,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>580734</v>
+        <v>580697</v>
       </c>
       <c r="R73" t="n">
-        <v>6963814</v>
+        <v>6963788</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8597,7 +8597,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133552487</v>
+        <v>133550186</v>
       </c>
       <c r="B75" t="n">
         <v>89338</v>
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>580983</v>
+        <v>580871</v>
       </c>
       <c r="R75" t="n">
-        <v>6963709</v>
+        <v>6963767</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8704,10 +8704,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133550186</v>
+        <v>133550179</v>
       </c>
       <c r="B76" t="n">
-        <v>89338</v>
+        <v>91957</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8715,21 +8715,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8739,13 +8739,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>580871</v>
+        <v>580862</v>
       </c>
       <c r="R76" t="n">
-        <v>6963767</v>
+        <v>6963713</v>
       </c>
       <c r="S76" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8811,32 +8811,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133550179</v>
+        <v>133550141</v>
       </c>
       <c r="B77" t="n">
-        <v>91957</v>
+        <v>99178</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8846,10 +8846,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>580862</v>
+        <v>580713</v>
       </c>
       <c r="R77" t="n">
-        <v>6963713</v>
+        <v>6963840</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8881,7 +8881,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8891,7 +8891,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>60 ex, troligen fler</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8918,10 +8923,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133552513</v>
+        <v>133552487</v>
       </c>
       <c r="B78" t="n">
-        <v>83335</v>
+        <v>89338</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8929,21 +8934,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>308</v>
+        <v>510</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8953,13 +8958,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>580785</v>
+        <v>580983</v>
       </c>
       <c r="R78" t="n">
-        <v>6963796</v>
+        <v>6963709</v>
       </c>
       <c r="S78" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8988,7 +8993,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8998,7 +9003,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9025,10 +9030,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133552499</v>
+        <v>133552513</v>
       </c>
       <c r="B79" t="n">
-        <v>91957</v>
+        <v>83335</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9036,21 +9041,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9060,13 +9065,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>580926</v>
+        <v>580785</v>
       </c>
       <c r="R79" t="n">
-        <v>6963805</v>
+        <v>6963796</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9095,7 +9100,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9105,7 +9110,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9132,10 +9137,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133552462</v>
+        <v>133552499</v>
       </c>
       <c r="B80" t="n">
-        <v>83335</v>
+        <v>91957</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9143,21 +9148,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9167,10 +9172,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>580738</v>
+        <v>580926</v>
       </c>
       <c r="R80" t="n">
-        <v>6963776</v>
+        <v>6963805</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9202,7 +9207,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9212,7 +9217,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9239,32 +9244,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133550141</v>
+        <v>133552462</v>
       </c>
       <c r="B81" t="n">
-        <v>99178</v>
+        <v>83335</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>308</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9274,10 +9279,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>580713</v>
+        <v>580738</v>
       </c>
       <c r="R81" t="n">
-        <v>6963840</v>
+        <v>6963776</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9309,7 +9314,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9319,12 +9324,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>60 ex, troligen fler</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9458,48 +9458,60 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>133552467</v>
+        <v>133550165</v>
       </c>
       <c r="B83" t="n">
-        <v>92182</v>
+        <v>57153</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3298</v>
+        <v>102612</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>580754</v>
+        <v>580753</v>
       </c>
       <c r="R83" t="n">
-        <v>6963789</v>
+        <v>6963702</v>
       </c>
       <c r="S83" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9528,7 +9540,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9538,7 +9550,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9565,32 +9577,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133552505</v>
+        <v>133550140</v>
       </c>
       <c r="B84" t="n">
-        <v>79358</v>
+        <v>99178</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9600,10 +9612,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>580836</v>
+        <v>580694</v>
       </c>
       <c r="R84" t="n">
-        <v>6963844</v>
+        <v>6963839</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9635,7 +9647,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9645,7 +9657,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>33 ex</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9672,32 +9689,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133552469</v>
+        <v>133552467</v>
       </c>
       <c r="B85" t="n">
-        <v>79358</v>
+        <v>92182</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9707,13 +9724,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>580751</v>
+        <v>580754</v>
       </c>
       <c r="R85" t="n">
-        <v>6963778</v>
+        <v>6963789</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9742,7 +9759,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9752,7 +9769,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9779,10 +9796,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133550165</v>
+        <v>133552505</v>
       </c>
       <c r="B86" t="n">
-        <v>57153</v>
+        <v>79358</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9790,49 +9807,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>580753</v>
+        <v>580836</v>
       </c>
       <c r="R86" t="n">
-        <v>6963702</v>
+        <v>6963844</v>
       </c>
       <c r="S86" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9861,7 +9866,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9871,7 +9876,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9898,32 +9903,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133550140</v>
+        <v>133552469</v>
       </c>
       <c r="B87" t="n">
-        <v>99178</v>
+        <v>79358</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9933,10 +9938,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>580694</v>
+        <v>580751</v>
       </c>
       <c r="R87" t="n">
-        <v>6963839</v>
+        <v>6963778</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9968,7 +9973,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9978,12 +9983,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>33 ex</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10336,7 +10336,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133552510</v>
+        <v>133552471</v>
       </c>
       <c r="B91" t="n">
         <v>83343</v>
@@ -10371,10 +10371,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>580829</v>
+        <v>580717</v>
       </c>
       <c r="R91" t="n">
-        <v>6963885</v>
+        <v>6963694</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10416,7 +10416,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10443,7 +10443,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133552471</v>
+        <v>133552510</v>
       </c>
       <c r="B92" t="n">
         <v>83343</v>
@@ -10478,10 +10478,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>580717</v>
+        <v>580829</v>
       </c>
       <c r="R92" t="n">
-        <v>6963694</v>
+        <v>6963885</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10550,7 +10550,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133552455</v>
+        <v>133552512</v>
       </c>
       <c r="B93" t="n">
         <v>99178</v>
@@ -10585,10 +10585,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>580733</v>
+        <v>580803</v>
       </c>
       <c r="R93" t="n">
-        <v>6963814</v>
+        <v>6963894</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10630,12 +10630,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>200 ex</t>
+          <t>150 + ex</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10662,7 +10662,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133552512</v>
+        <v>133552455</v>
       </c>
       <c r="B94" t="n">
         <v>99178</v>
@@ -10697,10 +10697,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>580803</v>
+        <v>580733</v>
       </c>
       <c r="R94" t="n">
-        <v>6963894</v>
+        <v>6963814</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10742,12 +10742,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>150 + ex</t>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10881,10 +10881,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133550146</v>
+        <v>133552501</v>
       </c>
       <c r="B96" t="n">
-        <v>79358</v>
+        <v>89338</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10892,21 +10892,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10916,13 +10916,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>580687</v>
+        <v>580895</v>
       </c>
       <c r="R96" t="n">
-        <v>6963819</v>
+        <v>6963822</v>
       </c>
       <c r="S96" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10961,7 +10961,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10988,32 +10988,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>133550152</v>
+        <v>133550146</v>
       </c>
       <c r="B97" t="n">
-        <v>98043</v>
+        <v>79358</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11023,13 +11023,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>580698</v>
+        <v>580687</v>
       </c>
       <c r="R97" t="n">
-        <v>6963783</v>
+        <v>6963819</v>
       </c>
       <c r="S97" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11068,7 +11068,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11095,60 +11095,48 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>133550187</v>
+        <v>133550152</v>
       </c>
       <c r="B98" t="n">
-        <v>57153</v>
+        <v>98043</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>102612</v>
+        <v>221945</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>580843</v>
+        <v>580698</v>
       </c>
       <c r="R98" t="n">
-        <v>6963778</v>
+        <v>6963783</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11177,7 +11165,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11187,7 +11175,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11214,10 +11202,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>133552501</v>
+        <v>133550187</v>
       </c>
       <c r="B99" t="n">
-        <v>89338</v>
+        <v>57153</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11225,37 +11213,49 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>510</v>
+        <v>102612</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>580895</v>
+        <v>580843</v>
       </c>
       <c r="R99" t="n">
-        <v>6963822</v>
+        <v>6963778</v>
       </c>
       <c r="S99" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11321,32 +11321,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133550161</v>
+        <v>133552477</v>
       </c>
       <c r="B100" t="n">
-        <v>79358</v>
+        <v>80478</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11356,13 +11356,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>580727</v>
+        <v>580764</v>
       </c>
       <c r="R100" t="n">
-        <v>6963764</v>
+        <v>6963638</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11428,10 +11428,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133552495</v>
+        <v>133550161</v>
       </c>
       <c r="B101" t="n">
-        <v>57975</v>
+        <v>79358</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11439,45 +11439,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>580953</v>
+        <v>580727</v>
       </c>
       <c r="R101" t="n">
-        <v>6963811</v>
+        <v>6963764</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11506,7 +11498,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11516,12 +11508,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Ett färskt ringhack på tall</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11548,48 +11535,56 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133552477</v>
+        <v>133552495</v>
       </c>
       <c r="B102" t="n">
-        <v>80478</v>
+        <v>57975</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>580764</v>
+        <v>580953</v>
       </c>
       <c r="R102" t="n">
-        <v>6963638</v>
+        <v>6963811</v>
       </c>
       <c r="S102" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11618,7 +11613,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11628,7 +11623,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Ett färskt ringhack på tall</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11655,10 +11655,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133552500</v>
+        <v>133550190</v>
       </c>
       <c r="B103" t="n">
-        <v>79390</v>
+        <v>79358</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11666,21 +11666,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11690,13 +11690,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>580902</v>
+        <v>580838</v>
       </c>
       <c r="R103" t="n">
-        <v>6963823</v>
+        <v>6963811</v>
       </c>
       <c r="S103" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11735,7 +11735,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11762,10 +11767,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133550188</v>
+        <v>133552500</v>
       </c>
       <c r="B104" t="n">
-        <v>79358</v>
+        <v>79390</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11773,21 +11778,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11797,13 +11802,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>580833</v>
+        <v>580902</v>
       </c>
       <c r="R104" t="n">
-        <v>6963785</v>
+        <v>6963823</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11832,7 +11837,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11842,7 +11847,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11869,7 +11874,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133550158</v>
+        <v>133550188</v>
       </c>
       <c r="B105" t="n">
         <v>79358</v>
@@ -11904,10 +11909,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>580720</v>
+        <v>580833</v>
       </c>
       <c r="R105" t="n">
-        <v>6963787</v>
+        <v>6963785</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11939,7 +11944,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11949,7 +11954,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11976,10 +11981,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133552465</v>
+        <v>133550158</v>
       </c>
       <c r="B106" t="n">
-        <v>57975</v>
+        <v>79358</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11987,45 +11992,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>580724</v>
+        <v>580720</v>
       </c>
       <c r="R106" t="n">
-        <v>6963746</v>
+        <v>6963787</v>
       </c>
       <c r="S106" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12054,7 +12051,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12064,12 +12061,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12096,10 +12088,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133550190</v>
+        <v>133552465</v>
       </c>
       <c r="B107" t="n">
-        <v>79358</v>
+        <v>57975</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12107,34 +12099,42 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>580838</v>
+        <v>580724</v>
       </c>
       <c r="R107" t="n">
-        <v>6963811</v>
+        <v>6963746</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Med apotecier</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD107" t="b">

--- a/artfynd/A 21339-2024 artfynd.xlsx
+++ b/artfynd/A 21339-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133550168</v>
+        <v>133552483</v>
       </c>
       <c r="B3" t="n">
-        <v>83207</v>
+        <v>89338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580801</v>
+        <v>580906</v>
       </c>
       <c r="R3" t="n">
-        <v>6963652</v>
+        <v>6963679</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133552483</v>
+        <v>133552449</v>
       </c>
       <c r="B4" t="n">
-        <v>89338</v>
+        <v>91957</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580906</v>
+        <v>580689</v>
       </c>
       <c r="R4" t="n">
-        <v>6963679</v>
+        <v>6963874</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133552511</v>
+        <v>133550175</v>
       </c>
       <c r="B6" t="n">
-        <v>79390</v>
+        <v>79358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580865</v>
+        <v>580879</v>
       </c>
       <c r="R6" t="n">
-        <v>6963889</v>
+        <v>6963696</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133552449</v>
+        <v>133550168</v>
       </c>
       <c r="B7" t="n">
-        <v>91957</v>
+        <v>83207</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580689</v>
+        <v>580801</v>
       </c>
       <c r="R7" t="n">
-        <v>6963874</v>
+        <v>6963652</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133550175</v>
+        <v>133552511</v>
       </c>
       <c r="B8" t="n">
-        <v>79358</v>
+        <v>79390</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580879</v>
+        <v>580865</v>
       </c>
       <c r="R8" t="n">
-        <v>6963696</v>
+        <v>6963889</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1536,32 +1536,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133550154</v>
+        <v>133552461</v>
       </c>
       <c r="B10" t="n">
-        <v>99178</v>
+        <v>83326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6439</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,13 +1571,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580712</v>
+        <v>580740</v>
       </c>
       <c r="R10" t="n">
-        <v>6963788</v>
+        <v>6963795</v>
       </c>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,12 +1616,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:59</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>70 ex</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,32 +1643,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133552456</v>
+        <v>133550154</v>
       </c>
       <c r="B11" t="n">
-        <v>91957</v>
+        <v>99178</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1683,13 +1678,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580695</v>
+        <v>580712</v>
       </c>
       <c r="R11" t="n">
-        <v>6963806</v>
+        <v>6963788</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1718,7 +1713,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1723,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133552475</v>
+        <v>133552452</v>
       </c>
       <c r="B12" t="n">
-        <v>79358</v>
+        <v>83343</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,21 +1766,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,13 +1790,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580801</v>
+        <v>580698</v>
       </c>
       <c r="R12" t="n">
-        <v>6963655</v>
+        <v>6963860</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,32 +1862,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133550157</v>
+        <v>133552456</v>
       </c>
       <c r="B13" t="n">
-        <v>99178</v>
+        <v>91957</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,13 +1897,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580715</v>
+        <v>580695</v>
       </c>
       <c r="R13" t="n">
-        <v>6963786</v>
+        <v>6963806</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,12 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>150 ex</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133550153</v>
+        <v>133550174</v>
       </c>
       <c r="B14" t="n">
-        <v>80473</v>
+        <v>79358</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,21 +1980,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2009,13 +2004,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580704</v>
+        <v>580879</v>
       </c>
       <c r="R14" t="n">
-        <v>6963785</v>
+        <v>6963690</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2044,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,12 +2049,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Stora fina exemplar av lunglav, handflata storlek.</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,32 +2076,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133552468</v>
+        <v>133550157</v>
       </c>
       <c r="B15" t="n">
-        <v>98043</v>
+        <v>99178</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2121,13 +2111,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580758</v>
+        <v>580715</v>
       </c>
       <c r="R15" t="n">
-        <v>6963787</v>
+        <v>6963786</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2156,7 +2146,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2166,7 +2156,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2193,32 +2188,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133552461</v>
+        <v>133550153</v>
       </c>
       <c r="B16" t="n">
-        <v>83326</v>
+        <v>80473</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6439</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2228,13 +2223,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580740</v>
+        <v>580704</v>
       </c>
       <c r="R16" t="n">
-        <v>6963795</v>
+        <v>6963785</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2263,7 +2258,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2273,7 +2268,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Stora fina exemplar av lunglav, handflata storlek.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,32 +2300,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133552452</v>
+        <v>133552468</v>
       </c>
       <c r="B17" t="n">
-        <v>83343</v>
+        <v>98043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2335,13 +2335,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580698</v>
+        <v>580758</v>
       </c>
       <c r="R17" t="n">
-        <v>6963860</v>
+        <v>6963787</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,7 +2407,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133550174</v>
+        <v>133552475</v>
       </c>
       <c r="B18" t="n">
         <v>79358</v>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580879</v>
+        <v>580801</v>
       </c>
       <c r="R18" t="n">
-        <v>6963690</v>
+        <v>6963655</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2514,10 +2514,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133552509</v>
+        <v>133552492</v>
       </c>
       <c r="B19" t="n">
-        <v>79358</v>
+        <v>79116</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2525,21 +2525,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580814</v>
+        <v>580892</v>
       </c>
       <c r="R19" t="n">
-        <v>6963859</v>
+        <v>6963759</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2621,10 +2621,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133552492</v>
+        <v>133550164</v>
       </c>
       <c r="B20" t="n">
-        <v>79116</v>
+        <v>79358</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2632,21 +2632,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2656,13 +2656,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580892</v>
+        <v>580751</v>
       </c>
       <c r="R20" t="n">
-        <v>6963759</v>
+        <v>6963748</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2728,7 +2728,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133550164</v>
+        <v>133552509</v>
       </c>
       <c r="B21" t="n">
         <v>79358</v>
@@ -2763,13 +2763,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580751</v>
+        <v>580814</v>
       </c>
       <c r="R21" t="n">
-        <v>6963748</v>
+        <v>6963859</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2835,32 +2835,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133550184</v>
+        <v>133552451</v>
       </c>
       <c r="B22" t="n">
-        <v>99178</v>
+        <v>91920</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580867</v>
+        <v>580669</v>
       </c>
       <c r="R22" t="n">
-        <v>6963739</v>
+        <v>6963873</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2915,12 +2915,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>36 ex</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3268,32 +3263,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133552451</v>
+        <v>133550184</v>
       </c>
       <c r="B26" t="n">
-        <v>91920</v>
+        <v>99178</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3303,10 +3298,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580669</v>
+        <v>580867</v>
       </c>
       <c r="R26" t="n">
-        <v>6963873</v>
+        <v>6963739</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3338,7 +3333,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3348,7 +3343,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>36 ex</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4017,48 +4017,56 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133550148</v>
+        <v>133550180</v>
       </c>
       <c r="B33" t="n">
-        <v>99178</v>
+        <v>57975</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>580696</v>
+        <v>580876</v>
       </c>
       <c r="R33" t="n">
-        <v>6963788</v>
+        <v>6963707</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4087,7 +4095,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4097,12 +4105,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>120 ex</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4129,56 +4137,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133550180</v>
+        <v>133550163</v>
       </c>
       <c r="B34" t="n">
-        <v>57975</v>
+        <v>98043</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>580876</v>
+        <v>580728</v>
       </c>
       <c r="R34" t="n">
-        <v>6963707</v>
+        <v>6963787</v>
       </c>
       <c r="S34" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4217,12 +4217,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:14</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4356,32 +4351,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133550138</v>
+        <v>133550148</v>
       </c>
       <c r="B36" t="n">
-        <v>79358</v>
+        <v>99178</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4391,13 +4386,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>580712</v>
+        <v>580696</v>
       </c>
       <c r="R36" t="n">
-        <v>6963853</v>
+        <v>6963788</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4426,7 +4421,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4436,7 +4431,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4463,32 +4463,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133550163</v>
+        <v>133550138</v>
       </c>
       <c r="B37" t="n">
-        <v>98043</v>
+        <v>79358</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>580728</v>
+        <v>580712</v>
       </c>
       <c r="R37" t="n">
-        <v>6963787</v>
+        <v>6963853</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4570,10 +4570,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133552453</v>
+        <v>133552497</v>
       </c>
       <c r="B38" t="n">
-        <v>79358</v>
+        <v>79115</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4605,13 +4605,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>580737</v>
+        <v>580939</v>
       </c>
       <c r="R38" t="n">
-        <v>6963844</v>
+        <v>6963799</v>
       </c>
       <c r="S38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4677,27 +4677,27 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133550132</v>
+        <v>133552478</v>
       </c>
       <c r="B39" t="n">
-        <v>79358</v>
+        <v>80484</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>580695</v>
+        <v>580763</v>
       </c>
       <c r="R39" t="n">
-        <v>6963885</v>
+        <v>6963637</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4784,7 +4784,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133550176</v>
+        <v>133552453</v>
       </c>
       <c r="B40" t="n">
         <v>79358</v>
@@ -4819,13 +4819,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>580874</v>
+        <v>580737</v>
       </c>
       <c r="R40" t="n">
-        <v>6963718</v>
+        <v>6963844</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4891,32 +4891,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133550182</v>
+        <v>133550136</v>
       </c>
       <c r="B41" t="n">
-        <v>79358</v>
+        <v>99178</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4926,10 +4926,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>580856</v>
+        <v>580702</v>
       </c>
       <c r="R41" t="n">
-        <v>6963747</v>
+        <v>6963851</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4961,7 +4961,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4971,7 +4971,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4998,10 +5003,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133552494</v>
+        <v>133550132</v>
       </c>
       <c r="B42" t="n">
-        <v>79390</v>
+        <v>79358</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5009,21 +5014,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5033,10 +5038,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>580955</v>
+        <v>580695</v>
       </c>
       <c r="R42" t="n">
-        <v>6963798</v>
+        <v>6963885</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5068,7 +5073,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5078,7 +5083,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5105,10 +5110,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133550166</v>
+        <v>133550176</v>
       </c>
       <c r="B43" t="n">
-        <v>57153</v>
+        <v>79358</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5116,49 +5121,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580800</v>
+        <v>580874</v>
       </c>
       <c r="R43" t="n">
-        <v>6963652</v>
+        <v>6963718</v>
       </c>
       <c r="S43" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5187,7 +5180,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5197,7 +5190,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5224,10 +5217,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133552497</v>
+        <v>133550182</v>
       </c>
       <c r="B44" t="n">
-        <v>79115</v>
+        <v>79358</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5235,21 +5228,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5259,10 +5252,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>580939</v>
+        <v>580856</v>
       </c>
       <c r="R44" t="n">
-        <v>6963799</v>
+        <v>6963747</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5294,7 +5287,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5304,7 +5297,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5331,32 +5324,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133550136</v>
+        <v>133552494</v>
       </c>
       <c r="B45" t="n">
-        <v>99178</v>
+        <v>79390</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5366,10 +5359,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580702</v>
+        <v>580955</v>
       </c>
       <c r="R45" t="n">
-        <v>6963851</v>
+        <v>6963798</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5401,7 +5394,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5411,12 +5404,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>150 ex</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5443,48 +5431,60 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133552478</v>
+        <v>133550166</v>
       </c>
       <c r="B46" t="n">
-        <v>80484</v>
+        <v>57153</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6463</v>
+        <v>102612</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>580763</v>
+        <v>580800</v>
       </c>
       <c r="R46" t="n">
-        <v>6963637</v>
+        <v>6963652</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5550,32 +5550,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133552503</v>
+        <v>133550162</v>
       </c>
       <c r="B47" t="n">
-        <v>89338</v>
+        <v>99178</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>580844</v>
+        <v>580728</v>
       </c>
       <c r="R47" t="n">
-        <v>6963844</v>
+        <v>6963787</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5630,7 +5630,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5657,10 +5662,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133550160</v>
+        <v>133552508</v>
       </c>
       <c r="B48" t="n">
-        <v>92228</v>
+        <v>57975</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5668,37 +5673,45 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>580715</v>
+        <v>580813</v>
       </c>
       <c r="R48" t="n">
-        <v>6963743</v>
+        <v>6963779</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5727,7 +5740,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5737,7 +5750,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5764,10 +5782,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133552448</v>
+        <v>133552490</v>
       </c>
       <c r="B49" t="n">
-        <v>91957</v>
+        <v>80473</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5775,21 +5793,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5799,10 +5817,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>580691</v>
+        <v>580853</v>
       </c>
       <c r="R49" t="n">
-        <v>6963879</v>
+        <v>6963702</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5834,7 +5852,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5844,7 +5862,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5871,10 +5889,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133552508</v>
+        <v>133552491</v>
       </c>
       <c r="B50" t="n">
-        <v>57975</v>
+        <v>79358</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5882,42 +5900,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>580813</v>
+        <v>580883</v>
       </c>
       <c r="R50" t="n">
-        <v>6963779</v>
+        <v>6963753</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5949,7 +5959,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5959,12 +5969,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:04</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5991,10 +5996,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133552491</v>
+        <v>133552482</v>
       </c>
       <c r="B51" t="n">
-        <v>79358</v>
+        <v>83343</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6002,21 +6007,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6026,10 +6031,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>580883</v>
+        <v>580879</v>
       </c>
       <c r="R51" t="n">
-        <v>6963753</v>
+        <v>6963658</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6061,7 +6066,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6071,7 +6076,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6205,32 +6210,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133550162</v>
+        <v>133552448</v>
       </c>
       <c r="B53" t="n">
-        <v>99178</v>
+        <v>91957</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6240,10 +6245,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>580728</v>
+        <v>580691</v>
       </c>
       <c r="R53" t="n">
-        <v>6963787</v>
+        <v>6963879</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6275,7 +6280,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6285,12 +6290,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:34</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>50 ex</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6429,10 +6429,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133552490</v>
+        <v>133552503</v>
       </c>
       <c r="B55" t="n">
-        <v>80473</v>
+        <v>89338</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6440,21 +6440,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6464,10 +6464,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>580853</v>
+        <v>580844</v>
       </c>
       <c r="R55" t="n">
-        <v>6963702</v>
+        <v>6963844</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6499,7 +6499,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6536,10 +6536,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133552482</v>
+        <v>133550160</v>
       </c>
       <c r="B56" t="n">
-        <v>83343</v>
+        <v>92228</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6547,21 +6547,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6571,13 +6571,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>580879</v>
+        <v>580715</v>
       </c>
       <c r="R56" t="n">
-        <v>6963658</v>
+        <v>6963743</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6643,7 +6643,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133552450</v>
+        <v>133552458</v>
       </c>
       <c r="B57" t="n">
         <v>79358</v>
@@ -6678,13 +6678,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>580683</v>
+        <v>580716</v>
       </c>
       <c r="R57" t="n">
-        <v>6963870</v>
+        <v>6963787</v>
       </c>
       <c r="S57" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6713,7 +6713,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6750,7 +6750,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133550143</v>
+        <v>133552450</v>
       </c>
       <c r="B58" t="n">
         <v>79358</v>
@@ -6785,13 +6785,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>580713</v>
+        <v>580683</v>
       </c>
       <c r="R58" t="n">
-        <v>6963831</v>
+        <v>6963870</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6857,10 +6857,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133552458</v>
+        <v>133552473</v>
       </c>
       <c r="B59" t="n">
-        <v>79358</v>
+        <v>80473</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6868,21 +6868,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6892,10 +6892,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>580716</v>
+        <v>580754</v>
       </c>
       <c r="R59" t="n">
-        <v>6963787</v>
+        <v>6963659</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6964,10 +6964,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133552473</v>
+        <v>133550143</v>
       </c>
       <c r="B60" t="n">
-        <v>80473</v>
+        <v>79358</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6975,21 +6975,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6999,10 +6999,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>580754</v>
+        <v>580713</v>
       </c>
       <c r="R60" t="n">
-        <v>6963659</v>
+        <v>6963831</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7285,32 +7285,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133552507</v>
+        <v>133550133</v>
       </c>
       <c r="B63" t="n">
-        <v>80423</v>
+        <v>99178</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7320,13 +7320,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>580830</v>
+        <v>580685</v>
       </c>
       <c r="R63" t="n">
-        <v>6963821</v>
+        <v>6963865</v>
       </c>
       <c r="S63" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7365,7 +7365,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>100 ex</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7392,32 +7397,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133550170</v>
+        <v>133550134</v>
       </c>
       <c r="B64" t="n">
-        <v>79390</v>
+        <v>99178</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7427,10 +7432,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>580801</v>
+        <v>580691</v>
       </c>
       <c r="R64" t="n">
-        <v>6963652</v>
+        <v>6963863</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7462,7 +7467,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7472,7 +7477,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7499,32 +7509,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133550133</v>
+        <v>133550170</v>
       </c>
       <c r="B65" t="n">
-        <v>99178</v>
+        <v>79390</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7534,10 +7544,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>580685</v>
+        <v>580801</v>
       </c>
       <c r="R65" t="n">
-        <v>6963865</v>
+        <v>6963652</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7569,7 +7579,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7579,12 +7589,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>100 ex</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7611,32 +7616,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133550134</v>
+        <v>133552507</v>
       </c>
       <c r="B66" t="n">
-        <v>99178</v>
+        <v>80423</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7646,13 +7651,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>580691</v>
+        <v>580830</v>
       </c>
       <c r="R66" t="n">
-        <v>6963863</v>
+        <v>6963821</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7681,7 +7686,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7691,12 +7696,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>200 ex</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7723,10 +7723,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133550172</v>
+        <v>133552484</v>
       </c>
       <c r="B67" t="n">
-        <v>91957</v>
+        <v>79358</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7734,21 +7734,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7758,10 +7758,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>580870</v>
+        <v>580938</v>
       </c>
       <c r="R67" t="n">
-        <v>6963663</v>
+        <v>6963702</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7830,10 +7830,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133552484</v>
+        <v>133550172</v>
       </c>
       <c r="B68" t="n">
-        <v>79358</v>
+        <v>91957</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7841,21 +7841,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7865,10 +7865,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>580938</v>
+        <v>580870</v>
       </c>
       <c r="R68" t="n">
-        <v>6963702</v>
+        <v>6963663</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7900,7 +7900,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8378,10 +8378,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133550149</v>
+        <v>133550139</v>
       </c>
       <c r="B73" t="n">
-        <v>79358</v>
+        <v>80473</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8389,21 +8389,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8413,13 +8413,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>580697</v>
+        <v>580689</v>
       </c>
       <c r="R73" t="n">
-        <v>6963788</v>
+        <v>6963841</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8458,7 +8458,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8485,10 +8490,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133550139</v>
+        <v>133550149</v>
       </c>
       <c r="B74" t="n">
-        <v>80473</v>
+        <v>79358</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8496,21 +8501,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8520,13 +8525,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>580689</v>
+        <v>580697</v>
       </c>
       <c r="R74" t="n">
-        <v>6963841</v>
+        <v>6963788</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8555,7 +8560,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8565,12 +8570,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:19</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8597,10 +8597,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133550186</v>
+        <v>133550179</v>
       </c>
       <c r="B75" t="n">
-        <v>89338</v>
+        <v>91957</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8608,21 +8608,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>580871</v>
+        <v>580862</v>
       </c>
       <c r="R75" t="n">
-        <v>6963767</v>
+        <v>6963713</v>
       </c>
       <c r="S75" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8704,10 +8704,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133550179</v>
+        <v>133552462</v>
       </c>
       <c r="B76" t="n">
-        <v>91957</v>
+        <v>83335</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8715,21 +8715,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8739,10 +8739,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>580862</v>
+        <v>580738</v>
       </c>
       <c r="R76" t="n">
-        <v>6963713</v>
+        <v>6963776</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8811,32 +8811,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133550141</v>
+        <v>133550173</v>
       </c>
       <c r="B77" t="n">
-        <v>99178</v>
+        <v>80473</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8846,13 +8846,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>580713</v>
+        <v>580878</v>
       </c>
       <c r="R77" t="n">
-        <v>6963840</v>
+        <v>6963692</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8891,12 +8891,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>60 ex, troligen fler</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9030,10 +9025,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133552513</v>
+        <v>133550186</v>
       </c>
       <c r="B79" t="n">
-        <v>83335</v>
+        <v>89338</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9041,21 +9036,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>308</v>
+        <v>510</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9065,10 +9060,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>580785</v>
+        <v>580871</v>
       </c>
       <c r="R79" t="n">
-        <v>6963796</v>
+        <v>6963767</v>
       </c>
       <c r="S79" t="n">
         <v>6</v>
@@ -9100,7 +9095,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9110,7 +9105,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9137,10 +9132,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133552499</v>
+        <v>133552513</v>
       </c>
       <c r="B80" t="n">
-        <v>91957</v>
+        <v>83335</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9148,21 +9143,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9172,13 +9167,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>580926</v>
+        <v>580785</v>
       </c>
       <c r="R80" t="n">
-        <v>6963805</v>
+        <v>6963796</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9207,7 +9202,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9217,7 +9212,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9244,10 +9239,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133552462</v>
+        <v>133552499</v>
       </c>
       <c r="B81" t="n">
-        <v>83335</v>
+        <v>91957</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9255,21 +9250,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9279,10 +9274,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>580738</v>
+        <v>580926</v>
       </c>
       <c r="R81" t="n">
-        <v>6963776</v>
+        <v>6963805</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9314,7 +9309,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9324,7 +9319,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9351,32 +9346,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133550173</v>
+        <v>133550141</v>
       </c>
       <c r="B82" t="n">
-        <v>80473</v>
+        <v>99178</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9386,13 +9381,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>580878</v>
+        <v>580713</v>
       </c>
       <c r="R82" t="n">
-        <v>6963692</v>
+        <v>6963840</v>
       </c>
       <c r="S82" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9421,7 +9416,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9431,7 +9426,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>60 ex, troligen fler</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9458,10 +9458,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>133550165</v>
+        <v>133552505</v>
       </c>
       <c r="B83" t="n">
-        <v>57153</v>
+        <v>79358</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9469,49 +9469,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>580753</v>
+        <v>580836</v>
       </c>
       <c r="R83" t="n">
-        <v>6963702</v>
+        <v>6963844</v>
       </c>
       <c r="S83" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9540,7 +9528,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9550,7 +9538,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9577,48 +9565,60 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133550140</v>
+        <v>133550165</v>
       </c>
       <c r="B84" t="n">
-        <v>99178</v>
+        <v>57153</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>580694</v>
+        <v>580753</v>
       </c>
       <c r="R84" t="n">
-        <v>6963839</v>
+        <v>6963702</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9647,7 +9647,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9657,12 +9657,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>33 ex</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9689,32 +9684,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133552467</v>
+        <v>133550140</v>
       </c>
       <c r="B85" t="n">
-        <v>92182</v>
+        <v>99178</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9724,13 +9719,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>580754</v>
+        <v>580694</v>
       </c>
       <c r="R85" t="n">
-        <v>6963789</v>
+        <v>6963839</v>
       </c>
       <c r="S85" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9759,7 +9754,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9769,7 +9764,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>33 ex</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9796,10 +9796,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133552505</v>
+        <v>133552463</v>
       </c>
       <c r="B86" t="n">
-        <v>79358</v>
+        <v>80473</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9807,21 +9807,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9831,10 +9831,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>580836</v>
+        <v>580725</v>
       </c>
       <c r="R86" t="n">
-        <v>6963844</v>
+        <v>6963773</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9866,7 +9866,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9903,32 +9903,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133552469</v>
+        <v>133552467</v>
       </c>
       <c r="B87" t="n">
-        <v>79358</v>
+        <v>92182</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9938,13 +9938,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>580751</v>
+        <v>580754</v>
       </c>
       <c r="R87" t="n">
-        <v>6963778</v>
+        <v>6963789</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9983,7 +9983,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10010,10 +10010,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133552476</v>
+        <v>133552469</v>
       </c>
       <c r="B88" t="n">
-        <v>80473</v>
+        <v>79358</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10021,21 +10021,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10045,10 +10045,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>580767</v>
+        <v>580751</v>
       </c>
       <c r="R88" t="n">
-        <v>6963639</v>
+        <v>6963778</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10080,7 +10080,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10090,7 +10090,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10117,7 +10117,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133552463</v>
+        <v>133552476</v>
       </c>
       <c r="B89" t="n">
         <v>80473</v>
@@ -10152,10 +10152,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>580725</v>
+        <v>580767</v>
       </c>
       <c r="R89" t="n">
-        <v>6963773</v>
+        <v>6963639</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10187,7 +10187,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10197,7 +10197,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10224,32 +10224,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133550193</v>
+        <v>133552471</v>
       </c>
       <c r="B90" t="n">
-        <v>99178</v>
+        <v>83343</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10259,10 +10259,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>580781</v>
+        <v>580717</v>
       </c>
       <c r="R90" t="n">
-        <v>6963825</v>
+        <v>6963694</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10294,7 +10294,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10304,12 +10304,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>16:41</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Ca 60 ex</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10336,10 +10331,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133552471</v>
+        <v>133552493</v>
       </c>
       <c r="B91" t="n">
-        <v>83343</v>
+        <v>89338</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10347,21 +10342,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10371,10 +10366,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>580717</v>
+        <v>580914</v>
       </c>
       <c r="R91" t="n">
-        <v>6963694</v>
+        <v>6963757</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10406,7 +10401,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10416,7 +10411,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10443,32 +10438,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133552510</v>
+        <v>133550193</v>
       </c>
       <c r="B92" t="n">
-        <v>83343</v>
+        <v>99178</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10478,10 +10473,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>580829</v>
+        <v>580781</v>
       </c>
       <c r="R92" t="n">
-        <v>6963885</v>
+        <v>6963825</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10513,7 +10508,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10523,7 +10518,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Ca 60 ex</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10550,32 +10550,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133552512</v>
+        <v>133552510</v>
       </c>
       <c r="B93" t="n">
-        <v>99178</v>
+        <v>83343</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10585,10 +10585,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>580803</v>
+        <v>580829</v>
       </c>
       <c r="R93" t="n">
-        <v>6963894</v>
+        <v>6963885</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10630,12 +10630,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>150 + ex</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10774,32 +10769,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133552493</v>
+        <v>133552512</v>
       </c>
       <c r="B95" t="n">
-        <v>89338</v>
+        <v>99178</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10809,10 +10804,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>580914</v>
+        <v>580803</v>
       </c>
       <c r="R95" t="n">
-        <v>6963757</v>
+        <v>6963894</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10844,7 +10839,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10854,7 +10849,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>150 + ex</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10988,32 +10988,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>133550146</v>
+        <v>133550152</v>
       </c>
       <c r="B97" t="n">
-        <v>79358</v>
+        <v>98043</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11023,13 +11023,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>580687</v>
+        <v>580698</v>
       </c>
       <c r="R97" t="n">
-        <v>6963819</v>
+        <v>6963783</v>
       </c>
       <c r="S97" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11068,7 +11068,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11095,48 +11095,60 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>133550152</v>
+        <v>133550187</v>
       </c>
       <c r="B98" t="n">
-        <v>98043</v>
+        <v>57153</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>221945</v>
+        <v>102612</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>580698</v>
+        <v>580843</v>
       </c>
       <c r="R98" t="n">
-        <v>6963783</v>
+        <v>6963778</v>
       </c>
       <c r="S98" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11165,7 +11177,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11175,7 +11187,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11202,10 +11214,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>133550187</v>
+        <v>133550146</v>
       </c>
       <c r="B99" t="n">
-        <v>57153</v>
+        <v>79358</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11213,46 +11225,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>580843</v>
+        <v>580687</v>
       </c>
       <c r="R99" t="n">
-        <v>6963778</v>
+        <v>6963819</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11284,7 +11284,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11321,32 +11321,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133552477</v>
+        <v>133550161</v>
       </c>
       <c r="B100" t="n">
-        <v>80478</v>
+        <v>79358</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11356,13 +11356,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>580764</v>
+        <v>580727</v>
       </c>
       <c r="R100" t="n">
-        <v>6963638</v>
+        <v>6963764</v>
       </c>
       <c r="S100" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11428,10 +11428,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133550161</v>
+        <v>133552495</v>
       </c>
       <c r="B101" t="n">
-        <v>79358</v>
+        <v>57975</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11439,37 +11439,45 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>580727</v>
+        <v>580953</v>
       </c>
       <c r="R101" t="n">
-        <v>6963764</v>
+        <v>6963811</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11498,7 +11506,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11508,7 +11516,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Ett färskt ringhack på tall</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11535,56 +11548,48 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133552495</v>
+        <v>133552477</v>
       </c>
       <c r="B102" t="n">
-        <v>57975</v>
+        <v>80478</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>580953</v>
+        <v>580764</v>
       </c>
       <c r="R102" t="n">
-        <v>6963811</v>
+        <v>6963638</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11613,7 +11618,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11623,12 +11628,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Ett färskt ringhack på tall</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11655,7 +11655,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133550190</v>
+        <v>133550158</v>
       </c>
       <c r="B103" t="n">
         <v>79358</v>
@@ -11690,13 +11690,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>580838</v>
+        <v>580720</v>
       </c>
       <c r="R103" t="n">
-        <v>6963811</v>
+        <v>6963787</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11735,12 +11735,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11767,10 +11762,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133552500</v>
+        <v>133552465</v>
       </c>
       <c r="B104" t="n">
-        <v>79390</v>
+        <v>57975</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11778,37 +11773,45 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>580902</v>
+        <v>580724</v>
       </c>
       <c r="R104" t="n">
-        <v>6963823</v>
+        <v>6963746</v>
       </c>
       <c r="S104" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11837,7 +11840,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11847,7 +11850,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11874,7 +11882,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133550188</v>
+        <v>133550190</v>
       </c>
       <c r="B105" t="n">
         <v>79358</v>
@@ -11909,13 +11917,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>580833</v>
+        <v>580838</v>
       </c>
       <c r="R105" t="n">
-        <v>6963785</v>
+        <v>6963811</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11944,7 +11952,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11954,7 +11962,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11981,7 +11994,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133550158</v>
+        <v>133550177</v>
       </c>
       <c r="B106" t="n">
         <v>79358</v>
@@ -12016,13 +12029,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>580720</v>
+        <v>580864</v>
       </c>
       <c r="R106" t="n">
-        <v>6963787</v>
+        <v>6963715</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12051,7 +12064,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12061,7 +12074,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12088,10 +12101,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133552465</v>
+        <v>133552500</v>
       </c>
       <c r="B107" t="n">
-        <v>57975</v>
+        <v>79390</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12099,45 +12112,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>580724</v>
+        <v>580902</v>
       </c>
       <c r="R107" t="n">
-        <v>6963746</v>
+        <v>6963823</v>
       </c>
       <c r="S107" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12166,7 +12171,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12176,12 +12181,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12208,7 +12208,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>133550177</v>
+        <v>133550188</v>
       </c>
       <c r="B108" t="n">
         <v>79358</v>
@@ -12243,13 +12243,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>580864</v>
+        <v>580833</v>
       </c>
       <c r="R108" t="n">
-        <v>6963715</v>
+        <v>6963785</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12288,7 +12288,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD108" t="b">

--- a/artfynd/A 21339-2024 artfynd.xlsx
+++ b/artfynd/A 21339-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133552483</v>
+        <v>133550175</v>
       </c>
       <c r="B3" t="n">
-        <v>89338</v>
+        <v>79358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580906</v>
+        <v>580879</v>
       </c>
       <c r="R3" t="n">
-        <v>6963679</v>
+        <v>6963696</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133552449</v>
+        <v>133550168</v>
       </c>
       <c r="B4" t="n">
-        <v>91957</v>
+        <v>83207</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580689</v>
+        <v>580801</v>
       </c>
       <c r="R4" t="n">
-        <v>6963874</v>
+        <v>6963652</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133552481</v>
+        <v>133552511</v>
       </c>
       <c r="B5" t="n">
-        <v>89338</v>
+        <v>79390</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580869</v>
+        <v>580865</v>
       </c>
       <c r="R5" t="n">
-        <v>6963663</v>
+        <v>6963889</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133550175</v>
+        <v>133552483</v>
       </c>
       <c r="B6" t="n">
-        <v>79358</v>
+        <v>89338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580879</v>
+        <v>580906</v>
       </c>
       <c r="R6" t="n">
-        <v>6963696</v>
+        <v>6963679</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133550168</v>
+        <v>133552449</v>
       </c>
       <c r="B7" t="n">
-        <v>83207</v>
+        <v>91957</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580801</v>
+        <v>580689</v>
       </c>
       <c r="R7" t="n">
-        <v>6963652</v>
+        <v>6963874</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133552511</v>
+        <v>133552481</v>
       </c>
       <c r="B8" t="n">
-        <v>79390</v>
+        <v>89338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>510</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580865</v>
+        <v>580869</v>
       </c>
       <c r="R8" t="n">
-        <v>6963889</v>
+        <v>6963663</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2835,32 +2835,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133552451</v>
+        <v>133552457</v>
       </c>
       <c r="B22" t="n">
-        <v>91920</v>
+        <v>91957</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580669</v>
+        <v>580720</v>
       </c>
       <c r="R22" t="n">
-        <v>6963873</v>
+        <v>6963788</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2942,10 +2942,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133552457</v>
+        <v>133550171</v>
       </c>
       <c r="B23" t="n">
-        <v>91957</v>
+        <v>80473</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2953,21 +2953,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2977,13 +2977,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580720</v>
+        <v>580857</v>
       </c>
       <c r="R23" t="n">
-        <v>6963788</v>
+        <v>6963688</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3049,10 +3049,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133550171</v>
+        <v>133552464</v>
       </c>
       <c r="B24" t="n">
-        <v>80473</v>
+        <v>91957</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3060,21 +3060,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3084,13 +3084,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580857</v>
+        <v>580720</v>
       </c>
       <c r="R24" t="n">
-        <v>6963688</v>
+        <v>6963748</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3156,32 +3156,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133552464</v>
+        <v>133550184</v>
       </c>
       <c r="B25" t="n">
-        <v>91957</v>
+        <v>99178</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3191,10 +3191,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580720</v>
+        <v>580867</v>
       </c>
       <c r="R25" t="n">
-        <v>6963748</v>
+        <v>6963739</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3236,7 +3236,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>36 ex</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3263,32 +3268,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133550184</v>
+        <v>133552451</v>
       </c>
       <c r="B26" t="n">
-        <v>99178</v>
+        <v>91920</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3298,10 +3303,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580867</v>
+        <v>580669</v>
       </c>
       <c r="R26" t="n">
-        <v>6963739</v>
+        <v>6963873</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3333,7 +3338,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3343,12 +3348,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>36 ex</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -7723,10 +7723,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133552484</v>
+        <v>133550172</v>
       </c>
       <c r="B67" t="n">
-        <v>79358</v>
+        <v>91957</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7734,21 +7734,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7758,10 +7758,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>580938</v>
+        <v>580870</v>
       </c>
       <c r="R67" t="n">
-        <v>6963702</v>
+        <v>6963663</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7830,10 +7830,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133550172</v>
+        <v>133552460</v>
       </c>
       <c r="B68" t="n">
-        <v>91957</v>
+        <v>83343</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7841,21 +7841,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7865,10 +7865,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>580870</v>
+        <v>580722</v>
       </c>
       <c r="R68" t="n">
-        <v>6963663</v>
+        <v>6963787</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7900,7 +7900,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7937,10 +7937,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133552460</v>
+        <v>133552506</v>
       </c>
       <c r="B69" t="n">
-        <v>83343</v>
+        <v>57975</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7948,34 +7948,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>580722</v>
+        <v>580826</v>
       </c>
       <c r="R69" t="n">
-        <v>6963787</v>
+        <v>6963830</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8007,7 +8015,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8017,7 +8025,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8044,10 +8057,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133552506</v>
+        <v>133550144</v>
       </c>
       <c r="B70" t="n">
-        <v>57975</v>
+        <v>91957</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8055,42 +8068,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>580826</v>
+        <v>580699</v>
       </c>
       <c r="R70" t="n">
-        <v>6963830</v>
+        <v>6963819</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8122,7 +8127,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8132,12 +8137,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8164,10 +8164,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133550144</v>
+        <v>133552484</v>
       </c>
       <c r="B71" t="n">
-        <v>91957</v>
+        <v>79358</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8175,21 +8175,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8199,10 +8199,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>580699</v>
+        <v>580938</v>
       </c>
       <c r="R71" t="n">
-        <v>6963819</v>
+        <v>6963702</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9565,60 +9565,48 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133550165</v>
+        <v>133552467</v>
       </c>
       <c r="B84" t="n">
-        <v>57153</v>
+        <v>92182</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>102612</v>
+        <v>3298</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>580753</v>
+        <v>580754</v>
       </c>
       <c r="R84" t="n">
-        <v>6963702</v>
+        <v>6963789</v>
       </c>
       <c r="S84" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9647,7 +9635,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9657,7 +9645,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9684,32 +9672,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133550140</v>
+        <v>133552469</v>
       </c>
       <c r="B85" t="n">
-        <v>99178</v>
+        <v>79358</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9719,10 +9707,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>580694</v>
+        <v>580751</v>
       </c>
       <c r="R85" t="n">
-        <v>6963839</v>
+        <v>6963778</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9754,7 +9742,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9764,12 +9752,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>33 ex</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9796,7 +9779,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133552463</v>
+        <v>133552476</v>
       </c>
       <c r="B86" t="n">
         <v>80473</v>
@@ -9831,10 +9814,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>580725</v>
+        <v>580767</v>
       </c>
       <c r="R86" t="n">
-        <v>6963773</v>
+        <v>6963639</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9866,7 +9849,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9876,7 +9859,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9903,48 +9886,60 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133552467</v>
+        <v>133550165</v>
       </c>
       <c r="B87" t="n">
-        <v>92182</v>
+        <v>57153</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>3298</v>
+        <v>102612</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>580754</v>
+        <v>580753</v>
       </c>
       <c r="R87" t="n">
-        <v>6963789</v>
+        <v>6963702</v>
       </c>
       <c r="S87" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9973,7 +9968,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9983,7 +9978,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10010,32 +10005,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133552469</v>
+        <v>133550140</v>
       </c>
       <c r="B88" t="n">
-        <v>79358</v>
+        <v>99178</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10045,10 +10040,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>580751</v>
+        <v>580694</v>
       </c>
       <c r="R88" t="n">
-        <v>6963778</v>
+        <v>6963839</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10080,7 +10075,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10090,7 +10085,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>33 ex</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10117,7 +10117,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133552476</v>
+        <v>133552463</v>
       </c>
       <c r="B89" t="n">
         <v>80473</v>
@@ -10152,10 +10152,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>580767</v>
+        <v>580725</v>
       </c>
       <c r="R89" t="n">
-        <v>6963639</v>
+        <v>6963773</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10187,7 +10187,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10197,7 +10197,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11762,10 +11762,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133552465</v>
+        <v>133550190</v>
       </c>
       <c r="B104" t="n">
-        <v>57975</v>
+        <v>79358</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11773,42 +11773,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>580724</v>
+        <v>580838</v>
       </c>
       <c r="R104" t="n">
-        <v>6963746</v>
+        <v>6963811</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11840,7 +11832,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11850,12 +11842,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11882,7 +11874,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133550190</v>
+        <v>133550177</v>
       </c>
       <c r="B105" t="n">
         <v>79358</v>
@@ -11917,10 +11909,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>580838</v>
+        <v>580864</v>
       </c>
       <c r="R105" t="n">
-        <v>6963811</v>
+        <v>6963715</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11952,7 +11944,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11962,12 +11954,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11994,10 +11981,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133550177</v>
+        <v>133552500</v>
       </c>
       <c r="B106" t="n">
-        <v>79358</v>
+        <v>79390</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12005,21 +11992,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12029,13 +12016,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>580864</v>
+        <v>580902</v>
       </c>
       <c r="R106" t="n">
-        <v>6963715</v>
+        <v>6963823</v>
       </c>
       <c r="S106" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12064,7 +12051,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12074,7 +12061,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12101,10 +12088,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133552500</v>
+        <v>133550188</v>
       </c>
       <c r="B107" t="n">
-        <v>79390</v>
+        <v>79358</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12112,21 +12099,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12136,13 +12123,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>580902</v>
+        <v>580833</v>
       </c>
       <c r="R107" t="n">
-        <v>6963823</v>
+        <v>6963785</v>
       </c>
       <c r="S107" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12171,7 +12158,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12181,7 +12168,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12208,10 +12195,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>133550188</v>
+        <v>133552465</v>
       </c>
       <c r="B108" t="n">
-        <v>79358</v>
+        <v>57975</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12219,37 +12206,45 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>580833</v>
+        <v>580724</v>
       </c>
       <c r="R108" t="n">
-        <v>6963785</v>
+        <v>6963746</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12278,7 +12273,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12288,7 +12283,12 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD108" t="b">

--- a/artfynd/A 21339-2024 artfynd.xlsx
+++ b/artfynd/A 21339-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133550175</v>
+        <v>133552483</v>
       </c>
       <c r="B3" t="n">
-        <v>79358</v>
+        <v>89338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580879</v>
+        <v>580906</v>
       </c>
       <c r="R3" t="n">
-        <v>6963696</v>
+        <v>6963679</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133550168</v>
+        <v>133552449</v>
       </c>
       <c r="B4" t="n">
-        <v>83207</v>
+        <v>91957</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580801</v>
+        <v>580689</v>
       </c>
       <c r="R4" t="n">
-        <v>6963652</v>
+        <v>6963874</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133552511</v>
+        <v>133552481</v>
       </c>
       <c r="B5" t="n">
-        <v>79390</v>
+        <v>89338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580865</v>
+        <v>580869</v>
       </c>
       <c r="R5" t="n">
-        <v>6963889</v>
+        <v>6963663</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133552483</v>
+        <v>133550175</v>
       </c>
       <c r="B6" t="n">
-        <v>89338</v>
+        <v>79358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580906</v>
+        <v>580879</v>
       </c>
       <c r="R6" t="n">
-        <v>6963679</v>
+        <v>6963696</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133552449</v>
+        <v>133550168</v>
       </c>
       <c r="B7" t="n">
-        <v>91957</v>
+        <v>83207</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580689</v>
+        <v>580801</v>
       </c>
       <c r="R7" t="n">
-        <v>6963874</v>
+        <v>6963652</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133552481</v>
+        <v>133552511</v>
       </c>
       <c r="B8" t="n">
-        <v>89338</v>
+        <v>79390</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>510</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580869</v>
+        <v>580865</v>
       </c>
       <c r="R8" t="n">
-        <v>6963663</v>
+        <v>6963889</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,32 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133550155</v>
+        <v>133552468</v>
       </c>
       <c r="B9" t="n">
-        <v>80473</v>
+        <v>98043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,13 +1459,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580715</v>
+        <v>580758</v>
       </c>
       <c r="R9" t="n">
-        <v>6963791</v>
+        <v>6963787</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,12 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,32 +1531,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133552461</v>
+        <v>133552475</v>
       </c>
       <c r="B10" t="n">
-        <v>83326</v>
+        <v>79358</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580740</v>
+        <v>580801</v>
       </c>
       <c r="R10" t="n">
-        <v>6963795</v>
+        <v>6963655</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1606,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1643,32 +1638,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133550154</v>
+        <v>133550155</v>
       </c>
       <c r="B11" t="n">
-        <v>99178</v>
+        <v>80473</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1678,13 +1673,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580712</v>
+        <v>580715</v>
       </c>
       <c r="R11" t="n">
-        <v>6963788</v>
+        <v>6963791</v>
       </c>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1713,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1723,12 +1718,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>70 ex</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,32 +1750,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133552452</v>
+        <v>133552461</v>
       </c>
       <c r="B12" t="n">
-        <v>83343</v>
+        <v>83326</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,13 +1785,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580698</v>
+        <v>580740</v>
       </c>
       <c r="R12" t="n">
-        <v>6963860</v>
+        <v>6963795</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1825,7 +1820,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1830,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,32 +1857,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133552456</v>
+        <v>133550154</v>
       </c>
       <c r="B13" t="n">
-        <v>91957</v>
+        <v>99178</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,13 +1892,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580695</v>
+        <v>580712</v>
       </c>
       <c r="R13" t="n">
-        <v>6963806</v>
+        <v>6963788</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1932,7 +1927,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1937,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133550174</v>
+        <v>133552452</v>
       </c>
       <c r="B14" t="n">
-        <v>79358</v>
+        <v>83343</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,21 +1980,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2004,13 +2004,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580879</v>
+        <v>580698</v>
       </c>
       <c r="R14" t="n">
-        <v>6963690</v>
+        <v>6963860</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,32 +2076,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133550157</v>
+        <v>133552456</v>
       </c>
       <c r="B15" t="n">
-        <v>99178</v>
+        <v>91957</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580715</v>
+        <v>580695</v>
       </c>
       <c r="R15" t="n">
-        <v>6963786</v>
+        <v>6963806</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2156,12 +2156,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>150 ex</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2188,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133550153</v>
+        <v>133550174</v>
       </c>
       <c r="B16" t="n">
-        <v>80473</v>
+        <v>79358</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,21 +2194,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2223,13 +2218,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580704</v>
+        <v>580879</v>
       </c>
       <c r="R16" t="n">
-        <v>6963785</v>
+        <v>6963690</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2258,7 +2253,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2268,12 +2263,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Stora fina exemplar av lunglav, handflata storlek.</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,32 +2290,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133552468</v>
+        <v>133550157</v>
       </c>
       <c r="B17" t="n">
-        <v>98043</v>
+        <v>99178</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2335,13 +2325,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580758</v>
+        <v>580715</v>
       </c>
       <c r="R17" t="n">
-        <v>6963787</v>
+        <v>6963786</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2370,7 +2360,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2370,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,10 +2402,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133552475</v>
+        <v>133550153</v>
       </c>
       <c r="B18" t="n">
-        <v>79358</v>
+        <v>80473</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2418,21 +2413,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2442,13 +2437,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580801</v>
+        <v>580704</v>
       </c>
       <c r="R18" t="n">
-        <v>6963655</v>
+        <v>6963785</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2477,7 +2472,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2487,7 +2482,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Stora fina exemplar av lunglav, handflata storlek.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2835,32 +2835,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133552457</v>
+        <v>133552451</v>
       </c>
       <c r="B22" t="n">
-        <v>91957</v>
+        <v>91920</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580720</v>
+        <v>580669</v>
       </c>
       <c r="R22" t="n">
-        <v>6963788</v>
+        <v>6963873</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2942,10 +2942,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133550171</v>
+        <v>133552457</v>
       </c>
       <c r="B23" t="n">
-        <v>80473</v>
+        <v>91957</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2953,21 +2953,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2977,13 +2977,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580857</v>
+        <v>580720</v>
       </c>
       <c r="R23" t="n">
-        <v>6963688</v>
+        <v>6963788</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3049,10 +3049,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133552464</v>
+        <v>133550171</v>
       </c>
       <c r="B24" t="n">
-        <v>91957</v>
+        <v>80473</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3060,21 +3060,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3084,13 +3084,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580720</v>
+        <v>580857</v>
       </c>
       <c r="R24" t="n">
-        <v>6963748</v>
+        <v>6963688</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3156,32 +3156,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133550184</v>
+        <v>133552464</v>
       </c>
       <c r="B25" t="n">
-        <v>99178</v>
+        <v>91957</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3191,10 +3191,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580867</v>
+        <v>580720</v>
       </c>
       <c r="R25" t="n">
-        <v>6963739</v>
+        <v>6963748</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3236,12 +3236,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>36 ex</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3268,32 +3263,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133552451</v>
+        <v>133550184</v>
       </c>
       <c r="B26" t="n">
-        <v>91920</v>
+        <v>99178</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3303,10 +3298,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580669</v>
+        <v>580867</v>
       </c>
       <c r="R26" t="n">
-        <v>6963873</v>
+        <v>6963739</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3338,7 +3333,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3348,7 +3343,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>36 ex</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4570,10 +4570,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133552497</v>
+        <v>133552453</v>
       </c>
       <c r="B38" t="n">
-        <v>79115</v>
+        <v>79358</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4605,13 +4605,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>580939</v>
+        <v>580737</v>
       </c>
       <c r="R38" t="n">
-        <v>6963799</v>
+        <v>6963844</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4677,32 +4677,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133552478</v>
+        <v>133550136</v>
       </c>
       <c r="B39" t="n">
-        <v>80484</v>
+        <v>99178</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>580763</v>
+        <v>580702</v>
       </c>
       <c r="R39" t="n">
-        <v>6963637</v>
+        <v>6963851</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4757,7 +4757,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4784,7 +4789,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133552453</v>
+        <v>133550132</v>
       </c>
       <c r="B40" t="n">
         <v>79358</v>
@@ -4819,13 +4824,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>580737</v>
+        <v>580695</v>
       </c>
       <c r="R40" t="n">
-        <v>6963844</v>
+        <v>6963885</v>
       </c>
       <c r="S40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4854,7 +4859,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4864,7 +4869,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4891,32 +4896,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133550136</v>
+        <v>133550176</v>
       </c>
       <c r="B41" t="n">
-        <v>99178</v>
+        <v>79358</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4926,10 +4931,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>580702</v>
+        <v>580874</v>
       </c>
       <c r="R41" t="n">
-        <v>6963851</v>
+        <v>6963718</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4961,7 +4966,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4971,12 +4976,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>150 ex</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5003,7 +5003,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133550132</v>
+        <v>133550182</v>
       </c>
       <c r="B42" t="n">
         <v>79358</v>
@@ -5038,10 +5038,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>580695</v>
+        <v>580856</v>
       </c>
       <c r="R42" t="n">
-        <v>6963885</v>
+        <v>6963747</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5073,7 +5073,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5110,10 +5110,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133550176</v>
+        <v>133552494</v>
       </c>
       <c r="B43" t="n">
-        <v>79358</v>
+        <v>79390</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5121,21 +5121,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5145,10 +5145,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580874</v>
+        <v>580955</v>
       </c>
       <c r="R43" t="n">
-        <v>6963718</v>
+        <v>6963798</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5217,10 +5217,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133550182</v>
+        <v>133550166</v>
       </c>
       <c r="B44" t="n">
-        <v>79358</v>
+        <v>57153</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5228,37 +5228,49 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>580856</v>
+        <v>580800</v>
       </c>
       <c r="R44" t="n">
-        <v>6963747</v>
+        <v>6963652</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5287,7 +5299,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5297,7 +5309,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5324,10 +5336,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133552494</v>
+        <v>133552497</v>
       </c>
       <c r="B45" t="n">
-        <v>79390</v>
+        <v>79115</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5335,21 +5347,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5359,10 +5371,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580955</v>
+        <v>580939</v>
       </c>
       <c r="R45" t="n">
-        <v>6963798</v>
+        <v>6963799</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5394,7 +5406,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5404,7 +5416,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5431,60 +5443,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133550166</v>
+        <v>133552478</v>
       </c>
       <c r="B46" t="n">
-        <v>57153</v>
+        <v>80484</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102612</v>
+        <v>6463</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>580800</v>
+        <v>580763</v>
       </c>
       <c r="R46" t="n">
-        <v>6963652</v>
+        <v>6963637</v>
       </c>
       <c r="S46" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -11762,10 +11762,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133550190</v>
+        <v>133552465</v>
       </c>
       <c r="B104" t="n">
-        <v>79358</v>
+        <v>57975</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11773,34 +11773,42 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>580838</v>
+        <v>580724</v>
       </c>
       <c r="R104" t="n">
-        <v>6963811</v>
+        <v>6963746</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11832,7 +11840,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11842,12 +11850,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Med apotecier</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11874,7 +11882,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133550177</v>
+        <v>133550190</v>
       </c>
       <c r="B105" t="n">
         <v>79358</v>
@@ -11909,10 +11917,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>580864</v>
+        <v>580838</v>
       </c>
       <c r="R105" t="n">
-        <v>6963715</v>
+        <v>6963811</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11944,7 +11952,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11954,7 +11962,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11981,10 +11994,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133552500</v>
+        <v>133550177</v>
       </c>
       <c r="B106" t="n">
-        <v>79390</v>
+        <v>79358</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11992,21 +12005,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12016,13 +12029,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>580902</v>
+        <v>580864</v>
       </c>
       <c r="R106" t="n">
-        <v>6963823</v>
+        <v>6963715</v>
       </c>
       <c r="S106" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12051,7 +12064,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12061,7 +12074,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12088,10 +12101,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133550188</v>
+        <v>133552500</v>
       </c>
       <c r="B107" t="n">
-        <v>79358</v>
+        <v>79390</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12099,21 +12112,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12123,13 +12136,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>580833</v>
+        <v>580902</v>
       </c>
       <c r="R107" t="n">
-        <v>6963785</v>
+        <v>6963823</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12158,7 +12171,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12168,7 +12181,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12195,10 +12208,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>133552465</v>
+        <v>133550188</v>
       </c>
       <c r="B108" t="n">
-        <v>57975</v>
+        <v>79358</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12206,45 +12219,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>580724</v>
+        <v>580833</v>
       </c>
       <c r="R108" t="n">
-        <v>6963746</v>
+        <v>6963785</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12273,7 +12278,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12283,12 +12288,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD108" t="b">

--- a/artfynd/A 21339-2024 artfynd.xlsx
+++ b/artfynd/A 21339-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133552483</v>
+        <v>133550175</v>
       </c>
       <c r="B3" t="n">
-        <v>89338</v>
+        <v>79358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580906</v>
+        <v>580879</v>
       </c>
       <c r="R3" t="n">
-        <v>6963679</v>
+        <v>6963696</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133552449</v>
+        <v>133550168</v>
       </c>
       <c r="B4" t="n">
-        <v>91957</v>
+        <v>83207</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580689</v>
+        <v>580801</v>
       </c>
       <c r="R4" t="n">
-        <v>6963874</v>
+        <v>6963652</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133552481</v>
+        <v>133552511</v>
       </c>
       <c r="B5" t="n">
-        <v>89338</v>
+        <v>79390</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580869</v>
+        <v>580865</v>
       </c>
       <c r="R5" t="n">
-        <v>6963663</v>
+        <v>6963889</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133550175</v>
+        <v>133552483</v>
       </c>
       <c r="B6" t="n">
-        <v>79358</v>
+        <v>89338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580879</v>
+        <v>580906</v>
       </c>
       <c r="R6" t="n">
-        <v>6963696</v>
+        <v>6963679</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133550168</v>
+        <v>133552449</v>
       </c>
       <c r="B7" t="n">
-        <v>83207</v>
+        <v>91957</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580801</v>
+        <v>580689</v>
       </c>
       <c r="R7" t="n">
-        <v>6963652</v>
+        <v>6963874</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133552511</v>
+        <v>133552481</v>
       </c>
       <c r="B8" t="n">
-        <v>79390</v>
+        <v>89338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>510</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580865</v>
+        <v>580869</v>
       </c>
       <c r="R8" t="n">
-        <v>6963889</v>
+        <v>6963663</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,32 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133552468</v>
+        <v>133550155</v>
       </c>
       <c r="B9" t="n">
-        <v>98043</v>
+        <v>80473</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,13 +1459,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580758</v>
+        <v>580715</v>
       </c>
       <c r="R9" t="n">
-        <v>6963787</v>
+        <v>6963791</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,32 +1536,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133552475</v>
+        <v>133552461</v>
       </c>
       <c r="B10" t="n">
-        <v>79358</v>
+        <v>83326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580801</v>
+        <v>580740</v>
       </c>
       <c r="R10" t="n">
-        <v>6963655</v>
+        <v>6963795</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1601,7 +1606,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1616,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,32 +1643,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133550155</v>
+        <v>133550154</v>
       </c>
       <c r="B11" t="n">
-        <v>80473</v>
+        <v>99178</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,13 +1678,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580715</v>
+        <v>580712</v>
       </c>
       <c r="R11" t="n">
-        <v>6963791</v>
+        <v>6963788</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1708,7 +1713,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,12 +1723,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1750,32 +1755,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133552461</v>
+        <v>133552452</v>
       </c>
       <c r="B12" t="n">
-        <v>83326</v>
+        <v>83343</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6439</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,13 +1790,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580740</v>
+        <v>580698</v>
       </c>
       <c r="R12" t="n">
-        <v>6963795</v>
+        <v>6963860</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1820,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1830,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1857,32 +1862,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133550154</v>
+        <v>133552456</v>
       </c>
       <c r="B13" t="n">
-        <v>99178</v>
+        <v>91957</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,13 +1897,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580712</v>
+        <v>580695</v>
       </c>
       <c r="R13" t="n">
-        <v>6963788</v>
+        <v>6963806</v>
       </c>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1927,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1937,12 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:59</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>70 ex</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133552452</v>
+        <v>133550174</v>
       </c>
       <c r="B14" t="n">
-        <v>83343</v>
+        <v>79358</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,21 +1980,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2004,13 +2004,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580698</v>
+        <v>580879</v>
       </c>
       <c r="R14" t="n">
-        <v>6963860</v>
+        <v>6963690</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,32 +2076,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133552456</v>
+        <v>133550157</v>
       </c>
       <c r="B15" t="n">
-        <v>91957</v>
+        <v>99178</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580695</v>
+        <v>580715</v>
       </c>
       <c r="R15" t="n">
-        <v>6963806</v>
+        <v>6963786</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2156,7 +2156,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2183,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133550174</v>
+        <v>133550153</v>
       </c>
       <c r="B16" t="n">
-        <v>79358</v>
+        <v>80473</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2194,21 +2199,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2218,13 +2223,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580879</v>
+        <v>580704</v>
       </c>
       <c r="R16" t="n">
-        <v>6963690</v>
+        <v>6963785</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2253,7 +2258,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2263,7 +2268,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Stora fina exemplar av lunglav, handflata storlek.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2290,32 +2300,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133550157</v>
+        <v>133552468</v>
       </c>
       <c r="B17" t="n">
-        <v>99178</v>
+        <v>98043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2325,13 +2335,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580715</v>
+        <v>580758</v>
       </c>
       <c r="R17" t="n">
-        <v>6963786</v>
+        <v>6963787</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2360,7 +2370,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2370,12 +2380,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>150 ex</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2402,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133550153</v>
+        <v>133552475</v>
       </c>
       <c r="B18" t="n">
-        <v>80473</v>
+        <v>79358</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2413,21 +2418,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2437,13 +2442,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580704</v>
+        <v>580801</v>
       </c>
       <c r="R18" t="n">
-        <v>6963785</v>
+        <v>6963655</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2472,7 +2477,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2482,12 +2487,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Stora fina exemplar av lunglav, handflata storlek.</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2835,32 +2835,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133552451</v>
+        <v>133552457</v>
       </c>
       <c r="B22" t="n">
-        <v>91920</v>
+        <v>91957</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580669</v>
+        <v>580720</v>
       </c>
       <c r="R22" t="n">
-        <v>6963873</v>
+        <v>6963788</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2942,10 +2942,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133552457</v>
+        <v>133550171</v>
       </c>
       <c r="B23" t="n">
-        <v>91957</v>
+        <v>80473</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2953,21 +2953,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2977,13 +2977,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580720</v>
+        <v>580857</v>
       </c>
       <c r="R23" t="n">
-        <v>6963788</v>
+        <v>6963688</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3049,10 +3049,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133550171</v>
+        <v>133552464</v>
       </c>
       <c r="B24" t="n">
-        <v>80473</v>
+        <v>91957</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3060,21 +3060,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3084,13 +3084,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580857</v>
+        <v>580720</v>
       </c>
       <c r="R24" t="n">
-        <v>6963688</v>
+        <v>6963748</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3156,32 +3156,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133552464</v>
+        <v>133550184</v>
       </c>
       <c r="B25" t="n">
-        <v>91957</v>
+        <v>99178</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3191,10 +3191,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580720</v>
+        <v>580867</v>
       </c>
       <c r="R25" t="n">
-        <v>6963748</v>
+        <v>6963739</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3236,7 +3236,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>36 ex</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3263,32 +3268,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133550184</v>
+        <v>133552451</v>
       </c>
       <c r="B26" t="n">
-        <v>99178</v>
+        <v>91920</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3298,10 +3303,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580867</v>
+        <v>580669</v>
       </c>
       <c r="R26" t="n">
-        <v>6963739</v>
+        <v>6963873</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3333,7 +3338,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3343,12 +3348,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>36 ex</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -10224,32 +10224,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133552471</v>
+        <v>133550193</v>
       </c>
       <c r="B90" t="n">
-        <v>83343</v>
+        <v>99178</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10259,10 +10259,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>580717</v>
+        <v>580781</v>
       </c>
       <c r="R90" t="n">
-        <v>6963694</v>
+        <v>6963825</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10294,7 +10294,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10304,7 +10304,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ca 60 ex</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10331,10 +10336,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133552493</v>
+        <v>133552510</v>
       </c>
       <c r="B91" t="n">
-        <v>89338</v>
+        <v>83343</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10342,21 +10347,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>510</v>
+        <v>6440</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10366,10 +10371,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>580914</v>
+        <v>580829</v>
       </c>
       <c r="R91" t="n">
-        <v>6963757</v>
+        <v>6963885</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10401,7 +10406,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10411,7 +10416,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10438,7 +10443,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133550193</v>
+        <v>133552455</v>
       </c>
       <c r="B92" t="n">
         <v>99178</v>
@@ -10473,10 +10478,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>580781</v>
+        <v>580733</v>
       </c>
       <c r="R92" t="n">
-        <v>6963825</v>
+        <v>6963814</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10508,7 +10513,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10518,12 +10523,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Ca 60 ex</t>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10550,32 +10555,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133552510</v>
+        <v>133552512</v>
       </c>
       <c r="B93" t="n">
-        <v>83343</v>
+        <v>99178</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10585,10 +10590,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>580829</v>
+        <v>580803</v>
       </c>
       <c r="R93" t="n">
-        <v>6963885</v>
+        <v>6963894</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10620,7 +10625,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10630,7 +10635,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>150 + ex</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10657,32 +10667,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133552455</v>
+        <v>133552471</v>
       </c>
       <c r="B94" t="n">
-        <v>99178</v>
+        <v>83343</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10692,10 +10702,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>580733</v>
+        <v>580717</v>
       </c>
       <c r="R94" t="n">
-        <v>6963814</v>
+        <v>6963694</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10727,7 +10737,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10737,12 +10747,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>200 ex</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10769,32 +10774,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133552512</v>
+        <v>133552493</v>
       </c>
       <c r="B95" t="n">
-        <v>99178</v>
+        <v>89338</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10804,10 +10809,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>580803</v>
+        <v>580914</v>
       </c>
       <c r="R95" t="n">
-        <v>6963894</v>
+        <v>6963757</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10839,7 +10844,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10849,12 +10854,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>150 + ex</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11762,10 +11762,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133552465</v>
+        <v>133550190</v>
       </c>
       <c r="B104" t="n">
-        <v>57975</v>
+        <v>79358</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11773,42 +11773,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>580724</v>
+        <v>580838</v>
       </c>
       <c r="R104" t="n">
-        <v>6963746</v>
+        <v>6963811</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11840,7 +11832,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11850,12 +11842,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11882,7 +11874,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133550190</v>
+        <v>133550177</v>
       </c>
       <c r="B105" t="n">
         <v>79358</v>
@@ -11917,10 +11909,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>580838</v>
+        <v>580864</v>
       </c>
       <c r="R105" t="n">
-        <v>6963811</v>
+        <v>6963715</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11952,7 +11944,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11962,12 +11954,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11994,10 +11981,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133550177</v>
+        <v>133552500</v>
       </c>
       <c r="B106" t="n">
-        <v>79358</v>
+        <v>79390</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12005,21 +11992,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12029,13 +12016,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>580864</v>
+        <v>580902</v>
       </c>
       <c r="R106" t="n">
-        <v>6963715</v>
+        <v>6963823</v>
       </c>
       <c r="S106" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12064,7 +12051,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12074,7 +12061,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12101,10 +12088,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133552500</v>
+        <v>133550188</v>
       </c>
       <c r="B107" t="n">
-        <v>79390</v>
+        <v>79358</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12112,21 +12099,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12136,13 +12123,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>580902</v>
+        <v>580833</v>
       </c>
       <c r="R107" t="n">
-        <v>6963823</v>
+        <v>6963785</v>
       </c>
       <c r="S107" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12171,7 +12158,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12181,7 +12168,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12208,10 +12195,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>133550188</v>
+        <v>133552465</v>
       </c>
       <c r="B108" t="n">
-        <v>79358</v>
+        <v>57975</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12219,37 +12206,45 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>580833</v>
+        <v>580724</v>
       </c>
       <c r="R108" t="n">
-        <v>6963785</v>
+        <v>6963746</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12278,7 +12273,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12288,7 +12283,12 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD108" t="b">

--- a/artfynd/A 21339-2024 artfynd.xlsx
+++ b/artfynd/A 21339-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133550167</v>
       </c>
       <c r="B2" t="n">
-        <v>89338</v>
+        <v>89339</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133550175</v>
+        <v>133552483</v>
       </c>
       <c r="B3" t="n">
-        <v>79358</v>
+        <v>89339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580879</v>
+        <v>580906</v>
       </c>
       <c r="R3" t="n">
-        <v>6963696</v>
+        <v>6963679</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133550168</v>
+        <v>133550175</v>
       </c>
       <c r="B4" t="n">
-        <v>83207</v>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580801</v>
+        <v>580879</v>
       </c>
       <c r="R4" t="n">
-        <v>6963652</v>
+        <v>6963696</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133552511</v>
+        <v>133550168</v>
       </c>
       <c r="B5" t="n">
-        <v>79390</v>
+        <v>83208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580865</v>
+        <v>580801</v>
       </c>
       <c r="R5" t="n">
-        <v>6963889</v>
+        <v>6963652</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133552483</v>
+        <v>133552481</v>
       </c>
       <c r="B6" t="n">
-        <v>89338</v>
+        <v>89339</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580906</v>
+        <v>580869</v>
       </c>
       <c r="R6" t="n">
-        <v>6963679</v>
+        <v>6963663</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133552449</v>
+        <v>133552511</v>
       </c>
       <c r="B7" t="n">
-        <v>91957</v>
+        <v>79391</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580689</v>
+        <v>580865</v>
       </c>
       <c r="R7" t="n">
-        <v>6963874</v>
+        <v>6963889</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133552481</v>
+        <v>133552449</v>
       </c>
       <c r="B8" t="n">
-        <v>89338</v>
+        <v>91959</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580869</v>
+        <v>580689</v>
       </c>
       <c r="R8" t="n">
-        <v>6963663</v>
+        <v>6963874</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,32 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133550155</v>
+        <v>133552468</v>
       </c>
       <c r="B9" t="n">
-        <v>80473</v>
+        <v>98045</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,13 +1459,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580715</v>
+        <v>580758</v>
       </c>
       <c r="R9" t="n">
-        <v>6963791</v>
+        <v>6963787</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,12 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,32 +1531,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133552461</v>
+        <v>133550155</v>
       </c>
       <c r="B10" t="n">
-        <v>83326</v>
+        <v>80474</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6439</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,13 +1566,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580740</v>
+        <v>580715</v>
       </c>
       <c r="R10" t="n">
-        <v>6963795</v>
+        <v>6963791</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1606,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,7 +1611,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1643,32 +1643,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133550154</v>
+        <v>133552461</v>
       </c>
       <c r="B11" t="n">
-        <v>99178</v>
+        <v>83327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6439</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1678,13 +1678,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580712</v>
+        <v>580740</v>
       </c>
       <c r="R11" t="n">
-        <v>6963788</v>
+        <v>6963795</v>
       </c>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1723,12 +1723,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:59</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>70 ex</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,32 +1750,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133552452</v>
+        <v>133550154</v>
       </c>
       <c r="B12" t="n">
-        <v>83343</v>
+        <v>99180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,13 +1785,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580698</v>
+        <v>580712</v>
       </c>
       <c r="R12" t="n">
-        <v>6963860</v>
+        <v>6963788</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1825,7 +1820,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1830,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133552456</v>
+        <v>133552452</v>
       </c>
       <c r="B13" t="n">
-        <v>91957</v>
+        <v>83344</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,21 +1873,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,13 +1897,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580695</v>
+        <v>580698</v>
       </c>
       <c r="R13" t="n">
-        <v>6963806</v>
+        <v>6963860</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133550174</v>
+        <v>133552456</v>
       </c>
       <c r="B14" t="n">
-        <v>79358</v>
+        <v>91959</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,21 +1980,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580879</v>
+        <v>580695</v>
       </c>
       <c r="R14" t="n">
-        <v>6963690</v>
+        <v>6963806</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,32 +2076,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133550157</v>
+        <v>133550174</v>
       </c>
       <c r="B15" t="n">
-        <v>99178</v>
+        <v>79359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580715</v>
+        <v>580879</v>
       </c>
       <c r="R15" t="n">
-        <v>6963786</v>
+        <v>6963690</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2156,12 +2156,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>150 ex</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2188,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133550153</v>
+        <v>133552475</v>
       </c>
       <c r="B16" t="n">
-        <v>80473</v>
+        <v>79359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,21 +2194,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2223,13 +2218,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580704</v>
+        <v>580801</v>
       </c>
       <c r="R16" t="n">
-        <v>6963785</v>
+        <v>6963655</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2258,7 +2253,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2268,12 +2263,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Stora fina exemplar av lunglav, handflata storlek.</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,32 +2290,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133552468</v>
+        <v>133550157</v>
       </c>
       <c r="B17" t="n">
-        <v>98043</v>
+        <v>99180</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2335,13 +2325,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580758</v>
+        <v>580715</v>
       </c>
       <c r="R17" t="n">
-        <v>6963787</v>
+        <v>6963786</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2370,7 +2360,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2380,7 +2370,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2407,10 +2402,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133552475</v>
+        <v>133550153</v>
       </c>
       <c r="B18" t="n">
-        <v>79358</v>
+        <v>80474</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2418,21 +2413,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2442,13 +2437,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580801</v>
+        <v>580704</v>
       </c>
       <c r="R18" t="n">
-        <v>6963655</v>
+        <v>6963785</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2477,7 +2472,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2487,7 +2482,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Stora fina exemplar av lunglav, handflata storlek.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2514,10 +2514,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133552492</v>
+        <v>133550164</v>
       </c>
       <c r="B19" t="n">
-        <v>79116</v>
+        <v>79359</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2525,21 +2525,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2549,13 +2549,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580892</v>
+        <v>580751</v>
       </c>
       <c r="R19" t="n">
-        <v>6963759</v>
+        <v>6963748</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2621,10 +2621,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133550164</v>
+        <v>133552509</v>
       </c>
       <c r="B20" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2656,13 +2656,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580751</v>
+        <v>580814</v>
       </c>
       <c r="R20" t="n">
-        <v>6963748</v>
+        <v>6963859</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2728,10 +2728,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133552509</v>
+        <v>133552492</v>
       </c>
       <c r="B21" t="n">
-        <v>79358</v>
+        <v>79117</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2739,21 +2739,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580814</v>
+        <v>580892</v>
       </c>
       <c r="R21" t="n">
-        <v>6963859</v>
+        <v>6963759</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2838,7 +2838,7 @@
         <v>133552457</v>
       </c>
       <c r="B22" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>133550171</v>
       </c>
       <c r="B23" t="n">
-        <v>80473</v>
+        <v>80474</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>133552464</v>
       </c>
       <c r="B24" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3156,32 +3156,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133550184</v>
+        <v>133552451</v>
       </c>
       <c r="B25" t="n">
-        <v>99178</v>
+        <v>91922</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3191,10 +3191,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580867</v>
+        <v>580669</v>
       </c>
       <c r="R25" t="n">
-        <v>6963739</v>
+        <v>6963873</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3236,12 +3236,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>36 ex</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3268,32 +3263,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133552451</v>
+        <v>133550184</v>
       </c>
       <c r="B26" t="n">
-        <v>91920</v>
+        <v>99180</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3303,10 +3298,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580669</v>
+        <v>580867</v>
       </c>
       <c r="R26" t="n">
-        <v>6963873</v>
+        <v>6963739</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3338,7 +3333,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3348,7 +3343,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>36 ex</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3378,7 +3378,7 @@
         <v>133550156</v>
       </c>
       <c r="B27" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>133550185</v>
       </c>
       <c r="B28" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>133550191</v>
       </c>
       <c r="B29" t="n">
-        <v>92228</v>
+        <v>92230</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>133552472</v>
       </c>
       <c r="B30" t="n">
-        <v>91971</v>
+        <v>91973</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
         <v>133552447</v>
       </c>
       <c r="B31" t="n">
-        <v>79390</v>
+        <v>79391</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3910,32 +3910,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133552502</v>
+        <v>133552488</v>
       </c>
       <c r="B32" t="n">
-        <v>80367</v>
+        <v>89339</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6456</v>
+        <v>510</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3945,10 +3945,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>580865</v>
+        <v>580943</v>
       </c>
       <c r="R32" t="n">
-        <v>6963830</v>
+        <v>6963738</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4017,56 +4017,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133550180</v>
+        <v>133552502</v>
       </c>
       <c r="B33" t="n">
-        <v>57975</v>
+        <v>80368</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>580876</v>
+        <v>580865</v>
       </c>
       <c r="R33" t="n">
-        <v>6963707</v>
+        <v>6963830</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4095,7 +4087,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4105,12 +4097,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:14</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4137,32 +4124,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133550163</v>
+        <v>133550148</v>
       </c>
       <c r="B34" t="n">
-        <v>98043</v>
+        <v>99180</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4172,13 +4159,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>580728</v>
+        <v>580696</v>
       </c>
       <c r="R34" t="n">
-        <v>6963787</v>
+        <v>6963788</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4207,7 +4194,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4217,7 +4204,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4244,10 +4236,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133552488</v>
+        <v>133550138</v>
       </c>
       <c r="B35" t="n">
-        <v>89338</v>
+        <v>79359</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4255,21 +4247,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4279,10 +4271,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>580943</v>
+        <v>580712</v>
       </c>
       <c r="R35" t="n">
-        <v>6963738</v>
+        <v>6963853</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4314,7 +4306,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4324,7 +4316,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4351,48 +4343,56 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133550148</v>
+        <v>133550180</v>
       </c>
       <c r="B36" t="n">
-        <v>99178</v>
+        <v>57975</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>580696</v>
+        <v>580876</v>
       </c>
       <c r="R36" t="n">
-        <v>6963788</v>
+        <v>6963707</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>120 ex</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4463,32 +4463,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133550138</v>
+        <v>133550163</v>
       </c>
       <c r="B37" t="n">
-        <v>79358</v>
+        <v>98045</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>580712</v>
+        <v>580728</v>
       </c>
       <c r="R37" t="n">
-        <v>6963853</v>
+        <v>6963787</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4570,10 +4570,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133552453</v>
+        <v>133552497</v>
       </c>
       <c r="B38" t="n">
-        <v>79358</v>
+        <v>79116</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4605,13 +4605,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>580737</v>
+        <v>580939</v>
       </c>
       <c r="R38" t="n">
-        <v>6963844</v>
+        <v>6963799</v>
       </c>
       <c r="S38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4677,32 +4677,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133550136</v>
+        <v>133552453</v>
       </c>
       <c r="B39" t="n">
-        <v>99178</v>
+        <v>79359</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4712,13 +4712,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>580702</v>
+        <v>580737</v>
       </c>
       <c r="R39" t="n">
-        <v>6963851</v>
+        <v>6963844</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4757,12 +4757,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>150 ex</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4789,32 +4784,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133550132</v>
+        <v>133550136</v>
       </c>
       <c r="B40" t="n">
-        <v>79358</v>
+        <v>99180</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4824,10 +4819,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>580695</v>
+        <v>580702</v>
       </c>
       <c r="R40" t="n">
-        <v>6963885</v>
+        <v>6963851</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4859,7 +4854,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4869,7 +4864,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4896,10 +4896,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133550176</v>
+        <v>133550132</v>
       </c>
       <c r="B41" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4931,10 +4931,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>580874</v>
+        <v>580695</v>
       </c>
       <c r="R41" t="n">
-        <v>6963718</v>
+        <v>6963885</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5006,7 +5006,7 @@
         <v>133550182</v>
       </c>
       <c r="B42" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5110,32 +5110,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133552494</v>
+        <v>133552478</v>
       </c>
       <c r="B43" t="n">
-        <v>79390</v>
+        <v>80485</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>185</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5145,10 +5145,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580955</v>
+        <v>580763</v>
       </c>
       <c r="R43" t="n">
-        <v>6963798</v>
+        <v>6963637</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5217,10 +5217,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133550166</v>
+        <v>133552494</v>
       </c>
       <c r="B44" t="n">
-        <v>57153</v>
+        <v>79391</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5228,49 +5228,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>102612</v>
+        <v>185</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>580800</v>
+        <v>580955</v>
       </c>
       <c r="R44" t="n">
-        <v>6963652</v>
+        <v>6963798</v>
       </c>
       <c r="S44" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5299,7 +5287,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5309,7 +5297,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5336,10 +5324,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133552497</v>
+        <v>133550166</v>
       </c>
       <c r="B45" t="n">
-        <v>79115</v>
+        <v>57153</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5347,37 +5335,49 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>102612</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580939</v>
+        <v>580800</v>
       </c>
       <c r="R45" t="n">
-        <v>6963799</v>
+        <v>6963652</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5443,27 +5443,27 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133552478</v>
+        <v>133550176</v>
       </c>
       <c r="B46" t="n">
-        <v>80484</v>
+        <v>79359</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5478,10 +5478,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>580763</v>
+        <v>580874</v>
       </c>
       <c r="R46" t="n">
-        <v>6963637</v>
+        <v>6963718</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5553,7 +5553,7 @@
         <v>133550162</v>
       </c>
       <c r="B47" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5782,32 +5782,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133552490</v>
+        <v>133550147</v>
       </c>
       <c r="B49" t="n">
-        <v>80473</v>
+        <v>99180</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5817,13 +5817,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>580853</v>
+        <v>580689</v>
       </c>
       <c r="R49" t="n">
-        <v>6963702</v>
+        <v>6963814</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5862,7 +5862,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5889,10 +5894,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133552491</v>
+        <v>133552490</v>
       </c>
       <c r="B50" t="n">
-        <v>79358</v>
+        <v>80474</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5900,21 +5905,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5924,10 +5929,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>580883</v>
+        <v>580853</v>
       </c>
       <c r="R50" t="n">
-        <v>6963753</v>
+        <v>6963702</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5959,7 +5964,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5969,7 +5974,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5996,10 +6001,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133552482</v>
+        <v>133552503</v>
       </c>
       <c r="B51" t="n">
-        <v>83343</v>
+        <v>89339</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6007,21 +6012,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6031,10 +6036,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>580879</v>
+        <v>580844</v>
       </c>
       <c r="R51" t="n">
-        <v>6963658</v>
+        <v>6963844</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6066,7 +6071,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6076,7 +6081,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6103,10 +6108,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133552486</v>
+        <v>133552491</v>
       </c>
       <c r="B52" t="n">
-        <v>83343</v>
+        <v>79359</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6114,21 +6119,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6138,10 +6143,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>580985</v>
+        <v>580883</v>
       </c>
       <c r="R52" t="n">
-        <v>6963707</v>
+        <v>6963753</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6173,7 +6178,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6183,7 +6188,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6210,10 +6215,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133552448</v>
+        <v>133552482</v>
       </c>
       <c r="B53" t="n">
-        <v>91957</v>
+        <v>83344</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6221,21 +6226,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6245,10 +6250,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>580691</v>
+        <v>580879</v>
       </c>
       <c r="R53" t="n">
-        <v>6963879</v>
+        <v>6963658</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6280,7 +6285,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6290,7 +6295,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6317,32 +6322,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133550147</v>
+        <v>133552486</v>
       </c>
       <c r="B54" t="n">
-        <v>99178</v>
+        <v>83344</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6352,13 +6357,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>580689</v>
+        <v>580985</v>
       </c>
       <c r="R54" t="n">
-        <v>6963814</v>
+        <v>6963707</v>
       </c>
       <c r="S54" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6387,7 +6392,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6397,12 +6402,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>70 ex</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6429,10 +6429,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133552503</v>
+        <v>133550160</v>
       </c>
       <c r="B55" t="n">
-        <v>89338</v>
+        <v>92230</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6440,21 +6440,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6464,13 +6464,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>580844</v>
+        <v>580715</v>
       </c>
       <c r="R55" t="n">
-        <v>6963844</v>
+        <v>6963743</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6536,10 +6536,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133550160</v>
+        <v>133552448</v>
       </c>
       <c r="B56" t="n">
-        <v>92228</v>
+        <v>91959</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6547,21 +6547,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6571,13 +6571,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>580715</v>
+        <v>580691</v>
       </c>
       <c r="R56" t="n">
-        <v>6963743</v>
+        <v>6963879</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6643,10 +6643,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133552458</v>
+        <v>133550143</v>
       </c>
       <c r="B57" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>580716</v>
+        <v>580713</v>
       </c>
       <c r="R57" t="n">
-        <v>6963787</v>
+        <v>6963831</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6713,7 +6713,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6750,10 +6750,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133552450</v>
+        <v>133552458</v>
       </c>
       <c r="B58" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6785,13 +6785,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>580683</v>
+        <v>580716</v>
       </c>
       <c r="R58" t="n">
-        <v>6963870</v>
+        <v>6963787</v>
       </c>
       <c r="S58" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6857,10 +6857,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133552473</v>
+        <v>133552450</v>
       </c>
       <c r="B59" t="n">
-        <v>80473</v>
+        <v>79359</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6868,21 +6868,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6892,13 +6892,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>580754</v>
+        <v>580683</v>
       </c>
       <c r="R59" t="n">
-        <v>6963659</v>
+        <v>6963870</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6964,10 +6964,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133550143</v>
+        <v>133552473</v>
       </c>
       <c r="B60" t="n">
-        <v>79358</v>
+        <v>80474</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6975,21 +6975,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6999,10 +6999,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>580713</v>
+        <v>580754</v>
       </c>
       <c r="R60" t="n">
-        <v>6963831</v>
+        <v>6963659</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7074,7 +7074,7 @@
         <v>133552485</v>
       </c>
       <c r="B61" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         <v>133552466</v>
       </c>
       <c r="B62" t="n">
-        <v>83343</v>
+        <v>83344</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         <v>133550133</v>
       </c>
       <c r="B63" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7397,32 +7397,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133550134</v>
+        <v>133552507</v>
       </c>
       <c r="B64" t="n">
-        <v>99178</v>
+        <v>80424</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7432,13 +7432,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>580691</v>
+        <v>580830</v>
       </c>
       <c r="R64" t="n">
-        <v>6963863</v>
+        <v>6963821</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7477,12 +7477,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>200 ex</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7509,32 +7504,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133550170</v>
+        <v>133550134</v>
       </c>
       <c r="B65" t="n">
-        <v>79390</v>
+        <v>99180</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7544,10 +7539,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>580801</v>
+        <v>580691</v>
       </c>
       <c r="R65" t="n">
-        <v>6963652</v>
+        <v>6963863</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7579,7 +7574,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7589,7 +7584,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7616,32 +7616,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133552507</v>
+        <v>133550170</v>
       </c>
       <c r="B66" t="n">
-        <v>80423</v>
+        <v>79391</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229497</v>
+        <v>185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7651,13 +7651,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>580830</v>
+        <v>580801</v>
       </c>
       <c r="R66" t="n">
-        <v>6963821</v>
+        <v>6963652</v>
       </c>
       <c r="S66" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7726,7 +7726,7 @@
         <v>133550172</v>
       </c>
       <c r="B67" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7830,10 +7830,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133552460</v>
+        <v>133552484</v>
       </c>
       <c r="B68" t="n">
-        <v>83343</v>
+        <v>79359</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7841,21 +7841,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7865,10 +7865,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>580722</v>
+        <v>580938</v>
       </c>
       <c r="R68" t="n">
-        <v>6963787</v>
+        <v>6963702</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7900,7 +7900,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7937,10 +7937,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133552506</v>
+        <v>133552460</v>
       </c>
       <c r="B69" t="n">
-        <v>57975</v>
+        <v>83344</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7948,42 +7948,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>580826</v>
+        <v>580722</v>
       </c>
       <c r="R69" t="n">
-        <v>6963830</v>
+        <v>6963787</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8015,7 +8007,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8025,12 +8017,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8060,7 +8047,7 @@
         <v>133550144</v>
       </c>
       <c r="B70" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8164,10 +8151,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133552484</v>
+        <v>133552506</v>
       </c>
       <c r="B71" t="n">
-        <v>79358</v>
+        <v>57975</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8175,34 +8162,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>580938</v>
+        <v>580826</v>
       </c>
       <c r="R71" t="n">
-        <v>6963702</v>
+        <v>6963830</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8234,7 +8229,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8244,7 +8239,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8271,10 +8271,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133552454</v>
+        <v>133550149</v>
       </c>
       <c r="B72" t="n">
-        <v>91957</v>
+        <v>79359</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8282,21 +8282,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8306,13 +8306,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>580734</v>
+        <v>580697</v>
       </c>
       <c r="R72" t="n">
-        <v>6963814</v>
+        <v>6963788</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8351,7 +8351,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8378,10 +8378,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133550139</v>
+        <v>133552454</v>
       </c>
       <c r="B73" t="n">
-        <v>80473</v>
+        <v>91959</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8389,21 +8389,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8413,10 +8413,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>580689</v>
+        <v>580734</v>
       </c>
       <c r="R73" t="n">
-        <v>6963841</v>
+        <v>6963814</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8448,7 +8448,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8458,12 +8458,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:19</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8490,10 +8485,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133550149</v>
+        <v>133550139</v>
       </c>
       <c r="B74" t="n">
-        <v>79358</v>
+        <v>80474</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8501,21 +8496,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8525,13 +8520,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>580697</v>
+        <v>580689</v>
       </c>
       <c r="R74" t="n">
-        <v>6963788</v>
+        <v>6963841</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8560,7 +8555,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8570,7 +8565,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8597,10 +8597,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133550179</v>
+        <v>133552487</v>
       </c>
       <c r="B75" t="n">
-        <v>91957</v>
+        <v>89339</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8608,21 +8608,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8632,10 +8632,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>580862</v>
+        <v>580983</v>
       </c>
       <c r="R75" t="n">
-        <v>6963713</v>
+        <v>6963709</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8667,7 +8667,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8704,10 +8704,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133552462</v>
+        <v>133550179</v>
       </c>
       <c r="B76" t="n">
-        <v>83335</v>
+        <v>91959</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8715,21 +8715,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8739,10 +8739,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>580738</v>
+        <v>580862</v>
       </c>
       <c r="R76" t="n">
-        <v>6963776</v>
+        <v>6963713</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8811,10 +8811,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133550173</v>
+        <v>133552513</v>
       </c>
       <c r="B77" t="n">
-        <v>80473</v>
+        <v>83336</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8822,21 +8822,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8846,13 +8846,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>580878</v>
+        <v>580785</v>
       </c>
       <c r="R77" t="n">
-        <v>6963692</v>
+        <v>6963796</v>
       </c>
       <c r="S77" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8918,10 +8918,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133552487</v>
+        <v>133552462</v>
       </c>
       <c r="B78" t="n">
-        <v>89338</v>
+        <v>83336</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8929,21 +8929,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>510</v>
+        <v>308</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8953,10 +8953,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>580983</v>
+        <v>580738</v>
       </c>
       <c r="R78" t="n">
-        <v>6963709</v>
+        <v>6963776</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8988,7 +8988,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9025,32 +9025,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133550186</v>
+        <v>133550141</v>
       </c>
       <c r="B79" t="n">
-        <v>89338</v>
+        <v>99180</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9060,13 +9060,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>580871</v>
+        <v>580713</v>
       </c>
       <c r="R79" t="n">
-        <v>6963767</v>
+        <v>6963840</v>
       </c>
       <c r="S79" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9105,7 +9105,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>60 ex, troligen fler</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9132,10 +9137,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133552513</v>
+        <v>133550173</v>
       </c>
       <c r="B80" t="n">
-        <v>83335</v>
+        <v>80474</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9143,21 +9148,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9167,13 +9172,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>580785</v>
+        <v>580878</v>
       </c>
       <c r="R80" t="n">
-        <v>6963796</v>
+        <v>6963692</v>
       </c>
       <c r="S80" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9202,7 +9207,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9212,7 +9217,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9239,10 +9244,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133552499</v>
+        <v>133550186</v>
       </c>
       <c r="B81" t="n">
-        <v>91957</v>
+        <v>89339</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9250,21 +9255,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9274,13 +9279,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>580926</v>
+        <v>580871</v>
       </c>
       <c r="R81" t="n">
-        <v>6963805</v>
+        <v>6963767</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9309,7 +9314,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9319,7 +9324,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9346,32 +9351,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133550141</v>
+        <v>133552499</v>
       </c>
       <c r="B82" t="n">
-        <v>99178</v>
+        <v>91959</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9381,10 +9386,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>580713</v>
+        <v>580926</v>
       </c>
       <c r="R82" t="n">
-        <v>6963840</v>
+        <v>6963805</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9416,7 +9421,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9426,12 +9431,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:29</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>60 ex, troligen fler</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9458,32 +9458,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>133552505</v>
+        <v>133552467</v>
       </c>
       <c r="B83" t="n">
-        <v>79358</v>
+        <v>92184</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9493,13 +9493,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>580836</v>
+        <v>580754</v>
       </c>
       <c r="R83" t="n">
-        <v>6963844</v>
+        <v>6963789</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9538,7 +9538,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9565,32 +9565,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133552467</v>
+        <v>133552505</v>
       </c>
       <c r="B84" t="n">
-        <v>92182</v>
+        <v>79359</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>580754</v>
+        <v>580836</v>
       </c>
       <c r="R84" t="n">
-        <v>6963789</v>
+        <v>6963844</v>
       </c>
       <c r="S84" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9645,7 +9645,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9675,7 +9675,7 @@
         <v>133552469</v>
       </c>
       <c r="B85" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9779,10 +9779,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133552476</v>
+        <v>133550165</v>
       </c>
       <c r="B86" t="n">
-        <v>80473</v>
+        <v>57153</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9790,37 +9790,49 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>580767</v>
+        <v>580753</v>
       </c>
       <c r="R86" t="n">
-        <v>6963639</v>
+        <v>6963702</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9849,7 +9861,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9859,7 +9871,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9886,60 +9898,48 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133550165</v>
+        <v>133550140</v>
       </c>
       <c r="B87" t="n">
-        <v>57153</v>
+        <v>99180</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>580753</v>
+        <v>580694</v>
       </c>
       <c r="R87" t="n">
-        <v>6963702</v>
+        <v>6963839</v>
       </c>
       <c r="S87" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9968,7 +9968,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9978,7 +9978,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>33 ex</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10005,32 +10010,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133550140</v>
+        <v>133552476</v>
       </c>
       <c r="B88" t="n">
-        <v>99178</v>
+        <v>80474</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10040,10 +10045,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>580694</v>
+        <v>580767</v>
       </c>
       <c r="R88" t="n">
-        <v>6963839</v>
+        <v>6963639</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10075,7 +10080,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10085,12 +10090,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:21</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>33 ex</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10120,7 +10120,7 @@
         <v>133552463</v>
       </c>
       <c r="B89" t="n">
-        <v>80473</v>
+        <v>80474</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         <v>133550193</v>
       </c>
       <c r="B90" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>133552510</v>
       </c>
       <c r="B91" t="n">
-        <v>83343</v>
+        <v>83344</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10443,32 +10443,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133552455</v>
+        <v>133552471</v>
       </c>
       <c r="B92" t="n">
-        <v>99178</v>
+        <v>83344</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10478,10 +10478,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>580733</v>
+        <v>580717</v>
       </c>
       <c r="R92" t="n">
-        <v>6963814</v>
+        <v>6963694</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10523,12 +10523,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>200 ex</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10555,10 +10550,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133552512</v>
+        <v>133552455</v>
       </c>
       <c r="B93" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10590,10 +10585,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>580803</v>
+        <v>580733</v>
       </c>
       <c r="R93" t="n">
-        <v>6963894</v>
+        <v>6963814</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10625,7 +10620,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10635,12 +10630,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>150 + ex</t>
+          <t>200 ex</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10667,32 +10662,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133552471</v>
+        <v>133552512</v>
       </c>
       <c r="B94" t="n">
-        <v>83343</v>
+        <v>99180</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10702,10 +10697,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>580717</v>
+        <v>580803</v>
       </c>
       <c r="R94" t="n">
-        <v>6963694</v>
+        <v>6963894</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10737,7 +10732,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10747,7 +10742,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>150 + ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10777,7 +10777,7 @@
         <v>133552493</v>
       </c>
       <c r="B95" t="n">
-        <v>89338</v>
+        <v>89339</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>133552501</v>
       </c>
       <c r="B96" t="n">
-        <v>89338</v>
+        <v>89339</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10988,32 +10988,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>133550152</v>
+        <v>133550146</v>
       </c>
       <c r="B97" t="n">
-        <v>98043</v>
+        <v>79359</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11023,13 +11023,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>580698</v>
+        <v>580687</v>
       </c>
       <c r="R97" t="n">
-        <v>6963783</v>
+        <v>6963819</v>
       </c>
       <c r="S97" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11068,7 +11068,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11095,60 +11095,48 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>133550187</v>
+        <v>133550152</v>
       </c>
       <c r="B98" t="n">
-        <v>57153</v>
+        <v>98045</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>102612</v>
+        <v>221945</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>580843</v>
+        <v>580698</v>
       </c>
       <c r="R98" t="n">
-        <v>6963778</v>
+        <v>6963783</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11177,7 +11165,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11187,7 +11175,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11214,10 +11202,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>133550146</v>
+        <v>133550187</v>
       </c>
       <c r="B99" t="n">
-        <v>79358</v>
+        <v>57153</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11225,34 +11213,46 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>580687</v>
+        <v>580843</v>
       </c>
       <c r="R99" t="n">
-        <v>6963819</v>
+        <v>6963778</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11284,7 +11284,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11321,32 +11321,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133550161</v>
+        <v>133552477</v>
       </c>
       <c r="B100" t="n">
-        <v>79358</v>
+        <v>80479</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11356,13 +11356,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>580727</v>
+        <v>580764</v>
       </c>
       <c r="R100" t="n">
-        <v>6963764</v>
+        <v>6963638</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11428,10 +11428,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133552495</v>
+        <v>133550161</v>
       </c>
       <c r="B101" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11439,45 +11439,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>580953</v>
+        <v>580727</v>
       </c>
       <c r="R101" t="n">
-        <v>6963811</v>
+        <v>6963764</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11506,7 +11498,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11516,12 +11508,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:41</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Ett färskt ringhack på tall</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11548,48 +11535,56 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133552477</v>
+        <v>133552495</v>
       </c>
       <c r="B102" t="n">
-        <v>80478</v>
+        <v>57975</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>580764</v>
+        <v>580953</v>
       </c>
       <c r="R102" t="n">
-        <v>6963638</v>
+        <v>6963811</v>
       </c>
       <c r="S102" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11618,7 +11613,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11628,7 +11623,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Ett färskt ringhack på tall</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11655,10 +11655,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133550158</v>
+        <v>133552500</v>
       </c>
       <c r="B103" t="n">
-        <v>79358</v>
+        <v>79391</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11666,21 +11666,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11690,13 +11690,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>580720</v>
+        <v>580902</v>
       </c>
       <c r="R103" t="n">
-        <v>6963787</v>
+        <v>6963823</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11735,7 +11735,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11762,10 +11762,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133550190</v>
+        <v>133550188</v>
       </c>
       <c r="B104" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11797,13 +11797,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>580838</v>
+        <v>580833</v>
       </c>
       <c r="R104" t="n">
-        <v>6963811</v>
+        <v>6963785</v>
       </c>
       <c r="S104" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11842,12 +11842,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:59</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Med apotecier</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11874,10 +11869,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133550177</v>
+        <v>133550158</v>
       </c>
       <c r="B105" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11909,13 +11904,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>580864</v>
+        <v>580720</v>
       </c>
       <c r="R105" t="n">
-        <v>6963715</v>
+        <v>6963787</v>
       </c>
       <c r="S105" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11944,7 +11939,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11954,7 +11949,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11981,10 +11976,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133552500</v>
+        <v>133552465</v>
       </c>
       <c r="B106" t="n">
-        <v>79390</v>
+        <v>57975</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11992,37 +11987,45 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>580902</v>
+        <v>580724</v>
       </c>
       <c r="R106" t="n">
-        <v>6963823</v>
+        <v>6963746</v>
       </c>
       <c r="S106" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12051,7 +12054,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12061,7 +12064,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12088,10 +12096,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133550188</v>
+        <v>133550190</v>
       </c>
       <c r="B107" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12123,13 +12131,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>580833</v>
+        <v>580838</v>
       </c>
       <c r="R107" t="n">
-        <v>6963785</v>
+        <v>6963811</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12158,7 +12166,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12168,7 +12176,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12195,10 +12208,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>133552465</v>
+        <v>133550177</v>
       </c>
       <c r="B108" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12206,42 +12219,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>580724</v>
+        <v>580864</v>
       </c>
       <c r="R108" t="n">
-        <v>6963746</v>
+        <v>6963715</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12273,7 +12278,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12283,12 +12288,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD108" t="b">

--- a/artfynd/A 21339-2024 artfynd.xlsx
+++ b/artfynd/A 21339-2024 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133550175</v>
+        <v>133552449</v>
       </c>
       <c r="B4" t="n">
-        <v>79359</v>
+        <v>91959</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580879</v>
+        <v>580689</v>
       </c>
       <c r="R4" t="n">
-        <v>6963696</v>
+        <v>6963874</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133550168</v>
+        <v>133550175</v>
       </c>
       <c r="B5" t="n">
-        <v>83208</v>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580801</v>
+        <v>580879</v>
       </c>
       <c r="R5" t="n">
-        <v>6963652</v>
+        <v>6963696</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133552481</v>
+        <v>133550168</v>
       </c>
       <c r="B6" t="n">
-        <v>89339</v>
+        <v>83208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580869</v>
+        <v>580801</v>
       </c>
       <c r="R6" t="n">
-        <v>6963663</v>
+        <v>6963652</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133552511</v>
+        <v>133552481</v>
       </c>
       <c r="B7" t="n">
-        <v>79391</v>
+        <v>89339</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>510</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580865</v>
+        <v>580869</v>
       </c>
       <c r="R7" t="n">
-        <v>6963889</v>
+        <v>6963663</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133552449</v>
+        <v>133552511</v>
       </c>
       <c r="B8" t="n">
-        <v>91959</v>
+        <v>79391</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580689</v>
+        <v>580865</v>
       </c>
       <c r="R8" t="n">
-        <v>6963874</v>
+        <v>6963889</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,32 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133552468</v>
+        <v>133550174</v>
       </c>
       <c r="B9" t="n">
-        <v>98045</v>
+        <v>79359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580758</v>
+        <v>580879</v>
       </c>
       <c r="R9" t="n">
-        <v>6963787</v>
+        <v>6963690</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133550155</v>
+        <v>133552475</v>
       </c>
       <c r="B10" t="n">
-        <v>80474</v>
+        <v>79359</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,13 +1566,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580715</v>
+        <v>580801</v>
       </c>
       <c r="R10" t="n">
-        <v>6963791</v>
+        <v>6963655</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,12 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1643,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133552461</v>
+        <v>133552468</v>
       </c>
       <c r="B11" t="n">
-        <v>83327</v>
+        <v>98045</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6439</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1678,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580740</v>
+        <v>580758</v>
       </c>
       <c r="R11" t="n">
-        <v>6963795</v>
+        <v>6963787</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1713,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1723,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1750,32 +1745,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133550154</v>
+        <v>133550155</v>
       </c>
       <c r="B12" t="n">
-        <v>99180</v>
+        <v>80474</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,13 +1780,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580712</v>
+        <v>580715</v>
       </c>
       <c r="R12" t="n">
-        <v>6963788</v>
+        <v>6963791</v>
       </c>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1820,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1830,12 +1825,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>70 ex</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,32 +1857,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133552452</v>
+        <v>133552461</v>
       </c>
       <c r="B13" t="n">
-        <v>83344</v>
+        <v>83327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,13 +1892,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580698</v>
+        <v>580740</v>
       </c>
       <c r="R13" t="n">
-        <v>6963860</v>
+        <v>6963795</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1932,7 +1927,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1937,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,32 +1964,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133552456</v>
+        <v>133550154</v>
       </c>
       <c r="B14" t="n">
-        <v>91959</v>
+        <v>99180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2004,13 +1999,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580695</v>
+        <v>580712</v>
       </c>
       <c r="R14" t="n">
-        <v>6963806</v>
+        <v>6963788</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2039,7 +2034,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2049,7 +2044,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133550174</v>
+        <v>133552452</v>
       </c>
       <c r="B15" t="n">
-        <v>79359</v>
+        <v>83344</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2087,21 +2087,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580879</v>
+        <v>580698</v>
       </c>
       <c r="R15" t="n">
-        <v>6963690</v>
+        <v>6963860</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2183,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133552475</v>
+        <v>133552456</v>
       </c>
       <c r="B16" t="n">
-        <v>79359</v>
+        <v>91959</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2194,21 +2194,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580801</v>
+        <v>580695</v>
       </c>
       <c r="R16" t="n">
-        <v>6963655</v>
+        <v>6963806</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2621,10 +2621,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133552509</v>
+        <v>133552492</v>
       </c>
       <c r="B20" t="n">
-        <v>79359</v>
+        <v>79117</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2632,21 +2632,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580814</v>
+        <v>580892</v>
       </c>
       <c r="R20" t="n">
-        <v>6963859</v>
+        <v>6963759</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2728,10 +2728,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133552492</v>
+        <v>133552509</v>
       </c>
       <c r="B21" t="n">
-        <v>79117</v>
+        <v>79359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2739,21 +2739,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580892</v>
+        <v>580814</v>
       </c>
       <c r="R21" t="n">
-        <v>6963759</v>
+        <v>6963859</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3482,10 +3482,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133550185</v>
+        <v>133550191</v>
       </c>
       <c r="B28" t="n">
-        <v>79359</v>
+        <v>92230</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3493,21 +3493,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3517,13 +3517,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580867</v>
+        <v>580787</v>
       </c>
       <c r="R28" t="n">
-        <v>6963739</v>
+        <v>6963783</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3589,10 +3589,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133550191</v>
+        <v>133552472</v>
       </c>
       <c r="B29" t="n">
-        <v>92230</v>
+        <v>91973</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3600,21 +3600,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3624,10 +3624,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580787</v>
+        <v>580713</v>
       </c>
       <c r="R29" t="n">
-        <v>6963783</v>
+        <v>6963690</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3696,10 +3696,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133552472</v>
+        <v>133550185</v>
       </c>
       <c r="B30" t="n">
-        <v>91973</v>
+        <v>79359</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3731,13 +3731,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580713</v>
+        <v>580867</v>
       </c>
       <c r="R30" t="n">
-        <v>6963690</v>
+        <v>6963739</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3910,32 +3910,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133552488</v>
+        <v>133550163</v>
       </c>
       <c r="B32" t="n">
-        <v>89339</v>
+        <v>98045</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>510</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3945,10 +3945,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>580943</v>
+        <v>580728</v>
       </c>
       <c r="R32" t="n">
-        <v>6963738</v>
+        <v>6963787</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4017,32 +4017,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133552502</v>
+        <v>133552488</v>
       </c>
       <c r="B33" t="n">
-        <v>80368</v>
+        <v>89339</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6456</v>
+        <v>510</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4052,10 +4052,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>580865</v>
+        <v>580943</v>
       </c>
       <c r="R33" t="n">
-        <v>6963830</v>
+        <v>6963738</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4087,7 +4087,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4124,32 +4124,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133550148</v>
+        <v>133552502</v>
       </c>
       <c r="B34" t="n">
-        <v>99180</v>
+        <v>80368</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4159,13 +4159,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>580696</v>
+        <v>580865</v>
       </c>
       <c r="R34" t="n">
-        <v>6963788</v>
+        <v>6963830</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4204,12 +4204,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:49</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>120 ex</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4236,32 +4231,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133550138</v>
+        <v>133550148</v>
       </c>
       <c r="B35" t="n">
-        <v>79359</v>
+        <v>99180</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4271,13 +4266,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>580712</v>
+        <v>580696</v>
       </c>
       <c r="R35" t="n">
-        <v>6963853</v>
+        <v>6963788</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4306,7 +4301,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4316,7 +4311,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>120 ex</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4343,10 +4343,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133550180</v>
+        <v>133550138</v>
       </c>
       <c r="B36" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4354,45 +4354,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>580876</v>
+        <v>580712</v>
       </c>
       <c r="R36" t="n">
-        <v>6963707</v>
+        <v>6963853</v>
       </c>
       <c r="S36" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4421,7 +4413,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4431,12 +4423,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:14</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4463,48 +4450,56 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133550163</v>
+        <v>133550180</v>
       </c>
       <c r="B37" t="n">
-        <v>98045</v>
+        <v>57975</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>580728</v>
+        <v>580876</v>
       </c>
       <c r="R37" t="n">
-        <v>6963787</v>
+        <v>6963707</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4533,7 +4528,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4543,7 +4538,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4570,10 +4570,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133552497</v>
+        <v>133552453</v>
       </c>
       <c r="B38" t="n">
-        <v>79116</v>
+        <v>79359</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4605,13 +4605,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>580939</v>
+        <v>580737</v>
       </c>
       <c r="R38" t="n">
-        <v>6963799</v>
+        <v>6963844</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4677,7 +4677,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133552453</v>
+        <v>133550132</v>
       </c>
       <c r="B39" t="n">
         <v>79359</v>
@@ -4712,13 +4712,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>580737</v>
+        <v>580695</v>
       </c>
       <c r="R39" t="n">
-        <v>6963844</v>
+        <v>6963885</v>
       </c>
       <c r="S39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4784,32 +4784,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133550136</v>
+        <v>133550176</v>
       </c>
       <c r="B40" t="n">
-        <v>99180</v>
+        <v>79359</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4819,10 +4819,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>580702</v>
+        <v>580874</v>
       </c>
       <c r="R40" t="n">
-        <v>6963851</v>
+        <v>6963718</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4864,12 +4864,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>150 ex</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4896,10 +4891,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133550132</v>
+        <v>133552497</v>
       </c>
       <c r="B41" t="n">
-        <v>79359</v>
+        <v>79116</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4907,21 +4902,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4931,10 +4926,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>580695</v>
+        <v>580939</v>
       </c>
       <c r="R41" t="n">
-        <v>6963885</v>
+        <v>6963799</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4966,7 +4961,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4976,7 +4971,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5003,32 +4998,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133550182</v>
+        <v>133550136</v>
       </c>
       <c r="B42" t="n">
-        <v>79359</v>
+        <v>99180</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5038,10 +5033,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>580856</v>
+        <v>580702</v>
       </c>
       <c r="R42" t="n">
-        <v>6963747</v>
+        <v>6963851</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5073,7 +5068,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5083,7 +5078,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>150 ex</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5110,27 +5110,27 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133552478</v>
+        <v>133550182</v>
       </c>
       <c r="B43" t="n">
-        <v>80485</v>
+        <v>79359</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5145,10 +5145,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580763</v>
+        <v>580856</v>
       </c>
       <c r="R43" t="n">
-        <v>6963637</v>
+        <v>6963747</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5217,32 +5217,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133552494</v>
+        <v>133552478</v>
       </c>
       <c r="B44" t="n">
-        <v>79391</v>
+        <v>80485</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>185</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5252,10 +5252,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>580955</v>
+        <v>580763</v>
       </c>
       <c r="R44" t="n">
-        <v>6963798</v>
+        <v>6963637</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5287,7 +5287,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5324,10 +5324,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133550166</v>
+        <v>133552494</v>
       </c>
       <c r="B45" t="n">
-        <v>57153</v>
+        <v>79391</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5335,49 +5335,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>102612</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580800</v>
+        <v>580955</v>
       </c>
       <c r="R45" t="n">
-        <v>6963652</v>
+        <v>6963798</v>
       </c>
       <c r="S45" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5406,7 +5394,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5416,7 +5404,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5443,10 +5431,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133550176</v>
+        <v>133550166</v>
       </c>
       <c r="B46" t="n">
-        <v>79359</v>
+        <v>57153</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5454,37 +5442,49 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>580874</v>
+        <v>580800</v>
       </c>
       <c r="R46" t="n">
-        <v>6963718</v>
+        <v>6963652</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5550,32 +5550,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133550162</v>
+        <v>133552491</v>
       </c>
       <c r="B47" t="n">
-        <v>99180</v>
+        <v>79359</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>580728</v>
+        <v>580883</v>
       </c>
       <c r="R47" t="n">
-        <v>6963787</v>
+        <v>6963753</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5630,12 +5630,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:34</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>50 ex</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5662,53 +5657,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133552508</v>
+        <v>133550162</v>
       </c>
       <c r="B48" t="n">
-        <v>57975</v>
+        <v>99180</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Svartbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>580813</v>
+        <v>580728</v>
       </c>
       <c r="R48" t="n">
-        <v>6963779</v>
+        <v>6963787</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5740,7 +5727,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5750,12 +5737,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5782,48 +5769,56 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133550147</v>
+        <v>133552508</v>
       </c>
       <c r="B49" t="n">
-        <v>99180</v>
+        <v>57975</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t